--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>فریم 3 کامل, counts 2482</t>
+          <t>فریم 3 کامل, counts: V channels 2482 (2V pin), I channels 610 (0.49V)</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>valid=true، همه globals به‌روز: v_in≈22205mV? Wait 2V pin → V24≈22352mV, v_bat12≈12058mV, current≈485mA, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
+          <t>valid=true، همه globals به‌روز: 2V pin → V24≈22352mV, V12≈12058mV, Current≈486mA با I counts 610, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>PASS: فریم3 → valid true. FAIL: still false.</t>
+          <t>PASS: فریم3 → valid true با V24≈22352 و I≈486mA. FAIL: still false.</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr"/>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>counts 4095 → CountsToMv 3300، V24≈36882mV (3300*76000/6800)، V12≈19901mV، Current≈800mA? Actually max counts 4095 → current≈ 3300*1000/(101*10)=3267mA</t>
+          <t>counts 4095 → CountsToMv 3300، V24≈36882mV (3300*76000/6800)، V12≈19897mV، Current≈3267mA (3300*1000/(101*10)=3267)</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>counts 4095</t>
+          <t>counts 4095 (فول)</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>مقادیر محاسبه شده ±tolerance. PASS. FAIL: خطا.</t>
+          <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>PASS: فول مطابق فرمول. FAIL: خطا.</t>
+          <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
         </is>
       </c>
       <c r="J24" s="16" t="inlineStr"/>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>برای V24=24V واقعی، counts مورد انتظار را محاسبه و سپس با DMM روی PA2 vs محاسبه مقایسه کن</t>
+          <t>برای V24=24V واقعی، ADC pin≈2147mV → counts≈2665 → V24≈24000mV را محاسبه و با DMM روی PA2 مقایسه کن</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>V24=24V (≈2146 counts)</t>
+          <t>V24=24V (pin≈2147mV, counts≈2665)</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>counts≈2146 → adcPin≈1729mV → V24≈19327? Wait compute actual 24V → pin 24*6800/76000≈2147mV → counts≈2663. tolerance ± resistor 1% + ADC ±1 LSB. PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
+          <t>ADC pin≈2147mV، counts≈2665، V24≈24000mV ±tolerance (1% مقاومت + 1LSB). PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>PASS: within 1% + LSB. FAIL: &gt;2%.</t>
+          <t>PASS: 2665→24000 within 1%. FAIL: &gt;2%.</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
@@ -3378,8 +3378,8 @@
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -3401,8 +3401,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -3424,8 +3424,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -3447,8 +3447,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -3466,8 +3466,8 @@
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -3485,8 +3485,8 @@
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
+          <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$P$25</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,8 +117,29 @@
     <font>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -160,8 +182,13 @@
         <bgColor rgb="00E9EDF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -227,11 +254,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -314,6 +355,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3802,4 +3855,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول اندازه‌گیری (Measurement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Measurement_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,28 @@
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -999,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2424,6 +2446,76 @@
       </c>
       <c r="O25" s="18" t="inlineStr"/>
       <c r="P25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ME-022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>snapshot zeroing مصرف‌کننده</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Measurement خاموش</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>task_control و task_comm و task_protection با valid=false و 9 فیلد صفر اجرا شوند</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>بدون indeterminate struct</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:P25"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1168,7 +1168,10 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>func__Measurement_Init را صدا بزن یا برد را Reset کن، سپس globals و snapshot را بخوان</t>
+          <t>گام ۱: برد را Reset کن ولی هنوز Start را نزن (تازه بعد از Reset و قبل از Start هستیم).
+گام ۲: func__Measurement_Init را صدا بزن (یا همان Reset کافی است).
+گام ۳: حداکثر 100 میلی‌ثانیه بعد، متغیرهای سراسری (globals) و snapshot را بخوان.
+گام ۴: باید valid=false باشد، همهٔ ولتاژ و جریان‌ها (mV و mA) صفر باشند و input_present هم false باشد؛ هر مقدار غیرصفر یعنی رد تست.</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -1230,7 +1233,10 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>یک فریم ADC معتبر (5 کانال) را اعمال کن (مثلاً 2V روی همه)، یک Run صدا بزن، valid را بخوان</t>
+          <t>گام ۱: Init و Start را با موفقیت انجام بده (ادامهٔ MS-001).
+گام ۲: یک فریم کامل و پایدار ADC روی هر 5 کانال اعمال کن؛ مثلاً روی همه 2 ولت (counts حدود 2482).
+گام ۳: فقط یک بار func__Measurement_Run را صدا بزن و valid را بخوان.
+گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 1 شده باشد؛ valid شدن در فریم اول یعنی رد تست.</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -1292,7 +1298,10 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>فریم دوم معتبر را اعمال و یک Run دیگر</t>
+          <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
+گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
+گام ۳: یک Run دیگر بزن و valid را بخوان.
+گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -1354,7 +1363,10 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>فریم سوم معتبر را اعمال و Run</t>
+          <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
+گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
+گام ۳: یک Run بزن.
+گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -1416,7 +1428,10 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>یک فریم ناپایدار (simulate GetRaw false: مثلاً CNDTR در وسط) را اعمال و Run</t>
+          <t>گام ۱: از valid=true شروع کن (پایان MS-004).
+گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
+گام ۳: یک Run بزن.
+گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -1478,7 +1493,10 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>سه فریم معتبر پی‌درپی دوباره اعمال کن</t>
+          <t>گام ۱: ادامهٔ MS-005 (فریم خراب و warmup=0).
+گام ۲: سه فریم کامل و پایدار پشت سر هم اعمال کن و هر کدام یک Run بزن (در مجموع 30 میلی‌ثانیه).
+گام ۳: بعد از فریم اول و دوم هنوز باید valid=false باشد.
+گام ۴: دقیقاً بعد از فریم سوم باید valid=true شود؛ زودتر یا دیرتر شدن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
@@ -1540,7 +1558,10 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Vin=0V (counts 0) را اعمال کن اما سایر کانال‌ها معتبر، یک Run</t>
+          <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
+گام ۲: یک Run بزن.
+گام ۳: valid باید همچنان true بماند، چون قطع ورودی نباید ADC را نامعتبر کند.
+گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -1602,7 +1623,10 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>counts=1241 (≈1V pin) → V24≈11176mV را محاسبه و مقایسه کن (1V*76000/6800)</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
+گام ۳: اول خودت حساب کن: 1241 ضربدر 3300 تقسیم بر 4095 می‌شود حدود 1000 میلی‌ولت روی پایه؛ بعد ضربدر 76000 تقسیم بر 6800 می‌شود حدود 11176 میلی‌ولت.
+گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -1664,7 +1688,10 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>counts 2482 (2V pin) → V24≈22352mV</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
+گام ۳: مقدار v_bat24_mv را بخوان.
+گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -1726,7 +1753,10 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>counts 2482 (2V pin) → V12≈12058mV (2V*41000/6800)</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال باتری 12 ولت counts=2482 بده (2 ولت روی پایه).
+گام ۳: مقدار v_bat12_mv را بخوان.
+گام ۴: باید حدود 12058 میلی‌ولت باشد (2 ضربدر 41000 تقسیم بر 6800) با خطای حداکثر ±5 میلی‌ولت.</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -1788,7 +1818,10 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>counts 610 (≈0.49V pin, 0.485A) → Current≈485mA</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
+گام ۳: خودت حساب کن: 610 ضربدر 3300 ضربدر 1000 تقسیم بر (4095 ضربدر 101 ضربدر 10) می‌شود حدود 486 میلی‌آمپر.
+گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -1850,7 +1883,10 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>counts 1220 (≈0.98V pin, ≈0.97A)</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال جریان شارژ ۲ counts=1220 بده (حدود 0.98 ولت روی پایه).
+گام ۳: i_ch2 را بخوان.
+گام ۴: باید حدود 973 میلی‌آمپر باشد با خطای حداکثر ±1 میلی‌آمپر؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -1912,7 +1948,10 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>PB4=High (ورودی 24V حاضر) اعمال، snapshot بخوان</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: پایهٔ PB4 را High کن (یعنی ورودی 24 ولت حاضر است).
+گام ۳: یک Run بزن و snapshot را بخوان.
+گام ۴: input_present باید true باشد؛ false ماندن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -1974,7 +2013,10 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>PB4=Low (ورودی قطع) اعمال</t>
+          <t>گام ۱: از valid=true با ورودی حاضر شروع کن (input_present=true).
+گام ۲: پایهٔ PB4 را Low کن (ورودی قطع است).
+گام ۳: یک Run بزن و snapshot را بخوان.
+گام ۴: input_present باید false شده باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -2036,7 +2078,9 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>func__Measurement_GetSnapshot(NULL) صدا بزن</t>
+          <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
+گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
+گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -2098,7 +2142,10 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>حین func__Measurement_Run، از دو تسک هم‌زمان GetSnapshot بخوان و چک کن هیچ فیلدی نیمه‌به‌روزشده نباشد</t>
+          <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
+گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
+گام ۳: 20 میلی‌ثانیه این خواندن هم‌زمان را تکرار کن.
+گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -2160,7 +2207,10 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>اسکوپ روی یک GPIO toggle در ابتدای هر Run (یا Live Watch) 1s ضبط کن</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
+گام ۳: یک ثانیه ضبط کن و فاصلهٔ بین Runها را اندازه بگیر.
+گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -2222,7 +2272,10 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>DMA دو فریمی 2×5 را با CNDTR چک کن: قبل/بعد کپی شمارنده هم‌طرف باشد و frame 5 نمونه کامل کپی شود</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: شمارندهٔ DMA (یعنی CNDTR) را قبل و بعد از کپی بخوان؛ DMA دو فریمی است (2 ضربدر 5).
+گام ۳: چک کن حین کپی، شمارنده در همان نیمه مانده باشد و هر 5 نمونهٔ فریم کامل کپی شده باشد.
+گام ۴: GetRaw باید پنجرهٔ پایدار (stable=true) بدهد؛ کپی پاره یا تمام شدن retry یعنی رد تست.</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -2284,7 +2337,10 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>counts 0 → CountsToMv 0، V24 0، V12 0، Current 0</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی همهٔ کانال‌ها counts=0 بده.
+گام ۳: یک Run بزن و همهٔ خروجی‌ها را بخوان.
+گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -2346,7 +2402,10 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>counts 4095 → CountsToMv 3300، V24≈36882mV (3300*76000/6800)، V12≈19897mV، Current≈3267mA (3300*1000/(101*10)=3267)</t>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
+گام ۳: با دست حساب کن: ولتاژ پایه 3300 میلی‌ولت، V24 می‌شود 3300 ضربدر 76000 تقسیم بر 6800 یعنی حدود 36882 میلی‌ولت، V12 حدود 19897 میلی‌ولت و جریان 3300 ضربدر 1000 تقسیم بر (101 ضربدر 10) یعنی حدود 3267 میلی‌آمپر.
+گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -2408,7 +2467,10 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>برای V24=24V واقعی، ADC pin≈2147mV → counts≈2665 → V24≈24000mV را محاسبه و با DMM روی PA2 مقایسه کن</t>
+          <t>گام ۱: یک باتری/منبع واقعی دقیقاً 24 ولت به ورودی V24 بده.
+گام ۲: با مولتی‌متر (DMM) ولتاژ روی پایهٔ PA2 را اندازه بگیر؛ باید حدود 2147 میلی‌ولت باشد.
+گام ۳: counts را بخوان؛ باید حدود 2665 باشد.
+گام ۴: V24 خوانده‌شده باید حدود 24000 میلی‌ولت باشد. خطای مجاز 1 درصد مقاومت‌ها به‌علاوهٔ 1 LSB است؛ خطای کمتر از 1 درصد قبول و بیشتر از 2 درصد رد است.</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -2470,7 +2532,10 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>task_control و task_comm و task_protection با valid=false و 9 فیلد صفر اجرا شوند</t>
+          <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
+گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
+گام ۳: snapshot هر سه را بخوان: valid باید false و هر 9 فیلد صفر باشد (هیچ ساختار نامشخصی نباید باشد).
+گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2503,14 +2568,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -16,17 +16,19 @@
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$P$25</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,8 +140,127 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00C00000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00808080"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="7"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +306,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -367,6 +503,137 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,6 +997,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -755,162 +1023,177 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Measurement — ADC و کالیبراسیون</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>ChangeOver | ADC1 5ch + DMA + bsp_measurement | نسخه 1.0 — دوره 10ms، warmup 3 فریم، فرمول‌های BSP واقعی</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="9" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>این فایل مستقل فقط Measurement را اعتبارسنجی می‌کند؛ هر تست valid، فریم ADC، فرمول mV/mA، ورودی‌ها و snapshot اتمیک را چک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار عددی و tolerance از کالیبراسیون BSP تعریف شده است.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>پس از Init، valid=false؛ تا 3 فریم کامل و پایدار، valid همچنان false؛ پس از فریم سوم، valid=true و همه mV/mA/input_present به‌روز می‌شوند.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>فریم ناقص/ناپایدار → valid=false و warmup از نو (counter reset). قطع ورودی 24V نباید به تنهایی ADC را invalid کند.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>کالیبراسیون از bsp_measurement.c: Vref=3300mV، ADC=4095، Div24 69200+6800/6800 (≈11.176)، Div12 34200+6800/6800 (≈6.029)، شانت 10mΩ و گین 101.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>فرمول‌ها: CountsToMv = counts*3300/4095؛ V24 = adcPinMv*(76000)/6800؛ V12 = adcPinMv*(41000)/6800؛ Current = counts*3300*1000/(4095*101*10).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>زمان واقعی از کد: MEASUREMENT_PERIOD_MS=10ms، MEASUREMENT_WARMUP_FRAME_COUNT=3، DMA دو فریمی 2×5، CNDTR بررسی قبل/بعد، osKernelLock برای snapshot اتمیک.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>۱) برد را با منبع آزمایشگاهی تغذیه کن، هر 5 کانال ADC (PA1/2/3/5/7) را با ولتاژ دقیق و منبع جریان کالیبره اعمال کن؛ PB4 را برای input_present کنترل کن.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>۲) firmware commit c6b084f را پروگرام کن، در «تأیید نهایی» commit/برد/ابزار (DMM، اسکوپ، منبع دقیق) را ثبت کن.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>۳) تست warmup: پس از Init، فریم‌ها را با func__BspAdc_GetRaw یا Live Watch بشمار؛ valid را چک کن.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>۴) تست ولتاژ/جریان: هر کانال را با counts معلوم اعمال کن، مقدار mV/mA را با فرمول BSP محاسبه و با خوانش globals/snapshot مقایسه کن (tolerance ±1 LSB ≈ ±0.8mV pin، برای V24 ≈±9mV، برای V12 ≈±4.8mV، برای جریان ≈±0.8mA).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>۵) تست DMA: دو فریم متوالی را چک کن که CNDTR پایدار باشد و frame 5 نمونه بدون پارگی کپی شود (irq disable و counter قبل/بعد).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>۶) تست snapshot اتمیک: حین Run، از دو تسک snapshot را هم‌زمان بخوان و چک کن نیمه‌به‌روزشده نباشد (osKernelLock).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
@@ -929,22 +1212,22 @@
       <c r="P21" s="9" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>ایجاد مستقل Measurement_Board_Validation با ۲۱ تست، فرمول‌ها و tolerance از bsp_measurement.c، دوره 10ms و warmup 3</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
@@ -963,22 +1246,22 @@
       <c r="P22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="43" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
@@ -1009,6 +1292,10 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId2"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -1018,155 +1305,158 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Measurement</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>هر ردیف را با DMM/اسکوپ و محاسبه از فرمول BSP اندازه بگیر؛ مقدار حدسی ننویس. valid باید دقیقاً پس از ۳ فریم true شود.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="79" t="inlineStr">
         <is>
           <t>فرمول‌ها و tolerance از bsp_measurement.c واقعی است؛ PASS/FAIL با tolerance ±1 LSB + 1% مقاومت تعریف شده است.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="37" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="37" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="37" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="37" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="37" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>MS-001</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>پس از Reset، قبل از Start</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد را Reset کن ولی هنوز Start را نزن (تازه بعد از Reset و قبل از Start هستیم).
 گام ۲: func__Measurement_Init را صدا بزن (یا همان Reset کافی است).
@@ -1174,64 +1464,68 @@
 گام ۴: باید valid=false باشد، همهٔ ولتاژ و جریان‌ها (mV و mA) صفر باشند و input_present هم false باشد؛ هر مقدار غیرصفر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t>valid=false، همه mV/mA=0، input_present=false. PASS: valid false و صفر. FAIL: هر mV غیرصفر یا valid true.</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="48" t="inlineStr">
         <is>
           <t>PASS: Init صفر و invalid. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr"/>
+      <c r="K5" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr"/>
-      <c r="M5" s="18" t="inlineStr"/>
-      <c r="N5" s="18" t="inlineStr">
+      <c r="L5" s="53" t="inlineStr"/>
+      <c r="M5" s="48" t="inlineStr"/>
+      <c r="N5" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="18" t="inlineStr"/>
-      <c r="P5" s="18" t="inlineStr"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="O5" s="50" t="inlineStr"/>
+      <c r="P5" s="50" t="inlineStr"/>
+      <c r="Q5" s="54">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>MS-002</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>Warmup / فریم اول</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>پس از Init و Start موفق</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="57" t="inlineStr">
         <is>
           <t>گام ۱: Init و Start را با موفقیت انجام بده (ادامهٔ MS-001).
 گام ۲: یک فریم کامل و پایدار ADC روی هر 5 کانال اعمال کن؛ مثلاً روی همه 2 ولت (counts حدود 2482).
@@ -1239,64 +1533,68 @@
 گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 1 شده باشد؛ valid شدن در فریم اول یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>فریم 1 کامل و پایدار, counts≈2482 (2V)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="55" t="inlineStr">
         <is>
           <t>valid همچنان false، warmupCounter=1، globals هنوز 0 یا قدیمی اما valid=false. PASS: هنوز invalid. FAIL: valid true زودهنگام.</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>PASS: فریم1 → still false. FAIL: valid true.</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="J6" s="55" t="inlineStr"/>
+      <c r="K6" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="L6" s="59" t="inlineStr"/>
+      <c r="M6" s="55" t="inlineStr"/>
+      <c r="N6" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="O6" s="58" t="inlineStr"/>
+      <c r="P6" s="58" t="inlineStr"/>
+      <c r="Q6" s="60">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>MS-003</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>Warmup / فریم دوم</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>پس از MS-002</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="61" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
 گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
@@ -1304,64 +1602,68 @@
 گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>فریم 2 کامل, counts 2482</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="48" t="inlineStr">
         <is>
           <t>valid همچنان false، counter=2. PASS: still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="48" t="inlineStr">
         <is>
           <t>PASS: فریم2 still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="J7" s="51" t="inlineStr"/>
+      <c r="K7" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="L7" s="53" t="inlineStr"/>
+      <c r="M7" s="48" t="inlineStr"/>
+      <c r="N7" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="18" t="inlineStr"/>
-      <c r="P7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="O7" s="50" t="inlineStr"/>
+      <c r="P7" s="50" t="inlineStr"/>
+      <c r="Q7" s="54">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>MS-004</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Warmup / فریم سوم</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>پس از MS-003</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="57" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
 گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
@@ -1369,64 +1671,68 @@
 گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="58" t="inlineStr">
         <is>
           <t>فریم 3 کامل, counts: V channels 2482 (2V pin), I channels 610 (0.49V)</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="55" t="inlineStr">
         <is>
           <t>valid=true، همه globals به‌روز: 2V pin → V24≈22352mV, V12≈12058mV, Current≈486mA با I counts 610, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="55" t="inlineStr">
         <is>
           <t>PASS: فریم3 → valid true با V24≈22352 و I≈486mA. FAIL: still false.</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="J8" s="55" t="inlineStr"/>
+      <c r="K8" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr"/>
-      <c r="M8" s="20" t="inlineStr"/>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="L8" s="59" t="inlineStr"/>
+      <c r="M8" s="55" t="inlineStr"/>
+      <c r="N8" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O8" s="20" t="inlineStr"/>
-      <c r="P8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="O8" s="58" t="inlineStr"/>
+      <c r="P8" s="58" t="inlineStr"/>
+      <c r="Q8" s="60">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>MS-005</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>Warmup / فریم ناقص</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>پس از valid=true</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن (پایان MS-004).
 گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
@@ -1434,64 +1740,68 @@
 گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>فریم ناقص/ناپایدار (GetRaw false)</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>valid=false فوری، warmupCounter reset به 0، snapshot.valid false. PASS: invalid و reset. FAIL: همچنان true.</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>PASS: unstable → invalid+reset. FAIL: remains true.</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr"/>
+      <c r="K9" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="L9" s="53" t="inlineStr"/>
+      <c r="M9" s="48" t="inlineStr"/>
+      <c r="N9" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr"/>
-      <c r="P9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="O9" s="50" t="inlineStr"/>
+      <c r="P9" s="50" t="inlineStr"/>
+      <c r="Q9" s="54">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>MS-006</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Warmup / شروع دوباره</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>پس از MS-005</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="57" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-005 (فریم خراب و warmup=0).
 گام ۲: سه فریم کامل و پایدار پشت سر هم اعمال کن و هر کدام یک Run بزن (در مجموع 30 میلی‌ثانیه).
@@ -1499,64 +1809,68 @@
 گام ۴: دقیقاً بعد از فریم سوم باید valid=true شود؛ زودتر یا دیرتر شدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="58" t="inlineStr">
         <is>
           <t>3 فریم کامل</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="58" t="inlineStr">
         <is>
           <t>30ms</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="55" t="inlineStr">
         <is>
           <t>پس از فریم سوم دوباره valid=true. PASS: warmup دوباره 3 فریم. FAIL: valid زودتر یا دیرتر.</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="55" t="inlineStr">
         <is>
           <t>PASS: 3 فریم دوباره → true. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="J10" s="55" t="inlineStr"/>
+      <c r="K10" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="L10" s="59" t="inlineStr"/>
+      <c r="M10" s="55" t="inlineStr"/>
+      <c r="N10" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="O10" s="58" t="inlineStr"/>
+      <c r="P10" s="58" t="inlineStr"/>
+      <c r="Q10" s="60">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>MS-007</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>ورودی 24V قطع</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>valid=true با Vin=0</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
 گام ۲: یک Run بزن.
@@ -1564,64 +1878,68 @@
 گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>v_in 0V (counts 0), سایر 2V</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="48" t="inlineStr">
         <is>
           <t>valid همچنان true (قطع ورودی ADC را invalid نمی‌کند)، v_in_mv≈0، سایر مقادیر به‌روز. PASS: valid true با Vin صفر. FAIL: valid false.</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="48" t="inlineStr">
         <is>
           <t>PASS: Vin zero still valid. FAIL: invalid.</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="J11" s="51" t="inlineStr"/>
+      <c r="K11" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="18" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="L11" s="53" t="inlineStr"/>
+      <c r="M11" s="48" t="inlineStr"/>
+      <c r="N11" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr"/>
-      <c r="P11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="O11" s="50" t="inlineStr"/>
+      <c r="P11" s="50" t="inlineStr"/>
+      <c r="Q11" s="54">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>MS-008</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>بررسی v_in_mv</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
@@ -1629,64 +1947,68 @@
 گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="58" t="inlineStr">
         <is>
           <t>counts 1241 (1V)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="55" t="inlineStr">
         <is>
           <t>v_in_mv = 1241*3300/4095≈1000mV pin → *76000/6800≈11176mV. tolerance ±9mV. PASS: خوانش در tolerance. FAIL: &gt;20mV خطا.</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="55" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="L12" s="59" t="inlineStr"/>
+      <c r="M12" s="55" t="inlineStr"/>
+      <c r="N12" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="O12" s="58" t="inlineStr"/>
+      <c r="P12" s="58" t="inlineStr"/>
+      <c r="Q12" s="60">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>MS-009</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>بررسی v_bat24_mv</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
@@ -1694,64 +2016,68 @@
 گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>counts 2482</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="48" t="inlineStr">
         <is>
           <t>v_bat24_mv≈22352mV ±9mV. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="J13" s="51" t="inlineStr"/>
+      <c r="K13" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr"/>
-      <c r="M13" s="18" t="inlineStr"/>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="L13" s="53" t="inlineStr"/>
+      <c r="M13" s="48" t="inlineStr"/>
+      <c r="N13" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O13" s="18" t="inlineStr"/>
-      <c r="P13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="O13" s="50" t="inlineStr"/>
+      <c r="P13" s="50" t="inlineStr"/>
+      <c r="Q13" s="54">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>MS-010</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>بررسی v_bat12_mv</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال باتری 12 ولت counts=2482 بده (2 ولت روی پایه).
@@ -1759,64 +2085,68 @@
 گام ۴: باید حدود 12058 میلی‌ولت باشد (2 ضربدر 41000 تقسیم بر 6800) با خطای حداکثر ±5 میلی‌ولت.</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
         <is>
           <t>counts 2482</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="55" t="inlineStr">
         <is>
           <t>v_bat12_mv≈12058mV ±5mV. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="55" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V12. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="J14" s="55" t="inlineStr"/>
+      <c r="K14" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="20" t="inlineStr"/>
-      <c r="M14" s="20" t="inlineStr"/>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="L14" s="59" t="inlineStr"/>
+      <c r="M14" s="55" t="inlineStr"/>
+      <c r="N14" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="O14" s="58" t="inlineStr"/>
+      <c r="P14" s="58" t="inlineStr"/>
+      <c r="Q14" s="60">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>MS-011</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>بررسی current1</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
@@ -1824,64 +2154,68 @@
 گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>counts 610 (0.49V)</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="48" t="inlineStr">
         <is>
           <t>i_ch1≈ counts*3300*1000/(4095*101*10) ≈ 486mA ±1mA. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول جریان. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="J15" s="51" t="inlineStr"/>
+      <c r="K15" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr"/>
-      <c r="M15" s="18" t="inlineStr"/>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="L15" s="53" t="inlineStr"/>
+      <c r="M15" s="48" t="inlineStr"/>
+      <c r="N15" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr"/>
-      <c r="P15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="O15" s="50" t="inlineStr"/>
+      <c r="P15" s="50" t="inlineStr"/>
+      <c r="Q15" s="54">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>MS-012</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>بررسی current2</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال جریان شارژ ۲ counts=1220 بده (حدود 0.98 ولت روی پایه).
@@ -1889,64 +2223,68 @@
 گام ۴: باید حدود 973 میلی‌آمپر باشد با خطای حداکثر ±1 میلی‌آمپر؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="58" t="inlineStr">
         <is>
           <t>counts 1220</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="55" t="inlineStr">
         <is>
           <t>i_ch2≈ 973mA ±1mA. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="55" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="J16" s="55" t="inlineStr"/>
+      <c r="K16" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr"/>
-      <c r="M16" s="20" t="inlineStr"/>
-      <c r="N16" s="20" t="inlineStr">
+      <c r="L16" s="59" t="inlineStr"/>
+      <c r="M16" s="55" t="inlineStr"/>
+      <c r="N16" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="O16" s="58" t="inlineStr"/>
+      <c r="P16" s="58" t="inlineStr"/>
+      <c r="Q16" s="60">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>MS-013</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>بررسی input_present / High</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: پایهٔ PB4 را High کن (یعنی ورودی 24 ولت حاضر است).
@@ -1954,64 +2292,68 @@
 گام ۴: input_present باید true باشد؛ false ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>PB4 High</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="48" t="inlineStr">
         <is>
           <t>input_present=true. PASS: true. FAIL: false.</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="48" t="inlineStr">
         <is>
           <t>PASS: true. FAIL: false.</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="J17" s="51" t="inlineStr"/>
+      <c r="K17" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="18" t="inlineStr"/>
-      <c r="M17" s="18" t="inlineStr"/>
-      <c r="N17" s="18" t="inlineStr">
+      <c r="L17" s="53" t="inlineStr"/>
+      <c r="M17" s="48" t="inlineStr"/>
+      <c r="N17" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O17" s="18" t="inlineStr"/>
-      <c r="P17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="O17" s="50" t="inlineStr"/>
+      <c r="P17" s="50" t="inlineStr"/>
+      <c r="Q17" s="54">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>MS-014</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>بررسی input_present / Low</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true با ورودی حاضر شروع کن (input_present=true).
 گام ۲: پایهٔ PB4 را Low کن (ورودی قطع است).
@@ -2019,128 +2361,136 @@
 گام ۴: input_present باید false شده باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="58" t="inlineStr">
         <is>
           <t>PB4 Low</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="55" t="inlineStr">
         <is>
           <t>input_present=false. PASS. FAIL: true.</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="55" t="inlineStr">
         <is>
           <t>PASS: false. FAIL: true.</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="J18" s="55" t="inlineStr"/>
+      <c r="K18" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr"/>
-      <c r="M18" s="20" t="inlineStr"/>
-      <c r="N18" s="20" t="inlineStr">
+      <c r="L18" s="59" t="inlineStr"/>
+      <c r="M18" s="55" t="inlineStr"/>
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O18" s="20" t="inlineStr"/>
-      <c r="P18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="O18" s="58" t="inlineStr"/>
+      <c r="P18" s="58" t="inlineStr"/>
+      <c r="Q18" s="60">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>MS-015</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="48" t="inlineStr">
         <is>
           <t>NULL در GetSnapshot</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
 گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
 گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>NULL pointer</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="50" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="48" t="inlineStr">
         <is>
           <t>return false، بدون کرش، snapshot تغییر نکند. PASS: false. FAIL: کرش یا true.</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="48" t="inlineStr">
         <is>
           <t>PASS: NULL → false. FAIL: true/crash.</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="J19" s="51" t="inlineStr"/>
+      <c r="K19" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="18" t="inlineStr"/>
-      <c r="M19" s="18" t="inlineStr"/>
-      <c r="N19" s="18" t="inlineStr">
+      <c r="L19" s="53" t="inlineStr"/>
+      <c r="M19" s="48" t="inlineStr"/>
+      <c r="N19" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O19" s="18" t="inlineStr"/>
-      <c r="P19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="O19" s="50" t="inlineStr"/>
+      <c r="P19" s="50" t="inlineStr"/>
+      <c r="Q19" s="54">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>MS-016</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>Snapshot چندفیلدی اتمیک</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
 گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
@@ -2148,64 +2498,68 @@
 گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="58" t="inlineStr">
         <is>
           <t>concurrent read</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="58" t="inlineStr">
         <is>
           <t>20ms</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="55" t="inlineStr">
         <is>
           <t>هر دو snapshot کپی‌شده باید یا کامل قدیمی یا کامل جدید باشد، نه ترکیبی. با osKernelLock تضمین. PASS: atomic. FAIL: torn read.</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="55" t="inlineStr">
         <is>
           <t>PASS: no torn data. FAIL: partial.</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="J20" s="55" t="inlineStr"/>
+      <c r="K20" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr"/>
-      <c r="M20" s="20" t="inlineStr"/>
-      <c r="N20" s="20" t="inlineStr">
+      <c r="L20" s="59" t="inlineStr"/>
+      <c r="M20" s="55" t="inlineStr"/>
+      <c r="N20" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O20" s="20" t="inlineStr"/>
-      <c r="P20" s="20" t="inlineStr"/>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="O20" s="58" t="inlineStr"/>
+      <c r="P20" s="58" t="inlineStr"/>
+      <c r="Q20" s="60">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>MS-017</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>دوره 10ms تسک Measurement</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
@@ -2213,64 +2567,68 @@
 گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="50" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="48" t="inlineStr">
         <is>
           <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="48" t="inlineStr">
         <is>
           <t>PASS: 10ms period. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="J21" s="51" t="inlineStr"/>
+      <c r="K21" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr"/>
-      <c r="M21" s="18" t="inlineStr"/>
-      <c r="N21" s="18" t="inlineStr">
+      <c r="L21" s="53" t="inlineStr"/>
+      <c r="M21" s="48" t="inlineStr"/>
+      <c r="N21" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O21" s="18" t="inlineStr"/>
-      <c r="P21" s="18" t="inlineStr"/>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="O21" s="50" t="inlineStr"/>
+      <c r="P21" s="50" t="inlineStr"/>
+      <c r="Q21" s="54">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>MS-018</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>DMA frame کامل</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: شمارندهٔ DMA (یعنی CNDTR) را قبل و بعد از کپی بخوان؛ DMA دو فریمی است (2 ضربدر 5).
@@ -2278,64 +2636,68 @@
 گام ۴: GetRaw باید پنجرهٔ پایدار (stable=true) بدهد؛ کپی پاره یا تمام شدن retry یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="58" t="inlineStr">
         <is>
           <t>DMA CNDTR</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H22" s="55" t="inlineStr">
         <is>
           <t>GetRaw باید stable window true بدهد و 5 نمونه valid. PASS: stable copy. FAIL: torn یا retry exceed.</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="55" t="inlineStr">
         <is>
           <t>PASS: stable frame. FAIL: unstable.</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr"/>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="J22" s="55" t="inlineStr"/>
+      <c r="K22" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr"/>
-      <c r="M22" s="20" t="inlineStr"/>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="L22" s="59" t="inlineStr"/>
+      <c r="M22" s="55" t="inlineStr"/>
+      <c r="N22" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O22" s="20" t="inlineStr"/>
-      <c r="P22" s="20" t="inlineStr"/>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="O22" s="58" t="inlineStr"/>
+      <c r="P22" s="58" t="inlineStr"/>
+      <c r="Q22" s="60">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>MS-019</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>تطبیق فرمول و کالیبراسیون / صفر</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=0 بده.
@@ -2343,64 +2705,68 @@
 گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>counts 0</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="48" t="inlineStr">
         <is>
           <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="48" t="inlineStr">
         <is>
           <t>PASS: zero. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr"/>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="J23" s="51" t="inlineStr"/>
+      <c r="K23" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L23" s="18" t="inlineStr"/>
-      <c r="M23" s="18" t="inlineStr"/>
-      <c r="N23" s="18" t="inlineStr">
+      <c r="L23" s="53" t="inlineStr"/>
+      <c r="M23" s="48" t="inlineStr"/>
+      <c r="N23" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O23" s="18" t="inlineStr"/>
-      <c r="P23" s="18" t="inlineStr"/>
-    </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="O23" s="50" t="inlineStr"/>
+      <c r="P23" s="50" t="inlineStr"/>
+      <c r="Q23" s="54">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>MS-020</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>تطبیق فرمول / فول</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
@@ -2408,64 +2774,68 @@
 گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="58" t="inlineStr">
         <is>
           <t>counts 4095 (فول)</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H24" s="55" t="inlineStr">
         <is>
           <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="55" t="inlineStr">
         <is>
           <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="J24" s="55" t="inlineStr"/>
+      <c r="K24" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr"/>
-      <c r="M24" s="20" t="inlineStr"/>
-      <c r="N24" s="20" t="inlineStr">
+      <c r="L24" s="59" t="inlineStr"/>
+      <c r="M24" s="55" t="inlineStr"/>
+      <c r="N24" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O24" s="20" t="inlineStr"/>
-      <c r="P24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="O24" s="58" t="inlineStr"/>
+      <c r="P24" s="58" t="inlineStr"/>
+      <c r="Q24" s="60">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>MS-021</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="48" t="inlineStr">
         <is>
           <t>کالیبراسیون برد / tolerance</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری/منبع واقعی دقیقاً 24 ولت به ورودی V24 بده.
 گام ۲: با مولتی‌متر (DMM) ولتاژ روی پایهٔ PA2 را اندازه بگیر؛ باید حدود 2147 میلی‌ولت باشد.
@@ -2473,64 +2843,68 @@
 گام ۴: V24 خوانده‌شده باید حدود 24000 میلی‌ولت باشد. خطای مجاز 1 درصد مقاومت‌ها به‌علاوهٔ 1 LSB است؛ خطای کمتر از 1 درصد قبول و بیشتر از 2 درصد رد است.</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>V24=24V (pin≈2147mV, counts≈2665)</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="H25" s="48" t="inlineStr">
         <is>
           <t>ADC pin≈2147mV، counts≈2665، V24≈24000mV ±tolerance (1% مقاومت + 1LSB). PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="48" t="inlineStr">
         <is>
           <t>PASS: 2665→24000 within 1%. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr"/>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="J25" s="51" t="inlineStr"/>
+      <c r="K25" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L25" s="18" t="inlineStr"/>
-      <c r="M25" s="18" t="inlineStr"/>
-      <c r="N25" s="18" t="inlineStr">
+      <c r="L25" s="53" t="inlineStr"/>
+      <c r="M25" s="48" t="inlineStr"/>
+      <c r="N25" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O25" s="18" t="inlineStr"/>
-      <c r="P25" s="18" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="O25" s="50" t="inlineStr"/>
+      <c r="P25" s="50" t="inlineStr"/>
+      <c r="Q25" s="54">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>ME-022</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t>snapshot zeroing مصرف‌کننده</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="55" t="inlineStr">
         <is>
           <t>Measurement خاموش</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="55" t="inlineStr">
         <is>
           <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
 گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
@@ -2538,54 +2912,314 @@
 گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="58" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="58" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="55" t="inlineStr">
         <is>
           <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="55" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" s="55" t="n"/>
+      <c r="L26" s="62" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="M26" s="55" t="n"/>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="58" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="P26" s="58" t="n"/>
+      <c r="Q26" s="60" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="Q27" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="63">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="63">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="63">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="63">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="63">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="63">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="63">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="63">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="63">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="63">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="63">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="63">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="63">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="63">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="63">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="63">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="63">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="63">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="63">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="63">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="63">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="63">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="63">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="63">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Q63" s="63">
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Q64" s="63">
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="Q65" s="63">
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="Q66" s="63">
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P25"/>
+  <autoFilter ref="A4:Q26"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="L5:L106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -2595,6 +3229,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2610,430 +3245,430 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>مرجع Measurement — فرمول‌ها و کالیبراسیون</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Vref و ADC</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>Vref 3300mV، 12bit 4095</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="66" t="inlineStr">
         <is>
           <t>پایه</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="66" t="inlineStr">
         <is>
           <t>BSP_MEASUREMENT_VREF_MV/ADC_FULL_SCALE</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="66" t="inlineStr">
         <is>
           <t>مرجع STM32F1</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>MS-019,020</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>CountsToMv</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>counts*3300/4095</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="66" t="inlineStr">
         <is>
           <t>ولتاژ پایه ADC</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>func__BspMeasurement_CountsToMv</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>±0.8mV/LSB</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="67" t="inlineStr">
         <is>
           <t>MS-008..012</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>V24</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>adcPinMv*(69200+6800)/6800</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>منبع 24V</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>DIV24_TOP/BOTTOM</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>±9mV/LSB</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="67" t="inlineStr">
         <is>
           <t>MS-008,009</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>V12</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>adcPinMv*(34200+6800)/6800</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>منبع 12V</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="66" t="inlineStr">
         <is>
           <t>DIV12_TOP/BOTTOM</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="66" t="inlineStr">
         <is>
           <t>±4.8mV/LSB</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>MS-010</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>counts*3300*1000/(4095*101*10)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="66" t="inlineStr">
         <is>
           <t>SHUNT 10mΩ GAIN101</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="66" t="inlineStr">
         <is>
           <t>±0.8mA/LSB</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>MS-011,012</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>Warmup</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>3 فریم</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>valid پس از 3</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="66" t="inlineStr">
         <is>
           <t>MEASUREMENT_WARMUP_FRAME_COUNT=3</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="66" t="inlineStr">
         <is>
           <t>واحد: فریم کامل</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
         <is>
           <t>MS-002..006</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>GetRaw false → valid false + reset</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve"> warmup reset</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="66" t="inlineStr">
         <is>
           <t>ناپایدار</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>MS-005</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>Vin zero</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>Vin 0V still valid</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>invalid نشود</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="67" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="66" t="inlineStr">
         <is>
           <t>مستقل از Vin</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="67" t="inlineStr">
         <is>
           <t>MS-007</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>GetSnapshot NULL → false</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>بدون کرش</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="66" t="inlineStr">
         <is>
           <t>بررسی اشاره‌گر</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>MS-015</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>Atomic</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>osKernelLock</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>بدون torn read</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="67" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="66" t="inlineStr">
         <is>
           <t>CMSIS-RTOS2</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="67" t="inlineStr">
         <is>
           <t>MS-016</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>هر 10ms یک Run</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>MEASUREMENT_PERIOD_MS=10</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="66" t="inlineStr">
         <is>
           <t>osDelayUntil</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="67" t="inlineStr">
         <is>
           <t>MS-017</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>DMA</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>2×5 halfword circular</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>CNDTR stable</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>bsp_adc.c</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="66" t="inlineStr">
         <is>
           <t>2 فریم</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="67" t="inlineStr">
         <is>
           <t>MS-018</t>
         </is>
@@ -3044,6 +3679,24 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId16"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -3053,6 +3706,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3075,81 +3729,93 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="41" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="41" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="41" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="41" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="41" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="41" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -3319,6 +3985,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3334,43 +4001,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Measurement — ADC/ کالیبراسیون</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Measurement — ADC/ کالیبراسیون</t>
         </is>
@@ -3379,22 +4046,22 @@
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>2026-09-16 (1.0)</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="70" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -3403,17 +4070,17 @@
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
@@ -3423,13 +4090,13 @@
       <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr"/>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="70" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -3439,18 +4106,18 @@
       <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr"/>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
@@ -3459,12 +4126,12 @@
       <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
@@ -3475,12 +4142,12 @@
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>ADC 5ch + DMA + کالیبراسیون</t>
         </is>
@@ -3491,12 +4158,12 @@
       <c r="F10" s="11" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t>آستانه warmup</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>3 فریم</t>
         </is>
@@ -3507,12 +4174,12 @@
       <c r="F11" s="11" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>دوره</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
@@ -3523,12 +4190,12 @@
       <c r="F12" s="11" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>کالیبراسیون</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>Vref3300/4095 Div24/Div12 Shunt10 Gain101</t>
         </is>
@@ -3539,29 +4206,29 @@
       <c r="F13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
@@ -3570,16 +4237,16 @@
       <c r="F15" s="9" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="71">
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="42" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
@@ -3589,21 +4256,21 @@
       <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
@@ -3612,21 +4279,21 @@
       <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
@@ -3635,21 +4302,21 @@
       <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
@@ -3658,16 +4325,16 @@
       <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="71">
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
@@ -3677,16 +4344,16 @@
       <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="71">
         <f>IF(B16=0,"",TEXT(B17/B16,"0%"))</f>
         <v/>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
@@ -3696,34 +4363,34 @@
       <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="41" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="41" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
@@ -3731,7 +4398,7 @@
       <c r="F23" s="9" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
@@ -3743,7 +4410,7 @@
       <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
@@ -3755,7 +4422,7 @@
       <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
@@ -3767,7 +4434,7 @@
       <c r="F26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
@@ -3808,6 +4475,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3818,189 +4486,198 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>BoardTest</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>InputOk</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Charging</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>BatteryRun</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Buzzer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>Changeover</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>باز</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>در حال بررسی</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
         <is>
           <t>بسته</t>
         </is>
@@ -4014,7 +4691,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4026,55 +4703,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول اندازه‌گیری (Measurement)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>Measurement_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -4087,6 +4765,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -259,6 +262,13 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -408,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -634,6 +644,13 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1309,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2404,12 +2421,12 @@
     <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>MS-015</t>
+          <t>MS-017</t>
         </is>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>NULL در GetSnapshot</t>
+          <t>دوره 10ms تسک Measurement</t>
         </is>
       </c>
       <c r="C19" s="49" t="inlineStr">
@@ -2419,147 +2436,10 @@
       </c>
       <c r="D19" s="48" t="inlineStr">
         <is>
-          <t>هر زمان</t>
+          <t>valid=true</t>
         </is>
       </c>
       <c r="E19" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
-گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
-گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F19" s="50" t="inlineStr">
-        <is>
-          <t>NULL pointer</t>
-        </is>
-      </c>
-      <c r="G19" s="50" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>return false، بدون کرش، snapshot تغییر نکند. PASS: false. FAIL: کرش یا true.</t>
-        </is>
-      </c>
-      <c r="I19" s="48" t="inlineStr">
-        <is>
-          <t>PASS: NULL → false. FAIL: true/crash.</t>
-        </is>
-      </c>
-      <c r="J19" s="51" t="inlineStr"/>
-      <c r="K19" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L19" s="53" t="inlineStr"/>
-      <c r="M19" s="48" t="inlineStr"/>
-      <c r="N19" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O19" s="50" t="inlineStr"/>
-      <c r="P19" s="50" t="inlineStr"/>
-      <c r="Q19" s="54">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>MS-016</t>
-        </is>
-      </c>
-      <c r="B20" s="55" t="inlineStr">
-        <is>
-          <t>Snapshot چندفیلدی اتمیک</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="55" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E20" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
-گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
-گام ۳: 20 میلی‌ثانیه این خواندن هم‌زمان را تکرار کن.
-گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F20" s="58" t="inlineStr">
-        <is>
-          <t>concurrent read</t>
-        </is>
-      </c>
-      <c r="G20" s="58" t="inlineStr">
-        <is>
-          <t>20ms</t>
-        </is>
-      </c>
-      <c r="H20" s="55" t="inlineStr">
-        <is>
-          <t>هر دو snapshot کپی‌شده باید یا کامل قدیمی یا کامل جدید باشد، نه ترکیبی. با osKernelLock تضمین. PASS: atomic. FAIL: torn read.</t>
-        </is>
-      </c>
-      <c r="I20" s="55" t="inlineStr">
-        <is>
-          <t>PASS: no torn data. FAIL: partial.</t>
-        </is>
-      </c>
-      <c r="J20" s="55" t="inlineStr"/>
-      <c r="K20" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L20" s="59" t="inlineStr"/>
-      <c r="M20" s="55" t="inlineStr"/>
-      <c r="N20" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O20" s="58" t="inlineStr"/>
-      <c r="P20" s="58" t="inlineStr"/>
-      <c r="Q20" s="60">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>MS-017</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>دوره 10ms تسک Measurement</t>
-        </is>
-      </c>
-      <c r="C21" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D21" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
@@ -2567,137 +2447,68 @@
 گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F21" s="50" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="50" t="inlineStr">
+      <c r="G19" s="50" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="H19" s="48" t="inlineStr">
         <is>
           <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
         </is>
       </c>
-      <c r="I21" s="48" t="inlineStr">
+      <c r="I19" s="48" t="inlineStr">
         <is>
           <t>PASS: 10ms period. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J21" s="51" t="inlineStr"/>
-      <c r="K21" s="52" t="inlineStr">
+      <c r="J19" s="51" t="inlineStr"/>
+      <c r="K19" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="53" t="inlineStr"/>
-      <c r="M21" s="48" t="inlineStr"/>
-      <c r="N21" s="48" t="inlineStr">
+      <c r="L19" s="53" t="inlineStr"/>
+      <c r="M19" s="48" t="inlineStr"/>
+      <c r="N19" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O21" s="50" t="inlineStr"/>
-      <c r="P21" s="50" t="inlineStr"/>
-      <c r="Q21" s="54">
+      <c r="O19" s="50" t="inlineStr"/>
+      <c r="P19" s="50" t="inlineStr"/>
+      <c r="Q19" s="54">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>MS-018</t>
-        </is>
-      </c>
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t>DMA frame کامل</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
+        <is>
+          <t>MS-019</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>تطبیق فرمول و کالیبراسیون / صفر</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E22" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: شمارندهٔ DMA (یعنی CNDTR) را قبل و بعد از کپی بخوان؛ DMA دو فریمی است (2 ضربدر 5).
-گام ۳: چک کن حین کپی، شمارنده در همان نیمه مانده باشد و هر 5 نمونهٔ فریم کامل کپی شده باشد.
-گام ۴: GetRaw باید پنجرهٔ پایدار (stable=true) بدهد؛ کپی پاره یا تمام شدن retry یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F22" s="58" t="inlineStr">
-        <is>
-          <t>DMA CNDTR</t>
-        </is>
-      </c>
-      <c r="G22" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H22" s="55" t="inlineStr">
-        <is>
-          <t>GetRaw باید stable window true بدهد و 5 نمونه valid. PASS: stable copy. FAIL: torn یا retry exceed.</t>
-        </is>
-      </c>
-      <c r="I22" s="55" t="inlineStr">
-        <is>
-          <t>PASS: stable frame. FAIL: unstable.</t>
-        </is>
-      </c>
-      <c r="J22" s="55" t="inlineStr"/>
-      <c r="K22" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L22" s="59" t="inlineStr"/>
-      <c r="M22" s="55" t="inlineStr"/>
-      <c r="N22" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O22" s="58" t="inlineStr"/>
-      <c r="P22" s="58" t="inlineStr"/>
-      <c r="Q22" s="60">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>MS-019</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>تطبیق فرمول و کالیبراسیون / صفر</t>
-        </is>
-      </c>
-      <c r="C23" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D23" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E23" s="48" t="inlineStr">
+      <c r="E20" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=0 بده.
@@ -2705,68 +2516,68 @@
 گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="50" t="inlineStr">
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>counts 0</t>
         </is>
       </c>
-      <c r="G23" s="50" t="inlineStr">
+      <c r="G20" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H23" s="48" t="inlineStr">
+      <c r="H20" s="48" t="inlineStr">
         <is>
           <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="I23" s="48" t="inlineStr">
+      <c r="I20" s="48" t="inlineStr">
         <is>
           <t>PASS: zero. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="J23" s="51" t="inlineStr"/>
-      <c r="K23" s="52" t="inlineStr">
+      <c r="J20" s="51" t="inlineStr"/>
+      <c r="K20" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L23" s="53" t="inlineStr"/>
-      <c r="M23" s="48" t="inlineStr"/>
-      <c r="N23" s="48" t="inlineStr">
+      <c r="L20" s="53" t="inlineStr"/>
+      <c r="M20" s="48" t="inlineStr"/>
+      <c r="N20" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O23" s="50" t="inlineStr"/>
-      <c r="P23" s="50" t="inlineStr"/>
-      <c r="Q23" s="54">
+      <c r="O20" s="50" t="inlineStr"/>
+      <c r="P20" s="50" t="inlineStr"/>
+      <c r="Q20" s="54">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="47" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>MS-020</t>
         </is>
       </c>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>تطبیق فرمول / فول</t>
         </is>
       </c>
-      <c r="C24" s="56" t="inlineStr">
+      <c r="C21" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D21" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E24" s="55" t="inlineStr">
+      <c r="E21" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
@@ -2774,68 +2585,68 @@
 گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
-      <c r="F24" s="58" t="inlineStr">
+      <c r="F21" s="58" t="inlineStr">
         <is>
           <t>counts 4095 (فول)</t>
         </is>
       </c>
-      <c r="G24" s="58" t="inlineStr">
+      <c r="G21" s="58" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H24" s="55" t="inlineStr">
+      <c r="H21" s="55" t="inlineStr">
         <is>
           <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I24" s="55" t="inlineStr">
+      <c r="I21" s="55" t="inlineStr">
         <is>
           <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J24" s="55" t="inlineStr"/>
-      <c r="K24" s="55" t="inlineStr">
+      <c r="J21" s="55" t="inlineStr"/>
+      <c r="K21" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L24" s="59" t="inlineStr"/>
-      <c r="M24" s="55" t="inlineStr"/>
-      <c r="N24" s="55" t="inlineStr">
+      <c r="L21" s="59" t="inlineStr"/>
+      <c r="M21" s="55" t="inlineStr"/>
+      <c r="N21" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O24" s="58" t="inlineStr"/>
-      <c r="P24" s="58" t="inlineStr"/>
-      <c r="Q24" s="60">
+      <c r="O21" s="58" t="inlineStr"/>
+      <c r="P21" s="58" t="inlineStr"/>
+      <c r="Q21" s="60">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="47" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>MS-021</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B22" s="48" t="inlineStr">
         <is>
           <t>کالیبراسیون برد / tolerance</t>
         </is>
       </c>
-      <c r="C25" s="50" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D25" s="48" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E25" s="48" t="inlineStr">
+      <c r="E22" s="48" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری/منبع واقعی دقیقاً 24 ولت به ورودی V24 بده.
 گام ۲: با مولتی‌متر (DMM) ولتاژ روی پایهٔ PA2 را اندازه بگیر؛ باید حدود 2147 میلی‌ولت باشد.
@@ -2843,362 +2654,288 @@
 گام ۴: V24 خوانده‌شده باید حدود 24000 میلی‌ولت باشد. خطای مجاز 1 درصد مقاومت‌ها به‌علاوهٔ 1 LSB است؛ خطای کمتر از 1 درصد قبول و بیشتر از 2 درصد رد است.</t>
         </is>
       </c>
-      <c r="F25" s="50" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>V24=24V (pin≈2147mV, counts≈2665)</t>
         </is>
       </c>
-      <c r="G25" s="50" t="inlineStr">
+      <c r="G22" s="50" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H25" s="48" t="inlineStr">
+      <c r="H22" s="48" t="inlineStr">
         <is>
           <t>ADC pin≈2147mV، counts≈2665، V24≈24000mV ±tolerance (1% مقاومت + 1LSB). PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="I25" s="48" t="inlineStr">
+      <c r="I22" s="48" t="inlineStr">
         <is>
           <t>PASS: 2665→24000 within 1%. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="J25" s="51" t="inlineStr"/>
-      <c r="K25" s="52" t="inlineStr">
+      <c r="J22" s="51" t="inlineStr"/>
+      <c r="K22" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L25" s="53" t="inlineStr"/>
-      <c r="M25" s="48" t="inlineStr"/>
-      <c r="N25" s="48" t="inlineStr">
+      <c r="L22" s="53" t="inlineStr"/>
+      <c r="M22" s="48" t="inlineStr"/>
+      <c r="N22" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O25" s="50" t="inlineStr"/>
-      <c r="P25" s="50" t="inlineStr"/>
-      <c r="Q25" s="54">
+      <c r="O22" s="50" t="inlineStr"/>
+      <c r="P22" s="50" t="inlineStr"/>
+      <c r="Q22" s="54">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="Q23" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="Q24" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="Q25" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="47" t="inlineStr">
-        <is>
-          <t>ME-022</t>
-        </is>
-      </c>
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t>snapshot zeroing مصرف‌کننده</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D26" s="55" t="inlineStr">
-        <is>
-          <t>Measurement خاموش</t>
-        </is>
-      </c>
-      <c r="E26" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
-گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
-گام ۳: snapshot هر سه را بخوان: valid باید false و هر 9 فیلد صفر باشد (هیچ ساختار نامشخصی نباید باشد).
-گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
-        </is>
-      </c>
-      <c r="F26" s="58" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G26" s="58" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H26" s="55" t="inlineStr">
-        <is>
-          <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
-        </is>
-      </c>
-      <c r="I26" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="55" t="inlineStr">
-        <is>
-          <t>بدون indeterminate struct</t>
-        </is>
-      </c>
-      <c r="K26" s="55" t="n"/>
-      <c r="L26" s="62" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M26" s="55" t="n"/>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="58" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P26" s="58" t="n"/>
-      <c r="Q26" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q26" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="63">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="63">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="63">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="63">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="63">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="63">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="63">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="63">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="63">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="63">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="63">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="63">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="63">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="63">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="63">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="63">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="63">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="63">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="63">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="63">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="63">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="63">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="63">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="63">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="63">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="63">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="63">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="63">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="63">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="63">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="63">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="63">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="63">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="63">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="63">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="63">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="Q63" s="63">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="Q64" s="63">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="Q65" s="63">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="Q66" s="63">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q26"/>
+  <autoFilter ref="A4:Q62"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
@@ -3211,14 +2948,14 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D7" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
+    <hyperlink ref="D8" location="'برنامه تست'!A7"/>
+    <hyperlink ref="E8" location="'برنامه تست'!A7"/>
+    <hyperlink ref="E9" location="'برنامه تست'!A8"/>
+    <hyperlink ref="D10" location="'برنامه تست'!A9"/>
+    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3227,6 +2964,545 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="81" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>شناسه تست</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>ورودی‌ها</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="N4" s="37" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>MS-015</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>NULL در GetSnapshot</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>هر زمان</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
+گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
+گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>NULL pointer</t>
+        </is>
+      </c>
+      <c r="G5" s="50" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>return false، بدون کرش، snapshot تغییر نکند. PASS: false. FAIL: کرش یا true.</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>PASS: NULL → false. FAIL: true/crash.</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="n"/>
+      <c r="K5" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="53" t="n"/>
+      <c r="M5" s="48" t="n"/>
+      <c r="N5" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O5" s="50" t="n"/>
+      <c r="P5" s="50" t="n"/>
+      <c r="Q5" s="54">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>MS-016</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>Snapshot چندفیلدی اتمیک</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
+گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
+گام ۳: 20 میلی‌ثانیه این خواندن هم‌زمان را تکرار کن.
+گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>concurrent read</t>
+        </is>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>20ms</t>
+        </is>
+      </c>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>هر دو snapshot کپی‌شده باید یا کامل قدیمی یا کامل جدید باشد، نه ترکیبی. با osKernelLock تضمین. PASS: atomic. FAIL: torn read.</t>
+        </is>
+      </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>PASS: no torn data. FAIL: partial.</t>
+        </is>
+      </c>
+      <c r="J6" s="55" t="n"/>
+      <c r="K6" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="59" t="n"/>
+      <c r="M6" s="55" t="n"/>
+      <c r="N6" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O6" s="58" t="n"/>
+      <c r="P6" s="58" t="n"/>
+      <c r="Q6" s="60">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>MS-018</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>DMA frame کامل</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: شمارندهٔ DMA (یعنی CNDTR) را قبل و بعد از کپی بخوان؛ DMA دو فریمی است (2 ضربدر 5).
+گام ۳: چک کن حین کپی، شمارنده در همان نیمه مانده باشد و هر 5 نمونهٔ فریم کامل کپی شده باشد.
+گام ۴: GetRaw باید پنجرهٔ پایدار (stable=true) بدهد؛ کپی پاره یا تمام شدن retry یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>DMA CNDTR</t>
+        </is>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>GetRaw باید stable window true بدهد و 5 نمونه valid. PASS: stable copy. FAIL: torn یا retry exceed.</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>PASS: stable frame. FAIL: unstable.</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="55" t="n"/>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O7" s="58" t="n"/>
+      <c r="P7" s="58" t="n"/>
+      <c r="Q7" s="60">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>ME-022</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>snapshot zeroing مصرف‌کننده</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>Measurement خاموش</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
+گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
+گام ۳: snapshot هر سه را بخوان: valid باید false و هر 9 فیلد صفر باشد (هیچ ساختار نامشخصی نباید باشد).
+گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
+        </is>
+      </c>
+      <c r="F8" s="58" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H8" s="55" t="inlineStr">
+        <is>
+          <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="55" t="inlineStr">
+        <is>
+          <t>بدون indeterminate struct</t>
+        </is>
+      </c>
+      <c r="K8" s="55" t="n"/>
+      <c r="L8" s="62" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M8" s="55" t="n"/>
+      <c r="N8" s="55" t="n"/>
+      <c r="O8" s="58" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P8" s="58" t="n"/>
+      <c r="Q8" s="60" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="63">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="63">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="63">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="63">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="63">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="63">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="63">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="63">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="63">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="63">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="63">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="63">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="63">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="63">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="63">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="63">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="63">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="63">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q8"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3680,22 +3956,22 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId16"/>
+    <hyperlink ref="F4" location="'برنامه تست'!A20"/>
+    <hyperlink ref="F5" location="'برنامه تست'!A12"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A12"/>
+    <hyperlink ref="F7" location="'برنامه تست'!A14"/>
+    <hyperlink ref="F8" location="'برنامه تست'!A15"/>
+    <hyperlink ref="F9" location="'برنامه تست'!A6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId1"/>
+    <hyperlink ref="F10" location="'برنامه تست'!A9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink ref="F11" location="'برنامه تست'!A11"/>
+    <hyperlink ref="F12" location="'تست‌های برنامه‌نویسی'!A5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId3"/>
+    <hyperlink ref="F13" location="'تست‌های برنامه‌نویسی'!A6"/>
+    <hyperlink ref="F14" location="'برنامه تست'!A19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId4"/>
+    <hyperlink ref="F15" location="'تست‌های برنامه‌نویسی'!A7"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3703,7 +3979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3982,7 +4258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -4472,7 +4748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -4688,7 +4964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -270,7 +273,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -331,6 +334,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -418,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -651,6 +659,9 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1326,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1488,7 +1499,7 @@
       </c>
       <c r="G5" s="50" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>کمتر از یک ثانیه</t>
         </is>
       </c>
       <c r="H5" s="48" t="inlineStr">
@@ -1524,784 +1535,25 @@
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="47" t="inlineStr">
         <is>
-          <t>MS-002</t>
-        </is>
-      </c>
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>Warmup / فریم اول</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="inlineStr">
+          <t>MS-013</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>بررسی input_present / High</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
-        <is>
-          <t>پس از Init و Start موفق</t>
-        </is>
-      </c>
-      <c r="E6" s="57" t="inlineStr">
-        <is>
-          <t>گام ۱: Init و Start را با موفقیت انجام بده (ادامهٔ MS-001).
-گام ۲: یک فریم کامل و پایدار ADC روی هر 5 کانال اعمال کن؛ مثلاً روی همه 2 ولت (counts حدود 2482).
-گام ۳: فقط یک بار func__Measurement_Run را صدا بزن و valid را بخوان.
-گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 1 شده باشد؛ valid شدن در فریم اول یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F6" s="58" t="inlineStr">
-        <is>
-          <t>فریم 1 کامل و پایدار, counts≈2482 (2V)</t>
-        </is>
-      </c>
-      <c r="G6" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H6" s="55" t="inlineStr">
-        <is>
-          <t>valid همچنان false، warmupCounter=1، globals هنوز 0 یا قدیمی اما valid=false. PASS: هنوز invalid. FAIL: valid true زودهنگام.</t>
-        </is>
-      </c>
-      <c r="I6" s="55" t="inlineStr">
-        <is>
-          <t>PASS: فریم1 → still false. FAIL: valid true.</t>
-        </is>
-      </c>
-      <c r="J6" s="55" t="inlineStr"/>
-      <c r="K6" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr"/>
-      <c r="M6" s="55" t="inlineStr"/>
-      <c r="N6" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O6" s="58" t="inlineStr"/>
-      <c r="P6" s="58" t="inlineStr"/>
-      <c r="Q6" s="60">
-        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>MS-003</t>
-        </is>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>Warmup / فریم دوم</t>
-        </is>
-      </c>
-      <c r="C7" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="61" t="inlineStr">
-        <is>
-          <t>پس از MS-002</t>
-        </is>
-      </c>
-      <c r="E7" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
-گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
-گام ۳: یک Run دیگر بزن و valid را بخوان.
-گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F7" s="50" t="inlineStr">
-        <is>
-          <t>فریم 2 کامل, counts 2482</t>
-        </is>
-      </c>
-      <c r="G7" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H7" s="48" t="inlineStr">
-        <is>
-          <t>valid همچنان false، counter=2. PASS: still false. FAIL: true.</t>
-        </is>
-      </c>
-      <c r="I7" s="48" t="inlineStr">
-        <is>
-          <t>PASS: فریم2 still false. FAIL: true.</t>
-        </is>
-      </c>
-      <c r="J7" s="51" t="inlineStr"/>
-      <c r="K7" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L7" s="53" t="inlineStr"/>
-      <c r="M7" s="48" t="inlineStr"/>
-      <c r="N7" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O7" s="50" t="inlineStr"/>
-      <c r="P7" s="50" t="inlineStr"/>
-      <c r="Q7" s="54">
-        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>MS-004</t>
-        </is>
-      </c>
-      <c r="B8" s="55" t="inlineStr">
-        <is>
-          <t>Warmup / فریم سوم</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="57" t="inlineStr">
-        <is>
-          <t>پس از MS-003</t>
-        </is>
-      </c>
-      <c r="E8" s="57" t="inlineStr">
-        <is>
-          <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
-گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
-گام ۳: یک Run بزن.
-گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
-        </is>
-      </c>
-      <c r="F8" s="58" t="inlineStr">
-        <is>
-          <t>فریم 3 کامل, counts: V channels 2482 (2V pin), I channels 610 (0.49V)</t>
-        </is>
-      </c>
-      <c r="G8" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H8" s="55" t="inlineStr">
-        <is>
-          <t>valid=true، همه globals به‌روز: 2V pin → V24≈22352mV, V12≈12058mV, Current≈486mA با I counts 610, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
-        </is>
-      </c>
-      <c r="I8" s="55" t="inlineStr">
-        <is>
-          <t>PASS: فریم3 → valid true با V24≈22352 و I≈486mA. FAIL: still false.</t>
-        </is>
-      </c>
-      <c r="J8" s="55" t="inlineStr"/>
-      <c r="K8" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr"/>
-      <c r="M8" s="55" t="inlineStr"/>
-      <c r="N8" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O8" s="58" t="inlineStr"/>
-      <c r="P8" s="58" t="inlineStr"/>
-      <c r="Q8" s="60">
-        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>MS-005</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>Warmup / فریم ناقص</t>
-        </is>
-      </c>
-      <c r="C9" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>پس از valid=true</t>
-        </is>
-      </c>
-      <c r="E9" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن (پایان MS-004).
-گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
-گام ۳: یک Run بزن.
-گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F9" s="50" t="inlineStr">
-        <is>
-          <t>فریم ناقص/ناپایدار (GetRaw false)</t>
-        </is>
-      </c>
-      <c r="G9" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H9" s="48" t="inlineStr">
-        <is>
-          <t>valid=false فوری، warmupCounter reset به 0، snapshot.valid false. PASS: invalid و reset. FAIL: همچنان true.</t>
-        </is>
-      </c>
-      <c r="I9" s="48" t="inlineStr">
-        <is>
-          <t>PASS: unstable → invalid+reset. FAIL: remains true.</t>
-        </is>
-      </c>
-      <c r="J9" s="51" t="inlineStr"/>
-      <c r="K9" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L9" s="53" t="inlineStr"/>
-      <c r="M9" s="48" t="inlineStr"/>
-      <c r="N9" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O9" s="50" t="inlineStr"/>
-      <c r="P9" s="50" t="inlineStr"/>
-      <c r="Q9" s="54">
-        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>MS-006</t>
-        </is>
-      </c>
-      <c r="B10" s="55" t="inlineStr">
-        <is>
-          <t>Warmup / شروع دوباره</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>پس از MS-005</t>
-        </is>
-      </c>
-      <c r="E10" s="57" t="inlineStr">
-        <is>
-          <t>گام ۱: ادامهٔ MS-005 (فریم خراب و warmup=0).
-گام ۲: سه فریم کامل و پایدار پشت سر هم اعمال کن و هر کدام یک Run بزن (در مجموع 30 میلی‌ثانیه).
-گام ۳: بعد از فریم اول و دوم هنوز باید valid=false باشد.
-گام ۴: دقیقاً بعد از فریم سوم باید valid=true شود؛ زودتر یا دیرتر شدن یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F10" s="58" t="inlineStr">
-        <is>
-          <t>3 فریم کامل</t>
-        </is>
-      </c>
-      <c r="G10" s="58" t="inlineStr">
-        <is>
-          <t>30ms</t>
-        </is>
-      </c>
-      <c r="H10" s="55" t="inlineStr">
-        <is>
-          <t>پس از فریم سوم دوباره valid=true. PASS: warmup دوباره 3 فریم. FAIL: valid زودتر یا دیرتر.</t>
-        </is>
-      </c>
-      <c r="I10" s="55" t="inlineStr">
-        <is>
-          <t>PASS: 3 فریم دوباره → true. FAIL: otherwise.</t>
-        </is>
-      </c>
-      <c r="J10" s="55" t="inlineStr"/>
-      <c r="K10" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr"/>
-      <c r="M10" s="55" t="inlineStr"/>
-      <c r="N10" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O10" s="58" t="inlineStr"/>
-      <c r="P10" s="58" t="inlineStr"/>
-      <c r="Q10" s="60">
-        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>MS-007</t>
-        </is>
-      </c>
-      <c r="B11" s="48" t="inlineStr">
-        <is>
-          <t>ورودی 24V قطع</t>
-        </is>
-      </c>
-      <c r="C11" s="50" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>valid=true با Vin=0</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
-گام ۲: یک Run بزن.
-گام ۳: valid باید همچنان true بماند، چون قطع ورودی نباید ADC را نامعتبر کند.
-گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F11" s="50" t="inlineStr">
-        <is>
-          <t>v_in 0V (counts 0), سایر 2V</t>
-        </is>
-      </c>
-      <c r="G11" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H11" s="48" t="inlineStr">
-        <is>
-          <t>valid همچنان true (قطع ورودی ADC را invalid نمی‌کند)، v_in_mv≈0، سایر مقادیر به‌روز. PASS: valid true با Vin صفر. FAIL: valid false.</t>
-        </is>
-      </c>
-      <c r="I11" s="48" t="inlineStr">
-        <is>
-          <t>PASS: Vin zero still valid. FAIL: invalid.</t>
-        </is>
-      </c>
-      <c r="J11" s="51" t="inlineStr"/>
-      <c r="K11" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L11" s="53" t="inlineStr"/>
-      <c r="M11" s="48" t="inlineStr"/>
-      <c r="N11" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O11" s="50" t="inlineStr"/>
-      <c r="P11" s="50" t="inlineStr"/>
-      <c r="Q11" s="54">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>MS-008</t>
-        </is>
-      </c>
-      <c r="B12" s="55" t="inlineStr">
-        <is>
-          <t>بررسی v_in_mv</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="55" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E12" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
-گام ۳: اول خودت حساب کن: 1241 ضربدر 3300 تقسیم بر 4095 می‌شود حدود 1000 میلی‌ولت روی پایه؛ بعد ضربدر 76000 تقسیم بر 6800 می‌شود حدود 11176 میلی‌ولت.
-گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F12" s="58" t="inlineStr">
-        <is>
-          <t>counts 1241 (1V)</t>
-        </is>
-      </c>
-      <c r="G12" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H12" s="55" t="inlineStr">
-        <is>
-          <t>v_in_mv = 1241*3300/4095≈1000mV pin → *76000/6800≈11176mV. tolerance ±9mV. PASS: خوانش در tolerance. FAIL: &gt;20mV خطا.</t>
-        </is>
-      </c>
-      <c r="I12" s="55" t="inlineStr">
-        <is>
-          <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J12" s="55" t="inlineStr"/>
-      <c r="K12" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L12" s="59" t="inlineStr"/>
-      <c r="M12" s="55" t="inlineStr"/>
-      <c r="N12" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O12" s="58" t="inlineStr"/>
-      <c r="P12" s="58" t="inlineStr"/>
-      <c r="Q12" s="60">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>MS-009</t>
-        </is>
-      </c>
-      <c r="B13" s="48" t="inlineStr">
-        <is>
-          <t>بررسی v_bat24_mv</t>
-        </is>
-      </c>
-      <c r="C13" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
-گام ۳: مقدار v_bat24_mv را بخوان.
-گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F13" s="50" t="inlineStr">
-        <is>
-          <t>counts 2482</t>
-        </is>
-      </c>
-      <c r="G13" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>v_bat24_mv≈22352mV ±9mV. PASS. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="I13" s="48" t="inlineStr">
-        <is>
-          <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J13" s="51" t="inlineStr"/>
-      <c r="K13" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L13" s="53" t="inlineStr"/>
-      <c r="M13" s="48" t="inlineStr"/>
-      <c r="N13" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O13" s="50" t="inlineStr"/>
-      <c r="P13" s="50" t="inlineStr"/>
-      <c r="Q13" s="54">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>MS-010</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="inlineStr">
-        <is>
-          <t>بررسی v_bat12_mv</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="55" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E14" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی کانال باتری 12 ولت counts=2482 بده (2 ولت روی پایه).
-گام ۳: مقدار v_bat12_mv را بخوان.
-گام ۴: باید حدود 12058 میلی‌ولت باشد (2 ضربدر 41000 تقسیم بر 6800) با خطای حداکثر ±5 میلی‌ولت.</t>
-        </is>
-      </c>
-      <c r="F14" s="58" t="inlineStr">
-        <is>
-          <t>counts 2482</t>
-        </is>
-      </c>
-      <c r="G14" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H14" s="55" t="inlineStr">
-        <is>
-          <t>v_bat12_mv≈12058mV ±5mV. PASS. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="I14" s="55" t="inlineStr">
-        <is>
-          <t>PASS: مطابق فرمول V12. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J14" s="55" t="inlineStr"/>
-      <c r="K14" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L14" s="59" t="inlineStr"/>
-      <c r="M14" s="55" t="inlineStr"/>
-      <c r="N14" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O14" s="58" t="inlineStr"/>
-      <c r="P14" s="58" t="inlineStr"/>
-      <c r="Q14" s="60">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>MS-011</t>
-        </is>
-      </c>
-      <c r="B15" s="48" t="inlineStr">
-        <is>
-          <t>بررسی current1</t>
-        </is>
-      </c>
-      <c r="C15" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
-گام ۳: خودت حساب کن: 610 ضربدر 3300 ضربدر 1000 تقسیم بر (4095 ضربدر 101 ضربدر 10) می‌شود حدود 486 میلی‌آمپر.
-گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
-        </is>
-      </c>
-      <c r="F15" s="50" t="inlineStr">
-        <is>
-          <t>counts 610 (0.49V)</t>
-        </is>
-      </c>
-      <c r="G15" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>i_ch1≈ counts*3300*1000/(4095*101*10) ≈ 486mA ±1mA. PASS. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="I15" s="48" t="inlineStr">
-        <is>
-          <t>PASS: مطابق فرمول جریان. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J15" s="51" t="inlineStr"/>
-      <c r="K15" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L15" s="53" t="inlineStr"/>
-      <c r="M15" s="48" t="inlineStr"/>
-      <c r="N15" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O15" s="50" t="inlineStr"/>
-      <c r="P15" s="50" t="inlineStr"/>
-      <c r="Q15" s="54">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>MS-012</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="inlineStr">
-        <is>
-          <t>بررسی current2</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="55" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E16" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی کانال جریان شارژ ۲ counts=1220 بده (حدود 0.98 ولت روی پایه).
-گام ۳: i_ch2 را بخوان.
-گام ۴: باید حدود 973 میلی‌آمپر باشد با خطای حداکثر ±1 میلی‌آمپر؛ بیشتر یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F16" s="58" t="inlineStr">
-        <is>
-          <t>counts 1220</t>
-        </is>
-      </c>
-      <c r="G16" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H16" s="55" t="inlineStr">
-        <is>
-          <t>i_ch2≈ 973mA ±1mA. PASS. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="I16" s="55" t="inlineStr">
-        <is>
-          <t>PASS: مطابق فرمول. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J16" s="55" t="inlineStr"/>
-      <c r="K16" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L16" s="59" t="inlineStr"/>
-      <c r="M16" s="55" t="inlineStr"/>
-      <c r="N16" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O16" s="58" t="inlineStr"/>
-      <c r="P16" s="58" t="inlineStr"/>
-      <c r="Q16" s="60">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>MS-013</t>
-        </is>
-      </c>
-      <c r="B17" s="48" t="inlineStr">
-        <is>
-          <t>بررسی input_present / High</t>
-        </is>
-      </c>
-      <c r="C17" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E17" s="48" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: پایهٔ PB4 را High کن (یعنی ورودی 24 ولت حاضر است).
@@ -2309,68 +1561,68 @@
 گام ۴: input_present باید true باشد؛ false ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="50" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>PB4 High</t>
         </is>
       </c>
-      <c r="G17" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t>input_present=true. PASS: true. FAIL: false.</t>
         </is>
       </c>
-      <c r="I17" s="48" t="inlineStr">
+      <c r="I6" s="48" t="inlineStr">
         <is>
           <t>PASS: true. FAIL: false.</t>
         </is>
       </c>
-      <c r="J17" s="51" t="inlineStr"/>
-      <c r="K17" s="52" t="inlineStr">
+      <c r="J6" s="51" t="inlineStr"/>
+      <c r="K6" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="53" t="inlineStr"/>
-      <c r="M17" s="48" t="inlineStr"/>
-      <c r="N17" s="48" t="inlineStr">
+      <c r="L6" s="53" t="inlineStr"/>
+      <c r="M6" s="48" t="inlineStr"/>
+      <c r="N6" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O17" s="50" t="inlineStr"/>
-      <c r="P17" s="50" t="inlineStr"/>
-      <c r="Q17" s="54">
+      <c r="O6" s="50" t="inlineStr"/>
+      <c r="P6" s="50" t="inlineStr"/>
+      <c r="Q6" s="54">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>MS-014</t>
         </is>
       </c>
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>بررسی input_present / Low</t>
         </is>
       </c>
-      <c r="C18" s="56" t="inlineStr">
+      <c r="C7" s="56" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E7" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true با ورودی حاضر شروع کن (input_present=true).
 گام ۲: پایهٔ PB4 را Low کن (ورودی قطع است).
@@ -2378,275 +1630,68 @@
 گام ۴: input_present باید false شده باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F18" s="58" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>PB4 Low</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
         <is>
           <t>input_present=false. PASS. FAIL: true.</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I7" s="55" t="inlineStr">
         <is>
           <t>PASS: false. FAIL: true.</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr"/>
-      <c r="K18" s="55" t="inlineStr">
+      <c r="J7" s="55" t="inlineStr"/>
+      <c r="K7" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="59" t="inlineStr"/>
-      <c r="M18" s="55" t="inlineStr"/>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="L7" s="59" t="inlineStr"/>
+      <c r="M7" s="55" t="inlineStr"/>
+      <c r="N7" s="55" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O18" s="58" t="inlineStr"/>
-      <c r="P18" s="58" t="inlineStr"/>
-      <c r="Q18" s="60">
+      <c r="O7" s="58" t="inlineStr"/>
+      <c r="P7" s="58" t="inlineStr"/>
+      <c r="Q7" s="60">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="40.5" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>MS-017</t>
-        </is>
-      </c>
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>دوره 10ms تسک Measurement</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="48" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>MS-021</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>کالیبراسیون برد / tolerance</t>
+        </is>
+      </c>
+      <c r="C8" s="50" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E19" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
-گام ۳: یک ثانیه ضبط کن و فاصلهٔ بین Runها را اندازه بگیر.
-گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F19" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="50" t="inlineStr">
-        <is>
-          <t>1s</t>
-        </is>
-      </c>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
-        </is>
-      </c>
-      <c r="I19" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 10ms period. FAIL: otherwise.</t>
-        </is>
-      </c>
-      <c r="J19" s="51" t="inlineStr"/>
-      <c r="K19" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L19" s="53" t="inlineStr"/>
-      <c r="M19" s="48" t="inlineStr"/>
-      <c r="N19" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O19" s="50" t="inlineStr"/>
-      <c r="P19" s="50" t="inlineStr"/>
-      <c r="Q19" s="54">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>MS-019</t>
-        </is>
-      </c>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>تطبیق فرمول و کالیبراسیون / صفر</t>
-        </is>
-      </c>
-      <c r="C20" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E20" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی همهٔ کانال‌ها counts=0 بده.
-گام ۳: یک Run بزن و همهٔ خروجی‌ها را بخوان.
-گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F20" s="50" t="inlineStr">
-        <is>
-          <t>counts 0</t>
-        </is>
-      </c>
-      <c r="G20" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
-        </is>
-      </c>
-      <c r="I20" s="48" t="inlineStr">
-        <is>
-          <t>PASS: zero. FAIL: non-zero.</t>
-        </is>
-      </c>
-      <c r="J20" s="51" t="inlineStr"/>
-      <c r="K20" s="52" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L20" s="53" t="inlineStr"/>
-      <c r="M20" s="48" t="inlineStr"/>
-      <c r="N20" s="48" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O20" s="50" t="inlineStr"/>
-      <c r="P20" s="50" t="inlineStr"/>
-      <c r="Q20" s="54">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>MS-020</t>
-        </is>
-      </c>
-      <c r="B21" s="55" t="inlineStr">
-        <is>
-          <t>تطبیق فرمول / فول</t>
-        </is>
-      </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D21" s="55" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E21" s="55" t="inlineStr">
-        <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
-گام ۳: با دست حساب کن: ولتاژ پایه 3300 میلی‌ولت، V24 می‌شود 3300 ضربدر 76000 تقسیم بر 6800 یعنی حدود 36882 میلی‌ولت، V12 حدود 19897 میلی‌ولت و جریان 3300 ضربدر 1000 تقسیم بر (101 ضربدر 10) یعنی حدود 3267 میلی‌آمپر.
-گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
-        </is>
-      </c>
-      <c r="F21" s="58" t="inlineStr">
-        <is>
-          <t>counts 4095 (فول)</t>
-        </is>
-      </c>
-      <c r="G21" s="58" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H21" s="55" t="inlineStr">
-        <is>
-          <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="I21" s="55" t="inlineStr">
-        <is>
-          <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
-        </is>
-      </c>
-      <c r="J21" s="55" t="inlineStr"/>
-      <c r="K21" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L21" s="59" t="inlineStr"/>
-      <c r="M21" s="55" t="inlineStr"/>
-      <c r="N21" s="55" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O21" s="58" t="inlineStr"/>
-      <c r="P21" s="58" t="inlineStr"/>
-      <c r="Q21" s="60">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>MS-021</t>
-        </is>
-      </c>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>کالیبراسیون برد / tolerance</t>
-        </is>
-      </c>
-      <c r="C22" s="50" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D22" s="48" t="inlineStr">
-        <is>
-          <t>valid=true</t>
-        </is>
-      </c>
-      <c r="E22" s="48" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری/منبع واقعی دقیقاً 24 ولت به ورودی V24 بده.
 گام ۲: با مولتی‌متر (DMM) ولتاژ روی پایهٔ PA2 را اندازه بگیر؛ باید حدود 2147 میلی‌ولت باشد.
@@ -2654,308 +1699,510 @@
 گام ۴: V24 خوانده‌شده باید حدود 24000 میلی‌ولت باشد. خطای مجاز 1 درصد مقاومت‌ها به‌علاوهٔ 1 LSB است؛ خطای کمتر از 1 درصد قبول و بیشتر از 2 درصد رد است.</t>
         </is>
       </c>
-      <c r="F22" s="50" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>V24=24V (pin≈2147mV, counts≈2665)</t>
         </is>
       </c>
-      <c r="G22" s="50" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H22" s="48" t="inlineStr">
+      <c r="G8" s="50" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
         <is>
           <t>ADC pin≈2147mV، counts≈2665، V24≈24000mV ±tolerance (1% مقاومت + 1LSB). PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="I22" s="48" t="inlineStr">
+      <c r="I8" s="48" t="inlineStr">
         <is>
           <t>PASS: 2665→24000 within 1%. FAIL: &gt;2%.</t>
         </is>
       </c>
-      <c r="J22" s="51" t="inlineStr"/>
-      <c r="K22" s="52" t="inlineStr">
+      <c r="J8" s="51" t="inlineStr"/>
+      <c r="K8" s="52" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L22" s="53" t="inlineStr"/>
-      <c r="M22" s="48" t="inlineStr"/>
-      <c r="N22" s="48" t="inlineStr">
+      <c r="L8" s="53" t="inlineStr"/>
+      <c r="M8" s="48" t="inlineStr"/>
+      <c r="N8" s="48" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O22" s="50" t="inlineStr"/>
-      <c r="P22" s="50" t="inlineStr"/>
-      <c r="Q22" s="54">
+      <c r="O8" s="50" t="inlineStr"/>
+      <c r="P8" s="50" t="inlineStr"/>
+      <c r="Q8" s="54">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="Q9" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="Q10" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="Q11" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="Q12" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="Q13" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="Q14" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="Q15" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="Q16" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="Q17" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="Q18" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="Q19" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="Q20" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="Q21" s="63">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="Q22" s="63">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="Q23" s="63">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
       <c r="Q24" s="63">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
       <c r="Q25" s="63">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="Q26" s="63">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="63">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="63">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="63">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="63">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="63">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="63">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="63">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="63">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="63">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="63">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="63">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="63">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="63">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="63">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="63">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="63">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="63">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="63">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="63">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="63">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="63">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="63">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="Q49" s="63">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="Q50" s="63">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="Q51" s="63">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="Q52" s="63">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="Q53" s="63">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="Q54" s="63">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="Q55" s="63">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="Q56" s="63">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="Q57" s="63">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="Q58" s="63">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="Q59" s="63">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="Q60" s="63">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Q61" s="63">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="Q62" s="63">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="47" t="inlineStr">
+        <is>
+          <t>MS-023</t>
+        </is>
+      </c>
+      <c r="B49" s="48" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="C49" s="50" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D49" s="48" t="inlineStr">
+        <is>
+          <t>منبع دقیق آزمایشگاهی و مولتی‌متر</t>
+        </is>
+      </c>
+      <c r="E49" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: منبع را دقیقاً روی 24.0 ولت تنظیم کن و به ورودی وصل کن؛ یک باتری 24 ولت هم وصل باشد.
+گام ۲: ولتاژ منبع را با مولتی‌متر خودت هم اندازه بگیر.
+گام ۳: در پنل عددهای ولتاژ ورودی و باتری را بخوان.
+گام ۴: هر دو باید نزدیک همان عددی باشند که مولتی‌متر می‌گوید؛ اختلاف زیاد یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F49" s="48" t="inlineStr">
+        <is>
+          <t>ورودی و باتری 24 ولت</t>
+        </is>
+      </c>
+      <c r="G49" s="50" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H49" s="48" t="inlineStr">
+        <is>
+          <t>عددهای پنل نزدیک مقدار واقعی مولتی‌متر</t>
+        </is>
+      </c>
+      <c r="I49" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="48" t="inlineStr">
+        <is>
+          <t>اختلاف پنل با مولتی‌متر کم و منطقی باشد</t>
+        </is>
+      </c>
+      <c r="K49" s="48" t="inlineStr"/>
+      <c r="L49" s="83" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M49" s="48" t="n"/>
+      <c r="N49" s="48" t="n"/>
+      <c r="O49" s="50" t="n"/>
+      <c r="P49" s="50" t="n"/>
+      <c r="Q49" s="54">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1">
+      <c r="A50" s="47" t="inlineStr">
+        <is>
+          <t>MS-024</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="C50" s="58" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D50" s="55" t="inlineStr">
+        <is>
+          <t>دستگاه روشن و پنل عددها را نشان می‌دهد</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه روشن باشد و در پنل عددهای ولتاژ را ببین.
+گام ۲: ورودی را کامل قطع کن (صفر ولت).
+گام ۳: پنل را نگاه کن: ولتاژ ورودی باید صفر نشان داده شود ولی بقیهٔ عددها (باتری و جریان‌ها) زنده و درست بمانند.
+گام ۴: دستگاه نباید خطای اندازه‌گیری بگیرد یا خاموش شود.</t>
+        </is>
+      </c>
+      <c r="F50" s="55" t="inlineStr">
+        <is>
+          <t>قطع کامل ورودی</t>
+        </is>
+      </c>
+      <c r="G50" s="58" t="inlineStr">
+        <is>
+          <t>چند ثانیه</t>
+        </is>
+      </c>
+      <c r="H50" s="55" t="inlineStr">
+        <is>
+          <t>ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم</t>
+        </is>
+      </c>
+      <c r="I50" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="55" t="inlineStr">
+        <is>
+          <t>فقط ورودی صفر شود و دستگاه عادی بماند</t>
+        </is>
+      </c>
+      <c r="K50" s="55" t="inlineStr"/>
+      <c r="L50" s="83" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="58" t="n"/>
+      <c r="P50" s="58" t="n"/>
+      <c r="Q50" s="60">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="47" t="inlineStr">
+        <is>
+          <t>MS-025</t>
+        </is>
+      </c>
+      <c r="B51" s="48" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="C51" s="50" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D51" s="48" t="inlineStr">
+        <is>
+          <t>بار معلوم و مولتی‌متر سری</t>
+        </is>
+      </c>
+      <c r="E51" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: یک بار معلوم روی مسیر شارژ بگذار و جریان واقعی را با مولتی‌متر اندازه بگیر (مثلاً باری که حدود 500 میلی‌آمپر می‌کشد).
+گام ۲: شارژ را راه بینداز.
+گام ۳: جریان نشان‌داده‌شده در پنل را با عدد مولتی‌متر مقایسه کن.
+گام ۴: باید نزدیک هم باشند؛ اختلاف زیاد یعنی رد.</t>
+        </is>
+      </c>
+      <c r="F51" s="48" t="inlineStr">
+        <is>
+          <t>بار حدود 500 میلی‌آمپر</t>
+        </is>
+      </c>
+      <c r="G51" s="50" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H51" s="48" t="inlineStr">
+        <is>
+          <t>جریان پنل نزدیک جریان واقعی</t>
+        </is>
+      </c>
+      <c r="I51" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="48" t="inlineStr">
+        <is>
+          <t>اختلاف جریان پنل با مولتی‌متر کم باشد</t>
+        </is>
+      </c>
+      <c r="K51" s="48" t="inlineStr"/>
+      <c r="L51" s="83" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M51" s="48" t="n"/>
+      <c r="N51" s="48" t="n"/>
+      <c r="O51" s="50" t="n"/>
+      <c r="P51" s="50" t="n"/>
+      <c r="Q51" s="54">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q62"/>
+  <autoFilter ref="A4:Q51"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="L5:L106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="L49 L50 L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
-    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D7" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
-    <hyperlink ref="D8" location="'برنامه تست'!A7"/>
-    <hyperlink ref="E8" location="'برنامه تست'!A7"/>
-    <hyperlink ref="E9" location="'برنامه تست'!A8"/>
-    <hyperlink ref="D10" location="'برنامه تست'!A9"/>
-    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2964,6 +2211,1241 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="81" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>شناسه تست</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>ورودی‌ها</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="N4" s="37" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>MS-002</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Warmup / فریم اول</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>پس از Init و Start موفق</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>گام ۱: Init و Start را با موفقیت انجام بده (ادامهٔ MS-001).
+گام ۲: یک فریم کامل و پایدار ADC روی هر 5 کانال اعمال کن؛ مثلاً روی همه 2 ولت (counts حدود 2482).
+گام ۳: فقط یک بار func__Measurement_Run را صدا بزن و valid را بخوان.
+گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 1 شده باشد؛ valid شدن در فریم اول یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>فریم 1 کامل و پایدار, counts≈2482 (2V)</t>
+        </is>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>valid همچنان false، warmupCounter=1، globals هنوز 0 یا قدیمی اما valid=false. PASS: هنوز invalid. FAIL: valid true زودهنگام.</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>PASS: فریم1 → still false. FAIL: valid true.</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="59" t="n"/>
+      <c r="M5" s="55" t="n"/>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O5" s="58" t="n"/>
+      <c r="P5" s="58" t="n"/>
+      <c r="Q5" s="60">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>MS-003</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>Warmup / فریم دوم</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>پس از MS-002</t>
+        </is>
+      </c>
+      <c r="E6" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
+گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
+گام ۳: یک Run دیگر بزن و valid را بخوان.
+گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
+        <is>
+          <t>فریم 2 کامل, counts 2482</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H6" s="48" t="inlineStr">
+        <is>
+          <t>valid همچنان false، counter=2. PASS: still false. FAIL: true.</t>
+        </is>
+      </c>
+      <c r="I6" s="48" t="inlineStr">
+        <is>
+          <t>PASS: فریم2 still false. FAIL: true.</t>
+        </is>
+      </c>
+      <c r="J6" s="51" t="n"/>
+      <c r="K6" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="53" t="n"/>
+      <c r="M6" s="48" t="n"/>
+      <c r="N6" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O6" s="50" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="54">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>MS-004</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Warmup / فریم سوم</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>پس از MS-003</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
+گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
+گام ۳: یک Run بزن.
+گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>فریم 3 کامل, counts: V channels 2482 (2V pin), I channels 610 (0.49V)</t>
+        </is>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>valid=true، همه globals به‌روز: 2V pin → V24≈22352mV, V12≈12058mV, Current≈486mA با I counts 610, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>PASS: فریم3 → valid true با V24≈22352 و I≈486mA. FAIL: still false.</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="55" t="n"/>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O7" s="58" t="n"/>
+      <c r="P7" s="58" t="n"/>
+      <c r="Q7" s="60">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>MS-005</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>Warmup / فریم ناقص</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>پس از valid=true</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن (پایان MS-004).
+گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
+گام ۳: یک Run بزن.
+گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F8" s="50" t="inlineStr">
+        <is>
+          <t>فریم ناقص/ناپایدار (GetRaw false)</t>
+        </is>
+      </c>
+      <c r="G8" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>valid=false فوری، warmupCounter reset به 0، snapshot.valid false. PASS: invalid و reset. FAIL: همچنان true.</t>
+        </is>
+      </c>
+      <c r="I8" s="48" t="inlineStr">
+        <is>
+          <t>PASS: unstable → invalid+reset. FAIL: remains true.</t>
+        </is>
+      </c>
+      <c r="J8" s="51" t="n"/>
+      <c r="K8" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L8" s="53" t="n"/>
+      <c r="M8" s="48" t="n"/>
+      <c r="N8" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="54">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>MS-006</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>Warmup / شروع دوباره</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>پس از MS-005</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="inlineStr">
+        <is>
+          <t>گام ۱: ادامهٔ MS-005 (فریم خراب و warmup=0).
+گام ۲: سه فریم کامل و پایدار پشت سر هم اعمال کن و هر کدام یک Run بزن (در مجموع 30 میلی‌ثانیه).
+گام ۳: بعد از فریم اول و دوم هنوز باید valid=false باشد.
+گام ۴: دقیقاً بعد از فریم سوم باید valid=true شود؛ زودتر یا دیرتر شدن یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>3 فریم کامل</t>
+        </is>
+      </c>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>30ms</t>
+        </is>
+      </c>
+      <c r="H9" s="55" t="inlineStr">
+        <is>
+          <t>پس از فریم سوم دوباره valid=true. PASS: warmup دوباره 3 فریم. FAIL: valid زودتر یا دیرتر.</t>
+        </is>
+      </c>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>PASS: 3 فریم دوباره → true. FAIL: otherwise.</t>
+        </is>
+      </c>
+      <c r="J9" s="55" t="n"/>
+      <c r="K9" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="59" t="n"/>
+      <c r="M9" s="55" t="n"/>
+      <c r="N9" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O9" s="58" t="n"/>
+      <c r="P9" s="58" t="n"/>
+      <c r="Q9" s="60">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>MS-007</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>ورودی 24V قطع</t>
+        </is>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="inlineStr">
+        <is>
+          <t>valid=true با Vin=0</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
+گام ۲: یک Run بزن.
+گام ۳: valid باید همچنان true بماند، چون قطع ورودی نباید ADC را نامعتبر کند.
+گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F10" s="50" t="inlineStr">
+        <is>
+          <t>v_in 0V (counts 0), سایر 2V</t>
+        </is>
+      </c>
+      <c r="G10" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H10" s="48" t="inlineStr">
+        <is>
+          <t>valid همچنان true (قطع ورودی ADC را invalid نمی‌کند)، v_in_mv≈0، سایر مقادیر به‌روز. PASS: valid true با Vin صفر. FAIL: valid false.</t>
+        </is>
+      </c>
+      <c r="I10" s="48" t="inlineStr">
+        <is>
+          <t>PASS: Vin zero still valid. FAIL: invalid.</t>
+        </is>
+      </c>
+      <c r="J10" s="51" t="n"/>
+      <c r="K10" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L10" s="53" t="n"/>
+      <c r="M10" s="48" t="n"/>
+      <c r="N10" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O10" s="50" t="n"/>
+      <c r="P10" s="50" t="n"/>
+      <c r="Q10" s="54">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>MS-008</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>بررسی v_in_mv</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
+گام ۳: اول خودت حساب کن: 1241 ضربدر 3300 تقسیم بر 4095 می‌شود حدود 1000 میلی‌ولت روی پایه؛ بعد ضربدر 76000 تقسیم بر 6800 می‌شود حدود 11176 میلی‌ولت.
+گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F11" s="58" t="inlineStr">
+        <is>
+          <t>counts 1241 (1V)</t>
+        </is>
+      </c>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H11" s="55" t="inlineStr">
+        <is>
+          <t>v_in_mv = 1241*3300/4095≈1000mV pin → *76000/6800≈11176mV. tolerance ±9mV. PASS: خوانش در tolerance. FAIL: &gt;20mV خطا.</t>
+        </is>
+      </c>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="n"/>
+      <c r="K11" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L11" s="59" t="n"/>
+      <c r="M11" s="55" t="n"/>
+      <c r="N11" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O11" s="58" t="n"/>
+      <c r="P11" s="58" t="n"/>
+      <c r="Q11" s="60">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>MS-009</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>بررسی v_bat24_mv</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
+گام ۳: مقدار v_bat24_mv را بخوان.
+گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
+        <is>
+          <t>counts 2482</t>
+        </is>
+      </c>
+      <c r="G12" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H12" s="48" t="inlineStr">
+        <is>
+          <t>v_bat24_mv≈22352mV ±9mV. PASS. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="I12" s="48" t="inlineStr">
+        <is>
+          <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J12" s="51" t="n"/>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L12" s="53" t="n"/>
+      <c r="M12" s="48" t="n"/>
+      <c r="N12" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O12" s="50" t="n"/>
+      <c r="P12" s="50" t="n"/>
+      <c r="Q12" s="54">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>MS-010</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>بررسی v_bat12_mv</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال باتری 12 ولت counts=2482 بده (2 ولت روی پایه).
+گام ۳: مقدار v_bat12_mv را بخوان.
+گام ۴: باید حدود 12058 میلی‌ولت باشد (2 ضربدر 41000 تقسیم بر 6800) با خطای حداکثر ±5 میلی‌ولت.</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>counts 2482</t>
+        </is>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H13" s="55" t="inlineStr">
+        <is>
+          <t>v_bat12_mv≈12058mV ±5mV. PASS. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="inlineStr">
+        <is>
+          <t>PASS: مطابق فرمول V12. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="n"/>
+      <c r="K13" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L13" s="59" t="n"/>
+      <c r="M13" s="55" t="n"/>
+      <c r="N13" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O13" s="58" t="n"/>
+      <c r="P13" s="58" t="n"/>
+      <c r="Q13" s="60">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>MS-011</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>بررسی current1</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
+گام ۳: خودت حساب کن: 610 ضربدر 3300 ضربدر 1000 تقسیم بر (4095 ضربدر 101 ضربدر 10) می‌شود حدود 486 میلی‌آمپر.
+گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
+        </is>
+      </c>
+      <c r="F14" s="50" t="inlineStr">
+        <is>
+          <t>counts 610 (0.49V)</t>
+        </is>
+      </c>
+      <c r="G14" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H14" s="48" t="inlineStr">
+        <is>
+          <t>i_ch1≈ counts*3300*1000/(4095*101*10) ≈ 486mA ±1mA. PASS. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="I14" s="48" t="inlineStr">
+        <is>
+          <t>PASS: مطابق فرمول جریان. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J14" s="51" t="n"/>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L14" s="53" t="n"/>
+      <c r="M14" s="48" t="n"/>
+      <c r="N14" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="54">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>MS-012</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>بررسی current2</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی کانال جریان شارژ ۲ counts=1220 بده (حدود 0.98 ولت روی پایه).
+گام ۳: i_ch2 را بخوان.
+گام ۴: باید حدود 973 میلی‌آمپر باشد با خطای حداکثر ±1 میلی‌آمپر؛ بیشتر یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F15" s="58" t="inlineStr">
+        <is>
+          <t>counts 1220</t>
+        </is>
+      </c>
+      <c r="G15" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H15" s="55" t="inlineStr">
+        <is>
+          <t>i_ch2≈ 973mA ±1mA. PASS. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="inlineStr">
+        <is>
+          <t>PASS: مطابق فرمول. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J15" s="55" t="n"/>
+      <c r="K15" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L15" s="59" t="n"/>
+      <c r="M15" s="55" t="n"/>
+      <c r="N15" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O15" s="58" t="n"/>
+      <c r="P15" s="58" t="n"/>
+      <c r="Q15" s="60">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>MS-017</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>دوره 10ms تسک Measurement</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D16" s="48" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
+گام ۳: یک ثانیه ضبط کن و فاصلهٔ بین Runها را اندازه بگیر.
+گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="50" t="inlineStr">
+        <is>
+          <t>1s</t>
+        </is>
+      </c>
+      <c r="H16" s="48" t="inlineStr">
+        <is>
+          <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
+        </is>
+      </c>
+      <c r="I16" s="48" t="inlineStr">
+        <is>
+          <t>PASS: 10ms period. FAIL: otherwise.</t>
+        </is>
+      </c>
+      <c r="J16" s="51" t="n"/>
+      <c r="K16" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L16" s="53" t="n"/>
+      <c r="M16" s="48" t="n"/>
+      <c r="N16" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="54">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>MS-019</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>تطبیق فرمول و کالیبراسیون / صفر</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی همهٔ کانال‌ها counts=0 بده.
+گام ۳: یک Run بزن و همهٔ خروجی‌ها را بخوان.
+گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="inlineStr">
+        <is>
+          <t>counts 0</t>
+        </is>
+      </c>
+      <c r="G17" s="50" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H17" s="48" t="inlineStr">
+        <is>
+          <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
+        </is>
+      </c>
+      <c r="I17" s="48" t="inlineStr">
+        <is>
+          <t>PASS: zero. FAIL: non-zero.</t>
+        </is>
+      </c>
+      <c r="J17" s="51" t="n"/>
+      <c r="K17" s="52" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L17" s="53" t="n"/>
+      <c r="M17" s="48" t="n"/>
+      <c r="N17" s="48" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="54">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>MS-020</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>تطبیق فرمول / فول</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="inlineStr">
+        <is>
+          <t>valid=true</t>
+        </is>
+      </c>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>گام ۱: از valid=true شروع کن.
+گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
+گام ۳: با دست حساب کن: ولتاژ پایه 3300 میلی‌ولت، V24 می‌شود 3300 ضربدر 76000 تقسیم بر 6800 یعنی حدود 36882 میلی‌ولت، V12 حدود 19897 میلی‌ولت و جریان 3300 ضربدر 1000 تقسیم بر (101 ضربدر 10) یعنی حدود 3267 میلی‌آمپر.
+گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
+        </is>
+      </c>
+      <c r="F18" s="58" t="inlineStr">
+        <is>
+          <t>counts 4095 (فول)</t>
+        </is>
+      </c>
+      <c r="G18" s="58" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H18" s="55" t="inlineStr">
+        <is>
+          <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="I18" s="55" t="inlineStr">
+        <is>
+          <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
+        </is>
+      </c>
+      <c r="J18" s="55" t="n"/>
+      <c r="K18" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L18" s="59" t="n"/>
+      <c r="M18" s="55" t="n"/>
+      <c r="N18" s="55" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O18" s="58" t="n"/>
+      <c r="P18" s="58" t="n"/>
+      <c r="Q18" s="60">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="63">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="63">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="63">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="63">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="63">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="63">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="63">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="63">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="63">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="63">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="63">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="63">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="63">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="63">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="63">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="63">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="63">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="63">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="63">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="63">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q18"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D6" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="E6" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="D7" location="'تست‌های آزمایشگاهی'!A6"/>
+    <hyperlink ref="E7" location="'تست‌های آزمایشگاهی'!A6"/>
+    <hyperlink ref="E8" location="'تست‌های آزمایشگاهی'!A7"/>
+    <hyperlink ref="D9" location="'تست‌های آزمایشگاهی'!A8"/>
+    <hyperlink ref="E9" location="'تست‌های آزمایشگاهی'!A8"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3502,7 +3984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3956,20 +4438,20 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F4" location="'برنامه تست'!A20"/>
-    <hyperlink ref="F5" location="'برنامه تست'!A12"/>
-    <hyperlink ref="F6" location="'برنامه تست'!A12"/>
-    <hyperlink ref="F7" location="'برنامه تست'!A14"/>
-    <hyperlink ref="F8" location="'برنامه تست'!A15"/>
-    <hyperlink ref="F9" location="'برنامه تست'!A6"/>
+    <hyperlink ref="F4" location="'تست‌های آزمایشگاهی'!A17"/>
+    <hyperlink ref="F5" location="'تست‌های آزمایشگاهی'!A11"/>
+    <hyperlink ref="F6" location="'تست‌های آزمایشگاهی'!A11"/>
+    <hyperlink ref="F7" location="'تست‌های آزمایشگاهی'!A13"/>
+    <hyperlink ref="F8" location="'تست‌های آزمایشگاهی'!A14"/>
+    <hyperlink ref="F9" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId1"/>
-    <hyperlink ref="F10" location="'برنامه تست'!A9"/>
+    <hyperlink ref="F10" location="'تست‌های آزمایشگاهی'!A8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
-    <hyperlink ref="F11" location="'برنامه تست'!A11"/>
+    <hyperlink ref="F11" location="'تست‌های آزمایشگاهی'!A10"/>
     <hyperlink ref="F12" location="'تست‌های برنامه‌نویسی'!A5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId3"/>
     <hyperlink ref="F13" location="'تست‌های برنامه‌نویسی'!A6"/>
-    <hyperlink ref="F14" location="'برنامه تست'!A19"/>
+    <hyperlink ref="F14" location="'تست‌های آزمایشگاهی'!A16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId4"/>
     <hyperlink ref="F15" location="'تست‌های برنامه‌نویسی'!A7"/>
   </hyperlinks>
@@ -3979,7 +4461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4258,7 +4740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -4748,7 +5230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -4964,7 +5446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1481,35 +1481,34 @@
       </c>
       <c r="D5" s="48" t="inlineStr">
         <is>
-          <t>پس از Reset، قبل از Start</t>
+          <t>دستگاه خاموش؛ باتری و برق شهر وصل؛ مولتی‌متر دستی آماده</t>
         </is>
       </c>
       <c r="E5" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: برد را Reset کن ولی هنوز Start را نزن (تازه بعد از Reset و قبل از Start هستیم).
-گام ۲: func__Measurement_Init را صدا بزن (یا همان Reset کافی است).
-گام ۳: حداکثر 100 میلی‌ثانیه بعد، متغیرهای سراسری (globals) و snapshot را بخوان.
-گام ۴: باید valid=false باشد، همهٔ ولتاژ و جریان‌ها (mV و mA) صفر باشند و input_present هم false باشد؛ هر مقدار غیرصفر یعنی رد تست.</t>
+          <t>گام ۱: دستگاه را روشن کن.
+گام ۲: عدد ولتاژ باتری و ورودی را در پنل بخوان.
+گام ۳: همان لحظه با مولتی‌متر روی ترمینال‌ها اندازه بگیر.</t>
         </is>
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>روشن‌کردن ساده</t>
         </is>
       </c>
       <c r="G5" s="50" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H5" s="48" t="inlineStr">
         <is>
-          <t>valid=false، همه mV/mA=0، input_present=false. PASS: valid false و صفر. FAIL: هر mV غیرصفر یا valid true.</t>
+          <t>عددهای پنل زنده‌اند و با مولتی‌متر دستی می‌خوانند (اختلاف در حد چند صدم ولت)</t>
         </is>
       </c>
       <c r="I5" s="48" t="inlineStr">
         <is>
-          <t>PASS: Init صفر و invalid. FAIL: otherwise.</t>
+          <t>نزدیکی عدد پنل و مولتی‌متر = قبول؛ عدد ثابت/خیالی یا اختلاف زیاد = رد</t>
         </is>
       </c>
       <c r="J5" s="51" t="inlineStr"/>
@@ -1550,35 +1549,33 @@
       </c>
       <c r="D6" s="48" t="inlineStr">
         <is>
-          <t>valid=true</t>
+          <t>دستگاه روی باتری روشن است و برق شهر قطع است</t>
         </is>
       </c>
       <c r="E6" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: از valid=true شروع کن.
-گام ۲: پایهٔ PB4 را High کن (یعنی ورودی 24 ولت حاضر است).
-گام ۳: یک Run بزن و snapshot را بخوان.
-گام ۴: input_present باید true باشد؛ false ماندن یعنی رد تست.</t>
+          <t>گام ۱: برق شهر را وصل کن.
+گام ۲: در پنل ببین ورودی «حاضر» می‌شود و عددش را با مولتی‌متر چک کن.</t>
         </is>
       </c>
       <c r="F6" s="50" t="inlineStr">
         <is>
-          <t>PB4 High</t>
+          <t>وصل‌کردن برق شهر</t>
         </is>
       </c>
       <c r="G6" s="50" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H6" s="48" t="inlineStr">
         <is>
-          <t>input_present=true. PASS: true. FAIL: false.</t>
+          <t>پنل ورودی را حاضر و با ولتاژ درست نشان می‌دهد</t>
         </is>
       </c>
       <c r="I6" s="48" t="inlineStr">
         <is>
-          <t>PASS: true. FAIL: false.</t>
+          <t>تشخیص درست وصل = قبول؛ هنوز قطع نشان دادن = رد</t>
         </is>
       </c>
       <c r="J6" s="51" t="inlineStr"/>
@@ -1619,35 +1616,33 @@
       </c>
       <c r="D7" s="55" t="inlineStr">
         <is>
-          <t>valid=true</t>
+          <t>دستگاه با برق شهر روشن است</t>
         </is>
       </c>
       <c r="E7" s="55" t="inlineStr">
         <is>
-          <t>گام ۱: از valid=true با ورودی حاضر شروع کن (input_present=true).
-گام ۲: پایهٔ PB4 را Low کن (ورودی قطع است).
-گام ۳: یک Run بزن و snapshot را بخوان.
-گام ۴: input_present باید false شده باشد؛ true ماندن یعنی رد تست.</t>
+          <t>گام ۱: برق شهر را بکش.
+گام ۲: در پنل ببین ورودی «قطع» می‌شود و دستگاه روی باتری می‌ماند.</t>
         </is>
       </c>
       <c r="F7" s="58" t="inlineStr">
         <is>
-          <t>PB4 Low</t>
+          <t>کشیدن برق شهر</t>
         </is>
       </c>
       <c r="G7" s="58" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H7" s="55" t="inlineStr">
         <is>
-          <t>input_present=false. PASS. FAIL: true.</t>
+          <t>پنل ورودی را قطع نشان می‌دهد و دستگاه بی‌وقفه روی باتری ادامه می‌دهد</t>
         </is>
       </c>
       <c r="I7" s="55" t="inlineStr">
         <is>
-          <t>PASS: false. FAIL: true.</t>
+          <t>تشخیص درست قطع و ادامهٔ کار = قبول؛ هنگ یا نشان اشتباه = رد</t>
         </is>
       </c>
       <c r="J7" s="55" t="inlineStr"/>
@@ -1688,35 +1683,33 @@
       </c>
       <c r="D8" s="48" t="inlineStr">
         <is>
-          <t>valid=true</t>
+          <t>مولتی‌متر مرجع مطمئن و پنل در حالت کالیبراسیون</t>
         </is>
       </c>
       <c r="E8" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: یک باتری/منبع واقعی دقیقاً 24 ولت به ورودی V24 بده.
-گام ۲: با مولتی‌متر (DMM) ولتاژ روی پایهٔ PA2 را اندازه بگیر؛ باید حدود 2147 میلی‌ولت باشد.
-گام ۳: counts را بخوان؛ باید حدود 2665 باشد.
-گام ۴: V24 خوانده‌شده باید حدود 24000 میلی‌ولت باشد. خطای مجاز 1 درصد مقاومت‌ها به‌علاوهٔ 1 LSB است؛ خطای کمتر از 1 درصد قبول و بیشتر از 2 درصد رد است.</t>
+          <t>گام ۱: طبق راهنمای پنل، در یک ولتاژ پایین و یک ولتاژ بالا عدد دستگاه را با مولتی‌متر یکی کن.
+گام ۲: در یک ولتاژ میانی هر دو را مقایسه کن.</t>
         </is>
       </c>
       <c r="F8" s="50" t="inlineStr">
         <is>
-          <t>V24=24V (pin≈2147mV, counts≈2665)</t>
+          <t>کالیبراسیون دو نقطه و چک میانی</t>
         </is>
       </c>
       <c r="G8" s="50" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H8" s="48" t="inlineStr">
         <is>
-          <t>ADC pin≈2147mV، counts≈2665، V24≈24000mV ±tolerance (1% مقاومت + 1LSB). PASS: خطا &lt;1% + LSB. FAIL: &gt;2%.</t>
+          <t>بعد از کالیبراسیون، عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند</t>
         </is>
       </c>
       <c r="I8" s="48" t="inlineStr">
         <is>
-          <t>PASS: 2665→24000 within 1%. FAIL: &gt;2%.</t>
+          <t>برابری در نقطهٔ میانی = قبول؛ اختلاف محسوس = رد</t>
         </is>
       </c>
       <c r="J8" s="51" t="inlineStr"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -272,6 +272,106 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="7"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00203764"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00C00000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -426,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -661,6 +761,143 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1051,249 +1288,546 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Measurement — ADC و کالیبراسیون</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
+      <c r="G1" s="85" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
+      <c r="O1" s="85" t="n"/>
+      <c r="P1" s="85" t="n"/>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="86" t="inlineStr">
         <is>
           <t>ChangeOver | ADC1 5ch + DMA + bsp_measurement | نسخه 1.0 — دوره 10ms، warmup 3 فریم، فرمول‌های BSP واقعی</t>
         </is>
       </c>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
+      <c r="G2" s="85" t="n"/>
+      <c r="H2" s="85" t="n"/>
+      <c r="I2" s="85" t="n"/>
+      <c r="J2" s="85" t="n"/>
+      <c r="K2" s="85" t="n"/>
+      <c r="L2" s="85" t="n"/>
+      <c r="M2" s="85" t="n"/>
+      <c r="N2" s="85" t="n"/>
+      <c r="O2" s="85" t="n"/>
+      <c r="P2" s="85" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="87" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
-      <c r="O3" s="8" t="n"/>
-      <c r="P3" s="9" t="n"/>
+      <c r="B3" s="88" t="n"/>
+      <c r="C3" s="88" t="n"/>
+      <c r="D3" s="88" t="n"/>
+      <c r="E3" s="88" t="n"/>
+      <c r="F3" s="88" t="n"/>
+      <c r="G3" s="88" t="n"/>
+      <c r="H3" s="88" t="n"/>
+      <c r="I3" s="88" t="n"/>
+      <c r="J3" s="88" t="n"/>
+      <c r="K3" s="88" t="n"/>
+      <c r="L3" s="88" t="n"/>
+      <c r="M3" s="88" t="n"/>
+      <c r="N3" s="88" t="n"/>
+      <c r="O3" s="88" t="n"/>
+      <c r="P3" s="89" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>این فایل مستقل فقط Measurement را اعتبارسنجی می‌کند؛ هر تست valid، فریم ADC، فرمول mV/mA، ورودی‌ها و snapshot اتمیک را چک می‌کند.</t>
         </is>
       </c>
+      <c r="B4" s="85" t="n"/>
+      <c r="C4" s="85" t="n"/>
+      <c r="D4" s="85" t="n"/>
+      <c r="E4" s="85" t="n"/>
+      <c r="F4" s="85" t="n"/>
+      <c r="G4" s="85" t="n"/>
+      <c r="H4" s="85" t="n"/>
+      <c r="I4" s="85" t="n"/>
+      <c r="J4" s="85" t="n"/>
+      <c r="K4" s="85" t="n"/>
+      <c r="L4" s="85" t="n"/>
+      <c r="M4" s="85" t="n"/>
+      <c r="N4" s="85" t="n"/>
+      <c r="O4" s="85" t="n"/>
+      <c r="P4" s="85" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار عددی و tolerance از کالیبراسیون BSP تعریف شده است.</t>
         </is>
       </c>
+      <c r="B5" s="85" t="n"/>
+      <c r="C5" s="85" t="n"/>
+      <c r="D5" s="85" t="n"/>
+      <c r="E5" s="85" t="n"/>
+      <c r="F5" s="85" t="n"/>
+      <c r="G5" s="85" t="n"/>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="85" t="n"/>
+      <c r="K5" s="85" t="n"/>
+      <c r="L5" s="85" t="n"/>
+      <c r="M5" s="85" t="n"/>
+      <c r="N5" s="85" t="n"/>
+      <c r="O5" s="85" t="n"/>
+      <c r="P5" s="85" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است.</t>
         </is>
       </c>
+      <c r="B6" s="85" t="n"/>
+      <c r="C6" s="85" t="n"/>
+      <c r="D6" s="85" t="n"/>
+      <c r="E6" s="85" t="n"/>
+      <c r="F6" s="85" t="n"/>
+      <c r="G6" s="85" t="n"/>
+      <c r="H6" s="85" t="n"/>
+      <c r="I6" s="85" t="n"/>
+      <c r="J6" s="85" t="n"/>
+      <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+      <c r="N6" s="85" t="n"/>
+      <c r="O6" s="85" t="n"/>
+      <c r="P6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
       </c>
+      <c r="B7" s="85" t="n"/>
+      <c r="C7" s="85" t="n"/>
+      <c r="D7" s="85" t="n"/>
+      <c r="E7" s="85" t="n"/>
+      <c r="F7" s="85" t="n"/>
+      <c r="G7" s="85" t="n"/>
+      <c r="H7" s="85" t="n"/>
+      <c r="I7" s="85" t="n"/>
+      <c r="J7" s="85" t="n"/>
+      <c r="K7" s="85" t="n"/>
+      <c r="L7" s="85" t="n"/>
+      <c r="M7" s="85" t="n"/>
+      <c r="N7" s="85" t="n"/>
+      <c r="O7" s="85" t="n"/>
+      <c r="P7" s="85" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>پس از Init، valid=false؛ تا 3 فریم کامل و پایدار، valid همچنان false؛ پس از فریم سوم، valid=true و همه mV/mA/input_present به‌روز می‌شوند.</t>
         </is>
       </c>
+      <c r="B8" s="85" t="n"/>
+      <c r="C8" s="85" t="n"/>
+      <c r="D8" s="85" t="n"/>
+      <c r="E8" s="85" t="n"/>
+      <c r="F8" s="85" t="n"/>
+      <c r="G8" s="85" t="n"/>
+      <c r="H8" s="85" t="n"/>
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="n"/>
+      <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="85" t="n"/>
+      <c r="P8" s="85" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>فریم ناقص/ناپایدار → valid=false و warmup از نو (counter reset). قطع ورودی 24V نباید به تنهایی ADC را invalid کند.</t>
         </is>
       </c>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="85" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="85" t="n"/>
+      <c r="F9" s="85" t="n"/>
+      <c r="G9" s="85" t="n"/>
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="85" t="n"/>
+      <c r="J9" s="85" t="n"/>
+      <c r="K9" s="85" t="n"/>
+      <c r="L9" s="85" t="n"/>
+      <c r="M9" s="85" t="n"/>
+      <c r="N9" s="85" t="n"/>
+      <c r="O9" s="85" t="n"/>
+      <c r="P9" s="85" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="92" t="inlineStr">
         <is>
           <t>کالیبراسیون از bsp_measurement.c: Vref=3300mV، ADC=4095، Div24 69200+6800/6800 (≈11.176)، Div12 34200+6800/6800 (≈6.029)، شانت 10mΩ و گین 101.</t>
         </is>
       </c>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="85" t="n"/>
+      <c r="D10" s="85" t="n"/>
+      <c r="E10" s="85" t="n"/>
+      <c r="F10" s="85" t="n"/>
+      <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="90" t="inlineStr">
         <is>
           <t>فرمول‌ها: CountsToMv = counts*3300/4095؛ V24 = adcPinMv*(76000)/6800؛ V12 = adcPinMv*(41000)/6800؛ Current = counts*3300*1000/(4095*101*10).</t>
         </is>
       </c>
+      <c r="B11" s="85" t="n"/>
+      <c r="C11" s="85" t="n"/>
+      <c r="D11" s="85" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="85" t="n"/>
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+      <c r="K11" s="85" t="n"/>
+      <c r="L11" s="85" t="n"/>
+      <c r="M11" s="85" t="n"/>
+      <c r="N11" s="85" t="n"/>
+      <c r="O11" s="85" t="n"/>
+      <c r="P11" s="85" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>زمان واقعی از کد: MEASUREMENT_PERIOD_MS=10ms، MEASUREMENT_WARMUP_FRAME_COUNT=3، DMA دو فریمی 2×5، CNDTR بررسی قبل/بعد، osKernelLock برای snapshot اتمیک.</t>
         </is>
       </c>
+      <c r="B12" s="85" t="n"/>
+      <c r="C12" s="85" t="n"/>
+      <c r="D12" s="85" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="85" t="n"/>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
       </c>
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="85" t="n"/>
+      <c r="D13" s="85" t="n"/>
+      <c r="E13" s="85" t="n"/>
+      <c r="F13" s="85" t="n"/>
+      <c r="G13" s="85" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+      <c r="K13" s="85" t="n"/>
+      <c r="L13" s="85" t="n"/>
+      <c r="M13" s="85" t="n"/>
+      <c r="N13" s="85" t="n"/>
+      <c r="O13" s="85" t="n"/>
+      <c r="P13" s="85" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>۱) برد را با منبع آزمایشگاهی تغذیه کن، هر 5 کانال ADC (PA1/2/3/5/7) را با ولتاژ دقیق و منبع جریان کالیبره اعمال کن؛ PB4 را برای input_present کنترل کن.</t>
         </is>
       </c>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="85" t="n"/>
+      <c r="D14" s="85" t="n"/>
+      <c r="E14" s="85" t="n"/>
+      <c r="F14" s="85" t="n"/>
+      <c r="G14" s="85" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="90" t="inlineStr">
         <is>
           <t>۲) firmware commit c6b084f را پروگرام کن، در «تأیید نهایی» commit/برد/ابزار (DMM، اسکوپ، منبع دقیق) را ثبت کن.</t>
         </is>
       </c>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="85" t="n"/>
+      <c r="D15" s="85" t="n"/>
+      <c r="E15" s="85" t="n"/>
+      <c r="F15" s="85" t="n"/>
+      <c r="G15" s="85" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
+      <c r="L15" s="85" t="n"/>
+      <c r="M15" s="85" t="n"/>
+      <c r="N15" s="85" t="n"/>
+      <c r="O15" s="85" t="n"/>
+      <c r="P15" s="85" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>۳) تست warmup: پس از Init، فریم‌ها را با func__BspAdc_GetRaw یا Live Watch بشمار؛ valid را چک کن.</t>
         </is>
       </c>
+      <c r="B16" s="85" t="n"/>
+      <c r="C16" s="85" t="n"/>
+      <c r="D16" s="85" t="n"/>
+      <c r="E16" s="85" t="n"/>
+      <c r="F16" s="85" t="n"/>
+      <c r="G16" s="85" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="90" t="inlineStr">
         <is>
           <t>۴) تست ولتاژ/جریان: هر کانال را با counts معلوم اعمال کن، مقدار mV/mA را با فرمول BSP محاسبه و با خوانش globals/snapshot مقایسه کن (tolerance ±1 LSB ≈ ±0.8mV pin، برای V24 ≈±9mV، برای V12 ≈±4.8mV، برای جریان ≈±0.8mA).</t>
         </is>
       </c>
+      <c r="B17" s="85" t="n"/>
+      <c r="C17" s="85" t="n"/>
+      <c r="D17" s="85" t="n"/>
+      <c r="E17" s="85" t="n"/>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="85" t="n"/>
+      <c r="H17" s="85" t="n"/>
+      <c r="I17" s="85" t="n"/>
+      <c r="J17" s="85" t="n"/>
+      <c r="K17" s="85" t="n"/>
+      <c r="L17" s="85" t="n"/>
+      <c r="M17" s="85" t="n"/>
+      <c r="N17" s="85" t="n"/>
+      <c r="O17" s="85" t="n"/>
+      <c r="P17" s="85" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="90" t="inlineStr">
         <is>
           <t>۵) تست DMA: دو فریم متوالی را چک کن که CNDTR پایدار باشد و frame 5 نمونه بدون پارگی کپی شود (irq disable و counter قبل/بعد).</t>
         </is>
       </c>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="85" t="n"/>
+      <c r="D18" s="85" t="n"/>
+      <c r="E18" s="85" t="n"/>
+      <c r="F18" s="85" t="n"/>
+      <c r="G18" s="85" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="90" t="inlineStr">
         <is>
           <t>۶) تست snapshot اتمیک: حین Run، از دو تسک snapshot را هم‌زمان بخوان و چک کن نیمه‌به‌روزشده نباشد (osKernelLock).</t>
         </is>
       </c>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="85" t="n"/>
+      <c r="D19" s="85" t="n"/>
+      <c r="E19" s="85" t="n"/>
+      <c r="F19" s="85" t="n"/>
+      <c r="G19" s="85" t="n"/>
+      <c r="H19" s="85" t="n"/>
+      <c r="I19" s="85" t="n"/>
+      <c r="J19" s="85" t="n"/>
+      <c r="K19" s="85" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
+      <c r="N19" s="85" t="n"/>
+      <c r="O19" s="85" t="n"/>
+      <c r="P19" s="85" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="93" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="n"/>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="94" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="41" t="inlineStr">
+      <c r="D21" s="94" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
+      <c r="E21" s="95" t="n"/>
+      <c r="F21" s="88" t="n"/>
+      <c r="G21" s="88" t="n"/>
+      <c r="H21" s="88" t="n"/>
+      <c r="I21" s="88" t="n"/>
+      <c r="J21" s="88" t="n"/>
+      <c r="K21" s="88" t="n"/>
+      <c r="L21" s="88" t="n"/>
+      <c r="M21" s="88" t="n"/>
+      <c r="N21" s="88" t="n"/>
+      <c r="O21" s="88" t="n"/>
+      <c r="P21" s="89" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="96" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="96" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C22" s="78" t="inlineStr">
+      <c r="C22" s="97" t="inlineStr">
         <is>
           <t>ایجاد مستقل Measurement_Board_Validation با ۲۱ تست، فرمول‌ها و tolerance از bsp_measurement.c، دوره 10ms و warmup 3</t>
         </is>
       </c>
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="96" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
+      <c r="E22" s="98" t="n"/>
+      <c r="F22" s="88" t="n"/>
+      <c r="G22" s="88" t="n"/>
+      <c r="H22" s="88" t="n"/>
+      <c r="I22" s="88" t="n"/>
+      <c r="J22" s="88" t="n"/>
+      <c r="K22" s="88" t="n"/>
+      <c r="L22" s="88" t="n"/>
+      <c r="M22" s="88" t="n"/>
+      <c r="N22" s="88" t="n"/>
+      <c r="O22" s="88" t="n"/>
+      <c r="P22" s="89" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="99" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="99" t="inlineStr">
         <is>
           <t>پنل دیالوگ تیره همرنگ + صف PMQ + Enter/Esc + snapshot zeroing task_control (62f3782)</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="99" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
+      <c r="E23" s="85" t="n"/>
+      <c r="F23" s="85" t="n"/>
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+      <c r="P23" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1360,640 +1894,1328 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Measurement</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
+      <c r="G1" s="85" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
+      <c r="O1" s="85" t="n"/>
+      <c r="P1" s="85" t="n"/>
+      <c r="Q1" s="85" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>هر ردیف را با DMM/اسکوپ و محاسبه از فرمول BSP اندازه بگیر؛ مقدار حدسی ننویس. valid باید دقیقاً پس از ۳ فریم true شود.</t>
         </is>
       </c>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
+      <c r="G2" s="85" t="n"/>
+      <c r="H2" s="85" t="n"/>
+      <c r="I2" s="85" t="n"/>
+      <c r="J2" s="85" t="n"/>
+      <c r="K2" s="85" t="n"/>
+      <c r="L2" s="85" t="n"/>
+      <c r="M2" s="85" t="n"/>
+      <c r="N2" s="85" t="n"/>
+      <c r="O2" s="85" t="n"/>
+      <c r="P2" s="85" t="n"/>
+      <c r="Q2" s="85" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="79" t="inlineStr">
+      <c r="A3" s="102" t="inlineStr">
         <is>
           <t>فرمول‌ها و tolerance از bsp_measurement.c واقعی است؛ PASS/FAIL با tolerance ±1 LSB + 1% مقاومت تعریف شده است.</t>
         </is>
       </c>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="85" t="n"/>
+      <c r="E3" s="85" t="n"/>
+      <c r="F3" s="85" t="n"/>
+      <c r="G3" s="85" t="n"/>
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="85" t="n"/>
+      <c r="J3" s="85" t="n"/>
+      <c r="K3" s="85" t="n"/>
+      <c r="L3" s="85" t="n"/>
+      <c r="M3" s="85" t="n"/>
+      <c r="N3" s="85" t="n"/>
+      <c r="O3" s="85" t="n"/>
+      <c r="P3" s="85" t="n"/>
+      <c r="Q3" s="85" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="87" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="87" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="87" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="87" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="87" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="87" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="87" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="87" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="87" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="87" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="87" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="87" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="87" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="87" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="87" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>MS-001</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="104" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>دستگاه خاموش؛ باتری و برق شهر وصل؛ مولتی‌متر دستی آماده</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: عدد ولتاژ باتری و ورودی را در پنل بخوان.
 گام ۳: همان لحظه با مولتی‌متر روی ترمینال‌ها اندازه بگیر.</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="106" t="inlineStr">
         <is>
           <t>روشن‌کردن ساده</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="106" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="104" t="inlineStr">
         <is>
           <t>عددهای پنل زنده‌اند و با مولتی‌متر دستی می‌خوانند (اختلاف در حد چند صدم ولت)</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="104" t="inlineStr">
         <is>
           <t>نزدیکی عدد پنل و مولتی‌متر = قبول؛ عدد ثابت/خیالی یا اختلاف زیاد = رد</t>
         </is>
       </c>
-      <c r="J5" s="51" t="inlineStr"/>
-      <c r="K5" s="52" t="inlineStr">
+      <c r="J5" s="107" t="inlineStr"/>
+      <c r="K5" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr"/>
-      <c r="M5" s="48" t="inlineStr"/>
-      <c r="N5" s="48" t="inlineStr">
+      <c r="L5" s="109" t="inlineStr"/>
+      <c r="M5" s="104" t="inlineStr"/>
+      <c r="N5" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr"/>
-      <c r="P5" s="50" t="inlineStr"/>
-      <c r="Q5" s="54">
+      <c r="O5" s="106" t="inlineStr"/>
+      <c r="P5" s="106" t="inlineStr"/>
+      <c r="Q5" s="110">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="103" t="inlineStr">
         <is>
           <t>MS-013</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>بررسی input_present / High</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="104" t="inlineStr">
         <is>
           <t>دستگاه روی باتری روشن است و برق شهر قطع است</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>گام ۱: برق شهر را وصل کن.
 گام ۲: در پنل ببین ورودی «حاضر» می‌شود و عددش را با مولتی‌متر چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="106" t="inlineStr">
         <is>
           <t>وصل‌کردن برق شهر</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G6" s="106" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="104" t="inlineStr">
         <is>
           <t>پنل ورودی را حاضر و با ولتاژ درست نشان می‌دهد</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="104" t="inlineStr">
         <is>
           <t>تشخیص درست وصل = قبول؛ هنوز قطع نشان دادن = رد</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr"/>
-      <c r="K6" s="52" t="inlineStr">
+      <c r="J6" s="107" t="inlineStr"/>
+      <c r="K6" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="53" t="inlineStr"/>
-      <c r="M6" s="48" t="inlineStr"/>
-      <c r="N6" s="48" t="inlineStr">
+      <c r="L6" s="109" t="inlineStr"/>
+      <c r="M6" s="104" t="inlineStr"/>
+      <c r="N6" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="50" t="inlineStr"/>
-      <c r="P6" s="50" t="inlineStr"/>
-      <c r="Q6" s="54">
+      <c r="O6" s="106" t="inlineStr"/>
+      <c r="P6" s="106" t="inlineStr"/>
+      <c r="Q6" s="110">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>MS-014</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="111" t="inlineStr">
         <is>
           <t>بررسی input_present / Low</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="55" t="inlineStr">
+      <c r="D7" s="111" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن است</t>
         </is>
       </c>
-      <c r="E7" s="55" t="inlineStr">
+      <c r="E7" s="111" t="inlineStr">
         <is>
           <t>گام ۱: برق شهر را بکش.
 گام ۲: در پنل ببین ورودی «قطع» می‌شود و دستگاه روی باتری می‌ماند.</t>
         </is>
       </c>
-      <c r="F7" s="58" t="inlineStr">
+      <c r="F7" s="113" t="inlineStr">
         <is>
           <t>کشیدن برق شهر</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="55" t="inlineStr">
+      <c r="H7" s="111" t="inlineStr">
         <is>
           <t>پنل ورودی را قطع نشان می‌دهد و دستگاه بی‌وقفه روی باتری ادامه می‌دهد</t>
         </is>
       </c>
-      <c r="I7" s="55" t="inlineStr">
+      <c r="I7" s="111" t="inlineStr">
         <is>
           <t>تشخیص درست قطع و ادامهٔ کار = قبول؛ هنگ یا نشان اشتباه = رد</t>
         </is>
       </c>
-      <c r="J7" s="55" t="inlineStr"/>
-      <c r="K7" s="55" t="inlineStr">
+      <c r="J7" s="111" t="inlineStr"/>
+      <c r="K7" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="59" t="inlineStr"/>
-      <c r="M7" s="55" t="inlineStr"/>
-      <c r="N7" s="55" t="inlineStr">
+      <c r="L7" s="114" t="inlineStr"/>
+      <c r="M7" s="111" t="inlineStr"/>
+      <c r="N7" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="58" t="inlineStr"/>
-      <c r="P7" s="58" t="inlineStr"/>
-      <c r="Q7" s="60">
+      <c r="O7" s="113" t="inlineStr"/>
+      <c r="P7" s="113" t="inlineStr"/>
+      <c r="Q7" s="115">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="103" t="inlineStr">
         <is>
           <t>MS-021</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>کالیبراسیون برد / tolerance</t>
         </is>
       </c>
-      <c r="C8" s="50" t="inlineStr">
+      <c r="C8" s="106" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D8" s="104" t="inlineStr">
         <is>
           <t>مولتی‌متر مرجع مطمئن و پنل در حالت کالیبراسیون</t>
         </is>
       </c>
-      <c r="E8" s="48" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr">
         <is>
           <t>گام ۱: طبق راهنمای پنل، در یک ولتاژ پایین و یک ولتاژ بالا عدد دستگاه را با مولتی‌متر یکی کن.
 گام ۲: در یک ولتاژ میانی هر دو را مقایسه کن.</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>کالیبراسیون دو نقطه و چک میانی</t>
         </is>
       </c>
-      <c r="G8" s="50" t="inlineStr">
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H8" s="48" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>بعد از کالیبراسیون، عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند</t>
         </is>
       </c>
-      <c r="I8" s="48" t="inlineStr">
+      <c r="I8" s="104" t="inlineStr">
         <is>
           <t>برابری در نقطهٔ میانی = قبول؛ اختلاف محسوس = رد</t>
         </is>
       </c>
-      <c r="J8" s="51" t="inlineStr"/>
-      <c r="K8" s="52" t="inlineStr">
+      <c r="J8" s="107" t="inlineStr"/>
+      <c r="K8" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="53" t="inlineStr"/>
-      <c r="M8" s="48" t="inlineStr"/>
-      <c r="N8" s="48" t="inlineStr">
+      <c r="L8" s="109" t="inlineStr"/>
+      <c r="M8" s="104" t="inlineStr"/>
+      <c r="N8" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O8" s="50" t="inlineStr"/>
-      <c r="P8" s="50" t="inlineStr"/>
-      <c r="Q8" s="54">
+      <c r="O8" s="106" t="inlineStr"/>
+      <c r="P8" s="106" t="inlineStr"/>
+      <c r="Q8" s="110">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="Q9" s="63">
+      <c r="A9" s="85" t="n"/>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="85" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="85" t="n"/>
+      <c r="F9" s="85" t="n"/>
+      <c r="G9" s="85" t="n"/>
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="85" t="n"/>
+      <c r="J9" s="85" t="n"/>
+      <c r="K9" s="85" t="n"/>
+      <c r="L9" s="85" t="n"/>
+      <c r="M9" s="85" t="n"/>
+      <c r="N9" s="85" t="n"/>
+      <c r="O9" s="85" t="n"/>
+      <c r="P9" s="85" t="n"/>
+      <c r="Q9" s="116">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="Q10" s="63">
+      <c r="A10" s="85" t="n"/>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="85" t="n"/>
+      <c r="D10" s="85" t="n"/>
+      <c r="E10" s="85" t="n"/>
+      <c r="F10" s="85" t="n"/>
+      <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
+      <c r="Q10" s="116">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="Q11" s="63">
+      <c r="A11" s="85" t="n"/>
+      <c r="B11" s="85" t="n"/>
+      <c r="C11" s="85" t="n"/>
+      <c r="D11" s="85" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="85" t="n"/>
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+      <c r="K11" s="85" t="n"/>
+      <c r="L11" s="85" t="n"/>
+      <c r="M11" s="85" t="n"/>
+      <c r="N11" s="85" t="n"/>
+      <c r="O11" s="85" t="n"/>
+      <c r="P11" s="85" t="n"/>
+      <c r="Q11" s="116">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="Q12" s="63">
+      <c r="A12" s="85" t="n"/>
+      <c r="B12" s="85" t="n"/>
+      <c r="C12" s="85" t="n"/>
+      <c r="D12" s="85" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="85" t="n"/>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
+      <c r="Q12" s="116">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="Q13" s="63">
+      <c r="A13" s="85" t="n"/>
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="85" t="n"/>
+      <c r="D13" s="85" t="n"/>
+      <c r="E13" s="85" t="n"/>
+      <c r="F13" s="85" t="n"/>
+      <c r="G13" s="85" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+      <c r="K13" s="85" t="n"/>
+      <c r="L13" s="85" t="n"/>
+      <c r="M13" s="85" t="n"/>
+      <c r="N13" s="85" t="n"/>
+      <c r="O13" s="85" t="n"/>
+      <c r="P13" s="85" t="n"/>
+      <c r="Q13" s="116">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="Q14" s="63">
+      <c r="A14" s="85" t="n"/>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="85" t="n"/>
+      <c r="D14" s="85" t="n"/>
+      <c r="E14" s="85" t="n"/>
+      <c r="F14" s="85" t="n"/>
+      <c r="G14" s="85" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
+      <c r="Q14" s="116">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="Q15" s="63">
+      <c r="A15" s="85" t="n"/>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="85" t="n"/>
+      <c r="D15" s="85" t="n"/>
+      <c r="E15" s="85" t="n"/>
+      <c r="F15" s="85" t="n"/>
+      <c r="G15" s="85" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
+      <c r="L15" s="85" t="n"/>
+      <c r="M15" s="85" t="n"/>
+      <c r="N15" s="85" t="n"/>
+      <c r="O15" s="85" t="n"/>
+      <c r="P15" s="85" t="n"/>
+      <c r="Q15" s="116">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="Q16" s="63">
+      <c r="A16" s="85" t="n"/>
+      <c r="B16" s="85" t="n"/>
+      <c r="C16" s="85" t="n"/>
+      <c r="D16" s="85" t="n"/>
+      <c r="E16" s="85" t="n"/>
+      <c r="F16" s="85" t="n"/>
+      <c r="G16" s="85" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
+      <c r="Q16" s="116">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="Q17" s="63">
+      <c r="A17" s="85" t="n"/>
+      <c r="B17" s="85" t="n"/>
+      <c r="C17" s="85" t="n"/>
+      <c r="D17" s="85" t="n"/>
+      <c r="E17" s="85" t="n"/>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="85" t="n"/>
+      <c r="H17" s="85" t="n"/>
+      <c r="I17" s="85" t="n"/>
+      <c r="J17" s="85" t="n"/>
+      <c r="K17" s="85" t="n"/>
+      <c r="L17" s="85" t="n"/>
+      <c r="M17" s="85" t="n"/>
+      <c r="N17" s="85" t="n"/>
+      <c r="O17" s="85" t="n"/>
+      <c r="P17" s="85" t="n"/>
+      <c r="Q17" s="116">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="Q18" s="63">
+      <c r="A18" s="85" t="n"/>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="85" t="n"/>
+      <c r="D18" s="85" t="n"/>
+      <c r="E18" s="85" t="n"/>
+      <c r="F18" s="85" t="n"/>
+      <c r="G18" s="85" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
+      <c r="Q18" s="116">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="40.5" customHeight="1">
-      <c r="Q19" s="63">
+      <c r="A19" s="85" t="n"/>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="85" t="n"/>
+      <c r="D19" s="85" t="n"/>
+      <c r="E19" s="85" t="n"/>
+      <c r="F19" s="85" t="n"/>
+      <c r="G19" s="85" t="n"/>
+      <c r="H19" s="85" t="n"/>
+      <c r="I19" s="85" t="n"/>
+      <c r="J19" s="85" t="n"/>
+      <c r="K19" s="85" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
+      <c r="N19" s="85" t="n"/>
+      <c r="O19" s="85" t="n"/>
+      <c r="P19" s="85" t="n"/>
+      <c r="Q19" s="116">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="Q20" s="63">
+      <c r="A20" s="85" t="n"/>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="n"/>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="116">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="Q21" s="63">
+      <c r="A21" s="85" t="n"/>
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="85" t="n"/>
+      <c r="D21" s="85" t="n"/>
+      <c r="E21" s="85" t="n"/>
+      <c r="F21" s="85" t="n"/>
+      <c r="G21" s="85" t="n"/>
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
+      <c r="J21" s="85" t="n"/>
+      <c r="K21" s="85" t="n"/>
+      <c r="L21" s="85" t="n"/>
+      <c r="M21" s="85" t="n"/>
+      <c r="N21" s="85" t="n"/>
+      <c r="O21" s="85" t="n"/>
+      <c r="P21" s="85" t="n"/>
+      <c r="Q21" s="116">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="Q22" s="63">
+      <c r="A22" s="85" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="85" t="n"/>
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="116">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="Q23" s="63">
+      <c r="A23" s="85" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="85" t="n"/>
+      <c r="D23" s="85" t="n"/>
+      <c r="E23" s="85" t="n"/>
+      <c r="F23" s="85" t="n"/>
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+      <c r="P23" s="85" t="n"/>
+      <c r="Q23" s="116">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="Q24" s="63">
+      <c r="A24" s="85" t="n"/>
+      <c r="B24" s="85" t="n"/>
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="85" t="n"/>
+      <c r="E24" s="85" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="116">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="Q25" s="63">
+      <c r="A25" s="85" t="n"/>
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="85" t="n"/>
+      <c r="E25" s="85" t="n"/>
+      <c r="F25" s="85" t="n"/>
+      <c r="G25" s="85" t="n"/>
+      <c r="H25" s="85" t="n"/>
+      <c r="I25" s="85" t="n"/>
+      <c r="J25" s="85" t="n"/>
+      <c r="K25" s="85" t="n"/>
+      <c r="L25" s="85" t="n"/>
+      <c r="M25" s="85" t="n"/>
+      <c r="N25" s="85" t="n"/>
+      <c r="O25" s="85" t="n"/>
+      <c r="P25" s="85" t="n"/>
+      <c r="Q25" s="116">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="Q26" s="63">
+      <c r="A26" s="85" t="n"/>
+      <c r="B26" s="85" t="n"/>
+      <c r="C26" s="85" t="n"/>
+      <c r="D26" s="85" t="n"/>
+      <c r="E26" s="85" t="n"/>
+      <c r="F26" s="85" t="n"/>
+      <c r="G26" s="85" t="n"/>
+      <c r="H26" s="85" t="n"/>
+      <c r="I26" s="85" t="n"/>
+      <c r="J26" s="85" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="116">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="63">
+      <c r="A27" s="85" t="n"/>
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="85" t="n"/>
+      <c r="D27" s="85" t="n"/>
+      <c r="E27" s="85" t="n"/>
+      <c r="F27" s="85" t="n"/>
+      <c r="G27" s="85" t="n"/>
+      <c r="H27" s="85" t="n"/>
+      <c r="I27" s="85" t="n"/>
+      <c r="J27" s="85" t="n"/>
+      <c r="K27" s="85" t="n"/>
+      <c r="L27" s="85" t="n"/>
+      <c r="M27" s="85" t="n"/>
+      <c r="N27" s="85" t="n"/>
+      <c r="O27" s="85" t="n"/>
+      <c r="P27" s="85" t="n"/>
+      <c r="Q27" s="116">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="63">
+      <c r="A28" s="85" t="n"/>
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="85" t="n"/>
+      <c r="D28" s="85" t="n"/>
+      <c r="E28" s="85" t="n"/>
+      <c r="F28" s="85" t="n"/>
+      <c r="G28" s="85" t="n"/>
+      <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
+      <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="116">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="63">
+      <c r="A29" s="85" t="n"/>
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="85" t="n"/>
+      <c r="D29" s="85" t="n"/>
+      <c r="E29" s="85" t="n"/>
+      <c r="F29" s="85" t="n"/>
+      <c r="G29" s="85" t="n"/>
+      <c r="H29" s="85" t="n"/>
+      <c r="I29" s="85" t="n"/>
+      <c r="J29" s="85" t="n"/>
+      <c r="K29" s="85" t="n"/>
+      <c r="L29" s="85" t="n"/>
+      <c r="M29" s="85" t="n"/>
+      <c r="N29" s="85" t="n"/>
+      <c r="O29" s="85" t="n"/>
+      <c r="P29" s="85" t="n"/>
+      <c r="Q29" s="116">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="63">
+      <c r="A30" s="85" t="n"/>
+      <c r="B30" s="85" t="n"/>
+      <c r="C30" s="85" t="n"/>
+      <c r="D30" s="85" t="n"/>
+      <c r="E30" s="85" t="n"/>
+      <c r="F30" s="85" t="n"/>
+      <c r="G30" s="85" t="n"/>
+      <c r="H30" s="85" t="n"/>
+      <c r="I30" s="85" t="n"/>
+      <c r="J30" s="85" t="n"/>
+      <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
+      <c r="O30" s="85" t="n"/>
+      <c r="P30" s="85" t="n"/>
+      <c r="Q30" s="116">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="63">
+      <c r="A31" s="85" t="n"/>
+      <c r="B31" s="85" t="n"/>
+      <c r="C31" s="85" t="n"/>
+      <c r="D31" s="85" t="n"/>
+      <c r="E31" s="85" t="n"/>
+      <c r="F31" s="85" t="n"/>
+      <c r="G31" s="85" t="n"/>
+      <c r="H31" s="85" t="n"/>
+      <c r="I31" s="85" t="n"/>
+      <c r="J31" s="85" t="n"/>
+      <c r="K31" s="85" t="n"/>
+      <c r="L31" s="85" t="n"/>
+      <c r="M31" s="85" t="n"/>
+      <c r="N31" s="85" t="n"/>
+      <c r="O31" s="85" t="n"/>
+      <c r="P31" s="85" t="n"/>
+      <c r="Q31" s="116">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="63">
+      <c r="A32" s="85" t="n"/>
+      <c r="B32" s="85" t="n"/>
+      <c r="C32" s="85" t="n"/>
+      <c r="D32" s="85" t="n"/>
+      <c r="E32" s="85" t="n"/>
+      <c r="F32" s="85" t="n"/>
+      <c r="G32" s="85" t="n"/>
+      <c r="H32" s="85" t="n"/>
+      <c r="I32" s="85" t="n"/>
+      <c r="J32" s="85" t="n"/>
+      <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="116">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="63">
+      <c r="A33" s="85" t="n"/>
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="85" t="n"/>
+      <c r="D33" s="85" t="n"/>
+      <c r="E33" s="85" t="n"/>
+      <c r="F33" s="85" t="n"/>
+      <c r="G33" s="85" t="n"/>
+      <c r="H33" s="85" t="n"/>
+      <c r="I33" s="85" t="n"/>
+      <c r="J33" s="85" t="n"/>
+      <c r="K33" s="85" t="n"/>
+      <c r="L33" s="85" t="n"/>
+      <c r="M33" s="85" t="n"/>
+      <c r="N33" s="85" t="n"/>
+      <c r="O33" s="85" t="n"/>
+      <c r="P33" s="85" t="n"/>
+      <c r="Q33" s="116">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="63">
+      <c r="A34" s="85" t="n"/>
+      <c r="B34" s="85" t="n"/>
+      <c r="C34" s="85" t="n"/>
+      <c r="D34" s="85" t="n"/>
+      <c r="E34" s="85" t="n"/>
+      <c r="F34" s="85" t="n"/>
+      <c r="G34" s="85" t="n"/>
+      <c r="H34" s="85" t="n"/>
+      <c r="I34" s="85" t="n"/>
+      <c r="J34" s="85" t="n"/>
+      <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
+      <c r="O34" s="85" t="n"/>
+      <c r="P34" s="85" t="n"/>
+      <c r="Q34" s="116">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="63">
+      <c r="A35" s="85" t="n"/>
+      <c r="B35" s="85" t="n"/>
+      <c r="C35" s="85" t="n"/>
+      <c r="D35" s="85" t="n"/>
+      <c r="E35" s="85" t="n"/>
+      <c r="F35" s="85" t="n"/>
+      <c r="G35" s="85" t="n"/>
+      <c r="H35" s="85" t="n"/>
+      <c r="I35" s="85" t="n"/>
+      <c r="J35" s="85" t="n"/>
+      <c r="K35" s="85" t="n"/>
+      <c r="L35" s="85" t="n"/>
+      <c r="M35" s="85" t="n"/>
+      <c r="N35" s="85" t="n"/>
+      <c r="O35" s="85" t="n"/>
+      <c r="P35" s="85" t="n"/>
+      <c r="Q35" s="116">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="63">
+      <c r="A36" s="85" t="n"/>
+      <c r="B36" s="85" t="n"/>
+      <c r="C36" s="85" t="n"/>
+      <c r="D36" s="85" t="n"/>
+      <c r="E36" s="85" t="n"/>
+      <c r="F36" s="85" t="n"/>
+      <c r="G36" s="85" t="n"/>
+      <c r="H36" s="85" t="n"/>
+      <c r="I36" s="85" t="n"/>
+      <c r="J36" s="85" t="n"/>
+      <c r="K36" s="85" t="n"/>
+      <c r="L36" s="85" t="n"/>
+      <c r="M36" s="85" t="n"/>
+      <c r="N36" s="85" t="n"/>
+      <c r="O36" s="85" t="n"/>
+      <c r="P36" s="85" t="n"/>
+      <c r="Q36" s="116">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="63">
+      <c r="A37" s="85" t="n"/>
+      <c r="B37" s="85" t="n"/>
+      <c r="C37" s="85" t="n"/>
+      <c r="D37" s="85" t="n"/>
+      <c r="E37" s="85" t="n"/>
+      <c r="F37" s="85" t="n"/>
+      <c r="G37" s="85" t="n"/>
+      <c r="H37" s="85" t="n"/>
+      <c r="I37" s="85" t="n"/>
+      <c r="J37" s="85" t="n"/>
+      <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
+      <c r="O37" s="85" t="n"/>
+      <c r="P37" s="85" t="n"/>
+      <c r="Q37" s="116">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="63">
+      <c r="A38" s="85" t="n"/>
+      <c r="B38" s="85" t="n"/>
+      <c r="C38" s="85" t="n"/>
+      <c r="D38" s="85" t="n"/>
+      <c r="E38" s="85" t="n"/>
+      <c r="F38" s="85" t="n"/>
+      <c r="G38" s="85" t="n"/>
+      <c r="H38" s="85" t="n"/>
+      <c r="I38" s="85" t="n"/>
+      <c r="J38" s="85" t="n"/>
+      <c r="K38" s="85" t="n"/>
+      <c r="L38" s="85" t="n"/>
+      <c r="M38" s="85" t="n"/>
+      <c r="N38" s="85" t="n"/>
+      <c r="O38" s="85" t="n"/>
+      <c r="P38" s="85" t="n"/>
+      <c r="Q38" s="116">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="63">
+      <c r="A39" s="85" t="n"/>
+      <c r="B39" s="85" t="n"/>
+      <c r="C39" s="85" t="n"/>
+      <c r="D39" s="85" t="n"/>
+      <c r="E39" s="85" t="n"/>
+      <c r="F39" s="85" t="n"/>
+      <c r="G39" s="85" t="n"/>
+      <c r="H39" s="85" t="n"/>
+      <c r="I39" s="85" t="n"/>
+      <c r="J39" s="85" t="n"/>
+      <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
+      <c r="M39" s="85" t="n"/>
+      <c r="N39" s="85" t="n"/>
+      <c r="O39" s="85" t="n"/>
+      <c r="P39" s="85" t="n"/>
+      <c r="Q39" s="116">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="63">
+      <c r="A40" s="85" t="n"/>
+      <c r="B40" s="85" t="n"/>
+      <c r="C40" s="85" t="n"/>
+      <c r="D40" s="85" t="n"/>
+      <c r="E40" s="85" t="n"/>
+      <c r="F40" s="85" t="n"/>
+      <c r="G40" s="85" t="n"/>
+      <c r="H40" s="85" t="n"/>
+      <c r="I40" s="85" t="n"/>
+      <c r="J40" s="85" t="n"/>
+      <c r="K40" s="85" t="n"/>
+      <c r="L40" s="85" t="n"/>
+      <c r="M40" s="85" t="n"/>
+      <c r="N40" s="85" t="n"/>
+      <c r="O40" s="85" t="n"/>
+      <c r="P40" s="85" t="n"/>
+      <c r="Q40" s="116">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="63">
+      <c r="A41" s="85" t="n"/>
+      <c r="B41" s="85" t="n"/>
+      <c r="C41" s="85" t="n"/>
+      <c r="D41" s="85" t="n"/>
+      <c r="E41" s="85" t="n"/>
+      <c r="F41" s="85" t="n"/>
+      <c r="G41" s="85" t="n"/>
+      <c r="H41" s="85" t="n"/>
+      <c r="I41" s="85" t="n"/>
+      <c r="J41" s="85" t="n"/>
+      <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
+      <c r="M41" s="85" t="n"/>
+      <c r="N41" s="85" t="n"/>
+      <c r="O41" s="85" t="n"/>
+      <c r="P41" s="85" t="n"/>
+      <c r="Q41" s="116">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="63">
+      <c r="A42" s="85" t="n"/>
+      <c r="B42" s="85" t="n"/>
+      <c r="C42" s="85" t="n"/>
+      <c r="D42" s="85" t="n"/>
+      <c r="E42" s="85" t="n"/>
+      <c r="F42" s="85" t="n"/>
+      <c r="G42" s="85" t="n"/>
+      <c r="H42" s="85" t="n"/>
+      <c r="I42" s="85" t="n"/>
+      <c r="J42" s="85" t="n"/>
+      <c r="K42" s="85" t="n"/>
+      <c r="L42" s="85" t="n"/>
+      <c r="M42" s="85" t="n"/>
+      <c r="N42" s="85" t="n"/>
+      <c r="O42" s="85" t="n"/>
+      <c r="P42" s="85" t="n"/>
+      <c r="Q42" s="116">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="63">
+      <c r="A43" s="85" t="n"/>
+      <c r="B43" s="85" t="n"/>
+      <c r="C43" s="85" t="n"/>
+      <c r="D43" s="85" t="n"/>
+      <c r="E43" s="85" t="n"/>
+      <c r="F43" s="85" t="n"/>
+      <c r="G43" s="85" t="n"/>
+      <c r="H43" s="85" t="n"/>
+      <c r="I43" s="85" t="n"/>
+      <c r="J43" s="85" t="n"/>
+      <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
+      <c r="M43" s="85" t="n"/>
+      <c r="N43" s="85" t="n"/>
+      <c r="O43" s="85" t="n"/>
+      <c r="P43" s="85" t="n"/>
+      <c r="Q43" s="116">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="63">
+      <c r="A44" s="85" t="n"/>
+      <c r="B44" s="85" t="n"/>
+      <c r="C44" s="85" t="n"/>
+      <c r="D44" s="85" t="n"/>
+      <c r="E44" s="85" t="n"/>
+      <c r="F44" s="85" t="n"/>
+      <c r="G44" s="85" t="n"/>
+      <c r="H44" s="85" t="n"/>
+      <c r="I44" s="85" t="n"/>
+      <c r="J44" s="85" t="n"/>
+      <c r="K44" s="85" t="n"/>
+      <c r="L44" s="85" t="n"/>
+      <c r="M44" s="85" t="n"/>
+      <c r="N44" s="85" t="n"/>
+      <c r="O44" s="85" t="n"/>
+      <c r="P44" s="85" t="n"/>
+      <c r="Q44" s="116">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="63">
+      <c r="A45" s="85" t="n"/>
+      <c r="B45" s="85" t="n"/>
+      <c r="C45" s="85" t="n"/>
+      <c r="D45" s="85" t="n"/>
+      <c r="E45" s="85" t="n"/>
+      <c r="F45" s="85" t="n"/>
+      <c r="G45" s="85" t="n"/>
+      <c r="H45" s="85" t="n"/>
+      <c r="I45" s="85" t="n"/>
+      <c r="J45" s="85" t="n"/>
+      <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
+      <c r="M45" s="85" t="n"/>
+      <c r="N45" s="85" t="n"/>
+      <c r="O45" s="85" t="n"/>
+      <c r="P45" s="85" t="n"/>
+      <c r="Q45" s="116">
         <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="63">
+      <c r="A46" s="85" t="n"/>
+      <c r="B46" s="85" t="n"/>
+      <c r="C46" s="85" t="n"/>
+      <c r="D46" s="85" t="n"/>
+      <c r="E46" s="85" t="n"/>
+      <c r="F46" s="85" t="n"/>
+      <c r="G46" s="85" t="n"/>
+      <c r="H46" s="85" t="n"/>
+      <c r="I46" s="85" t="n"/>
+      <c r="J46" s="85" t="n"/>
+      <c r="K46" s="85" t="n"/>
+      <c r="L46" s="85" t="n"/>
+      <c r="M46" s="85" t="n"/>
+      <c r="N46" s="85" t="n"/>
+      <c r="O46" s="85" t="n"/>
+      <c r="P46" s="85" t="n"/>
+      <c r="Q46" s="116">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="63">
+      <c r="A47" s="85" t="n"/>
+      <c r="B47" s="85" t="n"/>
+      <c r="C47" s="85" t="n"/>
+      <c r="D47" s="85" t="n"/>
+      <c r="E47" s="85" t="n"/>
+      <c r="F47" s="85" t="n"/>
+      <c r="G47" s="85" t="n"/>
+      <c r="H47" s="85" t="n"/>
+      <c r="I47" s="85" t="n"/>
+      <c r="J47" s="85" t="n"/>
+      <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
+      <c r="M47" s="85" t="n"/>
+      <c r="N47" s="85" t="n"/>
+      <c r="O47" s="85" t="n"/>
+      <c r="P47" s="85" t="n"/>
+      <c r="Q47" s="116">
         <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="63">
+      <c r="A48" s="85" t="n"/>
+      <c r="B48" s="85" t="n"/>
+      <c r="C48" s="85" t="n"/>
+      <c r="D48" s="85" t="n"/>
+      <c r="E48" s="85" t="n"/>
+      <c r="F48" s="85" t="n"/>
+      <c r="G48" s="85" t="n"/>
+      <c r="H48" s="85" t="n"/>
+      <c r="I48" s="85" t="n"/>
+      <c r="J48" s="85" t="n"/>
+      <c r="K48" s="85" t="n"/>
+      <c r="L48" s="85" t="n"/>
+      <c r="M48" s="85" t="n"/>
+      <c r="N48" s="85" t="n"/>
+      <c r="O48" s="85" t="n"/>
+      <c r="P48" s="85" t="n"/>
+      <c r="Q48" s="116">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="54" customHeight="1">
-      <c r="A49" s="47" t="inlineStr">
+      <c r="A49" s="103" t="inlineStr">
         <is>
           <t>MS-023</t>
         </is>
       </c>
-      <c r="B49" s="48" t="inlineStr">
+      <c r="B49" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C49" s="50" t="inlineStr">
+      <c r="C49" s="106" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D49" s="48" t="inlineStr">
+      <c r="D49" s="104" t="inlineStr">
         <is>
           <t>منبع دقیق آزمایشگاهی و مولتی‌متر</t>
         </is>
       </c>
-      <c r="E49" s="48" t="inlineStr">
+      <c r="E49" s="104" t="inlineStr">
         <is>
           <t>گام ۱: منبع را دقیقاً روی 24.0 ولت تنظیم کن و به ورودی وصل کن؛ یک باتری 24 ولت هم وصل باشد.
 گام ۲: ولتاژ منبع را با مولتی‌متر خودت هم اندازه بگیر.
@@ -2001,68 +3223,68 @@
 گام ۴: هر دو باید نزدیک همان عددی باشند که مولتی‌متر می‌گوید؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F49" s="48" t="inlineStr">
+      <c r="F49" s="104" t="inlineStr">
         <is>
           <t>ورودی و باتری 24 ولت</t>
         </is>
       </c>
-      <c r="G49" s="50" t="inlineStr">
+      <c r="G49" s="106" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H49" s="48" t="inlineStr">
+      <c r="H49" s="104" t="inlineStr">
         <is>
           <t>عددهای پنل نزدیک مقدار واقعی مولتی‌متر</t>
         </is>
       </c>
-      <c r="I49" s="48" t="inlineStr">
+      <c r="I49" s="104" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J49" s="48" t="inlineStr">
+      <c r="J49" s="104" t="inlineStr">
         <is>
           <t>اختلاف پنل با مولتی‌متر کم و منطقی باشد</t>
         </is>
       </c>
-      <c r="K49" s="48" t="inlineStr"/>
-      <c r="L49" s="83" t="inlineStr">
+      <c r="K49" s="104" t="inlineStr"/>
+      <c r="L49" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M49" s="48" t="n"/>
-      <c r="N49" s="48" t="n"/>
-      <c r="O49" s="50" t="n"/>
-      <c r="P49" s="50" t="n"/>
-      <c r="Q49" s="54">
+      <c r="M49" s="104" t="n"/>
+      <c r="N49" s="104" t="n"/>
+      <c r="O49" s="106" t="n"/>
+      <c r="P49" s="106" t="n"/>
+      <c r="Q49" s="110">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="54" customHeight="1">
-      <c r="A50" s="47" t="inlineStr">
+      <c r="A50" s="103" t="inlineStr">
         <is>
           <t>MS-024</t>
         </is>
       </c>
-      <c r="B50" s="55" t="inlineStr">
+      <c r="B50" s="111" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C50" s="58" t="inlineStr">
+      <c r="C50" s="113" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D50" s="55" t="inlineStr">
+      <c r="D50" s="111" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل عددها را نشان می‌دهد</t>
         </is>
       </c>
-      <c r="E50" s="55" t="inlineStr">
+      <c r="E50" s="111" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه روشن باشد و در پنل عددهای ولتاژ را ببین.
 گام ۲: ورودی را کامل قطع کن (صفر ولت).
@@ -2070,68 +3292,68 @@
 گام ۴: دستگاه نباید خطای اندازه‌گیری بگیرد یا خاموش شود.</t>
         </is>
       </c>
-      <c r="F50" s="55" t="inlineStr">
+      <c r="F50" s="111" t="inlineStr">
         <is>
           <t>قطع کامل ورودی</t>
         </is>
       </c>
-      <c r="G50" s="58" t="inlineStr">
+      <c r="G50" s="113" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H50" s="55" t="inlineStr">
+      <c r="H50" s="111" t="inlineStr">
         <is>
           <t>ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم</t>
         </is>
       </c>
-      <c r="I50" s="55" t="inlineStr">
+      <c r="I50" s="111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="55" t="inlineStr">
+      <c r="J50" s="111" t="inlineStr">
         <is>
           <t>فقط ورودی صفر شود و دستگاه عادی بماند</t>
         </is>
       </c>
-      <c r="K50" s="55" t="inlineStr"/>
-      <c r="L50" s="83" t="inlineStr">
+      <c r="K50" s="111" t="inlineStr"/>
+      <c r="L50" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="58" t="n"/>
-      <c r="P50" s="58" t="n"/>
-      <c r="Q50" s="60">
+      <c r="M50" s="111" t="n"/>
+      <c r="N50" s="111" t="n"/>
+      <c r="O50" s="113" t="n"/>
+      <c r="P50" s="113" t="n"/>
+      <c r="Q50" s="115">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="54" customHeight="1">
-      <c r="A51" s="47" t="inlineStr">
+      <c r="A51" s="103" t="inlineStr">
         <is>
           <t>MS-025</t>
         </is>
       </c>
-      <c r="B51" s="48" t="inlineStr">
+      <c r="B51" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C51" s="50" t="inlineStr">
+      <c r="C51" s="106" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D51" s="48" t="inlineStr">
+      <c r="D51" s="104" t="inlineStr">
         <is>
           <t>بار معلوم و مولتی‌متر سری</t>
         </is>
       </c>
-      <c r="E51" s="48" t="inlineStr">
+      <c r="E51" s="104" t="inlineStr">
         <is>
           <t>گام ۱: یک بار معلوم روی مسیر شارژ بگذار و جریان واقعی را با مولتی‌متر اندازه بگیر (مثلاً باری که حدود 500 میلی‌آمپر می‌کشد).
 گام ۲: شارژ را راه بینداز.
@@ -2139,42 +3361,42 @@
 گام ۴: باید نزدیک هم باشند؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F51" s="48" t="inlineStr">
+      <c r="F51" s="104" t="inlineStr">
         <is>
           <t>بار حدود 500 میلی‌آمپر</t>
         </is>
       </c>
-      <c r="G51" s="50" t="inlineStr">
+      <c r="G51" s="106" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H51" s="48" t="inlineStr">
+      <c r="H51" s="104" t="inlineStr">
         <is>
           <t>جریان پنل نزدیک جریان واقعی</t>
         </is>
       </c>
-      <c r="I51" s="48" t="inlineStr">
+      <c r="I51" s="104" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J51" s="48" t="inlineStr">
+      <c r="J51" s="104" t="inlineStr">
         <is>
           <t>اختلاف جریان پنل با مولتی‌متر کم باشد</t>
         </is>
       </c>
-      <c r="K51" s="48" t="inlineStr"/>
-      <c r="L51" s="83" t="inlineStr">
+      <c r="K51" s="104" t="inlineStr"/>
+      <c r="L51" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M51" s="48" t="n"/>
-      <c r="N51" s="48" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="54">
+      <c r="M51" s="104" t="n"/>
+      <c r="N51" s="104" t="n"/>
+      <c r="O51" s="106" t="n"/>
+      <c r="P51" s="106" t="n"/>
+      <c r="Q51" s="110">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
@@ -2233,125 +3455,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
+      <c r="G1" s="85" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
+      <c r="O1" s="85" t="n"/>
+      <c r="P1" s="85" t="n"/>
+      <c r="Q1" s="85" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
+      <c r="G2" s="85" t="n"/>
+      <c r="H2" s="85" t="n"/>
+      <c r="I2" s="85" t="n"/>
+      <c r="J2" s="85" t="n"/>
+      <c r="K2" s="85" t="n"/>
+      <c r="L2" s="85" t="n"/>
+      <c r="M2" s="85" t="n"/>
+      <c r="N2" s="85" t="n"/>
+      <c r="O2" s="85" t="n"/>
+      <c r="P2" s="85" t="n"/>
+      <c r="Q2" s="85" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="85" t="n"/>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="85" t="n"/>
+      <c r="E3" s="85" t="n"/>
+      <c r="F3" s="85" t="n"/>
+      <c r="G3" s="85" t="n"/>
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="85" t="n"/>
+      <c r="J3" s="85" t="n"/>
+      <c r="K3" s="85" t="n"/>
+      <c r="L3" s="85" t="n"/>
+      <c r="M3" s="85" t="n"/>
+      <c r="N3" s="85" t="n"/>
+      <c r="O3" s="85" t="n"/>
+      <c r="P3" s="85" t="n"/>
+      <c r="Q3" s="85" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="87" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="87" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="87" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="87" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="87" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="87" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="87" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="87" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="87" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="87" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="87" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="87" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="87" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="87" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="87" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>MS-002</t>
         </is>
       </c>
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="111" t="inlineStr">
         <is>
           <t>Warmup / فریم اول</t>
         </is>
       </c>
-      <c r="C5" s="56" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="55" t="inlineStr">
+      <c r="D5" s="111" t="inlineStr">
         <is>
           <t>پس از Init و Start موفق</t>
         </is>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="E5" s="120" t="inlineStr">
         <is>
           <t>گام ۱: Init و Start را با موفقیت انجام بده (ادامهٔ MS-001).
 گام ۲: یک فریم کامل و پایدار ADC روی هر 5 کانال اعمال کن؛ مثلاً روی همه 2 ولت (counts حدود 2482).
@@ -2359,68 +3631,68 @@
 گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 1 شده باشد؛ valid شدن در فریم اول یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="F5" s="113" t="inlineStr">
         <is>
           <t>فریم 1 کامل و پایدار, counts≈2482 (2V)</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="G5" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H5" s="55" t="inlineStr">
+      <c r="H5" s="111" t="inlineStr">
         <is>
           <t>valid همچنان false، warmupCounter=1، globals هنوز 0 یا قدیمی اما valid=false. PASS: هنوز invalid. FAIL: valid true زودهنگام.</t>
         </is>
       </c>
-      <c r="I5" s="55" t="inlineStr">
+      <c r="I5" s="111" t="inlineStr">
         <is>
           <t>PASS: فریم1 → still false. FAIL: valid true.</t>
         </is>
       </c>
-      <c r="J5" s="55" t="n"/>
-      <c r="K5" s="55" t="inlineStr">
+      <c r="J5" s="111" t="n"/>
+      <c r="K5" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="59" t="n"/>
-      <c r="M5" s="55" t="n"/>
-      <c r="N5" s="55" t="inlineStr">
+      <c r="L5" s="114" t="n"/>
+      <c r="M5" s="111" t="n"/>
+      <c r="N5" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="58" t="n"/>
-      <c r="P5" s="58" t="n"/>
-      <c r="Q5" s="60">
+      <c r="O5" s="113" t="n"/>
+      <c r="P5" s="113" t="n"/>
+      <c r="Q5" s="115">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="103" t="inlineStr">
         <is>
           <t>MS-003</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>Warmup / فریم دوم</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="121" t="inlineStr">
         <is>
           <t>پس از MS-002</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="121" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
 گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
@@ -2428,68 +3700,68 @@
 گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="106" t="inlineStr">
         <is>
           <t>فریم 2 کامل, counts 2482</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G6" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="104" t="inlineStr">
         <is>
           <t>valid همچنان false، counter=2. PASS: still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="104" t="inlineStr">
         <is>
           <t>PASS: فریم2 still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="J6" s="51" t="n"/>
-      <c r="K6" s="52" t="inlineStr">
+      <c r="J6" s="107" t="n"/>
+      <c r="K6" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="53" t="n"/>
-      <c r="M6" s="48" t="n"/>
-      <c r="N6" s="48" t="inlineStr">
+      <c r="L6" s="109" t="n"/>
+      <c r="M6" s="104" t="n"/>
+      <c r="N6" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="50" t="n"/>
-      <c r="P6" s="50" t="n"/>
-      <c r="Q6" s="54">
+      <c r="O6" s="106" t="n"/>
+      <c r="P6" s="106" t="n"/>
+      <c r="Q6" s="110">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>MS-004</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="111" t="inlineStr">
         <is>
           <t>Warmup / فریم سوم</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="120" t="inlineStr">
         <is>
           <t>پس از MS-003</t>
         </is>
       </c>
-      <c r="E7" s="57" t="inlineStr">
+      <c r="E7" s="120" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
 گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
@@ -2497,68 +3769,68 @@
 گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
         </is>
       </c>
-      <c r="F7" s="58" t="inlineStr">
+      <c r="F7" s="113" t="inlineStr">
         <is>
           <t>فریم 3 کامل, counts: V channels 2482 (2V pin), I channels 610 (0.49V)</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H7" s="55" t="inlineStr">
+      <c r="H7" s="111" t="inlineStr">
         <is>
           <t>valid=true، همه globals به‌روز: 2V pin → V24≈22352mV, V12≈12058mV, Current≈486mA با I counts 610, input_present per PB4. PASS: valid true و مقادیر محاسبه شده ±tolerance. FAIL: همچنان false.</t>
         </is>
       </c>
-      <c r="I7" s="55" t="inlineStr">
+      <c r="I7" s="111" t="inlineStr">
         <is>
           <t>PASS: فریم3 → valid true با V24≈22352 و I≈486mA. FAIL: still false.</t>
         </is>
       </c>
-      <c r="J7" s="55" t="n"/>
-      <c r="K7" s="55" t="inlineStr">
+      <c r="J7" s="111" t="n"/>
+      <c r="K7" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="59" t="n"/>
-      <c r="M7" s="55" t="n"/>
-      <c r="N7" s="55" t="inlineStr">
+      <c r="L7" s="114" t="n"/>
+      <c r="M7" s="111" t="n"/>
+      <c r="N7" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="58" t="n"/>
-      <c r="P7" s="58" t="n"/>
-      <c r="Q7" s="60">
+      <c r="O7" s="113" t="n"/>
+      <c r="P7" s="113" t="n"/>
+      <c r="Q7" s="115">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="103" t="inlineStr">
         <is>
           <t>MS-005</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>Warmup / فریم ناقص</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D8" s="104" t="inlineStr">
         <is>
           <t>پس از valid=true</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="121" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن (پایان MS-004).
 گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
@@ -2566,68 +3838,68 @@
 گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>فریم ناقص/ناپایدار (GetRaw false)</t>
         </is>
       </c>
-      <c r="G8" s="50" t="inlineStr">
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H8" s="48" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>valid=false فوری، warmupCounter reset به 0، snapshot.valid false. PASS: invalid و reset. FAIL: همچنان true.</t>
         </is>
       </c>
-      <c r="I8" s="48" t="inlineStr">
+      <c r="I8" s="104" t="inlineStr">
         <is>
           <t>PASS: unstable → invalid+reset. FAIL: remains true.</t>
         </is>
       </c>
-      <c r="J8" s="51" t="n"/>
-      <c r="K8" s="52" t="inlineStr">
+      <c r="J8" s="107" t="n"/>
+      <c r="K8" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="53" t="n"/>
-      <c r="M8" s="48" t="n"/>
-      <c r="N8" s="48" t="inlineStr">
+      <c r="L8" s="109" t="n"/>
+      <c r="M8" s="104" t="n"/>
+      <c r="N8" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O8" s="50" t="n"/>
-      <c r="P8" s="50" t="n"/>
-      <c r="Q8" s="54">
+      <c r="O8" s="106" t="n"/>
+      <c r="P8" s="106" t="n"/>
+      <c r="Q8" s="110">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="103" t="inlineStr">
         <is>
           <t>MS-006</t>
         </is>
       </c>
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="111" t="inlineStr">
         <is>
           <t>Warmup / شروع دوباره</t>
         </is>
       </c>
-      <c r="C9" s="56" t="inlineStr">
+      <c r="C9" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="120" t="inlineStr">
         <is>
           <t>پس از MS-005</t>
         </is>
       </c>
-      <c r="E9" s="57" t="inlineStr">
+      <c r="E9" s="120" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-005 (فریم خراب و warmup=0).
 گام ۲: سه فریم کامل و پایدار پشت سر هم اعمال کن و هر کدام یک Run بزن (در مجموع 30 میلی‌ثانیه).
@@ -2635,68 +3907,68 @@
 گام ۴: دقیقاً بعد از فریم سوم باید valid=true شود؛ زودتر یا دیرتر شدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
+      <c r="F9" s="113" t="inlineStr">
         <is>
           <t>3 فریم کامل</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G9" s="113" t="inlineStr">
         <is>
           <t>30ms</t>
         </is>
       </c>
-      <c r="H9" s="55" t="inlineStr">
+      <c r="H9" s="111" t="inlineStr">
         <is>
           <t>پس از فریم سوم دوباره valid=true. PASS: warmup دوباره 3 فریم. FAIL: valid زودتر یا دیرتر.</t>
         </is>
       </c>
-      <c r="I9" s="55" t="inlineStr">
+      <c r="I9" s="111" t="inlineStr">
         <is>
           <t>PASS: 3 فریم دوباره → true. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J9" s="55" t="n"/>
-      <c r="K9" s="55" t="inlineStr">
+      <c r="J9" s="111" t="n"/>
+      <c r="K9" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="59" t="n"/>
-      <c r="M9" s="55" t="n"/>
-      <c r="N9" s="55" t="inlineStr">
+      <c r="L9" s="114" t="n"/>
+      <c r="M9" s="111" t="n"/>
+      <c r="N9" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O9" s="58" t="n"/>
-      <c r="P9" s="58" t="n"/>
-      <c r="Q9" s="60">
+      <c r="O9" s="113" t="n"/>
+      <c r="P9" s="113" t="n"/>
+      <c r="Q9" s="115">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="103" t="inlineStr">
         <is>
           <t>MS-007</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="104" t="inlineStr">
         <is>
           <t>ورودی 24V قطع</t>
         </is>
       </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="106" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="48" t="inlineStr">
+      <c r="D10" s="104" t="inlineStr">
         <is>
           <t>valid=true با Vin=0</t>
         </is>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="104" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
 گام ۲: یک Run بزن.
@@ -2704,68 +3976,68 @@
 گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="50" t="inlineStr">
+      <c r="F10" s="106" t="inlineStr">
         <is>
           <t>v_in 0V (counts 0), سایر 2V</t>
         </is>
       </c>
-      <c r="G10" s="50" t="inlineStr">
+      <c r="G10" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H10" s="48" t="inlineStr">
+      <c r="H10" s="104" t="inlineStr">
         <is>
           <t>valid همچنان true (قطع ورودی ADC را invalid نمی‌کند)، v_in_mv≈0، سایر مقادیر به‌روز. PASS: valid true با Vin صفر. FAIL: valid false.</t>
         </is>
       </c>
-      <c r="I10" s="48" t="inlineStr">
+      <c r="I10" s="104" t="inlineStr">
         <is>
           <t>PASS: Vin zero still valid. FAIL: invalid.</t>
         </is>
       </c>
-      <c r="J10" s="51" t="n"/>
-      <c r="K10" s="52" t="inlineStr">
+      <c r="J10" s="107" t="n"/>
+      <c r="K10" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="53" t="n"/>
-      <c r="M10" s="48" t="n"/>
-      <c r="N10" s="48" t="inlineStr">
+      <c r="L10" s="109" t="n"/>
+      <c r="M10" s="104" t="n"/>
+      <c r="N10" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O10" s="50" t="n"/>
-      <c r="P10" s="50" t="n"/>
-      <c r="Q10" s="54">
+      <c r="O10" s="106" t="n"/>
+      <c r="P10" s="106" t="n"/>
+      <c r="Q10" s="110">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="103" t="inlineStr">
         <is>
           <t>MS-008</t>
         </is>
       </c>
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="111" t="inlineStr">
         <is>
           <t>بررسی v_in_mv</t>
         </is>
       </c>
-      <c r="C11" s="56" t="inlineStr">
+      <c r="C11" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="55" t="inlineStr">
+      <c r="D11" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E11" s="55" t="inlineStr">
+      <c r="E11" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
@@ -2773,68 +4045,68 @@
 گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F11" s="58" t="inlineStr">
+      <c r="F11" s="113" t="inlineStr">
         <is>
           <t>counts 1241 (1V)</t>
         </is>
       </c>
-      <c r="G11" s="58" t="inlineStr">
+      <c r="G11" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H11" s="55" t="inlineStr">
+      <c r="H11" s="111" t="inlineStr">
         <is>
           <t>v_in_mv = 1241*3300/4095≈1000mV pin → *76000/6800≈11176mV. tolerance ±9mV. PASS: خوانش در tolerance. FAIL: &gt;20mV خطا.</t>
         </is>
       </c>
-      <c r="I11" s="55" t="inlineStr">
+      <c r="I11" s="111" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J11" s="55" t="n"/>
-      <c r="K11" s="55" t="inlineStr">
+      <c r="J11" s="111" t="n"/>
+      <c r="K11" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="59" t="n"/>
-      <c r="M11" s="55" t="n"/>
-      <c r="N11" s="55" t="inlineStr">
+      <c r="L11" s="114" t="n"/>
+      <c r="M11" s="111" t="n"/>
+      <c r="N11" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O11" s="58" t="n"/>
-      <c r="P11" s="58" t="n"/>
-      <c r="Q11" s="60">
+      <c r="O11" s="113" t="n"/>
+      <c r="P11" s="113" t="n"/>
+      <c r="Q11" s="115">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="103" t="inlineStr">
         <is>
           <t>MS-009</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>بررسی v_bat24_mv</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="48" t="inlineStr">
+      <c r="D12" s="104" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E12" s="48" t="inlineStr">
+      <c r="E12" s="104" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
@@ -2842,68 +4114,68 @@
 گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="50" t="inlineStr">
+      <c r="F12" s="106" t="inlineStr">
         <is>
           <t>counts 2482</t>
         </is>
       </c>
-      <c r="G12" s="50" t="inlineStr">
+      <c r="G12" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H12" s="48" t="inlineStr">
+      <c r="H12" s="104" t="inlineStr">
         <is>
           <t>v_bat24_mv≈22352mV ±9mV. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I12" s="48" t="inlineStr">
+      <c r="I12" s="104" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J12" s="51" t="n"/>
-      <c r="K12" s="52" t="inlineStr">
+      <c r="J12" s="107" t="n"/>
+      <c r="K12" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="53" t="n"/>
-      <c r="M12" s="48" t="n"/>
-      <c r="N12" s="48" t="inlineStr">
+      <c r="L12" s="109" t="n"/>
+      <c r="M12" s="104" t="n"/>
+      <c r="N12" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O12" s="50" t="n"/>
-      <c r="P12" s="50" t="n"/>
-      <c r="Q12" s="54">
+      <c r="O12" s="106" t="n"/>
+      <c r="P12" s="106" t="n"/>
+      <c r="Q12" s="110">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>MS-010</t>
         </is>
       </c>
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="111" t="inlineStr">
         <is>
           <t>بررسی v_bat12_mv</t>
         </is>
       </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E13" s="55" t="inlineStr">
+      <c r="E13" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال باتری 12 ولت counts=2482 بده (2 ولت روی پایه).
@@ -2911,68 +4183,68 @@
 گام ۴: باید حدود 12058 میلی‌ولت باشد (2 ضربدر 41000 تقسیم بر 6800) با خطای حداکثر ±5 میلی‌ولت.</t>
         </is>
       </c>
-      <c r="F13" s="58" t="inlineStr">
+      <c r="F13" s="113" t="inlineStr">
         <is>
           <t>counts 2482</t>
         </is>
       </c>
-      <c r="G13" s="58" t="inlineStr">
+      <c r="G13" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H13" s="55" t="inlineStr">
+      <c r="H13" s="111" t="inlineStr">
         <is>
           <t>v_bat12_mv≈12058mV ±5mV. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I13" s="55" t="inlineStr">
+      <c r="I13" s="111" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V12. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J13" s="55" t="n"/>
-      <c r="K13" s="55" t="inlineStr">
+      <c r="J13" s="111" t="n"/>
+      <c r="K13" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="59" t="n"/>
-      <c r="M13" s="55" t="n"/>
-      <c r="N13" s="55" t="inlineStr">
+      <c r="L13" s="114" t="n"/>
+      <c r="M13" s="111" t="n"/>
+      <c r="N13" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O13" s="58" t="n"/>
-      <c r="P13" s="58" t="n"/>
-      <c r="Q13" s="60">
+      <c r="O13" s="113" t="n"/>
+      <c r="P13" s="113" t="n"/>
+      <c r="Q13" s="115">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="103" t="inlineStr">
         <is>
           <t>MS-011</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="104" t="inlineStr">
         <is>
           <t>بررسی current1</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="48" t="inlineStr">
+      <c r="D14" s="104" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E14" s="48" t="inlineStr">
+      <c r="E14" s="104" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
@@ -2980,68 +4252,68 @@
 گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
         </is>
       </c>
-      <c r="F14" s="50" t="inlineStr">
+      <c r="F14" s="106" t="inlineStr">
         <is>
           <t>counts 610 (0.49V)</t>
         </is>
       </c>
-      <c r="G14" s="50" t="inlineStr">
+      <c r="G14" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H14" s="48" t="inlineStr">
+      <c r="H14" s="104" t="inlineStr">
         <is>
           <t>i_ch1≈ counts*3300*1000/(4095*101*10) ≈ 486mA ±1mA. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I14" s="48" t="inlineStr">
+      <c r="I14" s="104" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول جریان. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J14" s="51" t="n"/>
-      <c r="K14" s="52" t="inlineStr">
+      <c r="J14" s="107" t="n"/>
+      <c r="K14" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="53" t="n"/>
-      <c r="M14" s="48" t="n"/>
-      <c r="N14" s="48" t="inlineStr">
+      <c r="L14" s="109" t="n"/>
+      <c r="M14" s="104" t="n"/>
+      <c r="N14" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O14" s="50" t="n"/>
-      <c r="P14" s="50" t="n"/>
-      <c r="Q14" s="54">
+      <c r="O14" s="106" t="n"/>
+      <c r="P14" s="106" t="n"/>
+      <c r="Q14" s="110">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="103" t="inlineStr">
         <is>
           <t>MS-012</t>
         </is>
       </c>
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="111" t="inlineStr">
         <is>
           <t>بررسی current2</t>
         </is>
       </c>
-      <c r="C15" s="56" t="inlineStr">
+      <c r="C15" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="55" t="inlineStr">
+      <c r="D15" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E15" s="55" t="inlineStr">
+      <c r="E15" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال جریان شارژ ۲ counts=1220 بده (حدود 0.98 ولت روی پایه).
@@ -3049,68 +4321,68 @@
 گام ۴: باید حدود 973 میلی‌آمپر باشد با خطای حداکثر ±1 میلی‌آمپر؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F15" s="58" t="inlineStr">
+      <c r="F15" s="113" t="inlineStr">
         <is>
           <t>counts 1220</t>
         </is>
       </c>
-      <c r="G15" s="58" t="inlineStr">
+      <c r="G15" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H15" s="55" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>i_ch2≈ 973mA ±1mA. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I15" s="55" t="inlineStr">
+      <c r="I15" s="111" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J15" s="55" t="n"/>
-      <c r="K15" s="55" t="inlineStr">
+      <c r="J15" s="111" t="n"/>
+      <c r="K15" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="59" t="n"/>
-      <c r="M15" s="55" t="n"/>
-      <c r="N15" s="55" t="inlineStr">
+      <c r="L15" s="114" t="n"/>
+      <c r="M15" s="111" t="n"/>
+      <c r="N15" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O15" s="58" t="n"/>
-      <c r="P15" s="58" t="n"/>
-      <c r="Q15" s="60">
+      <c r="O15" s="113" t="n"/>
+      <c r="P15" s="113" t="n"/>
+      <c r="Q15" s="115">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="103" t="inlineStr">
         <is>
           <t>MS-017</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="104" t="inlineStr">
         <is>
           <t>دوره 10ms تسک Measurement</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="D16" s="104" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E16" s="48" t="inlineStr">
+      <c r="E16" s="104" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
@@ -3118,68 +4390,68 @@
 گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="F16" s="106" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="50" t="inlineStr">
+      <c r="G16" s="106" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H16" s="48" t="inlineStr">
+      <c r="H16" s="104" t="inlineStr">
         <is>
           <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
         </is>
       </c>
-      <c r="I16" s="48" t="inlineStr">
+      <c r="I16" s="104" t="inlineStr">
         <is>
           <t>PASS: 10ms period. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J16" s="51" t="n"/>
-      <c r="K16" s="52" t="inlineStr">
+      <c r="J16" s="107" t="n"/>
+      <c r="K16" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="53" t="n"/>
-      <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="inlineStr">
+      <c r="L16" s="109" t="n"/>
+      <c r="M16" s="104" t="n"/>
+      <c r="N16" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O16" s="50" t="n"/>
-      <c r="P16" s="50" t="n"/>
-      <c r="Q16" s="54">
+      <c r="O16" s="106" t="n"/>
+      <c r="P16" s="106" t="n"/>
+      <c r="Q16" s="110">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>MS-019</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="104" t="inlineStr">
         <is>
           <t>تطبیق فرمول و کالیبراسیون / صفر</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="48" t="inlineStr">
+      <c r="D17" s="104" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E17" s="48" t="inlineStr">
+      <c r="E17" s="104" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=0 بده.
@@ -3187,68 +4459,68 @@
 گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="50" t="inlineStr">
+      <c r="F17" s="106" t="inlineStr">
         <is>
           <t>counts 0</t>
         </is>
       </c>
-      <c r="G17" s="50" t="inlineStr">
+      <c r="G17" s="106" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="H17" s="104" t="inlineStr">
         <is>
           <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="I17" s="48" t="inlineStr">
+      <c r="I17" s="104" t="inlineStr">
         <is>
           <t>PASS: zero. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="J17" s="51" t="n"/>
-      <c r="K17" s="52" t="inlineStr">
+      <c r="J17" s="107" t="n"/>
+      <c r="K17" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="53" t="n"/>
-      <c r="M17" s="48" t="n"/>
-      <c r="N17" s="48" t="inlineStr">
+      <c r="L17" s="109" t="n"/>
+      <c r="M17" s="104" t="n"/>
+      <c r="N17" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O17" s="50" t="n"/>
-      <c r="P17" s="50" t="n"/>
-      <c r="Q17" s="54">
+      <c r="O17" s="106" t="n"/>
+      <c r="P17" s="106" t="n"/>
+      <c r="Q17" s="110">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="A18" s="103" t="inlineStr">
         <is>
           <t>MS-020</t>
         </is>
       </c>
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="111" t="inlineStr">
         <is>
           <t>تطبیق فرمول / فول</t>
         </is>
       </c>
-      <c r="C18" s="56" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
@@ -3256,162 +4528,482 @@
 گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
-      <c r="F18" s="58" t="inlineStr">
+      <c r="F18" s="113" t="inlineStr">
         <is>
           <t>counts 4095 (فول)</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
+      <c r="G18" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="H18" s="111" t="inlineStr">
         <is>
           <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I18" s="111" t="inlineStr">
         <is>
           <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J18" s="55" t="n"/>
-      <c r="K18" s="55" t="inlineStr">
+      <c r="J18" s="111" t="n"/>
+      <c r="K18" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="59" t="n"/>
-      <c r="M18" s="55" t="n"/>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="L18" s="114" t="n"/>
+      <c r="M18" s="111" t="n"/>
+      <c r="N18" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O18" s="58" t="n"/>
-      <c r="P18" s="58" t="n"/>
-      <c r="Q18" s="60">
+      <c r="O18" s="113" t="n"/>
+      <c r="P18" s="113" t="n"/>
+      <c r="Q18" s="115">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="63">
+      <c r="A19" s="85" t="n"/>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="85" t="n"/>
+      <c r="D19" s="85" t="n"/>
+      <c r="E19" s="85" t="n"/>
+      <c r="F19" s="85" t="n"/>
+      <c r="G19" s="85" t="n"/>
+      <c r="H19" s="85" t="n"/>
+      <c r="I19" s="85" t="n"/>
+      <c r="J19" s="85" t="n"/>
+      <c r="K19" s="85" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
+      <c r="N19" s="85" t="n"/>
+      <c r="O19" s="85" t="n"/>
+      <c r="P19" s="85" t="n"/>
+      <c r="Q19" s="116">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="63">
+      <c r="A20" s="85" t="n"/>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="n"/>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="116">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="63">
+      <c r="A21" s="85" t="n"/>
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="85" t="n"/>
+      <c r="D21" s="85" t="n"/>
+      <c r="E21" s="85" t="n"/>
+      <c r="F21" s="85" t="n"/>
+      <c r="G21" s="85" t="n"/>
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
+      <c r="J21" s="85" t="n"/>
+      <c r="K21" s="85" t="n"/>
+      <c r="L21" s="85" t="n"/>
+      <c r="M21" s="85" t="n"/>
+      <c r="N21" s="85" t="n"/>
+      <c r="O21" s="85" t="n"/>
+      <c r="P21" s="85" t="n"/>
+      <c r="Q21" s="116">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="63">
+      <c r="A22" s="85" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="85" t="n"/>
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="116">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="63">
+      <c r="A23" s="85" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="85" t="n"/>
+      <c r="D23" s="85" t="n"/>
+      <c r="E23" s="85" t="n"/>
+      <c r="F23" s="85" t="n"/>
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+      <c r="P23" s="85" t="n"/>
+      <c r="Q23" s="116">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="63">
+      <c r="A24" s="85" t="n"/>
+      <c r="B24" s="85" t="n"/>
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="85" t="n"/>
+      <c r="E24" s="85" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="116">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="63">
+      <c r="A25" s="85" t="n"/>
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="85" t="n"/>
+      <c r="E25" s="85" t="n"/>
+      <c r="F25" s="85" t="n"/>
+      <c r="G25" s="85" t="n"/>
+      <c r="H25" s="85" t="n"/>
+      <c r="I25" s="85" t="n"/>
+      <c r="J25" s="85" t="n"/>
+      <c r="K25" s="85" t="n"/>
+      <c r="L25" s="85" t="n"/>
+      <c r="M25" s="85" t="n"/>
+      <c r="N25" s="85" t="n"/>
+      <c r="O25" s="85" t="n"/>
+      <c r="P25" s="85" t="n"/>
+      <c r="Q25" s="116">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="63">
+      <c r="A26" s="85" t="n"/>
+      <c r="B26" s="85" t="n"/>
+      <c r="C26" s="85" t="n"/>
+      <c r="D26" s="85" t="n"/>
+      <c r="E26" s="85" t="n"/>
+      <c r="F26" s="85" t="n"/>
+      <c r="G26" s="85" t="n"/>
+      <c r="H26" s="85" t="n"/>
+      <c r="I26" s="85" t="n"/>
+      <c r="J26" s="85" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="116">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="63">
+      <c r="A27" s="85" t="n"/>
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="85" t="n"/>
+      <c r="D27" s="85" t="n"/>
+      <c r="E27" s="85" t="n"/>
+      <c r="F27" s="85" t="n"/>
+      <c r="G27" s="85" t="n"/>
+      <c r="H27" s="85" t="n"/>
+      <c r="I27" s="85" t="n"/>
+      <c r="J27" s="85" t="n"/>
+      <c r="K27" s="85" t="n"/>
+      <c r="L27" s="85" t="n"/>
+      <c r="M27" s="85" t="n"/>
+      <c r="N27" s="85" t="n"/>
+      <c r="O27" s="85" t="n"/>
+      <c r="P27" s="85" t="n"/>
+      <c r="Q27" s="116">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="63">
+      <c r="A28" s="85" t="n"/>
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="85" t="n"/>
+      <c r="D28" s="85" t="n"/>
+      <c r="E28" s="85" t="n"/>
+      <c r="F28" s="85" t="n"/>
+      <c r="G28" s="85" t="n"/>
+      <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
+      <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="116">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="63">
+      <c r="A29" s="85" t="n"/>
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="85" t="n"/>
+      <c r="D29" s="85" t="n"/>
+      <c r="E29" s="85" t="n"/>
+      <c r="F29" s="85" t="n"/>
+      <c r="G29" s="85" t="n"/>
+      <c r="H29" s="85" t="n"/>
+      <c r="I29" s="85" t="n"/>
+      <c r="J29" s="85" t="n"/>
+      <c r="K29" s="85" t="n"/>
+      <c r="L29" s="85" t="n"/>
+      <c r="M29" s="85" t="n"/>
+      <c r="N29" s="85" t="n"/>
+      <c r="O29" s="85" t="n"/>
+      <c r="P29" s="85" t="n"/>
+      <c r="Q29" s="116">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="63">
+      <c r="A30" s="85" t="n"/>
+      <c r="B30" s="85" t="n"/>
+      <c r="C30" s="85" t="n"/>
+      <c r="D30" s="85" t="n"/>
+      <c r="E30" s="85" t="n"/>
+      <c r="F30" s="85" t="n"/>
+      <c r="G30" s="85" t="n"/>
+      <c r="H30" s="85" t="n"/>
+      <c r="I30" s="85" t="n"/>
+      <c r="J30" s="85" t="n"/>
+      <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
+      <c r="O30" s="85" t="n"/>
+      <c r="P30" s="85" t="n"/>
+      <c r="Q30" s="116">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="63">
+      <c r="A31" s="85" t="n"/>
+      <c r="B31" s="85" t="n"/>
+      <c r="C31" s="85" t="n"/>
+      <c r="D31" s="85" t="n"/>
+      <c r="E31" s="85" t="n"/>
+      <c r="F31" s="85" t="n"/>
+      <c r="G31" s="85" t="n"/>
+      <c r="H31" s="85" t="n"/>
+      <c r="I31" s="85" t="n"/>
+      <c r="J31" s="85" t="n"/>
+      <c r="K31" s="85" t="n"/>
+      <c r="L31" s="85" t="n"/>
+      <c r="M31" s="85" t="n"/>
+      <c r="N31" s="85" t="n"/>
+      <c r="O31" s="85" t="n"/>
+      <c r="P31" s="85" t="n"/>
+      <c r="Q31" s="116">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="63">
+      <c r="A32" s="85" t="n"/>
+      <c r="B32" s="85" t="n"/>
+      <c r="C32" s="85" t="n"/>
+      <c r="D32" s="85" t="n"/>
+      <c r="E32" s="85" t="n"/>
+      <c r="F32" s="85" t="n"/>
+      <c r="G32" s="85" t="n"/>
+      <c r="H32" s="85" t="n"/>
+      <c r="I32" s="85" t="n"/>
+      <c r="J32" s="85" t="n"/>
+      <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="116">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="63">
+      <c r="A33" s="85" t="n"/>
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="85" t="n"/>
+      <c r="D33" s="85" t="n"/>
+      <c r="E33" s="85" t="n"/>
+      <c r="F33" s="85" t="n"/>
+      <c r="G33" s="85" t="n"/>
+      <c r="H33" s="85" t="n"/>
+      <c r="I33" s="85" t="n"/>
+      <c r="J33" s="85" t="n"/>
+      <c r="K33" s="85" t="n"/>
+      <c r="L33" s="85" t="n"/>
+      <c r="M33" s="85" t="n"/>
+      <c r="N33" s="85" t="n"/>
+      <c r="O33" s="85" t="n"/>
+      <c r="P33" s="85" t="n"/>
+      <c r="Q33" s="116">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="63">
+      <c r="A34" s="85" t="n"/>
+      <c r="B34" s="85" t="n"/>
+      <c r="C34" s="85" t="n"/>
+      <c r="D34" s="85" t="n"/>
+      <c r="E34" s="85" t="n"/>
+      <c r="F34" s="85" t="n"/>
+      <c r="G34" s="85" t="n"/>
+      <c r="H34" s="85" t="n"/>
+      <c r="I34" s="85" t="n"/>
+      <c r="J34" s="85" t="n"/>
+      <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
+      <c r="O34" s="85" t="n"/>
+      <c r="P34" s="85" t="n"/>
+      <c r="Q34" s="116">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="63">
+      <c r="A35" s="85" t="n"/>
+      <c r="B35" s="85" t="n"/>
+      <c r="C35" s="85" t="n"/>
+      <c r="D35" s="85" t="n"/>
+      <c r="E35" s="85" t="n"/>
+      <c r="F35" s="85" t="n"/>
+      <c r="G35" s="85" t="n"/>
+      <c r="H35" s="85" t="n"/>
+      <c r="I35" s="85" t="n"/>
+      <c r="J35" s="85" t="n"/>
+      <c r="K35" s="85" t="n"/>
+      <c r="L35" s="85" t="n"/>
+      <c r="M35" s="85" t="n"/>
+      <c r="N35" s="85" t="n"/>
+      <c r="O35" s="85" t="n"/>
+      <c r="P35" s="85" t="n"/>
+      <c r="Q35" s="116">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="63">
+      <c r="A36" s="85" t="n"/>
+      <c r="B36" s="85" t="n"/>
+      <c r="C36" s="85" t="n"/>
+      <c r="D36" s="85" t="n"/>
+      <c r="E36" s="85" t="n"/>
+      <c r="F36" s="85" t="n"/>
+      <c r="G36" s="85" t="n"/>
+      <c r="H36" s="85" t="n"/>
+      <c r="I36" s="85" t="n"/>
+      <c r="J36" s="85" t="n"/>
+      <c r="K36" s="85" t="n"/>
+      <c r="L36" s="85" t="n"/>
+      <c r="M36" s="85" t="n"/>
+      <c r="N36" s="85" t="n"/>
+      <c r="O36" s="85" t="n"/>
+      <c r="P36" s="85" t="n"/>
+      <c r="Q36" s="116">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="63">
+      <c r="A37" s="85" t="n"/>
+      <c r="B37" s="85" t="n"/>
+      <c r="C37" s="85" t="n"/>
+      <c r="D37" s="85" t="n"/>
+      <c r="E37" s="85" t="n"/>
+      <c r="F37" s="85" t="n"/>
+      <c r="G37" s="85" t="n"/>
+      <c r="H37" s="85" t="n"/>
+      <c r="I37" s="85" t="n"/>
+      <c r="J37" s="85" t="n"/>
+      <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
+      <c r="O37" s="85" t="n"/>
+      <c r="P37" s="85" t="n"/>
+      <c r="Q37" s="116">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="63">
+      <c r="A38" s="85" t="n"/>
+      <c r="B38" s="85" t="n"/>
+      <c r="C38" s="85" t="n"/>
+      <c r="D38" s="85" t="n"/>
+      <c r="E38" s="85" t="n"/>
+      <c r="F38" s="85" t="n"/>
+      <c r="G38" s="85" t="n"/>
+      <c r="H38" s="85" t="n"/>
+      <c r="I38" s="85" t="n"/>
+      <c r="J38" s="85" t="n"/>
+      <c r="K38" s="85" t="n"/>
+      <c r="L38" s="85" t="n"/>
+      <c r="M38" s="85" t="n"/>
+      <c r="N38" s="85" t="n"/>
+      <c r="O38" s="85" t="n"/>
+      <c r="P38" s="85" t="n"/>
+      <c r="Q38" s="116">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
@@ -3468,193 +5060,243 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
+      <c r="G1" s="85" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
+      <c r="O1" s="85" t="n"/>
+      <c r="P1" s="85" t="n"/>
+      <c r="Q1" s="85" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="81" t="inlineStr">
+      <c r="A2" s="85" t="n"/>
+      <c r="B2" s="119" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
+      <c r="G2" s="85" t="n"/>
+      <c r="H2" s="85" t="n"/>
+      <c r="I2" s="85" t="n"/>
+      <c r="J2" s="85" t="n"/>
+      <c r="K2" s="85" t="n"/>
+      <c r="L2" s="85" t="n"/>
+      <c r="M2" s="85" t="n"/>
+      <c r="N2" s="85" t="n"/>
+      <c r="O2" s="85" t="n"/>
+      <c r="P2" s="85" t="n"/>
+      <c r="Q2" s="85" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="85" t="n"/>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="85" t="n"/>
+      <c r="E3" s="85" t="n"/>
+      <c r="F3" s="85" t="n"/>
+      <c r="G3" s="85" t="n"/>
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="85" t="n"/>
+      <c r="J3" s="85" t="n"/>
+      <c r="K3" s="85" t="n"/>
+      <c r="L3" s="85" t="n"/>
+      <c r="M3" s="85" t="n"/>
+      <c r="N3" s="85" t="n"/>
+      <c r="O3" s="85" t="n"/>
+      <c r="P3" s="85" t="n"/>
+      <c r="Q3" s="85" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="87" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="87" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="87" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="87" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="87" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="87" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="87" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="87" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="87" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="87" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="87" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="87" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="87" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="87" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="n"/>
+      <c r="Q4" s="87" t="n"/>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>MS-015</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="104" t="inlineStr">
         <is>
           <t>NULL در GetSnapshot</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
 گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
 گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="106" t="inlineStr">
         <is>
           <t>NULL pointer</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="106" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="104" t="inlineStr">
         <is>
           <t>return false، بدون کرش، snapshot تغییر نکند. PASS: false. FAIL: کرش یا true.</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="104" t="inlineStr">
         <is>
           <t>PASS: NULL → false. FAIL: true/crash.</t>
         </is>
       </c>
-      <c r="J5" s="51" t="n"/>
-      <c r="K5" s="52" t="inlineStr">
+      <c r="J5" s="107" t="n"/>
+      <c r="K5" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="48" t="n"/>
-      <c r="N5" s="48" t="inlineStr">
+      <c r="L5" s="109" t="n"/>
+      <c r="M5" s="104" t="n"/>
+      <c r="N5" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="50" t="n"/>
-      <c r="P5" s="50" t="n"/>
-      <c r="Q5" s="54">
+      <c r="O5" s="106" t="n"/>
+      <c r="P5" s="106" t="n"/>
+      <c r="Q5" s="110">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="103" t="inlineStr">
         <is>
           <t>MS-016</t>
         </is>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
         <is>
           <t>Snapshot چندفیلدی اتمیک</t>
         </is>
       </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
+      <c r="D6" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E6" s="55" t="inlineStr">
+      <c r="E6" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
 گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
@@ -3662,68 +5304,68 @@
 گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="113" t="inlineStr">
         <is>
           <t>concurrent read</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="113" t="inlineStr">
         <is>
           <t>20ms</t>
         </is>
       </c>
-      <c r="H6" s="55" t="inlineStr">
+      <c r="H6" s="111" t="inlineStr">
         <is>
           <t>هر دو snapshot کپی‌شده باید یا کامل قدیمی یا کامل جدید باشد، نه ترکیبی. با osKernelLock تضمین. PASS: atomic. FAIL: torn read.</t>
         </is>
       </c>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="111" t="inlineStr">
         <is>
           <t>PASS: no torn data. FAIL: partial.</t>
         </is>
       </c>
-      <c r="J6" s="55" t="n"/>
-      <c r="K6" s="55" t="inlineStr">
+      <c r="J6" s="111" t="n"/>
+      <c r="K6" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="59" t="n"/>
-      <c r="M6" s="55" t="n"/>
-      <c r="N6" s="55" t="inlineStr">
+      <c r="L6" s="114" t="n"/>
+      <c r="M6" s="111" t="n"/>
+      <c r="N6" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="58" t="n"/>
-      <c r="P6" s="58" t="n"/>
-      <c r="Q6" s="60">
+      <c r="O6" s="113" t="n"/>
+      <c r="P6" s="113" t="n"/>
+      <c r="Q6" s="115">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>MS-018</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="111" t="inlineStr">
         <is>
           <t>DMA frame کامل</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="55" t="inlineStr">
+      <c r="D7" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E7" s="55" t="inlineStr">
+      <c r="E7" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: شمارندهٔ DMA (یعنی CNDTR) را قبل و بعد از کپی بخوان؛ DMA دو فریمی است (2 ضربدر 5).
@@ -3731,68 +5373,68 @@
 گام ۴: GetRaw باید پنجرهٔ پایدار (stable=true) بدهد؛ کپی پاره یا تمام شدن retry یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="58" t="inlineStr">
+      <c r="F7" s="113" t="inlineStr">
         <is>
           <t>DMA CNDTR</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H7" s="55" t="inlineStr">
+      <c r="H7" s="111" t="inlineStr">
         <is>
           <t>GetRaw باید stable window true بدهد و 5 نمونه valid. PASS: stable copy. FAIL: torn یا retry exceed.</t>
         </is>
       </c>
-      <c r="I7" s="55" t="inlineStr">
+      <c r="I7" s="111" t="inlineStr">
         <is>
           <t>PASS: stable frame. FAIL: unstable.</t>
         </is>
       </c>
-      <c r="J7" s="55" t="n"/>
-      <c r="K7" s="55" t="inlineStr">
+      <c r="J7" s="111" t="n"/>
+      <c r="K7" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="59" t="n"/>
-      <c r="M7" s="55" t="n"/>
-      <c r="N7" s="55" t="inlineStr">
+      <c r="L7" s="114" t="n"/>
+      <c r="M7" s="111" t="n"/>
+      <c r="N7" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="58" t="n"/>
-      <c r="P7" s="58" t="n"/>
-      <c r="Q7" s="60">
+      <c r="O7" s="113" t="n"/>
+      <c r="P7" s="113" t="n"/>
+      <c r="Q7" s="115">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="103" t="inlineStr">
         <is>
           <t>ME-022</t>
         </is>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
         <is>
           <t>snapshot zeroing مصرف‌کننده</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="55" t="inlineStr">
+      <c r="D8" s="111" t="inlineStr">
         <is>
           <t>Measurement خاموش</t>
         </is>
       </c>
-      <c r="E8" s="55" t="inlineStr">
+      <c r="E8" s="111" t="inlineStr">
         <is>
           <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
 گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
@@ -3800,167 +5442,487 @@
 گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
         </is>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="F8" s="113" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="58" t="inlineStr">
+      <c r="G8" s="113" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H8" s="55" t="inlineStr">
+      <c r="H8" s="111" t="inlineStr">
         <is>
           <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
         </is>
       </c>
-      <c r="I8" s="55" t="inlineStr">
+      <c r="I8" s="111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="55" t="inlineStr">
+      <c r="J8" s="111" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
       </c>
-      <c r="K8" s="55" t="n"/>
-      <c r="L8" s="62" t="inlineStr">
+      <c r="K8" s="111" t="n"/>
+      <c r="L8" s="122" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M8" s="55" t="n"/>
-      <c r="N8" s="55" t="n"/>
-      <c r="O8" s="58" t="inlineStr">
+      <c r="M8" s="111" t="n"/>
+      <c r="N8" s="111" t="n"/>
+      <c r="O8" s="113" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P8" s="58" t="n"/>
-      <c r="Q8" s="60" t="inlineStr">
+      <c r="P8" s="113" t="n"/>
+      <c r="Q8" s="115" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="63">
+      <c r="A9" s="85" t="n"/>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="85" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="85" t="n"/>
+      <c r="F9" s="85" t="n"/>
+      <c r="G9" s="85" t="n"/>
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="85" t="n"/>
+      <c r="J9" s="85" t="n"/>
+      <c r="K9" s="85" t="n"/>
+      <c r="L9" s="85" t="n"/>
+      <c r="M9" s="85" t="n"/>
+      <c r="N9" s="85" t="n"/>
+      <c r="O9" s="85" t="n"/>
+      <c r="P9" s="85" t="n"/>
+      <c r="Q9" s="116">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="63">
+      <c r="A10" s="85" t="n"/>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="85" t="n"/>
+      <c r="D10" s="85" t="n"/>
+      <c r="E10" s="85" t="n"/>
+      <c r="F10" s="85" t="n"/>
+      <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
+      <c r="Q10" s="116">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="63">
+      <c r="A11" s="85" t="n"/>
+      <c r="B11" s="85" t="n"/>
+      <c r="C11" s="85" t="n"/>
+      <c r="D11" s="85" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="85" t="n"/>
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+      <c r="K11" s="85" t="n"/>
+      <c r="L11" s="85" t="n"/>
+      <c r="M11" s="85" t="n"/>
+      <c r="N11" s="85" t="n"/>
+      <c r="O11" s="85" t="n"/>
+      <c r="P11" s="85" t="n"/>
+      <c r="Q11" s="116">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="63">
+      <c r="A12" s="85" t="n"/>
+      <c r="B12" s="85" t="n"/>
+      <c r="C12" s="85" t="n"/>
+      <c r="D12" s="85" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="85" t="n"/>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
+      <c r="Q12" s="116">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="63">
+      <c r="A13" s="85" t="n"/>
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="85" t="n"/>
+      <c r="D13" s="85" t="n"/>
+      <c r="E13" s="85" t="n"/>
+      <c r="F13" s="85" t="n"/>
+      <c r="G13" s="85" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+      <c r="K13" s="85" t="n"/>
+      <c r="L13" s="85" t="n"/>
+      <c r="M13" s="85" t="n"/>
+      <c r="N13" s="85" t="n"/>
+      <c r="O13" s="85" t="n"/>
+      <c r="P13" s="85" t="n"/>
+      <c r="Q13" s="116">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="63">
+      <c r="A14" s="85" t="n"/>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="85" t="n"/>
+      <c r="D14" s="85" t="n"/>
+      <c r="E14" s="85" t="n"/>
+      <c r="F14" s="85" t="n"/>
+      <c r="G14" s="85" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
+      <c r="Q14" s="116">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="63">
+      <c r="A15" s="85" t="n"/>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="85" t="n"/>
+      <c r="D15" s="85" t="n"/>
+      <c r="E15" s="85" t="n"/>
+      <c r="F15" s="85" t="n"/>
+      <c r="G15" s="85" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
+      <c r="L15" s="85" t="n"/>
+      <c r="M15" s="85" t="n"/>
+      <c r="N15" s="85" t="n"/>
+      <c r="O15" s="85" t="n"/>
+      <c r="P15" s="85" t="n"/>
+      <c r="Q15" s="116">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="63">
+      <c r="A16" s="85" t="n"/>
+      <c r="B16" s="85" t="n"/>
+      <c r="C16" s="85" t="n"/>
+      <c r="D16" s="85" t="n"/>
+      <c r="E16" s="85" t="n"/>
+      <c r="F16" s="85" t="n"/>
+      <c r="G16" s="85" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
+      <c r="Q16" s="116">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="63">
+      <c r="A17" s="85" t="n"/>
+      <c r="B17" s="85" t="n"/>
+      <c r="C17" s="85" t="n"/>
+      <c r="D17" s="85" t="n"/>
+      <c r="E17" s="85" t="n"/>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="85" t="n"/>
+      <c r="H17" s="85" t="n"/>
+      <c r="I17" s="85" t="n"/>
+      <c r="J17" s="85" t="n"/>
+      <c r="K17" s="85" t="n"/>
+      <c r="L17" s="85" t="n"/>
+      <c r="M17" s="85" t="n"/>
+      <c r="N17" s="85" t="n"/>
+      <c r="O17" s="85" t="n"/>
+      <c r="P17" s="85" t="n"/>
+      <c r="Q17" s="116">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="63">
+      <c r="A18" s="85" t="n"/>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="85" t="n"/>
+      <c r="D18" s="85" t="n"/>
+      <c r="E18" s="85" t="n"/>
+      <c r="F18" s="85" t="n"/>
+      <c r="G18" s="85" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
+      <c r="Q18" s="116">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="63">
+      <c r="A19" s="85" t="n"/>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="85" t="n"/>
+      <c r="D19" s="85" t="n"/>
+      <c r="E19" s="85" t="n"/>
+      <c r="F19" s="85" t="n"/>
+      <c r="G19" s="85" t="n"/>
+      <c r="H19" s="85" t="n"/>
+      <c r="I19" s="85" t="n"/>
+      <c r="J19" s="85" t="n"/>
+      <c r="K19" s="85" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
+      <c r="N19" s="85" t="n"/>
+      <c r="O19" s="85" t="n"/>
+      <c r="P19" s="85" t="n"/>
+      <c r="Q19" s="116">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="63">
+      <c r="A20" s="85" t="n"/>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="n"/>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="116">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="63">
+      <c r="A21" s="85" t="n"/>
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="85" t="n"/>
+      <c r="D21" s="85" t="n"/>
+      <c r="E21" s="85" t="n"/>
+      <c r="F21" s="85" t="n"/>
+      <c r="G21" s="85" t="n"/>
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
+      <c r="J21" s="85" t="n"/>
+      <c r="K21" s="85" t="n"/>
+      <c r="L21" s="85" t="n"/>
+      <c r="M21" s="85" t="n"/>
+      <c r="N21" s="85" t="n"/>
+      <c r="O21" s="85" t="n"/>
+      <c r="P21" s="85" t="n"/>
+      <c r="Q21" s="116">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="63">
+      <c r="A22" s="85" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="85" t="n"/>
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="116">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="63">
+      <c r="A23" s="85" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="85" t="n"/>
+      <c r="D23" s="85" t="n"/>
+      <c r="E23" s="85" t="n"/>
+      <c r="F23" s="85" t="n"/>
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+      <c r="P23" s="85" t="n"/>
+      <c r="Q23" s="116">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="63">
+      <c r="A24" s="85" t="n"/>
+      <c r="B24" s="85" t="n"/>
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="85" t="n"/>
+      <c r="E24" s="85" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="116">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="63">
+      <c r="A25" s="85" t="n"/>
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="85" t="n"/>
+      <c r="E25" s="85" t="n"/>
+      <c r="F25" s="85" t="n"/>
+      <c r="G25" s="85" t="n"/>
+      <c r="H25" s="85" t="n"/>
+      <c r="I25" s="85" t="n"/>
+      <c r="J25" s="85" t="n"/>
+      <c r="K25" s="85" t="n"/>
+      <c r="L25" s="85" t="n"/>
+      <c r="M25" s="85" t="n"/>
+      <c r="N25" s="85" t="n"/>
+      <c r="O25" s="85" t="n"/>
+      <c r="P25" s="85" t="n"/>
+      <c r="Q25" s="116">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="63">
+      <c r="A26" s="85" t="n"/>
+      <c r="B26" s="85" t="n"/>
+      <c r="C26" s="85" t="n"/>
+      <c r="D26" s="85" t="n"/>
+      <c r="E26" s="85" t="n"/>
+      <c r="F26" s="85" t="n"/>
+      <c r="G26" s="85" t="n"/>
+      <c r="H26" s="85" t="n"/>
+      <c r="I26" s="85" t="n"/>
+      <c r="J26" s="85" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="116">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="63">
+      <c r="A27" s="85" t="n"/>
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="85" t="n"/>
+      <c r="D27" s="85" t="n"/>
+      <c r="E27" s="85" t="n"/>
+      <c r="F27" s="85" t="n"/>
+      <c r="G27" s="85" t="n"/>
+      <c r="H27" s="85" t="n"/>
+      <c r="I27" s="85" t="n"/>
+      <c r="J27" s="85" t="n"/>
+      <c r="K27" s="85" t="n"/>
+      <c r="L27" s="85" t="n"/>
+      <c r="M27" s="85" t="n"/>
+      <c r="N27" s="85" t="n"/>
+      <c r="O27" s="85" t="n"/>
+      <c r="P27" s="85" t="n"/>
+      <c r="Q27" s="116">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="63">
+      <c r="A28" s="85" t="n"/>
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="85" t="n"/>
+      <c r="D28" s="85" t="n"/>
+      <c r="E28" s="85" t="n"/>
+      <c r="F28" s="85" t="n"/>
+      <c r="G28" s="85" t="n"/>
+      <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
+      <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="116">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
@@ -3996,430 +5958,440 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="123" t="inlineStr">
         <is>
           <t>مرجع Measurement — فرمول‌ها و کالیبراسیون</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="124" t="inlineStr">
         <is>
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="94" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="94" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="94" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="125" t="inlineStr">
         <is>
           <t>Vref و ADC</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="125" t="inlineStr">
         <is>
           <t>Vref 3300mV، 12bit 4095</t>
         </is>
       </c>
-      <c r="C4" s="66" t="inlineStr">
+      <c r="C4" s="125" t="inlineStr">
         <is>
           <t>پایه</t>
         </is>
       </c>
-      <c r="D4" s="66" t="inlineStr">
+      <c r="D4" s="125" t="inlineStr">
         <is>
           <t>BSP_MEASUREMENT_VREF_MV/ADC_FULL_SCALE</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr">
+      <c r="E4" s="125" t="inlineStr">
         <is>
           <t>مرجع STM32F1</t>
         </is>
       </c>
-      <c r="F4" s="67" t="inlineStr">
+      <c r="F4" s="126" t="inlineStr">
         <is>
           <t>MS-019,020</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="125" t="inlineStr">
         <is>
           <t>CountsToMv</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
+      <c r="B5" s="125" t="inlineStr">
         <is>
           <t>counts*3300/4095</t>
         </is>
       </c>
-      <c r="C5" s="66" t="inlineStr">
+      <c r="C5" s="125" t="inlineStr">
         <is>
           <t>ولتاژ پایه ADC</t>
         </is>
       </c>
-      <c r="D5" s="66" t="inlineStr">
+      <c r="D5" s="125" t="inlineStr">
         <is>
           <t>func__BspMeasurement_CountsToMv</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E5" s="125" t="inlineStr">
         <is>
           <t>±0.8mV/LSB</t>
         </is>
       </c>
-      <c r="F5" s="67" t="inlineStr">
+      <c r="F5" s="126" t="inlineStr">
         <is>
           <t>MS-008..012</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="125" t="inlineStr">
         <is>
           <t>V24</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="125" t="inlineStr">
         <is>
           <t>adcPinMv*(69200+6800)/6800</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="125" t="inlineStr">
         <is>
           <t>منبع 24V</t>
         </is>
       </c>
-      <c r="D6" s="66" t="inlineStr">
+      <c r="D6" s="125" t="inlineStr">
         <is>
           <t>DIV24_TOP/BOTTOM</t>
         </is>
       </c>
-      <c r="E6" s="66" t="inlineStr">
+      <c r="E6" s="125" t="inlineStr">
         <is>
           <t>±9mV/LSB</t>
         </is>
       </c>
-      <c r="F6" s="67" t="inlineStr">
+      <c r="F6" s="126" t="inlineStr">
         <is>
           <t>MS-008,009</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="125" t="inlineStr">
         <is>
           <t>V12</t>
         </is>
       </c>
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="125" t="inlineStr">
         <is>
           <t>adcPinMv*(34200+6800)/6800</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C7" s="125" t="inlineStr">
         <is>
           <t>منبع 12V</t>
         </is>
       </c>
-      <c r="D7" s="66" t="inlineStr">
+      <c r="D7" s="125" t="inlineStr">
         <is>
           <t>DIV12_TOP/BOTTOM</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="125" t="inlineStr">
         <is>
           <t>±4.8mV/LSB</t>
         </is>
       </c>
-      <c r="F7" s="67" t="inlineStr">
+      <c r="F7" s="126" t="inlineStr">
         <is>
           <t>MS-010</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="125" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="125" t="inlineStr">
         <is>
           <t>counts*3300*1000/(4095*101*10)</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="125" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D8" s="66" t="inlineStr">
+      <c r="D8" s="125" t="inlineStr">
         <is>
           <t>SHUNT 10mΩ GAIN101</t>
         </is>
       </c>
-      <c r="E8" s="66" t="inlineStr">
+      <c r="E8" s="125" t="inlineStr">
         <is>
           <t>±0.8mA/LSB</t>
         </is>
       </c>
-      <c r="F8" s="67" t="inlineStr">
+      <c r="F8" s="126" t="inlineStr">
         <is>
           <t>MS-011,012</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="125" t="inlineStr">
         <is>
           <t>Warmup</t>
         </is>
       </c>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="125" t="inlineStr">
         <is>
           <t>3 فریم</t>
         </is>
       </c>
-      <c r="C9" s="66" t="inlineStr">
+      <c r="C9" s="125" t="inlineStr">
         <is>
           <t>valid پس از 3</t>
         </is>
       </c>
-      <c r="D9" s="66" t="inlineStr">
+      <c r="D9" s="125" t="inlineStr">
         <is>
           <t>MEASUREMENT_WARMUP_FRAME_COUNT=3</t>
         </is>
       </c>
-      <c r="E9" s="66" t="inlineStr">
+      <c r="E9" s="125" t="inlineStr">
         <is>
           <t>واحد: فریم کامل</t>
         </is>
       </c>
-      <c r="F9" s="67" t="inlineStr">
+      <c r="F9" s="126" t="inlineStr">
         <is>
           <t>MS-002..006</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="125" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="125" t="inlineStr">
         <is>
           <t>GetRaw false → valid false + reset</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C10" s="125" t="inlineStr">
         <is>
           <t xml:space="preserve"> warmup reset</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="126" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E10" s="66" t="inlineStr">
+      <c r="E10" s="125" t="inlineStr">
         <is>
           <t>ناپایدار</t>
         </is>
       </c>
-      <c r="F10" s="67" t="inlineStr">
+      <c r="F10" s="126" t="inlineStr">
         <is>
           <t>MS-005</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="66" t="inlineStr">
+      <c r="A11" s="125" t="inlineStr">
         <is>
           <t>Vin zero</t>
         </is>
       </c>
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="125" t="inlineStr">
         <is>
           <t>Vin 0V still valid</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
+      <c r="C11" s="125" t="inlineStr">
         <is>
           <t>invalid نشود</t>
         </is>
       </c>
-      <c r="D11" s="67" t="inlineStr">
+      <c r="D11" s="126" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E11" s="66" t="inlineStr">
+      <c r="E11" s="125" t="inlineStr">
         <is>
           <t>مستقل از Vin</t>
         </is>
       </c>
-      <c r="F11" s="67" t="inlineStr">
+      <c r="F11" s="126" t="inlineStr">
         <is>
           <t>MS-007</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="A12" s="125" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="125" t="inlineStr">
         <is>
           <t>GetSnapshot NULL → false</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="C12" s="125" t="inlineStr">
         <is>
           <t>بدون کرش</t>
         </is>
       </c>
-      <c r="D12" s="66" t="inlineStr">
+      <c r="D12" s="125" t="inlineStr">
         <is>
           <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
-      <c r="E12" s="66" t="inlineStr">
+      <c r="E12" s="125" t="inlineStr">
         <is>
           <t>بررسی اشاره‌گر</t>
         </is>
       </c>
-      <c r="F12" s="67" t="inlineStr">
+      <c r="F12" s="126" t="inlineStr">
         <is>
           <t>MS-015</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="66" t="inlineStr">
+      <c r="A13" s="125" t="inlineStr">
         <is>
           <t>Atomic</t>
         </is>
       </c>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="B13" s="125" t="inlineStr">
         <is>
           <t>osKernelLock</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
+      <c r="C13" s="125" t="inlineStr">
         <is>
           <t>بدون torn read</t>
         </is>
       </c>
-      <c r="D13" s="67" t="inlineStr">
+      <c r="D13" s="126" t="inlineStr">
         <is>
           <t>measurement.c</t>
         </is>
       </c>
-      <c r="E13" s="66" t="inlineStr">
+      <c r="E13" s="125" t="inlineStr">
         <is>
           <t>CMSIS-RTOS2</t>
         </is>
       </c>
-      <c r="F13" s="67" t="inlineStr">
+      <c r="F13" s="126" t="inlineStr">
         <is>
           <t>MS-016</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="125" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B14" s="66" t="inlineStr">
+      <c r="B14" s="125" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="125" t="inlineStr">
         <is>
           <t>هر 10ms یک Run</t>
         </is>
       </c>
-      <c r="D14" s="66" t="inlineStr">
+      <c r="D14" s="125" t="inlineStr">
         <is>
           <t>MEASUREMENT_PERIOD_MS=10</t>
         </is>
       </c>
-      <c r="E14" s="66" t="inlineStr">
+      <c r="E14" s="125" t="inlineStr">
         <is>
           <t>osDelayUntil</t>
         </is>
       </c>
-      <c r="F14" s="67" t="inlineStr">
+      <c r="F14" s="126" t="inlineStr">
         <is>
           <t>MS-017</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="125" t="inlineStr">
         <is>
           <t>DMA</t>
         </is>
       </c>
-      <c r="B15" s="66" t="inlineStr">
+      <c r="B15" s="125" t="inlineStr">
         <is>
           <t>2×5 halfword circular</t>
         </is>
       </c>
-      <c r="C15" s="66" t="inlineStr">
+      <c r="C15" s="125" t="inlineStr">
         <is>
           <t>CNDTR stable</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="126" t="inlineStr">
         <is>
           <t>bsp_adc.c</t>
         </is>
       </c>
-      <c r="E15" s="66" t="inlineStr">
+      <c r="E15" s="125" t="inlineStr">
         <is>
           <t>2 فریم</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="126" t="inlineStr">
         <is>
           <t>MS-018</t>
         </is>
@@ -4480,247 +6452,259 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="123" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
+      <c r="G1" s="85" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="9" t="n"/>
+      <c r="B2" s="88" t="n"/>
+      <c r="C2" s="88" t="n"/>
+      <c r="D2" s="88" t="n"/>
+      <c r="E2" s="88" t="n"/>
+      <c r="F2" s="88" t="n"/>
+      <c r="G2" s="88" t="n"/>
+      <c r="H2" s="88" t="n"/>
+      <c r="I2" s="88" t="n"/>
+      <c r="J2" s="88" t="n"/>
+      <c r="K2" s="88" t="n"/>
+      <c r="L2" s="88" t="n"/>
+      <c r="M2" s="89" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="94" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="94" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="94" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="41" t="inlineStr">
+      <c r="G3" s="94" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="41" t="inlineStr">
+      <c r="H3" s="94" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="41" t="inlineStr">
+      <c r="I3" s="94" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="41" t="inlineStr">
+      <c r="J3" s="94" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="41" t="inlineStr">
+      <c r="K3" s="94" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="41" t="inlineStr">
+      <c r="L3" s="94" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="41" t="inlineStr">
+      <c r="M3" s="94" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="23" t="inlineStr"/>
-      <c r="B4" s="23" t="inlineStr"/>
-      <c r="C4" s="23" t="inlineStr"/>
-      <c r="D4" s="23" t="inlineStr"/>
-      <c r="E4" s="23" t="inlineStr"/>
-      <c r="F4" s="23" t="inlineStr"/>
-      <c r="G4" s="23" t="inlineStr"/>
-      <c r="H4" s="23" t="inlineStr"/>
-      <c r="I4" s="23" t="inlineStr"/>
-      <c r="J4" s="23" t="inlineStr"/>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="23" t="inlineStr"/>
-      <c r="M4" s="23" t="inlineStr"/>
+      <c r="A4" s="127" t="inlineStr"/>
+      <c r="B4" s="127" t="inlineStr"/>
+      <c r="C4" s="127" t="inlineStr"/>
+      <c r="D4" s="127" t="inlineStr"/>
+      <c r="E4" s="127" t="inlineStr"/>
+      <c r="F4" s="127" t="inlineStr"/>
+      <c r="G4" s="127" t="inlineStr"/>
+      <c r="H4" s="127" t="inlineStr"/>
+      <c r="I4" s="127" t="inlineStr"/>
+      <c r="J4" s="127" t="inlineStr"/>
+      <c r="K4" s="127" t="inlineStr"/>
+      <c r="L4" s="127" t="inlineStr"/>
+      <c r="M4" s="127" t="inlineStr"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="24" t="inlineStr"/>
-      <c r="B5" s="24" t="inlineStr"/>
-      <c r="C5" s="24" t="inlineStr"/>
-      <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="24" t="inlineStr"/>
-      <c r="F5" s="24" t="inlineStr"/>
-      <c r="G5" s="24" t="inlineStr"/>
-      <c r="H5" s="24" t="inlineStr"/>
-      <c r="I5" s="24" t="inlineStr"/>
-      <c r="J5" s="24" t="inlineStr"/>
-      <c r="K5" s="24" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr"/>
-      <c r="M5" s="24" t="inlineStr"/>
+      <c r="A5" s="128" t="inlineStr"/>
+      <c r="B5" s="128" t="inlineStr"/>
+      <c r="C5" s="128" t="inlineStr"/>
+      <c r="D5" s="128" t="inlineStr"/>
+      <c r="E5" s="128" t="inlineStr"/>
+      <c r="F5" s="128" t="inlineStr"/>
+      <c r="G5" s="128" t="inlineStr"/>
+      <c r="H5" s="128" t="inlineStr"/>
+      <c r="I5" s="128" t="inlineStr"/>
+      <c r="J5" s="128" t="inlineStr"/>
+      <c r="K5" s="128" t="inlineStr"/>
+      <c r="L5" s="128" t="inlineStr"/>
+      <c r="M5" s="128" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="23" t="inlineStr"/>
-      <c r="B6" s="23" t="inlineStr"/>
-      <c r="C6" s="23" t="inlineStr"/>
-      <c r="D6" s="23" t="inlineStr"/>
-      <c r="E6" s="23" t="inlineStr"/>
-      <c r="F6" s="23" t="inlineStr"/>
-      <c r="G6" s="23" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr"/>
-      <c r="I6" s="23" t="inlineStr"/>
-      <c r="J6" s="23" t="inlineStr"/>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="23" t="inlineStr"/>
-      <c r="M6" s="23" t="inlineStr"/>
+      <c r="A6" s="127" t="inlineStr"/>
+      <c r="B6" s="127" t="inlineStr"/>
+      <c r="C6" s="127" t="inlineStr"/>
+      <c r="D6" s="127" t="inlineStr"/>
+      <c r="E6" s="127" t="inlineStr"/>
+      <c r="F6" s="127" t="inlineStr"/>
+      <c r="G6" s="127" t="inlineStr"/>
+      <c r="H6" s="127" t="inlineStr"/>
+      <c r="I6" s="127" t="inlineStr"/>
+      <c r="J6" s="127" t="inlineStr"/>
+      <c r="K6" s="127" t="inlineStr"/>
+      <c r="L6" s="127" t="inlineStr"/>
+      <c r="M6" s="127" t="inlineStr"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="24" t="inlineStr"/>
-      <c r="B7" s="24" t="inlineStr"/>
-      <c r="C7" s="24" t="inlineStr"/>
-      <c r="D7" s="24" t="inlineStr"/>
-      <c r="E7" s="24" t="inlineStr"/>
-      <c r="F7" s="24" t="inlineStr"/>
-      <c r="G7" s="24" t="inlineStr"/>
-      <c r="H7" s="24" t="inlineStr"/>
-      <c r="I7" s="24" t="inlineStr"/>
-      <c r="J7" s="24" t="inlineStr"/>
-      <c r="K7" s="24" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr"/>
-      <c r="M7" s="24" t="inlineStr"/>
+      <c r="A7" s="128" t="inlineStr"/>
+      <c r="B7" s="128" t="inlineStr"/>
+      <c r="C7" s="128" t="inlineStr"/>
+      <c r="D7" s="128" t="inlineStr"/>
+      <c r="E7" s="128" t="inlineStr"/>
+      <c r="F7" s="128" t="inlineStr"/>
+      <c r="G7" s="128" t="inlineStr"/>
+      <c r="H7" s="128" t="inlineStr"/>
+      <c r="I7" s="128" t="inlineStr"/>
+      <c r="J7" s="128" t="inlineStr"/>
+      <c r="K7" s="128" t="inlineStr"/>
+      <c r="L7" s="128" t="inlineStr"/>
+      <c r="M7" s="128" t="inlineStr"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="23" t="inlineStr"/>
-      <c r="B8" s="23" t="inlineStr"/>
-      <c r="C8" s="23" t="inlineStr"/>
-      <c r="D8" s="23" t="inlineStr"/>
-      <c r="E8" s="23" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr"/>
-      <c r="G8" s="23" t="inlineStr"/>
-      <c r="H8" s="23" t="inlineStr"/>
-      <c r="I8" s="23" t="inlineStr"/>
-      <c r="J8" s="23" t="inlineStr"/>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="23" t="inlineStr"/>
-      <c r="M8" s="23" t="inlineStr"/>
+      <c r="A8" s="127" t="inlineStr"/>
+      <c r="B8" s="127" t="inlineStr"/>
+      <c r="C8" s="127" t="inlineStr"/>
+      <c r="D8" s="127" t="inlineStr"/>
+      <c r="E8" s="127" t="inlineStr"/>
+      <c r="F8" s="127" t="inlineStr"/>
+      <c r="G8" s="127" t="inlineStr"/>
+      <c r="H8" s="127" t="inlineStr"/>
+      <c r="I8" s="127" t="inlineStr"/>
+      <c r="J8" s="127" t="inlineStr"/>
+      <c r="K8" s="127" t="inlineStr"/>
+      <c r="L8" s="127" t="inlineStr"/>
+      <c r="M8" s="127" t="inlineStr"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="24" t="inlineStr"/>
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr"/>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr"/>
-      <c r="F9" s="24" t="inlineStr"/>
-      <c r="G9" s="24" t="inlineStr"/>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="24" t="inlineStr"/>
-      <c r="J9" s="24" t="inlineStr"/>
-      <c r="K9" s="24" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr"/>
-      <c r="M9" s="24" t="inlineStr"/>
+      <c r="A9" s="128" t="inlineStr"/>
+      <c r="B9" s="128" t="inlineStr"/>
+      <c r="C9" s="128" t="inlineStr"/>
+      <c r="D9" s="128" t="inlineStr"/>
+      <c r="E9" s="128" t="inlineStr"/>
+      <c r="F9" s="128" t="inlineStr"/>
+      <c r="G9" s="128" t="inlineStr"/>
+      <c r="H9" s="128" t="inlineStr"/>
+      <c r="I9" s="128" t="inlineStr"/>
+      <c r="J9" s="128" t="inlineStr"/>
+      <c r="K9" s="128" t="inlineStr"/>
+      <c r="L9" s="128" t="inlineStr"/>
+      <c r="M9" s="128" t="inlineStr"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="23" t="inlineStr"/>
-      <c r="B10" s="23" t="inlineStr"/>
-      <c r="C10" s="23" t="inlineStr"/>
-      <c r="D10" s="23" t="inlineStr"/>
-      <c r="E10" s="23" t="inlineStr"/>
-      <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="23" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr"/>
-      <c r="I10" s="23" t="inlineStr"/>
-      <c r="J10" s="23" t="inlineStr"/>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="23" t="inlineStr"/>
+      <c r="A10" s="127" t="inlineStr"/>
+      <c r="B10" s="127" t="inlineStr"/>
+      <c r="C10" s="127" t="inlineStr"/>
+      <c r="D10" s="127" t="inlineStr"/>
+      <c r="E10" s="127" t="inlineStr"/>
+      <c r="F10" s="127" t="inlineStr"/>
+      <c r="G10" s="127" t="inlineStr"/>
+      <c r="H10" s="127" t="inlineStr"/>
+      <c r="I10" s="127" t="inlineStr"/>
+      <c r="J10" s="127" t="inlineStr"/>
+      <c r="K10" s="127" t="inlineStr"/>
+      <c r="L10" s="127" t="inlineStr"/>
+      <c r="M10" s="127" t="inlineStr"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="24" t="inlineStr"/>
-      <c r="B11" s="24" t="inlineStr"/>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="24" t="inlineStr"/>
-      <c r="F11" s="24" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr"/>
-      <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="24" t="inlineStr"/>
-      <c r="J11" s="24" t="inlineStr"/>
-      <c r="K11" s="24" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr"/>
-      <c r="M11" s="24" t="inlineStr"/>
+      <c r="A11" s="128" t="inlineStr"/>
+      <c r="B11" s="128" t="inlineStr"/>
+      <c r="C11" s="128" t="inlineStr"/>
+      <c r="D11" s="128" t="inlineStr"/>
+      <c r="E11" s="128" t="inlineStr"/>
+      <c r="F11" s="128" t="inlineStr"/>
+      <c r="G11" s="128" t="inlineStr"/>
+      <c r="H11" s="128" t="inlineStr"/>
+      <c r="I11" s="128" t="inlineStr"/>
+      <c r="J11" s="128" t="inlineStr"/>
+      <c r="K11" s="128" t="inlineStr"/>
+      <c r="L11" s="128" t="inlineStr"/>
+      <c r="M11" s="128" t="inlineStr"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="23" t="inlineStr"/>
-      <c r="B12" s="23" t="inlineStr"/>
-      <c r="C12" s="23" t="inlineStr"/>
-      <c r="D12" s="23" t="inlineStr"/>
-      <c r="E12" s="23" t="inlineStr"/>
-      <c r="F12" s="23" t="inlineStr"/>
-      <c r="G12" s="23" t="inlineStr"/>
-      <c r="H12" s="23" t="inlineStr"/>
-      <c r="I12" s="23" t="inlineStr"/>
-      <c r="J12" s="23" t="inlineStr"/>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="23" t="inlineStr"/>
-      <c r="M12" s="23" t="inlineStr"/>
+      <c r="A12" s="127" t="inlineStr"/>
+      <c r="B12" s="127" t="inlineStr"/>
+      <c r="C12" s="127" t="inlineStr"/>
+      <c r="D12" s="127" t="inlineStr"/>
+      <c r="E12" s="127" t="inlineStr"/>
+      <c r="F12" s="127" t="inlineStr"/>
+      <c r="G12" s="127" t="inlineStr"/>
+      <c r="H12" s="127" t="inlineStr"/>
+      <c r="I12" s="127" t="inlineStr"/>
+      <c r="J12" s="127" t="inlineStr"/>
+      <c r="K12" s="127" t="inlineStr"/>
+      <c r="L12" s="127" t="inlineStr"/>
+      <c r="M12" s="127" t="inlineStr"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="24" t="inlineStr"/>
-      <c r="B13" s="24" t="inlineStr"/>
-      <c r="C13" s="24" t="inlineStr"/>
-      <c r="D13" s="24" t="inlineStr"/>
-      <c r="E13" s="24" t="inlineStr"/>
-      <c r="F13" s="24" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr"/>
-      <c r="H13" s="24" t="inlineStr"/>
-      <c r="I13" s="24" t="inlineStr"/>
-      <c r="J13" s="24" t="inlineStr"/>
-      <c r="K13" s="24" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr"/>
-      <c r="M13" s="24" t="inlineStr"/>
+      <c r="A13" s="128" t="inlineStr"/>
+      <c r="B13" s="128" t="inlineStr"/>
+      <c r="C13" s="128" t="inlineStr"/>
+      <c r="D13" s="128" t="inlineStr"/>
+      <c r="E13" s="128" t="inlineStr"/>
+      <c r="F13" s="128" t="inlineStr"/>
+      <c r="G13" s="128" t="inlineStr"/>
+      <c r="H13" s="128" t="inlineStr"/>
+      <c r="I13" s="128" t="inlineStr"/>
+      <c r="J13" s="128" t="inlineStr"/>
+      <c r="K13" s="128" t="inlineStr"/>
+      <c r="L13" s="128" t="inlineStr"/>
+      <c r="M13" s="128" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4752,444 +6736,474 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
+      <c r="A1" s="129" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Measurement — ADC/ کالیبراسیون</t>
         </is>
       </c>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+      <c r="D1" s="85" t="n"/>
+      <c r="E1" s="85" t="n"/>
+      <c r="F1" s="85" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="130" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+      <c r="D2" s="85" t="n"/>
+      <c r="E2" s="85" t="n"/>
+      <c r="F2" s="85" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="inlineStr">
+      <c r="A3" s="93" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="85" t="n"/>
+      <c r="E3" s="85" t="n"/>
+      <c r="F3" s="85" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="96" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="96" t="inlineStr">
         <is>
           <t>Measurement — ADC/ کالیبراسیون</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="9" t="n"/>
+      <c r="E4" s="98" t="n"/>
+      <c r="F4" s="89" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>2026-09-16 (1.0)</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="96" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="9" t="n"/>
+      <c r="E5" s="98" t="n"/>
+      <c r="F5" s="89" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="96" t="inlineStr">
         <is>
           <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="9" t="n"/>
+      <c r="D6" s="132" t="inlineStr"/>
+      <c r="E6" s="98" t="n"/>
+      <c r="F6" s="89" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr"/>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="B7" s="132" t="inlineStr"/>
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="9" t="n"/>
+      <c r="D7" s="132" t="inlineStr"/>
+      <c r="E7" s="98" t="n"/>
+      <c r="F7" s="89" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr"/>
-      <c r="C8" s="70" t="inlineStr">
+      <c r="B8" s="132" t="inlineStr"/>
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="96" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="E8" s="98" t="n"/>
+      <c r="F8" s="89" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr"/>
-      <c r="D9" s="27" t="inlineStr"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="C9" s="131" t="inlineStr"/>
+      <c r="D9" s="132" t="inlineStr"/>
+      <c r="E9" s="98" t="n"/>
+      <c r="F9" s="89" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="70" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="96" t="inlineStr">
         <is>
           <t>ADC 5ch + DMA + کالیبراسیون</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr"/>
-      <c r="D10" s="27" t="inlineStr"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="C10" s="131" t="inlineStr"/>
+      <c r="D10" s="132" t="inlineStr"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>آستانه warmup</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>3 فریم</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr"/>
-      <c r="D11" s="27" t="inlineStr"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="C11" s="131" t="inlineStr"/>
+      <c r="D11" s="132" t="inlineStr"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>دوره</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="96" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr"/>
-      <c r="D12" s="27" t="inlineStr"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="C12" s="131" t="inlineStr"/>
+      <c r="D12" s="132" t="inlineStr"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>کالیبراسیون</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Vref3300/4095 Div24/Div12 Shunt10 Gain101</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr"/>
-      <c r="D13" s="27" t="inlineStr"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="C13" s="131" t="inlineStr"/>
+      <c r="D13" s="132" t="inlineStr"/>
+      <c r="E13" s="98" t="n"/>
+      <c r="F13" s="98" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="85" t="n"/>
+      <c r="D14" s="85" t="n"/>
+      <c r="E14" s="85" t="n"/>
+      <c r="F14" s="85" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C15" s="41" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="94" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="9" t="n"/>
+      <c r="E15" s="88" t="n"/>
+      <c r="F15" s="89" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="96" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
       </c>
-      <c r="B16" s="71">
+      <c r="B16" s="133">
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C16" s="42" t="inlineStr">
+      <c r="C16" s="96" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="D16" s="96" t="inlineStr"/>
+      <c r="E16" s="88" t="n"/>
+      <c r="F16" s="89" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="96" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="133">
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="96" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="96" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="n"/>
+      <c r="E17" s="88" t="n"/>
+      <c r="F17" s="89" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="96" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="133">
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="96" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="96" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="E18" s="88" t="n"/>
+      <c r="F18" s="89" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="96" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="133">
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="96" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="96" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n"/>
+      <c r="E19" s="88" t="n"/>
+      <c r="F19" s="89" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="96" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
       </c>
-      <c r="B20" s="71">
+      <c r="B20" s="133">
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="96" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="D20" s="96" t="inlineStr"/>
+      <c r="E20" s="88" t="n"/>
+      <c r="F20" s="89" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B21" s="71">
+      <c r="B21" s="133">
         <f>IF(B16=0,"",TEXT(B17/B16,"0%"))</f>
         <v/>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="96" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="n"/>
+      <c r="D21" s="96" t="inlineStr"/>
+      <c r="E21" s="88" t="n"/>
+      <c r="F21" s="89" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="93" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="41" t="inlineStr">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C23" s="41" t="inlineStr">
+      <c r="C23" s="94" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D23" s="41" t="inlineStr">
+      <c r="D23" s="94" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E23" s="41" t="inlineStr">
+      <c r="E23" s="94" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
       </c>
-      <c r="F23" s="9" t="n"/>
+      <c r="F23" s="89" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="96" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="9" t="n"/>
+      <c r="B24" s="96" t="inlineStr"/>
+      <c r="C24" s="96" t="inlineStr"/>
+      <c r="D24" s="96" t="inlineStr"/>
+      <c r="E24" s="96" t="inlineStr"/>
+      <c r="F24" s="89" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="9" t="n"/>
+      <c r="B25" s="96" t="inlineStr"/>
+      <c r="C25" s="96" t="inlineStr"/>
+      <c r="D25" s="96" t="inlineStr"/>
+      <c r="E25" s="96" t="inlineStr"/>
+      <c r="F25" s="89" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="96" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="B26" s="96" t="inlineStr"/>
+      <c r="C26" s="96" t="inlineStr"/>
+      <c r="D26" s="96" t="inlineStr"/>
+      <c r="E26" s="96" t="inlineStr"/>
+      <c r="F26" s="89" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="69" t="inlineStr">
+      <c r="A27" s="130" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
       </c>
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="85" t="n"/>
+      <c r="D27" s="85" t="n"/>
+      <c r="E27" s="85" t="n"/>
+      <c r="F27" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -5237,198 +7251,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="134" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="134" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="134" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="134" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="134" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="85" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="134" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="134" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="134" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="134" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" s="85" t="n"/>
+    </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="134" t="inlineStr">
         <is>
           <t>BoardTest</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="134" t="inlineStr">
         <is>
           <t>InputOk</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="134" t="inlineStr">
         <is>
           <t>Charging</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="A18" s="134" t="inlineStr">
         <is>
           <t>BatteryRun</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="134" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="134" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" s="134" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="134" t="inlineStr">
         <is>
           <t>Buzzer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr">
+      <c r="A23" s="134" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A24" s="134" t="inlineStr">
         <is>
           <t>Changeover</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="85" t="n"/>
+    </row>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="93" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="134" t="inlineStr">
         <is>
           <t>باز</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="134" t="inlineStr">
         <is>
           <t>در حال بررسی</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="134" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="134" t="inlineStr">
         <is>
           <t>بسته</t>
         </is>
@@ -5454,60 +7472,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول اندازه‌گیری (Measurement)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="85" t="n"/>
+      <c r="C1" s="85" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="85" t="n"/>
+      <c r="B2" s="85" t="n"/>
+      <c r="C2" s="85" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Measurement_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="85" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="85" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="85" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="62">
+  <fonts count="63">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -372,6 +372,10 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -442,7 +446,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -522,11 +526,12 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -898,6 +903,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1266,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1293,21 +1313,6 @@
           <t>برگه تست و اعتبارسنجی عملی ماژول Measurement — ADC و کالیبراسیون</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="85" t="n"/>
-      <c r="G1" s="85" t="n"/>
-      <c r="H1" s="85" t="n"/>
-      <c r="I1" s="85" t="n"/>
-      <c r="J1" s="85" t="n"/>
-      <c r="K1" s="85" t="n"/>
-      <c r="L1" s="85" t="n"/>
-      <c r="M1" s="85" t="n"/>
-      <c r="N1" s="85" t="n"/>
-      <c r="O1" s="85" t="n"/>
-      <c r="P1" s="85" t="n"/>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="86" t="inlineStr">
@@ -1315,21 +1320,6 @@
           <t>ChangeOver | ADC1 5ch + DMA + bsp_measurement | نسخه 1.0 — دوره 10ms، warmup 3 فریم، فرمول‌های BSP واقعی</t>
         </is>
       </c>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-      <c r="D2" s="85" t="n"/>
-      <c r="E2" s="85" t="n"/>
-      <c r="F2" s="85" t="n"/>
-      <c r="G2" s="85" t="n"/>
-      <c r="H2" s="85" t="n"/>
-      <c r="I2" s="85" t="n"/>
-      <c r="J2" s="85" t="n"/>
-      <c r="K2" s="85" t="n"/>
-      <c r="L2" s="85" t="n"/>
-      <c r="M2" s="85" t="n"/>
-      <c r="N2" s="85" t="n"/>
-      <c r="O2" s="85" t="n"/>
-      <c r="P2" s="85" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="87" t="inlineStr">
@@ -1337,21 +1327,21 @@
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="88" t="n"/>
-      <c r="C3" s="88" t="n"/>
-      <c r="D3" s="88" t="n"/>
-      <c r="E3" s="88" t="n"/>
-      <c r="F3" s="88" t="n"/>
-      <c r="G3" s="88" t="n"/>
-      <c r="H3" s="88" t="n"/>
-      <c r="I3" s="88" t="n"/>
-      <c r="J3" s="88" t="n"/>
-      <c r="K3" s="88" t="n"/>
-      <c r="L3" s="88" t="n"/>
-      <c r="M3" s="88" t="n"/>
-      <c r="N3" s="88" t="n"/>
-      <c r="O3" s="88" t="n"/>
-      <c r="P3" s="89" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="9" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="90" t="inlineStr">
@@ -1359,21 +1349,6 @@
           <t>این فایل مستقل فقط Measurement را اعتبارسنجی می‌کند؛ هر تست valid، فریم ADC، فرمول mV/mA، ورودی‌ها و snapshot اتمیک را چک می‌کند.</t>
         </is>
       </c>
-      <c r="B4" s="85" t="n"/>
-      <c r="C4" s="85" t="n"/>
-      <c r="D4" s="85" t="n"/>
-      <c r="E4" s="85" t="n"/>
-      <c r="F4" s="85" t="n"/>
-      <c r="G4" s="85" t="n"/>
-      <c r="H4" s="85" t="n"/>
-      <c r="I4" s="85" t="n"/>
-      <c r="J4" s="85" t="n"/>
-      <c r="K4" s="85" t="n"/>
-      <c r="L4" s="85" t="n"/>
-      <c r="M4" s="85" t="n"/>
-      <c r="N4" s="85" t="n"/>
-      <c r="O4" s="85" t="n"/>
-      <c r="P4" s="85" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="90" t="inlineStr">
@@ -1381,21 +1356,6 @@
           <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار عددی و tolerance از کالیبراسیون BSP تعریف شده است.</t>
         </is>
       </c>
-      <c r="B5" s="85" t="n"/>
-      <c r="C5" s="85" t="n"/>
-      <c r="D5" s="85" t="n"/>
-      <c r="E5" s="85" t="n"/>
-      <c r="F5" s="85" t="n"/>
-      <c r="G5" s="85" t="n"/>
-      <c r="H5" s="85" t="n"/>
-      <c r="I5" s="85" t="n"/>
-      <c r="J5" s="85" t="n"/>
-      <c r="K5" s="85" t="n"/>
-      <c r="L5" s="85" t="n"/>
-      <c r="M5" s="85" t="n"/>
-      <c r="N5" s="85" t="n"/>
-      <c r="O5" s="85" t="n"/>
-      <c r="P5" s="85" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="90" t="inlineStr">
@@ -1403,21 +1363,6 @@
           <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است.</t>
         </is>
       </c>
-      <c r="B6" s="85" t="n"/>
-      <c r="C6" s="85" t="n"/>
-      <c r="D6" s="85" t="n"/>
-      <c r="E6" s="85" t="n"/>
-      <c r="F6" s="85" t="n"/>
-      <c r="G6" s="85" t="n"/>
-      <c r="H6" s="85" t="n"/>
-      <c r="I6" s="85" t="n"/>
-      <c r="J6" s="85" t="n"/>
-      <c r="K6" s="85" t="n"/>
-      <c r="L6" s="85" t="n"/>
-      <c r="M6" s="85" t="n"/>
-      <c r="N6" s="85" t="n"/>
-      <c r="O6" s="85" t="n"/>
-      <c r="P6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="91" t="inlineStr">
@@ -1425,21 +1370,6 @@
           <t>دامنه</t>
         </is>
       </c>
-      <c r="B7" s="85" t="n"/>
-      <c r="C7" s="85" t="n"/>
-      <c r="D7" s="85" t="n"/>
-      <c r="E7" s="85" t="n"/>
-      <c r="F7" s="85" t="n"/>
-      <c r="G7" s="85" t="n"/>
-      <c r="H7" s="85" t="n"/>
-      <c r="I7" s="85" t="n"/>
-      <c r="J7" s="85" t="n"/>
-      <c r="K7" s="85" t="n"/>
-      <c r="L7" s="85" t="n"/>
-      <c r="M7" s="85" t="n"/>
-      <c r="N7" s="85" t="n"/>
-      <c r="O7" s="85" t="n"/>
-      <c r="P7" s="85" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="90" t="inlineStr">
@@ -1447,21 +1377,6 @@
           <t>پس از Init، valid=false؛ تا 3 فریم کامل و پایدار، valid همچنان false؛ پس از فریم سوم، valid=true و همه mV/mA/input_present به‌روز می‌شوند.</t>
         </is>
       </c>
-      <c r="B8" s="85" t="n"/>
-      <c r="C8" s="85" t="n"/>
-      <c r="D8" s="85" t="n"/>
-      <c r="E8" s="85" t="n"/>
-      <c r="F8" s="85" t="n"/>
-      <c r="G8" s="85" t="n"/>
-      <c r="H8" s="85" t="n"/>
-      <c r="I8" s="85" t="n"/>
-      <c r="J8" s="85" t="n"/>
-      <c r="K8" s="85" t="n"/>
-      <c r="L8" s="85" t="n"/>
-      <c r="M8" s="85" t="n"/>
-      <c r="N8" s="85" t="n"/>
-      <c r="O8" s="85" t="n"/>
-      <c r="P8" s="85" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="90" t="inlineStr">
@@ -1469,21 +1384,6 @@
           <t>فریم ناقص/ناپایدار → valid=false و warmup از نو (counter reset). قطع ورودی 24V نباید به تنهایی ADC را invalid کند.</t>
         </is>
       </c>
-      <c r="B9" s="85" t="n"/>
-      <c r="C9" s="85" t="n"/>
-      <c r="D9" s="85" t="n"/>
-      <c r="E9" s="85" t="n"/>
-      <c r="F9" s="85" t="n"/>
-      <c r="G9" s="85" t="n"/>
-      <c r="H9" s="85" t="n"/>
-      <c r="I9" s="85" t="n"/>
-      <c r="J9" s="85" t="n"/>
-      <c r="K9" s="85" t="n"/>
-      <c r="L9" s="85" t="n"/>
-      <c r="M9" s="85" t="n"/>
-      <c r="N9" s="85" t="n"/>
-      <c r="O9" s="85" t="n"/>
-      <c r="P9" s="85" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="92" t="inlineStr">
@@ -1491,21 +1391,6 @@
           <t>کالیبراسیون از bsp_measurement.c: Vref=3300mV، ADC=4095، Div24 69200+6800/6800 (≈11.176)، Div12 34200+6800/6800 (≈6.029)، شانت 10mΩ و گین 101.</t>
         </is>
       </c>
-      <c r="B10" s="85" t="n"/>
-      <c r="C10" s="85" t="n"/>
-      <c r="D10" s="85" t="n"/>
-      <c r="E10" s="85" t="n"/>
-      <c r="F10" s="85" t="n"/>
-      <c r="G10" s="85" t="n"/>
-      <c r="H10" s="85" t="n"/>
-      <c r="I10" s="85" t="n"/>
-      <c r="J10" s="85" t="n"/>
-      <c r="K10" s="85" t="n"/>
-      <c r="L10" s="85" t="n"/>
-      <c r="M10" s="85" t="n"/>
-      <c r="N10" s="85" t="n"/>
-      <c r="O10" s="85" t="n"/>
-      <c r="P10" s="85" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="90" t="inlineStr">
@@ -1513,21 +1398,6 @@
           <t>فرمول‌ها: CountsToMv = counts*3300/4095؛ V24 = adcPinMv*(76000)/6800؛ V12 = adcPinMv*(41000)/6800؛ Current = counts*3300*1000/(4095*101*10).</t>
         </is>
       </c>
-      <c r="B11" s="85" t="n"/>
-      <c r="C11" s="85" t="n"/>
-      <c r="D11" s="85" t="n"/>
-      <c r="E11" s="85" t="n"/>
-      <c r="F11" s="85" t="n"/>
-      <c r="G11" s="85" t="n"/>
-      <c r="H11" s="85" t="n"/>
-      <c r="I11" s="85" t="n"/>
-      <c r="J11" s="85" t="n"/>
-      <c r="K11" s="85" t="n"/>
-      <c r="L11" s="85" t="n"/>
-      <c r="M11" s="85" t="n"/>
-      <c r="N11" s="85" t="n"/>
-      <c r="O11" s="85" t="n"/>
-      <c r="P11" s="85" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="90" t="inlineStr">
@@ -1535,21 +1405,6 @@
           <t>زمان واقعی از کد: MEASUREMENT_PERIOD_MS=10ms، MEASUREMENT_WARMUP_FRAME_COUNT=3، DMA دو فریمی 2×5، CNDTR بررسی قبل/بعد، osKernelLock برای snapshot اتمیک.</t>
         </is>
       </c>
-      <c r="B12" s="85" t="n"/>
-      <c r="C12" s="85" t="n"/>
-      <c r="D12" s="85" t="n"/>
-      <c r="E12" s="85" t="n"/>
-      <c r="F12" s="85" t="n"/>
-      <c r="G12" s="85" t="n"/>
-      <c r="H12" s="85" t="n"/>
-      <c r="I12" s="85" t="n"/>
-      <c r="J12" s="85" t="n"/>
-      <c r="K12" s="85" t="n"/>
-      <c r="L12" s="85" t="n"/>
-      <c r="M12" s="85" t="n"/>
-      <c r="N12" s="85" t="n"/>
-      <c r="O12" s="85" t="n"/>
-      <c r="P12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="91" t="inlineStr">
@@ -1557,21 +1412,6 @@
           <t>روش اجرای تست</t>
         </is>
       </c>
-      <c r="B13" s="85" t="n"/>
-      <c r="C13" s="85" t="n"/>
-      <c r="D13" s="85" t="n"/>
-      <c r="E13" s="85" t="n"/>
-      <c r="F13" s="85" t="n"/>
-      <c r="G13" s="85" t="n"/>
-      <c r="H13" s="85" t="n"/>
-      <c r="I13" s="85" t="n"/>
-      <c r="J13" s="85" t="n"/>
-      <c r="K13" s="85" t="n"/>
-      <c r="L13" s="85" t="n"/>
-      <c r="M13" s="85" t="n"/>
-      <c r="N13" s="85" t="n"/>
-      <c r="O13" s="85" t="n"/>
-      <c r="P13" s="85" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="90" t="inlineStr">
@@ -1579,21 +1419,6 @@
           <t>۱) برد را با منبع آزمایشگاهی تغذیه کن، هر 5 کانال ADC (PA1/2/3/5/7) را با ولتاژ دقیق و منبع جریان کالیبره اعمال کن؛ PB4 را برای input_present کنترل کن.</t>
         </is>
       </c>
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
-      <c r="H14" s="85" t="n"/>
-      <c r="I14" s="85" t="n"/>
-      <c r="J14" s="85" t="n"/>
-      <c r="K14" s="85" t="n"/>
-      <c r="L14" s="85" t="n"/>
-      <c r="M14" s="85" t="n"/>
-      <c r="N14" s="85" t="n"/>
-      <c r="O14" s="85" t="n"/>
-      <c r="P14" s="85" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="90" t="inlineStr">
@@ -1601,21 +1426,6 @@
           <t>۲) firmware commit c6b084f را پروگرام کن، در «تأیید نهایی» commit/برد/ابزار (DMM، اسکوپ، منبع دقیق) را ثبت کن.</t>
         </is>
       </c>
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="85" t="n"/>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
-      <c r="H15" s="85" t="n"/>
-      <c r="I15" s="85" t="n"/>
-      <c r="J15" s="85" t="n"/>
-      <c r="K15" s="85" t="n"/>
-      <c r="L15" s="85" t="n"/>
-      <c r="M15" s="85" t="n"/>
-      <c r="N15" s="85" t="n"/>
-      <c r="O15" s="85" t="n"/>
-      <c r="P15" s="85" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="90" t="inlineStr">
@@ -1623,21 +1433,6 @@
           <t>۳) تست warmup: پس از Init، فریم‌ها را با func__BspAdc_GetRaw یا Live Watch بشمار؛ valid را چک کن.</t>
         </is>
       </c>
-      <c r="B16" s="85" t="n"/>
-      <c r="C16" s="85" t="n"/>
-      <c r="D16" s="85" t="n"/>
-      <c r="E16" s="85" t="n"/>
-      <c r="F16" s="85" t="n"/>
-      <c r="G16" s="85" t="n"/>
-      <c r="H16" s="85" t="n"/>
-      <c r="I16" s="85" t="n"/>
-      <c r="J16" s="85" t="n"/>
-      <c r="K16" s="85" t="n"/>
-      <c r="L16" s="85" t="n"/>
-      <c r="M16" s="85" t="n"/>
-      <c r="N16" s="85" t="n"/>
-      <c r="O16" s="85" t="n"/>
-      <c r="P16" s="85" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="90" t="inlineStr">
@@ -1645,21 +1440,6 @@
           <t>۴) تست ولتاژ/جریان: هر کانال را با counts معلوم اعمال کن، مقدار mV/mA را با فرمول BSP محاسبه و با خوانش globals/snapshot مقایسه کن (tolerance ±1 LSB ≈ ±0.8mV pin، برای V24 ≈±9mV، برای V12 ≈±4.8mV، برای جریان ≈±0.8mA).</t>
         </is>
       </c>
-      <c r="B17" s="85" t="n"/>
-      <c r="C17" s="85" t="n"/>
-      <c r="D17" s="85" t="n"/>
-      <c r="E17" s="85" t="n"/>
-      <c r="F17" s="85" t="n"/>
-      <c r="G17" s="85" t="n"/>
-      <c r="H17" s="85" t="n"/>
-      <c r="I17" s="85" t="n"/>
-      <c r="J17" s="85" t="n"/>
-      <c r="K17" s="85" t="n"/>
-      <c r="L17" s="85" t="n"/>
-      <c r="M17" s="85" t="n"/>
-      <c r="N17" s="85" t="n"/>
-      <c r="O17" s="85" t="n"/>
-      <c r="P17" s="85" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="90" t="inlineStr">
@@ -1667,21 +1447,6 @@
           <t>۵) تست DMA: دو فریم متوالی را چک کن که CNDTR پایدار باشد و frame 5 نمونه بدون پارگی کپی شود (irq disable و counter قبل/بعد).</t>
         </is>
       </c>
-      <c r="B18" s="85" t="n"/>
-      <c r="C18" s="85" t="n"/>
-      <c r="D18" s="85" t="n"/>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="85" t="n"/>
-      <c r="G18" s="85" t="n"/>
-      <c r="H18" s="85" t="n"/>
-      <c r="I18" s="85" t="n"/>
-      <c r="J18" s="85" t="n"/>
-      <c r="K18" s="85" t="n"/>
-      <c r="L18" s="85" t="n"/>
-      <c r="M18" s="85" t="n"/>
-      <c r="N18" s="85" t="n"/>
-      <c r="O18" s="85" t="n"/>
-      <c r="P18" s="85" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="90" t="inlineStr">
@@ -1689,21 +1454,6 @@
           <t>۶) تست snapshot اتمیک: حین Run، از دو تسک snapshot را هم‌زمان بخوان و چک کن نیمه‌به‌روزشده نباشد (osKernelLock).</t>
         </is>
       </c>
-      <c r="B19" s="85" t="n"/>
-      <c r="C19" s="85" t="n"/>
-      <c r="D19" s="85" t="n"/>
-      <c r="E19" s="85" t="n"/>
-      <c r="F19" s="85" t="n"/>
-      <c r="G19" s="85" t="n"/>
-      <c r="H19" s="85" t="n"/>
-      <c r="I19" s="85" t="n"/>
-      <c r="J19" s="85" t="n"/>
-      <c r="K19" s="85" t="n"/>
-      <c r="L19" s="85" t="n"/>
-      <c r="M19" s="85" t="n"/>
-      <c r="N19" s="85" t="n"/>
-      <c r="O19" s="85" t="n"/>
-      <c r="P19" s="85" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="93" t="inlineStr">
@@ -1711,21 +1461,6 @@
           <t>تاریخچه نسخه</t>
         </is>
       </c>
-      <c r="B20" s="85" t="n"/>
-      <c r="C20" s="85" t="n"/>
-      <c r="D20" s="85" t="n"/>
-      <c r="E20" s="85" t="n"/>
-      <c r="F20" s="85" t="n"/>
-      <c r="G20" s="85" t="n"/>
-      <c r="H20" s="85" t="n"/>
-      <c r="I20" s="85" t="n"/>
-      <c r="J20" s="85" t="n"/>
-      <c r="K20" s="85" t="n"/>
-      <c r="L20" s="85" t="n"/>
-      <c r="M20" s="85" t="n"/>
-      <c r="N20" s="85" t="n"/>
-      <c r="O20" s="85" t="n"/>
-      <c r="P20" s="85" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="94" t="inlineStr">
@@ -1749,17 +1484,17 @@
         </is>
       </c>
       <c r="E21" s="95" t="n"/>
-      <c r="F21" s="88" t="n"/>
-      <c r="G21" s="88" t="n"/>
-      <c r="H21" s="88" t="n"/>
-      <c r="I21" s="88" t="n"/>
-      <c r="J21" s="88" t="n"/>
-      <c r="K21" s="88" t="n"/>
-      <c r="L21" s="88" t="n"/>
-      <c r="M21" s="88" t="n"/>
-      <c r="N21" s="88" t="n"/>
-      <c r="O21" s="88" t="n"/>
-      <c r="P21" s="89" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="9" t="n"/>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="96" t="inlineStr">
@@ -1783,17 +1518,17 @@
         </is>
       </c>
       <c r="E22" s="98" t="n"/>
-      <c r="F22" s="88" t="n"/>
-      <c r="G22" s="88" t="n"/>
-      <c r="H22" s="88" t="n"/>
-      <c r="I22" s="88" t="n"/>
-      <c r="J22" s="88" t="n"/>
-      <c r="K22" s="88" t="n"/>
-      <c r="L22" s="88" t="n"/>
-      <c r="M22" s="88" t="n"/>
-      <c r="N22" s="88" t="n"/>
-      <c r="O22" s="88" t="n"/>
-      <c r="P22" s="89" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="99" t="inlineStr">
@@ -1828,6 +1563,14 @@
       <c r="N23" s="85" t="n"/>
       <c r="O23" s="85" t="n"/>
       <c r="P23" s="85" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="135" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1899,21 +1642,6 @@
           <t>برنامه تست عملی — ماژول Measurement</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="85" t="n"/>
-      <c r="G1" s="85" t="n"/>
-      <c r="H1" s="85" t="n"/>
-      <c r="I1" s="85" t="n"/>
-      <c r="J1" s="85" t="n"/>
-      <c r="K1" s="85" t="n"/>
-      <c r="L1" s="85" t="n"/>
-      <c r="M1" s="85" t="n"/>
-      <c r="N1" s="85" t="n"/>
-      <c r="O1" s="85" t="n"/>
-      <c r="P1" s="85" t="n"/>
       <c r="Q1" s="85" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
@@ -1922,21 +1650,6 @@
           <t>هر ردیف را با DMM/اسکوپ و محاسبه از فرمول BSP اندازه بگیر؛ مقدار حدسی ننویس. valid باید دقیقاً پس از ۳ فریم true شود.</t>
         </is>
       </c>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-      <c r="D2" s="85" t="n"/>
-      <c r="E2" s="85" t="n"/>
-      <c r="F2" s="85" t="n"/>
-      <c r="G2" s="85" t="n"/>
-      <c r="H2" s="85" t="n"/>
-      <c r="I2" s="85" t="n"/>
-      <c r="J2" s="85" t="n"/>
-      <c r="K2" s="85" t="n"/>
-      <c r="L2" s="85" t="n"/>
-      <c r="M2" s="85" t="n"/>
-      <c r="N2" s="85" t="n"/>
-      <c r="O2" s="85" t="n"/>
-      <c r="P2" s="85" t="n"/>
       <c r="Q2" s="85" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -1945,21 +1658,6 @@
           <t>فرمول‌ها و tolerance از bsp_measurement.c واقعی است؛ PASS/FAIL با tolerance ±1 LSB + 1% مقاومت تعریف شده است.</t>
         </is>
       </c>
-      <c r="B3" s="85" t="n"/>
-      <c r="C3" s="85" t="n"/>
-      <c r="D3" s="85" t="n"/>
-      <c r="E3" s="85" t="n"/>
-      <c r="F3" s="85" t="n"/>
-      <c r="G3" s="85" t="n"/>
-      <c r="H3" s="85" t="n"/>
-      <c r="I3" s="85" t="n"/>
-      <c r="J3" s="85" t="n"/>
-      <c r="K3" s="85" t="n"/>
-      <c r="L3" s="85" t="n"/>
-      <c r="M3" s="85" t="n"/>
-      <c r="N3" s="85" t="n"/>
-      <c r="O3" s="85" t="n"/>
-      <c r="P3" s="85" t="n"/>
       <c r="Q3" s="85" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -2005,7 +1703,7 @@
       </c>
       <c r="I4" s="87" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="J4" s="87" t="inlineStr">
@@ -2090,24 +1788,27 @@
       </c>
       <c r="I5" s="104" t="inlineStr">
         <is>
-          <t>نزدیکی عدد پنل و مولتی‌متر = قبول؛ عدد ثابت/خیالی یا اختلاف زیاد = رد</t>
-        </is>
-      </c>
-      <c r="J5" s="107" t="inlineStr"/>
+          <t>باید ببینید: عددهای پنل زنده‌اند و با مولتی‌متر دستی می‌خوانند (اختلاف در حد چند صدم ولت). اگر عدد ثابت بود یا اختلاف زیاد داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J5" s="107" t="n"/>
       <c r="K5" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="109" t="inlineStr"/>
-      <c r="M5" s="104" t="inlineStr"/>
+      <c r="L5" s="109" t="n"/>
+      <c r="M5" s="104" t="n"/>
       <c r="N5" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O5" s="106" t="inlineStr"/>
-      <c r="P5" s="106" t="inlineStr"/>
+      <c r="O5" s="106" t="n"/>
+      <c r="P5" s="106">
+        <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
+        <v/>
+      </c>
       <c r="Q5" s="110">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
@@ -2157,24 +1858,27 @@
       </c>
       <c r="I6" s="104" t="inlineStr">
         <is>
-          <t>تشخیص درست وصل = قبول؛ هنوز قطع نشان دادن = رد</t>
-        </is>
-      </c>
-      <c r="J6" s="107" t="inlineStr"/>
+          <t>باید ببینید: پنل ورودی را حاضر و با ولتاژ درست نشان می‌دهد. اگر هنوز قطع نشان داد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J6" s="107" t="n"/>
       <c r="K6" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="109" t="inlineStr"/>
-      <c r="M6" s="104" t="inlineStr"/>
+      <c r="L6" s="109" t="n"/>
+      <c r="M6" s="104" t="n"/>
       <c r="N6" s="104" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O6" s="106" t="inlineStr"/>
-      <c r="P6" s="106" t="inlineStr"/>
+      <c r="O6" s="106" t="n"/>
+      <c r="P6" s="106">
+        <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
+        <v/>
+      </c>
       <c r="Q6" s="110">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
@@ -2224,24 +1928,27 @@
       </c>
       <c r="I7" s="111" t="inlineStr">
         <is>
-          <t>تشخیص درست قطع و ادامهٔ کار = قبول؛ هنگ یا نشان اشتباه = رد</t>
-        </is>
-      </c>
-      <c r="J7" s="111" t="inlineStr"/>
+          <t>باید ببینید: پنل ورودی را قطع نشان می‌دهد و دستگاه بی‌وقفه روی باتری ادامه می‌دهد. اگر هنگ کرد یا اشتباه نشان داد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J7" s="111" t="n"/>
       <c r="K7" s="111" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="114" t="inlineStr"/>
-      <c r="M7" s="111" t="inlineStr"/>
+      <c r="L7" s="114" t="n"/>
+      <c r="M7" s="111" t="n"/>
       <c r="N7" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
-      <c r="O7" s="113" t="inlineStr"/>
-      <c r="P7" s="113" t="inlineStr"/>
+      <c r="O7" s="113" t="n"/>
+      <c r="P7" s="113">
+        <f>IF(OR(K7="",K7="در انتظار"),"",IF(P7="",TODAY(),P7))</f>
+        <v/>
+      </c>
       <c r="Q7" s="115">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
@@ -2250,972 +1957,25 @@
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="103" t="inlineStr">
         <is>
-          <t>MS-021</t>
+          <t>MS-023</t>
         </is>
       </c>
       <c r="B8" s="104" t="inlineStr">
         <is>
-          <t>کالیبراسیون برد / tolerance</t>
+          <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
       <c r="C8" s="106" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>بالا</t>
         </is>
       </c>
       <c r="D8" s="104" t="inlineStr">
         <is>
-          <t>مولتی‌متر مرجع مطمئن و پنل در حالت کالیبراسیون</t>
+          <t>منبع دقیق آزمایشگاهی و مولتی‌متر</t>
         </is>
       </c>
       <c r="E8" s="104" t="inlineStr">
-        <is>
-          <t>گام ۱: طبق راهنمای پنل، در یک ولتاژ پایین و یک ولتاژ بالا عدد دستگاه را با مولتی‌متر یکی کن.
-گام ۲: در یک ولتاژ میانی هر دو را مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F8" s="106" t="inlineStr">
-        <is>
-          <t>کالیبراسیون دو نقطه و چک میانی</t>
-        </is>
-      </c>
-      <c r="G8" s="106" t="inlineStr">
-        <is>
-          <t>ربع ساعت</t>
-        </is>
-      </c>
-      <c r="H8" s="104" t="inlineStr">
-        <is>
-          <t>بعد از کالیبراسیون، عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند</t>
-        </is>
-      </c>
-      <c r="I8" s="104" t="inlineStr">
-        <is>
-          <t>برابری در نقطهٔ میانی = قبول؛ اختلاف محسوس = رد</t>
-        </is>
-      </c>
-      <c r="J8" s="107" t="inlineStr"/>
-      <c r="K8" s="108" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L8" s="109" t="inlineStr"/>
-      <c r="M8" s="104" t="inlineStr"/>
-      <c r="N8" s="104" t="inlineStr">
-        <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
-        </is>
-      </c>
-      <c r="O8" s="106" t="inlineStr"/>
-      <c r="P8" s="106" t="inlineStr"/>
-      <c r="Q8" s="110">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="85" t="n"/>
-      <c r="B9" s="85" t="n"/>
-      <c r="C9" s="85" t="n"/>
-      <c r="D9" s="85" t="n"/>
-      <c r="E9" s="85" t="n"/>
-      <c r="F9" s="85" t="n"/>
-      <c r="G9" s="85" t="n"/>
-      <c r="H9" s="85" t="n"/>
-      <c r="I9" s="85" t="n"/>
-      <c r="J9" s="85" t="n"/>
-      <c r="K9" s="85" t="n"/>
-      <c r="L9" s="85" t="n"/>
-      <c r="M9" s="85" t="n"/>
-      <c r="N9" s="85" t="n"/>
-      <c r="O9" s="85" t="n"/>
-      <c r="P9" s="85" t="n"/>
-      <c r="Q9" s="116">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="85" t="n"/>
-      <c r="B10" s="85" t="n"/>
-      <c r="C10" s="85" t="n"/>
-      <c r="D10" s="85" t="n"/>
-      <c r="E10" s="85" t="n"/>
-      <c r="F10" s="85" t="n"/>
-      <c r="G10" s="85" t="n"/>
-      <c r="H10" s="85" t="n"/>
-      <c r="I10" s="85" t="n"/>
-      <c r="J10" s="85" t="n"/>
-      <c r="K10" s="85" t="n"/>
-      <c r="L10" s="85" t="n"/>
-      <c r="M10" s="85" t="n"/>
-      <c r="N10" s="85" t="n"/>
-      <c r="O10" s="85" t="n"/>
-      <c r="P10" s="85" t="n"/>
-      <c r="Q10" s="116">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="85" t="n"/>
-      <c r="B11" s="85" t="n"/>
-      <c r="C11" s="85" t="n"/>
-      <c r="D11" s="85" t="n"/>
-      <c r="E11" s="85" t="n"/>
-      <c r="F11" s="85" t="n"/>
-      <c r="G11" s="85" t="n"/>
-      <c r="H11" s="85" t="n"/>
-      <c r="I11" s="85" t="n"/>
-      <c r="J11" s="85" t="n"/>
-      <c r="K11" s="85" t="n"/>
-      <c r="L11" s="85" t="n"/>
-      <c r="M11" s="85" t="n"/>
-      <c r="N11" s="85" t="n"/>
-      <c r="O11" s="85" t="n"/>
-      <c r="P11" s="85" t="n"/>
-      <c r="Q11" s="116">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="85" t="n"/>
-      <c r="B12" s="85" t="n"/>
-      <c r="C12" s="85" t="n"/>
-      <c r="D12" s="85" t="n"/>
-      <c r="E12" s="85" t="n"/>
-      <c r="F12" s="85" t="n"/>
-      <c r="G12" s="85" t="n"/>
-      <c r="H12" s="85" t="n"/>
-      <c r="I12" s="85" t="n"/>
-      <c r="J12" s="85" t="n"/>
-      <c r="K12" s="85" t="n"/>
-      <c r="L12" s="85" t="n"/>
-      <c r="M12" s="85" t="n"/>
-      <c r="N12" s="85" t="n"/>
-      <c r="O12" s="85" t="n"/>
-      <c r="P12" s="85" t="n"/>
-      <c r="Q12" s="116">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="85" t="n"/>
-      <c r="B13" s="85" t="n"/>
-      <c r="C13" s="85" t="n"/>
-      <c r="D13" s="85" t="n"/>
-      <c r="E13" s="85" t="n"/>
-      <c r="F13" s="85" t="n"/>
-      <c r="G13" s="85" t="n"/>
-      <c r="H13" s="85" t="n"/>
-      <c r="I13" s="85" t="n"/>
-      <c r="J13" s="85" t="n"/>
-      <c r="K13" s="85" t="n"/>
-      <c r="L13" s="85" t="n"/>
-      <c r="M13" s="85" t="n"/>
-      <c r="N13" s="85" t="n"/>
-      <c r="O13" s="85" t="n"/>
-      <c r="P13" s="85" t="n"/>
-      <c r="Q13" s="116">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="85" t="n"/>
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
-      <c r="H14" s="85" t="n"/>
-      <c r="I14" s="85" t="n"/>
-      <c r="J14" s="85" t="n"/>
-      <c r="K14" s="85" t="n"/>
-      <c r="L14" s="85" t="n"/>
-      <c r="M14" s="85" t="n"/>
-      <c r="N14" s="85" t="n"/>
-      <c r="O14" s="85" t="n"/>
-      <c r="P14" s="85" t="n"/>
-      <c r="Q14" s="116">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="85" t="n"/>
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="85" t="n"/>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
-      <c r="H15" s="85" t="n"/>
-      <c r="I15" s="85" t="n"/>
-      <c r="J15" s="85" t="n"/>
-      <c r="K15" s="85" t="n"/>
-      <c r="L15" s="85" t="n"/>
-      <c r="M15" s="85" t="n"/>
-      <c r="N15" s="85" t="n"/>
-      <c r="O15" s="85" t="n"/>
-      <c r="P15" s="85" t="n"/>
-      <c r="Q15" s="116">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="85" t="n"/>
-      <c r="B16" s="85" t="n"/>
-      <c r="C16" s="85" t="n"/>
-      <c r="D16" s="85" t="n"/>
-      <c r="E16" s="85" t="n"/>
-      <c r="F16" s="85" t="n"/>
-      <c r="G16" s="85" t="n"/>
-      <c r="H16" s="85" t="n"/>
-      <c r="I16" s="85" t="n"/>
-      <c r="J16" s="85" t="n"/>
-      <c r="K16" s="85" t="n"/>
-      <c r="L16" s="85" t="n"/>
-      <c r="M16" s="85" t="n"/>
-      <c r="N16" s="85" t="n"/>
-      <c r="O16" s="85" t="n"/>
-      <c r="P16" s="85" t="n"/>
-      <c r="Q16" s="116">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="85" t="n"/>
-      <c r="B17" s="85" t="n"/>
-      <c r="C17" s="85" t="n"/>
-      <c r="D17" s="85" t="n"/>
-      <c r="E17" s="85" t="n"/>
-      <c r="F17" s="85" t="n"/>
-      <c r="G17" s="85" t="n"/>
-      <c r="H17" s="85" t="n"/>
-      <c r="I17" s="85" t="n"/>
-      <c r="J17" s="85" t="n"/>
-      <c r="K17" s="85" t="n"/>
-      <c r="L17" s="85" t="n"/>
-      <c r="M17" s="85" t="n"/>
-      <c r="N17" s="85" t="n"/>
-      <c r="O17" s="85" t="n"/>
-      <c r="P17" s="85" t="n"/>
-      <c r="Q17" s="116">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="85" t="n"/>
-      <c r="B18" s="85" t="n"/>
-      <c r="C18" s="85" t="n"/>
-      <c r="D18" s="85" t="n"/>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="85" t="n"/>
-      <c r="G18" s="85" t="n"/>
-      <c r="H18" s="85" t="n"/>
-      <c r="I18" s="85" t="n"/>
-      <c r="J18" s="85" t="n"/>
-      <c r="K18" s="85" t="n"/>
-      <c r="L18" s="85" t="n"/>
-      <c r="M18" s="85" t="n"/>
-      <c r="N18" s="85" t="n"/>
-      <c r="O18" s="85" t="n"/>
-      <c r="P18" s="85" t="n"/>
-      <c r="Q18" s="116">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="40.5" customHeight="1">
-      <c r="A19" s="85" t="n"/>
-      <c r="B19" s="85" t="n"/>
-      <c r="C19" s="85" t="n"/>
-      <c r="D19" s="85" t="n"/>
-      <c r="E19" s="85" t="n"/>
-      <c r="F19" s="85" t="n"/>
-      <c r="G19" s="85" t="n"/>
-      <c r="H19" s="85" t="n"/>
-      <c r="I19" s="85" t="n"/>
-      <c r="J19" s="85" t="n"/>
-      <c r="K19" s="85" t="n"/>
-      <c r="L19" s="85" t="n"/>
-      <c r="M19" s="85" t="n"/>
-      <c r="N19" s="85" t="n"/>
-      <c r="O19" s="85" t="n"/>
-      <c r="P19" s="85" t="n"/>
-      <c r="Q19" s="116">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="85" t="n"/>
-      <c r="B20" s="85" t="n"/>
-      <c r="C20" s="85" t="n"/>
-      <c r="D20" s="85" t="n"/>
-      <c r="E20" s="85" t="n"/>
-      <c r="F20" s="85" t="n"/>
-      <c r="G20" s="85" t="n"/>
-      <c r="H20" s="85" t="n"/>
-      <c r="I20" s="85" t="n"/>
-      <c r="J20" s="85" t="n"/>
-      <c r="K20" s="85" t="n"/>
-      <c r="L20" s="85" t="n"/>
-      <c r="M20" s="85" t="n"/>
-      <c r="N20" s="85" t="n"/>
-      <c r="O20" s="85" t="n"/>
-      <c r="P20" s="85" t="n"/>
-      <c r="Q20" s="116">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="85" t="n"/>
-      <c r="B21" s="85" t="n"/>
-      <c r="C21" s="85" t="n"/>
-      <c r="D21" s="85" t="n"/>
-      <c r="E21" s="85" t="n"/>
-      <c r="F21" s="85" t="n"/>
-      <c r="G21" s="85" t="n"/>
-      <c r="H21" s="85" t="n"/>
-      <c r="I21" s="85" t="n"/>
-      <c r="J21" s="85" t="n"/>
-      <c r="K21" s="85" t="n"/>
-      <c r="L21" s="85" t="n"/>
-      <c r="M21" s="85" t="n"/>
-      <c r="N21" s="85" t="n"/>
-      <c r="O21" s="85" t="n"/>
-      <c r="P21" s="85" t="n"/>
-      <c r="Q21" s="116">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="85" t="n"/>
-      <c r="B22" s="85" t="n"/>
-      <c r="C22" s="85" t="n"/>
-      <c r="D22" s="85" t="n"/>
-      <c r="E22" s="85" t="n"/>
-      <c r="F22" s="85" t="n"/>
-      <c r="G22" s="85" t="n"/>
-      <c r="H22" s="85" t="n"/>
-      <c r="I22" s="85" t="n"/>
-      <c r="J22" s="85" t="n"/>
-      <c r="K22" s="85" t="n"/>
-      <c r="L22" s="85" t="n"/>
-      <c r="M22" s="85" t="n"/>
-      <c r="N22" s="85" t="n"/>
-      <c r="O22" s="85" t="n"/>
-      <c r="P22" s="85" t="n"/>
-      <c r="Q22" s="116">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="85" t="n"/>
-      <c r="B23" s="85" t="n"/>
-      <c r="C23" s="85" t="n"/>
-      <c r="D23" s="85" t="n"/>
-      <c r="E23" s="85" t="n"/>
-      <c r="F23" s="85" t="n"/>
-      <c r="G23" s="85" t="n"/>
-      <c r="H23" s="85" t="n"/>
-      <c r="I23" s="85" t="n"/>
-      <c r="J23" s="85" t="n"/>
-      <c r="K23" s="85" t="n"/>
-      <c r="L23" s="85" t="n"/>
-      <c r="M23" s="85" t="n"/>
-      <c r="N23" s="85" t="n"/>
-      <c r="O23" s="85" t="n"/>
-      <c r="P23" s="85" t="n"/>
-      <c r="Q23" s="116">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="85" t="n"/>
-      <c r="B24" s="85" t="n"/>
-      <c r="C24" s="85" t="n"/>
-      <c r="D24" s="85" t="n"/>
-      <c r="E24" s="85" t="n"/>
-      <c r="F24" s="85" t="n"/>
-      <c r="G24" s="85" t="n"/>
-      <c r="H24" s="85" t="n"/>
-      <c r="I24" s="85" t="n"/>
-      <c r="J24" s="85" t="n"/>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="85" t="n"/>
-      <c r="M24" s="85" t="n"/>
-      <c r="N24" s="85" t="n"/>
-      <c r="O24" s="85" t="n"/>
-      <c r="P24" s="85" t="n"/>
-      <c r="Q24" s="116">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="85" t="n"/>
-      <c r="B25" s="85" t="n"/>
-      <c r="C25" s="85" t="n"/>
-      <c r="D25" s="85" t="n"/>
-      <c r="E25" s="85" t="n"/>
-      <c r="F25" s="85" t="n"/>
-      <c r="G25" s="85" t="n"/>
-      <c r="H25" s="85" t="n"/>
-      <c r="I25" s="85" t="n"/>
-      <c r="J25" s="85" t="n"/>
-      <c r="K25" s="85" t="n"/>
-      <c r="L25" s="85" t="n"/>
-      <c r="M25" s="85" t="n"/>
-      <c r="N25" s="85" t="n"/>
-      <c r="O25" s="85" t="n"/>
-      <c r="P25" s="85" t="n"/>
-      <c r="Q25" s="116">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="85" t="n"/>
-      <c r="B26" s="85" t="n"/>
-      <c r="C26" s="85" t="n"/>
-      <c r="D26" s="85" t="n"/>
-      <c r="E26" s="85" t="n"/>
-      <c r="F26" s="85" t="n"/>
-      <c r="G26" s="85" t="n"/>
-      <c r="H26" s="85" t="n"/>
-      <c r="I26" s="85" t="n"/>
-      <c r="J26" s="85" t="n"/>
-      <c r="K26" s="85" t="n"/>
-      <c r="L26" s="85" t="n"/>
-      <c r="M26" s="85" t="n"/>
-      <c r="N26" s="85" t="n"/>
-      <c r="O26" s="85" t="n"/>
-      <c r="P26" s="85" t="n"/>
-      <c r="Q26" s="116">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="85" t="n"/>
-      <c r="B27" s="85" t="n"/>
-      <c r="C27" s="85" t="n"/>
-      <c r="D27" s="85" t="n"/>
-      <c r="E27" s="85" t="n"/>
-      <c r="F27" s="85" t="n"/>
-      <c r="G27" s="85" t="n"/>
-      <c r="H27" s="85" t="n"/>
-      <c r="I27" s="85" t="n"/>
-      <c r="J27" s="85" t="n"/>
-      <c r="K27" s="85" t="n"/>
-      <c r="L27" s="85" t="n"/>
-      <c r="M27" s="85" t="n"/>
-      <c r="N27" s="85" t="n"/>
-      <c r="O27" s="85" t="n"/>
-      <c r="P27" s="85" t="n"/>
-      <c r="Q27" s="116">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="85" t="n"/>
-      <c r="B28" s="85" t="n"/>
-      <c r="C28" s="85" t="n"/>
-      <c r="D28" s="85" t="n"/>
-      <c r="E28" s="85" t="n"/>
-      <c r="F28" s="85" t="n"/>
-      <c r="G28" s="85" t="n"/>
-      <c r="H28" s="85" t="n"/>
-      <c r="I28" s="85" t="n"/>
-      <c r="J28" s="85" t="n"/>
-      <c r="K28" s="85" t="n"/>
-      <c r="L28" s="85" t="n"/>
-      <c r="M28" s="85" t="n"/>
-      <c r="N28" s="85" t="n"/>
-      <c r="O28" s="85" t="n"/>
-      <c r="P28" s="85" t="n"/>
-      <c r="Q28" s="116">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="85" t="n"/>
-      <c r="B29" s="85" t="n"/>
-      <c r="C29" s="85" t="n"/>
-      <c r="D29" s="85" t="n"/>
-      <c r="E29" s="85" t="n"/>
-      <c r="F29" s="85" t="n"/>
-      <c r="G29" s="85" t="n"/>
-      <c r="H29" s="85" t="n"/>
-      <c r="I29" s="85" t="n"/>
-      <c r="J29" s="85" t="n"/>
-      <c r="K29" s="85" t="n"/>
-      <c r="L29" s="85" t="n"/>
-      <c r="M29" s="85" t="n"/>
-      <c r="N29" s="85" t="n"/>
-      <c r="O29" s="85" t="n"/>
-      <c r="P29" s="85" t="n"/>
-      <c r="Q29" s="116">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="85" t="n"/>
-      <c r="B30" s="85" t="n"/>
-      <c r="C30" s="85" t="n"/>
-      <c r="D30" s="85" t="n"/>
-      <c r="E30" s="85" t="n"/>
-      <c r="F30" s="85" t="n"/>
-      <c r="G30" s="85" t="n"/>
-      <c r="H30" s="85" t="n"/>
-      <c r="I30" s="85" t="n"/>
-      <c r="J30" s="85" t="n"/>
-      <c r="K30" s="85" t="n"/>
-      <c r="L30" s="85" t="n"/>
-      <c r="M30" s="85" t="n"/>
-      <c r="N30" s="85" t="n"/>
-      <c r="O30" s="85" t="n"/>
-      <c r="P30" s="85" t="n"/>
-      <c r="Q30" s="116">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="85" t="n"/>
-      <c r="B31" s="85" t="n"/>
-      <c r="C31" s="85" t="n"/>
-      <c r="D31" s="85" t="n"/>
-      <c r="E31" s="85" t="n"/>
-      <c r="F31" s="85" t="n"/>
-      <c r="G31" s="85" t="n"/>
-      <c r="H31" s="85" t="n"/>
-      <c r="I31" s="85" t="n"/>
-      <c r="J31" s="85" t="n"/>
-      <c r="K31" s="85" t="n"/>
-      <c r="L31" s="85" t="n"/>
-      <c r="M31" s="85" t="n"/>
-      <c r="N31" s="85" t="n"/>
-      <c r="O31" s="85" t="n"/>
-      <c r="P31" s="85" t="n"/>
-      <c r="Q31" s="116">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="85" t="n"/>
-      <c r="B32" s="85" t="n"/>
-      <c r="C32" s="85" t="n"/>
-      <c r="D32" s="85" t="n"/>
-      <c r="E32" s="85" t="n"/>
-      <c r="F32" s="85" t="n"/>
-      <c r="G32" s="85" t="n"/>
-      <c r="H32" s="85" t="n"/>
-      <c r="I32" s="85" t="n"/>
-      <c r="J32" s="85" t="n"/>
-      <c r="K32" s="85" t="n"/>
-      <c r="L32" s="85" t="n"/>
-      <c r="M32" s="85" t="n"/>
-      <c r="N32" s="85" t="n"/>
-      <c r="O32" s="85" t="n"/>
-      <c r="P32" s="85" t="n"/>
-      <c r="Q32" s="116">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="85" t="n"/>
-      <c r="B33" s="85" t="n"/>
-      <c r="C33" s="85" t="n"/>
-      <c r="D33" s="85" t="n"/>
-      <c r="E33" s="85" t="n"/>
-      <c r="F33" s="85" t="n"/>
-      <c r="G33" s="85" t="n"/>
-      <c r="H33" s="85" t="n"/>
-      <c r="I33" s="85" t="n"/>
-      <c r="J33" s="85" t="n"/>
-      <c r="K33" s="85" t="n"/>
-      <c r="L33" s="85" t="n"/>
-      <c r="M33" s="85" t="n"/>
-      <c r="N33" s="85" t="n"/>
-      <c r="O33" s="85" t="n"/>
-      <c r="P33" s="85" t="n"/>
-      <c r="Q33" s="116">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="85" t="n"/>
-      <c r="B34" s="85" t="n"/>
-      <c r="C34" s="85" t="n"/>
-      <c r="D34" s="85" t="n"/>
-      <c r="E34" s="85" t="n"/>
-      <c r="F34" s="85" t="n"/>
-      <c r="G34" s="85" t="n"/>
-      <c r="H34" s="85" t="n"/>
-      <c r="I34" s="85" t="n"/>
-      <c r="J34" s="85" t="n"/>
-      <c r="K34" s="85" t="n"/>
-      <c r="L34" s="85" t="n"/>
-      <c r="M34" s="85" t="n"/>
-      <c r="N34" s="85" t="n"/>
-      <c r="O34" s="85" t="n"/>
-      <c r="P34" s="85" t="n"/>
-      <c r="Q34" s="116">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="85" t="n"/>
-      <c r="B35" s="85" t="n"/>
-      <c r="C35" s="85" t="n"/>
-      <c r="D35" s="85" t="n"/>
-      <c r="E35" s="85" t="n"/>
-      <c r="F35" s="85" t="n"/>
-      <c r="G35" s="85" t="n"/>
-      <c r="H35" s="85" t="n"/>
-      <c r="I35" s="85" t="n"/>
-      <c r="J35" s="85" t="n"/>
-      <c r="K35" s="85" t="n"/>
-      <c r="L35" s="85" t="n"/>
-      <c r="M35" s="85" t="n"/>
-      <c r="N35" s="85" t="n"/>
-      <c r="O35" s="85" t="n"/>
-      <c r="P35" s="85" t="n"/>
-      <c r="Q35" s="116">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="85" t="n"/>
-      <c r="B36" s="85" t="n"/>
-      <c r="C36" s="85" t="n"/>
-      <c r="D36" s="85" t="n"/>
-      <c r="E36" s="85" t="n"/>
-      <c r="F36" s="85" t="n"/>
-      <c r="G36" s="85" t="n"/>
-      <c r="H36" s="85" t="n"/>
-      <c r="I36" s="85" t="n"/>
-      <c r="J36" s="85" t="n"/>
-      <c r="K36" s="85" t="n"/>
-      <c r="L36" s="85" t="n"/>
-      <c r="M36" s="85" t="n"/>
-      <c r="N36" s="85" t="n"/>
-      <c r="O36" s="85" t="n"/>
-      <c r="P36" s="85" t="n"/>
-      <c r="Q36" s="116">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="85" t="n"/>
-      <c r="B37" s="85" t="n"/>
-      <c r="C37" s="85" t="n"/>
-      <c r="D37" s="85" t="n"/>
-      <c r="E37" s="85" t="n"/>
-      <c r="F37" s="85" t="n"/>
-      <c r="G37" s="85" t="n"/>
-      <c r="H37" s="85" t="n"/>
-      <c r="I37" s="85" t="n"/>
-      <c r="J37" s="85" t="n"/>
-      <c r="K37" s="85" t="n"/>
-      <c r="L37" s="85" t="n"/>
-      <c r="M37" s="85" t="n"/>
-      <c r="N37" s="85" t="n"/>
-      <c r="O37" s="85" t="n"/>
-      <c r="P37" s="85" t="n"/>
-      <c r="Q37" s="116">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="85" t="n"/>
-      <c r="B38" s="85" t="n"/>
-      <c r="C38" s="85" t="n"/>
-      <c r="D38" s="85" t="n"/>
-      <c r="E38" s="85" t="n"/>
-      <c r="F38" s="85" t="n"/>
-      <c r="G38" s="85" t="n"/>
-      <c r="H38" s="85" t="n"/>
-      <c r="I38" s="85" t="n"/>
-      <c r="J38" s="85" t="n"/>
-      <c r="K38" s="85" t="n"/>
-      <c r="L38" s="85" t="n"/>
-      <c r="M38" s="85" t="n"/>
-      <c r="N38" s="85" t="n"/>
-      <c r="O38" s="85" t="n"/>
-      <c r="P38" s="85" t="n"/>
-      <c r="Q38" s="116">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="85" t="n"/>
-      <c r="B39" s="85" t="n"/>
-      <c r="C39" s="85" t="n"/>
-      <c r="D39" s="85" t="n"/>
-      <c r="E39" s="85" t="n"/>
-      <c r="F39" s="85" t="n"/>
-      <c r="G39" s="85" t="n"/>
-      <c r="H39" s="85" t="n"/>
-      <c r="I39" s="85" t="n"/>
-      <c r="J39" s="85" t="n"/>
-      <c r="K39" s="85" t="n"/>
-      <c r="L39" s="85" t="n"/>
-      <c r="M39" s="85" t="n"/>
-      <c r="N39" s="85" t="n"/>
-      <c r="O39" s="85" t="n"/>
-      <c r="P39" s="85" t="n"/>
-      <c r="Q39" s="116">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="85" t="n"/>
-      <c r="B40" s="85" t="n"/>
-      <c r="C40" s="85" t="n"/>
-      <c r="D40" s="85" t="n"/>
-      <c r="E40" s="85" t="n"/>
-      <c r="F40" s="85" t="n"/>
-      <c r="G40" s="85" t="n"/>
-      <c r="H40" s="85" t="n"/>
-      <c r="I40" s="85" t="n"/>
-      <c r="J40" s="85" t="n"/>
-      <c r="K40" s="85" t="n"/>
-      <c r="L40" s="85" t="n"/>
-      <c r="M40" s="85" t="n"/>
-      <c r="N40" s="85" t="n"/>
-      <c r="O40" s="85" t="n"/>
-      <c r="P40" s="85" t="n"/>
-      <c r="Q40" s="116">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="85" t="n"/>
-      <c r="B41" s="85" t="n"/>
-      <c r="C41" s="85" t="n"/>
-      <c r="D41" s="85" t="n"/>
-      <c r="E41" s="85" t="n"/>
-      <c r="F41" s="85" t="n"/>
-      <c r="G41" s="85" t="n"/>
-      <c r="H41" s="85" t="n"/>
-      <c r="I41" s="85" t="n"/>
-      <c r="J41" s="85" t="n"/>
-      <c r="K41" s="85" t="n"/>
-      <c r="L41" s="85" t="n"/>
-      <c r="M41" s="85" t="n"/>
-      <c r="N41" s="85" t="n"/>
-      <c r="O41" s="85" t="n"/>
-      <c r="P41" s="85" t="n"/>
-      <c r="Q41" s="116">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="85" t="n"/>
-      <c r="B42" s="85" t="n"/>
-      <c r="C42" s="85" t="n"/>
-      <c r="D42" s="85" t="n"/>
-      <c r="E42" s="85" t="n"/>
-      <c r="F42" s="85" t="n"/>
-      <c r="G42" s="85" t="n"/>
-      <c r="H42" s="85" t="n"/>
-      <c r="I42" s="85" t="n"/>
-      <c r="J42" s="85" t="n"/>
-      <c r="K42" s="85" t="n"/>
-      <c r="L42" s="85" t="n"/>
-      <c r="M42" s="85" t="n"/>
-      <c r="N42" s="85" t="n"/>
-      <c r="O42" s="85" t="n"/>
-      <c r="P42" s="85" t="n"/>
-      <c r="Q42" s="116">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="85" t="n"/>
-      <c r="B43" s="85" t="n"/>
-      <c r="C43" s="85" t="n"/>
-      <c r="D43" s="85" t="n"/>
-      <c r="E43" s="85" t="n"/>
-      <c r="F43" s="85" t="n"/>
-      <c r="G43" s="85" t="n"/>
-      <c r="H43" s="85" t="n"/>
-      <c r="I43" s="85" t="n"/>
-      <c r="J43" s="85" t="n"/>
-      <c r="K43" s="85" t="n"/>
-      <c r="L43" s="85" t="n"/>
-      <c r="M43" s="85" t="n"/>
-      <c r="N43" s="85" t="n"/>
-      <c r="O43" s="85" t="n"/>
-      <c r="P43" s="85" t="n"/>
-      <c r="Q43" s="116">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="85" t="n"/>
-      <c r="B44" s="85" t="n"/>
-      <c r="C44" s="85" t="n"/>
-      <c r="D44" s="85" t="n"/>
-      <c r="E44" s="85" t="n"/>
-      <c r="F44" s="85" t="n"/>
-      <c r="G44" s="85" t="n"/>
-      <c r="H44" s="85" t="n"/>
-      <c r="I44" s="85" t="n"/>
-      <c r="J44" s="85" t="n"/>
-      <c r="K44" s="85" t="n"/>
-      <c r="L44" s="85" t="n"/>
-      <c r="M44" s="85" t="n"/>
-      <c r="N44" s="85" t="n"/>
-      <c r="O44" s="85" t="n"/>
-      <c r="P44" s="85" t="n"/>
-      <c r="Q44" s="116">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="85" t="n"/>
-      <c r="B45" s="85" t="n"/>
-      <c r="C45" s="85" t="n"/>
-      <c r="D45" s="85" t="n"/>
-      <c r="E45" s="85" t="n"/>
-      <c r="F45" s="85" t="n"/>
-      <c r="G45" s="85" t="n"/>
-      <c r="H45" s="85" t="n"/>
-      <c r="I45" s="85" t="n"/>
-      <c r="J45" s="85" t="n"/>
-      <c r="K45" s="85" t="n"/>
-      <c r="L45" s="85" t="n"/>
-      <c r="M45" s="85" t="n"/>
-      <c r="N45" s="85" t="n"/>
-      <c r="O45" s="85" t="n"/>
-      <c r="P45" s="85" t="n"/>
-      <c r="Q45" s="116">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="85" t="n"/>
-      <c r="B46" s="85" t="n"/>
-      <c r="C46" s="85" t="n"/>
-      <c r="D46" s="85" t="n"/>
-      <c r="E46" s="85" t="n"/>
-      <c r="F46" s="85" t="n"/>
-      <c r="G46" s="85" t="n"/>
-      <c r="H46" s="85" t="n"/>
-      <c r="I46" s="85" t="n"/>
-      <c r="J46" s="85" t="n"/>
-      <c r="K46" s="85" t="n"/>
-      <c r="L46" s="85" t="n"/>
-      <c r="M46" s="85" t="n"/>
-      <c r="N46" s="85" t="n"/>
-      <c r="O46" s="85" t="n"/>
-      <c r="P46" s="85" t="n"/>
-      <c r="Q46" s="116">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="85" t="n"/>
-      <c r="B47" s="85" t="n"/>
-      <c r="C47" s="85" t="n"/>
-      <c r="D47" s="85" t="n"/>
-      <c r="E47" s="85" t="n"/>
-      <c r="F47" s="85" t="n"/>
-      <c r="G47" s="85" t="n"/>
-      <c r="H47" s="85" t="n"/>
-      <c r="I47" s="85" t="n"/>
-      <c r="J47" s="85" t="n"/>
-      <c r="K47" s="85" t="n"/>
-      <c r="L47" s="85" t="n"/>
-      <c r="M47" s="85" t="n"/>
-      <c r="N47" s="85" t="n"/>
-      <c r="O47" s="85" t="n"/>
-      <c r="P47" s="85" t="n"/>
-      <c r="Q47" s="116">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="85" t="n"/>
-      <c r="B48" s="85" t="n"/>
-      <c r="C48" s="85" t="n"/>
-      <c r="D48" s="85" t="n"/>
-      <c r="E48" s="85" t="n"/>
-      <c r="F48" s="85" t="n"/>
-      <c r="G48" s="85" t="n"/>
-      <c r="H48" s="85" t="n"/>
-      <c r="I48" s="85" t="n"/>
-      <c r="J48" s="85" t="n"/>
-      <c r="K48" s="85" t="n"/>
-      <c r="L48" s="85" t="n"/>
-      <c r="M48" s="85" t="n"/>
-      <c r="N48" s="85" t="n"/>
-      <c r="O48" s="85" t="n"/>
-      <c r="P48" s="85" t="n"/>
-      <c r="Q48" s="116">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="54" customHeight="1">
-      <c r="A49" s="103" t="inlineStr">
-        <is>
-          <t>MS-023</t>
-        </is>
-      </c>
-      <c r="B49" s="104" t="inlineStr">
-        <is>
-          <t>عملکرد واقعی اندازه‌گیری</t>
-        </is>
-      </c>
-      <c r="C49" s="106" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D49" s="104" t="inlineStr">
-        <is>
-          <t>منبع دقیق آزمایشگاهی و مولتی‌متر</t>
-        </is>
-      </c>
-      <c r="E49" s="104" t="inlineStr">
         <is>
           <t>گام ۱: منبع را دقیقاً روی 24.0 ولت تنظیم کن و به ورودی وصل کن؛ یک باتری 24 ولت هم وصل باشد.
 گام ۲: ولتاژ منبع را با مولتی‌متر خودت هم اندازه بگیر.
@@ -3223,68 +1983,141 @@
 گام ۴: هر دو باید نزدیک همان عددی باشند که مولتی‌متر می‌گوید؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F49" s="104" t="inlineStr">
+      <c r="F8" s="104" t="inlineStr">
         <is>
           <t>ورودی و باتری 24 ولت</t>
         </is>
       </c>
-      <c r="G49" s="106" t="inlineStr">
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H49" s="104" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>عددهای پنل نزدیک مقدار واقعی مولتی‌متر</t>
         </is>
       </c>
-      <c r="I49" s="104" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="104" t="inlineStr">
+      <c r="I8" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید: عددهای پنل نزدیک مقدار واقعی مولتی‌مترند. اگر دور بودند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J8" s="104" t="inlineStr">
         <is>
           <t>اختلاف پنل با مولتی‌متر کم و منطقی باشد</t>
         </is>
       </c>
-      <c r="K49" s="104" t="inlineStr"/>
-      <c r="L49" s="117" t="inlineStr">
+      <c r="K8" s="104" t="n"/>
+      <c r="L8" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M49" s="104" t="n"/>
-      <c r="N49" s="104" t="n"/>
-      <c r="O49" s="106" t="n"/>
-      <c r="P49" s="106" t="n"/>
-      <c r="Q49" s="110">
+      <c r="M8" s="104" t="n"/>
+      <c r="N8" s="104" t="n"/>
+      <c r="O8" s="106" t="n"/>
+      <c r="P8" s="106">
+        <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="110">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="54" customHeight="1">
-      <c r="A50" s="103" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="103" t="inlineStr">
+        <is>
+          <t>MS-021</t>
+        </is>
+      </c>
+      <c r="B9" s="104" t="inlineStr">
+        <is>
+          <t>کالیبراسیون برد / tolerance</t>
+        </is>
+      </c>
+      <c r="C9" s="106" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="104" t="inlineStr">
+        <is>
+          <t>مولتی‌متر مرجع مطمئن و پنل در حالت کالیبراسیون</t>
+        </is>
+      </c>
+      <c r="E9" s="104" t="inlineStr">
+        <is>
+          <t>گام ۱: طبق راهنمای پنل، در یک ولتاژ پایین و یک ولتاژ بالا عدد دستگاه را با مولتی‌متر یکی کن.
+گام ۲: در یک ولتاژ میانی هر دو را مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F9" s="106" t="inlineStr">
+        <is>
+          <t>کالیبراسیون دو نقطه و چک میانی</t>
+        </is>
+      </c>
+      <c r="G9" s="106" t="inlineStr">
+        <is>
+          <t>ربع ساعت</t>
+        </is>
+      </c>
+      <c r="H9" s="104" t="inlineStr">
+        <is>
+          <t>بعد از کالیبراسیون، عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند</t>
+        </is>
+      </c>
+      <c r="I9" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از کالیبراسیون عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند. اگر اختلاف محسوس داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J9" s="107" t="n"/>
+      <c r="K9" s="108" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="109" t="n"/>
+      <c r="M9" s="104" t="n"/>
+      <c r="N9" s="104" t="inlineStr">
+        <is>
+          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+        </is>
+      </c>
+      <c r="O9" s="106" t="n"/>
+      <c r="P9" s="106">
+        <f>IF(OR(K9="",K9="در انتظار"),"",IF(P9="",TODAY(),P9))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="110">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="103" t="inlineStr">
         <is>
           <t>MS-024</t>
         </is>
       </c>
-      <c r="B50" s="111" t="inlineStr">
+      <c r="B10" s="111" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C50" s="113" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D50" s="111" t="inlineStr">
+      <c r="C10" s="113" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="111" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل عددها را نشان می‌دهد</t>
         </is>
       </c>
-      <c r="E50" s="111" t="inlineStr">
+      <c r="E10" s="111" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه روشن باشد و در پنل عددهای ولتاژ را ببین.
 گام ۲: ورودی را کامل قطع کن (صفر ولت).
@@ -3292,68 +2125,71 @@
 گام ۴: دستگاه نباید خطای اندازه‌گیری بگیرد یا خاموش شود.</t>
         </is>
       </c>
-      <c r="F50" s="111" t="inlineStr">
+      <c r="F10" s="111" t="inlineStr">
         <is>
           <t>قطع کامل ورودی</t>
         </is>
       </c>
-      <c r="G50" s="113" t="inlineStr">
+      <c r="G10" s="113" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H50" s="111" t="inlineStr">
+      <c r="H10" s="111" t="inlineStr">
         <is>
           <t>ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم</t>
         </is>
       </c>
-      <c r="I50" s="111" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="111" t="inlineStr">
+      <c r="I10" s="111" t="inlineStr">
+        <is>
+          <t>باید ببینید: با ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم و عادی‌اند. اگر بقیه هم خراب شدند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J10" s="111" t="inlineStr">
         <is>
           <t>فقط ورودی صفر شود و دستگاه عادی بماند</t>
         </is>
       </c>
-      <c r="K50" s="111" t="inlineStr"/>
-      <c r="L50" s="117" t="inlineStr">
+      <c r="K10" s="111" t="n"/>
+      <c r="L10" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M50" s="111" t="n"/>
-      <c r="N50" s="111" t="n"/>
-      <c r="O50" s="113" t="n"/>
-      <c r="P50" s="113" t="n"/>
-      <c r="Q50" s="115">
+      <c r="M10" s="111" t="n"/>
+      <c r="N10" s="111" t="n"/>
+      <c r="O10" s="113" t="n"/>
+      <c r="P10" s="113">
+        <f>IF(OR(K10="",K10="در انتظار"),"",IF(P10="",TODAY(),P10))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="115">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="54" customHeight="1">
-      <c r="A51" s="103" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="103" t="inlineStr">
         <is>
           <t>MS-025</t>
         </is>
       </c>
-      <c r="B51" s="104" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C51" s="106" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D51" s="104" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>بار معلوم و مولتی‌متر سری</t>
         </is>
       </c>
-      <c r="E51" s="104" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>گام ۱: یک بار معلوم روی مسیر شارژ بگذار و جریان واقعی را با مولتی‌متر اندازه بگیر (مثلاً باری که حدود 500 میلی‌آمپر می‌کشد).
 گام ۲: شارژ را راه بینداز.
@@ -3361,45 +2197,808 @@
 گام ۴: باید نزدیک هم باشند؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F51" s="104" t="inlineStr">
+      <c r="F11" s="104" t="inlineStr">
         <is>
           <t>بار حدود 500 میلی‌آمپر</t>
         </is>
       </c>
-      <c r="G51" s="106" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H51" s="104" t="inlineStr">
+      <c r="H11" s="104" t="inlineStr">
         <is>
           <t>جریان پنل نزدیک جریان واقعی</t>
         </is>
       </c>
-      <c r="I51" s="104" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="104" t="inlineStr">
+      <c r="I11" s="104" t="inlineStr">
+        <is>
+          <t>باید ببینید: جریان پنل نزدیک جریان واقعی است. اگر دور بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="J11" s="104" t="inlineStr">
         <is>
           <t>اختلاف جریان پنل با مولتی‌متر کم باشد</t>
         </is>
       </c>
-      <c r="K51" s="104" t="inlineStr"/>
-      <c r="L51" s="117" t="inlineStr">
+      <c r="K11" s="104" t="n"/>
+      <c r="L11" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M51" s="104" t="n"/>
-      <c r="N51" s="104" t="n"/>
-      <c r="O51" s="106" t="n"/>
-      <c r="P51" s="106" t="n"/>
-      <c r="Q51" s="110">
+      <c r="M11" s="104" t="n"/>
+      <c r="N11" s="104" t="n"/>
+      <c r="O11" s="106" t="n"/>
+      <c r="P11" s="106">
+        <f>IF(OR(K11="",K11="در انتظار"),"",IF(P11="",TODAY(),P11))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="110">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="136" t="n"/>
+      <c r="B12" s="136" t="n"/>
+      <c r="C12" s="136" t="n"/>
+      <c r="D12" s="136" t="n"/>
+      <c r="E12" s="136" t="n"/>
+      <c r="F12" s="136" t="n"/>
+      <c r="G12" s="136" t="n"/>
+      <c r="H12" s="136" t="n"/>
+      <c r="I12" s="136" t="n"/>
+      <c r="J12" s="136" t="n"/>
+      <c r="K12" s="136" t="n"/>
+      <c r="L12" s="136" t="n"/>
+      <c r="M12" s="136" t="n"/>
+      <c r="N12" s="136" t="n"/>
+      <c r="O12" s="136" t="n"/>
+      <c r="P12" s="136" t="n"/>
+      <c r="Q12" s="137" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="136" t="n"/>
+      <c r="B13" s="136" t="n"/>
+      <c r="C13" s="136" t="n"/>
+      <c r="D13" s="136" t="n"/>
+      <c r="E13" s="136" t="n"/>
+      <c r="F13" s="136" t="n"/>
+      <c r="G13" s="136" t="n"/>
+      <c r="H13" s="136" t="n"/>
+      <c r="I13" s="136" t="n"/>
+      <c r="J13" s="136" t="n"/>
+      <c r="K13" s="136" t="n"/>
+      <c r="L13" s="136" t="n"/>
+      <c r="M13" s="136" t="n"/>
+      <c r="N13" s="136" t="n"/>
+      <c r="O13" s="136" t="n"/>
+      <c r="P13" s="136" t="n"/>
+      <c r="Q13" s="137" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="136" t="n"/>
+      <c r="B14" s="136" t="n"/>
+      <c r="C14" s="136" t="n"/>
+      <c r="D14" s="136" t="n"/>
+      <c r="E14" s="136" t="n"/>
+      <c r="F14" s="136" t="n"/>
+      <c r="G14" s="136" t="n"/>
+      <c r="H14" s="136" t="n"/>
+      <c r="I14" s="136" t="n"/>
+      <c r="J14" s="136" t="n"/>
+      <c r="K14" s="136" t="n"/>
+      <c r="L14" s="136" t="n"/>
+      <c r="M14" s="136" t="n"/>
+      <c r="N14" s="136" t="n"/>
+      <c r="O14" s="136" t="n"/>
+      <c r="P14" s="136" t="n"/>
+      <c r="Q14" s="137" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="136" t="n"/>
+      <c r="B15" s="136" t="n"/>
+      <c r="C15" s="136" t="n"/>
+      <c r="D15" s="136" t="n"/>
+      <c r="E15" s="136" t="n"/>
+      <c r="F15" s="136" t="n"/>
+      <c r="G15" s="136" t="n"/>
+      <c r="H15" s="136" t="n"/>
+      <c r="I15" s="136" t="n"/>
+      <c r="J15" s="136" t="n"/>
+      <c r="K15" s="136" t="n"/>
+      <c r="L15" s="136" t="n"/>
+      <c r="M15" s="136" t="n"/>
+      <c r="N15" s="136" t="n"/>
+      <c r="O15" s="136" t="n"/>
+      <c r="P15" s="136" t="n"/>
+      <c r="Q15" s="137" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="136" t="n"/>
+      <c r="B16" s="136" t="n"/>
+      <c r="C16" s="136" t="n"/>
+      <c r="D16" s="136" t="n"/>
+      <c r="E16" s="136" t="n"/>
+      <c r="F16" s="136" t="n"/>
+      <c r="G16" s="136" t="n"/>
+      <c r="H16" s="136" t="n"/>
+      <c r="I16" s="136" t="n"/>
+      <c r="J16" s="136" t="n"/>
+      <c r="K16" s="136" t="n"/>
+      <c r="L16" s="136" t="n"/>
+      <c r="M16" s="136" t="n"/>
+      <c r="N16" s="136" t="n"/>
+      <c r="O16" s="136" t="n"/>
+      <c r="P16" s="136" t="n"/>
+      <c r="Q16" s="137" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="136" t="n"/>
+      <c r="B17" s="136" t="n"/>
+      <c r="C17" s="136" t="n"/>
+      <c r="D17" s="136" t="n"/>
+      <c r="E17" s="136" t="n"/>
+      <c r="F17" s="136" t="n"/>
+      <c r="G17" s="136" t="n"/>
+      <c r="H17" s="136" t="n"/>
+      <c r="I17" s="136" t="n"/>
+      <c r="J17" s="136" t="n"/>
+      <c r="K17" s="136" t="n"/>
+      <c r="L17" s="136" t="n"/>
+      <c r="M17" s="136" t="n"/>
+      <c r="N17" s="136" t="n"/>
+      <c r="O17" s="136" t="n"/>
+      <c r="P17" s="136" t="n"/>
+      <c r="Q17" s="137" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="136" t="n"/>
+      <c r="B18" s="136" t="n"/>
+      <c r="C18" s="136" t="n"/>
+      <c r="D18" s="136" t="n"/>
+      <c r="E18" s="136" t="n"/>
+      <c r="F18" s="136" t="n"/>
+      <c r="G18" s="136" t="n"/>
+      <c r="H18" s="136" t="n"/>
+      <c r="I18" s="136" t="n"/>
+      <c r="J18" s="136" t="n"/>
+      <c r="K18" s="136" t="n"/>
+      <c r="L18" s="136" t="n"/>
+      <c r="M18" s="136" t="n"/>
+      <c r="N18" s="136" t="n"/>
+      <c r="O18" s="136" t="n"/>
+      <c r="P18" s="136" t="n"/>
+      <c r="Q18" s="137" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="136" t="n"/>
+      <c r="B19" s="136" t="n"/>
+      <c r="C19" s="136" t="n"/>
+      <c r="D19" s="136" t="n"/>
+      <c r="E19" s="136" t="n"/>
+      <c r="F19" s="136" t="n"/>
+      <c r="G19" s="136" t="n"/>
+      <c r="H19" s="136" t="n"/>
+      <c r="I19" s="136" t="n"/>
+      <c r="J19" s="136" t="n"/>
+      <c r="K19" s="136" t="n"/>
+      <c r="L19" s="136" t="n"/>
+      <c r="M19" s="136" t="n"/>
+      <c r="N19" s="136" t="n"/>
+      <c r="O19" s="136" t="n"/>
+      <c r="P19" s="136" t="n"/>
+      <c r="Q19" s="137" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="136" t="n"/>
+      <c r="B20" s="136" t="n"/>
+      <c r="C20" s="136" t="n"/>
+      <c r="D20" s="136" t="n"/>
+      <c r="E20" s="136" t="n"/>
+      <c r="F20" s="136" t="n"/>
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="136" t="n"/>
+      <c r="I20" s="136" t="n"/>
+      <c r="J20" s="136" t="n"/>
+      <c r="K20" s="136" t="n"/>
+      <c r="L20" s="136" t="n"/>
+      <c r="M20" s="136" t="n"/>
+      <c r="N20" s="136" t="n"/>
+      <c r="O20" s="136" t="n"/>
+      <c r="P20" s="136" t="n"/>
+      <c r="Q20" s="137" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="136" t="n"/>
+      <c r="B21" s="136" t="n"/>
+      <c r="C21" s="136" t="n"/>
+      <c r="D21" s="136" t="n"/>
+      <c r="E21" s="136" t="n"/>
+      <c r="F21" s="136" t="n"/>
+      <c r="G21" s="136" t="n"/>
+      <c r="H21" s="136" t="n"/>
+      <c r="I21" s="136" t="n"/>
+      <c r="J21" s="136" t="n"/>
+      <c r="K21" s="136" t="n"/>
+      <c r="L21" s="136" t="n"/>
+      <c r="M21" s="136" t="n"/>
+      <c r="N21" s="136" t="n"/>
+      <c r="O21" s="136" t="n"/>
+      <c r="P21" s="136" t="n"/>
+      <c r="Q21" s="137" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="136" t="n"/>
+      <c r="B22" s="136" t="n"/>
+      <c r="C22" s="136" t="n"/>
+      <c r="D22" s="136" t="n"/>
+      <c r="E22" s="136" t="n"/>
+      <c r="F22" s="136" t="n"/>
+      <c r="G22" s="136" t="n"/>
+      <c r="H22" s="136" t="n"/>
+      <c r="I22" s="136" t="n"/>
+      <c r="J22" s="136" t="n"/>
+      <c r="K22" s="136" t="n"/>
+      <c r="L22" s="136" t="n"/>
+      <c r="M22" s="136" t="n"/>
+      <c r="N22" s="136" t="n"/>
+      <c r="O22" s="136" t="n"/>
+      <c r="P22" s="136" t="n"/>
+      <c r="Q22" s="137" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="136" t="n"/>
+      <c r="B23" s="136" t="n"/>
+      <c r="C23" s="136" t="n"/>
+      <c r="D23" s="136" t="n"/>
+      <c r="E23" s="136" t="n"/>
+      <c r="F23" s="136" t="n"/>
+      <c r="G23" s="136" t="n"/>
+      <c r="H23" s="136" t="n"/>
+      <c r="I23" s="136" t="n"/>
+      <c r="J23" s="136" t="n"/>
+      <c r="K23" s="136" t="n"/>
+      <c r="L23" s="136" t="n"/>
+      <c r="M23" s="136" t="n"/>
+      <c r="N23" s="136" t="n"/>
+      <c r="O23" s="136" t="n"/>
+      <c r="P23" s="136" t="n"/>
+      <c r="Q23" s="137" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="136" t="n"/>
+      <c r="B24" s="136" t="n"/>
+      <c r="C24" s="136" t="n"/>
+      <c r="D24" s="136" t="n"/>
+      <c r="E24" s="136" t="n"/>
+      <c r="F24" s="136" t="n"/>
+      <c r="G24" s="136" t="n"/>
+      <c r="H24" s="136" t="n"/>
+      <c r="I24" s="136" t="n"/>
+      <c r="J24" s="136" t="n"/>
+      <c r="K24" s="136" t="n"/>
+      <c r="L24" s="136" t="n"/>
+      <c r="M24" s="136" t="n"/>
+      <c r="N24" s="136" t="n"/>
+      <c r="O24" s="136" t="n"/>
+      <c r="P24" s="136" t="n"/>
+      <c r="Q24" s="137" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="136" t="n"/>
+      <c r="B25" s="136" t="n"/>
+      <c r="C25" s="136" t="n"/>
+      <c r="D25" s="136" t="n"/>
+      <c r="E25" s="136" t="n"/>
+      <c r="F25" s="136" t="n"/>
+      <c r="G25" s="136" t="n"/>
+      <c r="H25" s="136" t="n"/>
+      <c r="I25" s="136" t="n"/>
+      <c r="J25" s="136" t="n"/>
+      <c r="K25" s="136" t="n"/>
+      <c r="L25" s="136" t="n"/>
+      <c r="M25" s="136" t="n"/>
+      <c r="N25" s="136" t="n"/>
+      <c r="O25" s="136" t="n"/>
+      <c r="P25" s="136" t="n"/>
+      <c r="Q25" s="137" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="136" t="n"/>
+      <c r="B26" s="136" t="n"/>
+      <c r="C26" s="136" t="n"/>
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="136" t="n"/>
+      <c r="F26" s="136" t="n"/>
+      <c r="G26" s="136" t="n"/>
+      <c r="H26" s="136" t="n"/>
+      <c r="I26" s="136" t="n"/>
+      <c r="J26" s="136" t="n"/>
+      <c r="K26" s="136" t="n"/>
+      <c r="L26" s="136" t="n"/>
+      <c r="M26" s="136" t="n"/>
+      <c r="N26" s="136" t="n"/>
+      <c r="O26" s="136" t="n"/>
+      <c r="P26" s="136" t="n"/>
+      <c r="Q26" s="137" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="136" t="n"/>
+      <c r="B27" s="136" t="n"/>
+      <c r="C27" s="136" t="n"/>
+      <c r="D27" s="136" t="n"/>
+      <c r="E27" s="136" t="n"/>
+      <c r="F27" s="136" t="n"/>
+      <c r="G27" s="136" t="n"/>
+      <c r="H27" s="136" t="n"/>
+      <c r="I27" s="136" t="n"/>
+      <c r="J27" s="136" t="n"/>
+      <c r="K27" s="136" t="n"/>
+      <c r="L27" s="136" t="n"/>
+      <c r="M27" s="136" t="n"/>
+      <c r="N27" s="136" t="n"/>
+      <c r="O27" s="136" t="n"/>
+      <c r="P27" s="136" t="n"/>
+      <c r="Q27" s="137" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="136" t="n"/>
+      <c r="B28" s="136" t="n"/>
+      <c r="C28" s="136" t="n"/>
+      <c r="D28" s="136" t="n"/>
+      <c r="E28" s="136" t="n"/>
+      <c r="F28" s="136" t="n"/>
+      <c r="G28" s="136" t="n"/>
+      <c r="H28" s="136" t="n"/>
+      <c r="I28" s="136" t="n"/>
+      <c r="J28" s="136" t="n"/>
+      <c r="K28" s="136" t="n"/>
+      <c r="L28" s="136" t="n"/>
+      <c r="M28" s="136" t="n"/>
+      <c r="N28" s="136" t="n"/>
+      <c r="O28" s="136" t="n"/>
+      <c r="P28" s="136" t="n"/>
+      <c r="Q28" s="137" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="136" t="n"/>
+      <c r="B29" s="136" t="n"/>
+      <c r="C29" s="136" t="n"/>
+      <c r="D29" s="136" t="n"/>
+      <c r="E29" s="136" t="n"/>
+      <c r="F29" s="136" t="n"/>
+      <c r="G29" s="136" t="n"/>
+      <c r="H29" s="136" t="n"/>
+      <c r="I29" s="136" t="n"/>
+      <c r="J29" s="136" t="n"/>
+      <c r="K29" s="136" t="n"/>
+      <c r="L29" s="136" t="n"/>
+      <c r="M29" s="136" t="n"/>
+      <c r="N29" s="136" t="n"/>
+      <c r="O29" s="136" t="n"/>
+      <c r="P29" s="136" t="n"/>
+      <c r="Q29" s="137" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="136" t="n"/>
+      <c r="B30" s="136" t="n"/>
+      <c r="C30" s="136" t="n"/>
+      <c r="D30" s="136" t="n"/>
+      <c r="E30" s="136" t="n"/>
+      <c r="F30" s="136" t="n"/>
+      <c r="G30" s="136" t="n"/>
+      <c r="H30" s="136" t="n"/>
+      <c r="I30" s="136" t="n"/>
+      <c r="J30" s="136" t="n"/>
+      <c r="K30" s="136" t="n"/>
+      <c r="L30" s="136" t="n"/>
+      <c r="M30" s="136" t="n"/>
+      <c r="N30" s="136" t="n"/>
+      <c r="O30" s="136" t="n"/>
+      <c r="P30" s="136" t="n"/>
+      <c r="Q30" s="137" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="136" t="n"/>
+      <c r="B31" s="136" t="n"/>
+      <c r="C31" s="136" t="n"/>
+      <c r="D31" s="136" t="n"/>
+      <c r="E31" s="136" t="n"/>
+      <c r="F31" s="136" t="n"/>
+      <c r="G31" s="136" t="n"/>
+      <c r="H31" s="136" t="n"/>
+      <c r="I31" s="136" t="n"/>
+      <c r="J31" s="136" t="n"/>
+      <c r="K31" s="136" t="n"/>
+      <c r="L31" s="136" t="n"/>
+      <c r="M31" s="136" t="n"/>
+      <c r="N31" s="136" t="n"/>
+      <c r="O31" s="136" t="n"/>
+      <c r="P31" s="136" t="n"/>
+      <c r="Q31" s="137" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="136" t="n"/>
+      <c r="B32" s="136" t="n"/>
+      <c r="C32" s="136" t="n"/>
+      <c r="D32" s="136" t="n"/>
+      <c r="E32" s="136" t="n"/>
+      <c r="F32" s="136" t="n"/>
+      <c r="G32" s="136" t="n"/>
+      <c r="H32" s="136" t="n"/>
+      <c r="I32" s="136" t="n"/>
+      <c r="J32" s="136" t="n"/>
+      <c r="K32" s="136" t="n"/>
+      <c r="L32" s="136" t="n"/>
+      <c r="M32" s="136" t="n"/>
+      <c r="N32" s="136" t="n"/>
+      <c r="O32" s="136" t="n"/>
+      <c r="P32" s="136" t="n"/>
+      <c r="Q32" s="137" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="136" t="n"/>
+      <c r="B33" s="136" t="n"/>
+      <c r="C33" s="136" t="n"/>
+      <c r="D33" s="136" t="n"/>
+      <c r="E33" s="136" t="n"/>
+      <c r="F33" s="136" t="n"/>
+      <c r="G33" s="136" t="n"/>
+      <c r="H33" s="136" t="n"/>
+      <c r="I33" s="136" t="n"/>
+      <c r="J33" s="136" t="n"/>
+      <c r="K33" s="136" t="n"/>
+      <c r="L33" s="136" t="n"/>
+      <c r="M33" s="136" t="n"/>
+      <c r="N33" s="136" t="n"/>
+      <c r="O33" s="136" t="n"/>
+      <c r="P33" s="136" t="n"/>
+      <c r="Q33" s="137" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="136" t="n"/>
+      <c r="B34" s="136" t="n"/>
+      <c r="C34" s="136" t="n"/>
+      <c r="D34" s="136" t="n"/>
+      <c r="E34" s="136" t="n"/>
+      <c r="F34" s="136" t="n"/>
+      <c r="G34" s="136" t="n"/>
+      <c r="H34" s="136" t="n"/>
+      <c r="I34" s="136" t="n"/>
+      <c r="J34" s="136" t="n"/>
+      <c r="K34" s="136" t="n"/>
+      <c r="L34" s="136" t="n"/>
+      <c r="M34" s="136" t="n"/>
+      <c r="N34" s="136" t="n"/>
+      <c r="O34" s="136" t="n"/>
+      <c r="P34" s="136" t="n"/>
+      <c r="Q34" s="137" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="136" t="n"/>
+      <c r="B35" s="136" t="n"/>
+      <c r="C35" s="136" t="n"/>
+      <c r="D35" s="136" t="n"/>
+      <c r="E35" s="136" t="n"/>
+      <c r="F35" s="136" t="n"/>
+      <c r="G35" s="136" t="n"/>
+      <c r="H35" s="136" t="n"/>
+      <c r="I35" s="136" t="n"/>
+      <c r="J35" s="136" t="n"/>
+      <c r="K35" s="136" t="n"/>
+      <c r="L35" s="136" t="n"/>
+      <c r="M35" s="136" t="n"/>
+      <c r="N35" s="136" t="n"/>
+      <c r="O35" s="136" t="n"/>
+      <c r="P35" s="136" t="n"/>
+      <c r="Q35" s="137" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="136" t="n"/>
+      <c r="B36" s="136" t="n"/>
+      <c r="C36" s="136" t="n"/>
+      <c r="D36" s="136" t="n"/>
+      <c r="E36" s="136" t="n"/>
+      <c r="F36" s="136" t="n"/>
+      <c r="G36" s="136" t="n"/>
+      <c r="H36" s="136" t="n"/>
+      <c r="I36" s="136" t="n"/>
+      <c r="J36" s="136" t="n"/>
+      <c r="K36" s="136" t="n"/>
+      <c r="L36" s="136" t="n"/>
+      <c r="M36" s="136" t="n"/>
+      <c r="N36" s="136" t="n"/>
+      <c r="O36" s="136" t="n"/>
+      <c r="P36" s="136" t="n"/>
+      <c r="Q36" s="137" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="136" t="n"/>
+      <c r="B37" s="136" t="n"/>
+      <c r="C37" s="136" t="n"/>
+      <c r="D37" s="136" t="n"/>
+      <c r="E37" s="136" t="n"/>
+      <c r="F37" s="136" t="n"/>
+      <c r="G37" s="136" t="n"/>
+      <c r="H37" s="136" t="n"/>
+      <c r="I37" s="136" t="n"/>
+      <c r="J37" s="136" t="n"/>
+      <c r="K37" s="136" t="n"/>
+      <c r="L37" s="136" t="n"/>
+      <c r="M37" s="136" t="n"/>
+      <c r="N37" s="136" t="n"/>
+      <c r="O37" s="136" t="n"/>
+      <c r="P37" s="136" t="n"/>
+      <c r="Q37" s="137" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="136" t="n"/>
+      <c r="B38" s="136" t="n"/>
+      <c r="C38" s="136" t="n"/>
+      <c r="D38" s="136" t="n"/>
+      <c r="E38" s="136" t="n"/>
+      <c r="F38" s="136" t="n"/>
+      <c r="G38" s="136" t="n"/>
+      <c r="H38" s="136" t="n"/>
+      <c r="I38" s="136" t="n"/>
+      <c r="J38" s="136" t="n"/>
+      <c r="K38" s="136" t="n"/>
+      <c r="L38" s="136" t="n"/>
+      <c r="M38" s="136" t="n"/>
+      <c r="N38" s="136" t="n"/>
+      <c r="O38" s="136" t="n"/>
+      <c r="P38" s="136" t="n"/>
+      <c r="Q38" s="137" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="136" t="n"/>
+      <c r="B39" s="136" t="n"/>
+      <c r="C39" s="136" t="n"/>
+      <c r="D39" s="136" t="n"/>
+      <c r="E39" s="136" t="n"/>
+      <c r="F39" s="136" t="n"/>
+      <c r="G39" s="136" t="n"/>
+      <c r="H39" s="136" t="n"/>
+      <c r="I39" s="136" t="n"/>
+      <c r="J39" s="136" t="n"/>
+      <c r="K39" s="136" t="n"/>
+      <c r="L39" s="136" t="n"/>
+      <c r="M39" s="136" t="n"/>
+      <c r="N39" s="136" t="n"/>
+      <c r="O39" s="136" t="n"/>
+      <c r="P39" s="136" t="n"/>
+      <c r="Q39" s="137" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="136" t="n"/>
+      <c r="B40" s="136" t="n"/>
+      <c r="C40" s="136" t="n"/>
+      <c r="D40" s="136" t="n"/>
+      <c r="E40" s="136" t="n"/>
+      <c r="F40" s="136" t="n"/>
+      <c r="G40" s="136" t="n"/>
+      <c r="H40" s="136" t="n"/>
+      <c r="I40" s="136" t="n"/>
+      <c r="J40" s="136" t="n"/>
+      <c r="K40" s="136" t="n"/>
+      <c r="L40" s="136" t="n"/>
+      <c r="M40" s="136" t="n"/>
+      <c r="N40" s="136" t="n"/>
+      <c r="O40" s="136" t="n"/>
+      <c r="P40" s="136" t="n"/>
+      <c r="Q40" s="137" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="136" t="n"/>
+      <c r="B41" s="136" t="n"/>
+      <c r="C41" s="136" t="n"/>
+      <c r="D41" s="136" t="n"/>
+      <c r="E41" s="136" t="n"/>
+      <c r="F41" s="136" t="n"/>
+      <c r="G41" s="136" t="n"/>
+      <c r="H41" s="136" t="n"/>
+      <c r="I41" s="136" t="n"/>
+      <c r="J41" s="136" t="n"/>
+      <c r="K41" s="136" t="n"/>
+      <c r="L41" s="136" t="n"/>
+      <c r="M41" s="136" t="n"/>
+      <c r="N41" s="136" t="n"/>
+      <c r="O41" s="136" t="n"/>
+      <c r="P41" s="136" t="n"/>
+      <c r="Q41" s="137" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="136" t="n"/>
+      <c r="B42" s="136" t="n"/>
+      <c r="C42" s="136" t="n"/>
+      <c r="D42" s="136" t="n"/>
+      <c r="E42" s="136" t="n"/>
+      <c r="F42" s="136" t="n"/>
+      <c r="G42" s="136" t="n"/>
+      <c r="H42" s="136" t="n"/>
+      <c r="I42" s="136" t="n"/>
+      <c r="J42" s="136" t="n"/>
+      <c r="K42" s="136" t="n"/>
+      <c r="L42" s="136" t="n"/>
+      <c r="M42" s="136" t="n"/>
+      <c r="N42" s="136" t="n"/>
+      <c r="O42" s="136" t="n"/>
+      <c r="P42" s="136" t="n"/>
+      <c r="Q42" s="137" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="136" t="n"/>
+      <c r="B43" s="136" t="n"/>
+      <c r="C43" s="136" t="n"/>
+      <c r="D43" s="136" t="n"/>
+      <c r="E43" s="136" t="n"/>
+      <c r="F43" s="136" t="n"/>
+      <c r="G43" s="136" t="n"/>
+      <c r="H43" s="136" t="n"/>
+      <c r="I43" s="136" t="n"/>
+      <c r="J43" s="136" t="n"/>
+      <c r="K43" s="136" t="n"/>
+      <c r="L43" s="136" t="n"/>
+      <c r="M43" s="136" t="n"/>
+      <c r="N43" s="136" t="n"/>
+      <c r="O43" s="136" t="n"/>
+      <c r="P43" s="136" t="n"/>
+      <c r="Q43" s="137" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="136" t="n"/>
+      <c r="B44" s="136" t="n"/>
+      <c r="C44" s="136" t="n"/>
+      <c r="D44" s="136" t="n"/>
+      <c r="E44" s="136" t="n"/>
+      <c r="F44" s="136" t="n"/>
+      <c r="G44" s="136" t="n"/>
+      <c r="H44" s="136" t="n"/>
+      <c r="I44" s="136" t="n"/>
+      <c r="J44" s="136" t="n"/>
+      <c r="K44" s="136" t="n"/>
+      <c r="L44" s="136" t="n"/>
+      <c r="M44" s="136" t="n"/>
+      <c r="N44" s="136" t="n"/>
+      <c r="O44" s="136" t="n"/>
+      <c r="P44" s="136" t="n"/>
+      <c r="Q44" s="137" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="136" t="n"/>
+      <c r="B45" s="136" t="n"/>
+      <c r="C45" s="136" t="n"/>
+      <c r="D45" s="136" t="n"/>
+      <c r="E45" s="136" t="n"/>
+      <c r="F45" s="136" t="n"/>
+      <c r="G45" s="136" t="n"/>
+      <c r="H45" s="136" t="n"/>
+      <c r="I45" s="136" t="n"/>
+      <c r="J45" s="136" t="n"/>
+      <c r="K45" s="136" t="n"/>
+      <c r="L45" s="136" t="n"/>
+      <c r="M45" s="136" t="n"/>
+      <c r="N45" s="136" t="n"/>
+      <c r="O45" s="136" t="n"/>
+      <c r="P45" s="136" t="n"/>
+      <c r="Q45" s="137" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="136" t="n"/>
+      <c r="B46" s="136" t="n"/>
+      <c r="C46" s="136" t="n"/>
+      <c r="D46" s="136" t="n"/>
+      <c r="E46" s="136" t="n"/>
+      <c r="F46" s="136" t="n"/>
+      <c r="G46" s="136" t="n"/>
+      <c r="H46" s="136" t="n"/>
+      <c r="I46" s="136" t="n"/>
+      <c r="J46" s="136" t="n"/>
+      <c r="K46" s="136" t="n"/>
+      <c r="L46" s="136" t="n"/>
+      <c r="M46" s="136" t="n"/>
+      <c r="N46" s="136" t="n"/>
+      <c r="O46" s="136" t="n"/>
+      <c r="P46" s="136" t="n"/>
+      <c r="Q46" s="137" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="136" t="n"/>
+      <c r="B47" s="136" t="n"/>
+      <c r="C47" s="136" t="n"/>
+      <c r="D47" s="136" t="n"/>
+      <c r="E47" s="136" t="n"/>
+      <c r="F47" s="136" t="n"/>
+      <c r="G47" s="136" t="n"/>
+      <c r="H47" s="136" t="n"/>
+      <c r="I47" s="136" t="n"/>
+      <c r="J47" s="136" t="n"/>
+      <c r="K47" s="136" t="n"/>
+      <c r="L47" s="136" t="n"/>
+      <c r="M47" s="136" t="n"/>
+      <c r="N47" s="136" t="n"/>
+      <c r="O47" s="136" t="n"/>
+      <c r="P47" s="136" t="n"/>
+      <c r="Q47" s="137" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="136" t="n"/>
+      <c r="B48" s="136" t="n"/>
+      <c r="C48" s="136" t="n"/>
+      <c r="D48" s="136" t="n"/>
+      <c r="E48" s="136" t="n"/>
+      <c r="F48" s="136" t="n"/>
+      <c r="G48" s="136" t="n"/>
+      <c r="H48" s="136" t="n"/>
+      <c r="I48" s="136" t="n"/>
+      <c r="J48" s="136" t="n"/>
+      <c r="K48" s="136" t="n"/>
+      <c r="L48" s="136" t="n"/>
+      <c r="M48" s="136" t="n"/>
+      <c r="N48" s="136" t="n"/>
+      <c r="O48" s="136" t="n"/>
+      <c r="P48" s="136" t="n"/>
+      <c r="Q48" s="137" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="138" t="n"/>
+      <c r="B49" s="139" t="n"/>
+      <c r="C49" s="140" t="n"/>
+      <c r="D49" s="139" t="n"/>
+      <c r="E49" s="139" t="n"/>
+      <c r="F49" s="139" t="n"/>
+      <c r="G49" s="140" t="n"/>
+      <c r="H49" s="139" t="n"/>
+      <c r="I49" s="139" t="n"/>
+      <c r="J49" s="139" t="n"/>
+      <c r="K49" s="139" t="n"/>
+      <c r="L49" s="140" t="n"/>
+      <c r="M49" s="139" t="n"/>
+      <c r="N49" s="139" t="n"/>
+      <c r="O49" s="140" t="n"/>
+      <c r="P49" s="140" t="n"/>
+      <c r="Q49" s="141" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="138" t="n"/>
+      <c r="B50" s="139" t="n"/>
+      <c r="C50" s="140" t="n"/>
+      <c r="D50" s="139" t="n"/>
+      <c r="E50" s="139" t="n"/>
+      <c r="F50" s="139" t="n"/>
+      <c r="G50" s="140" t="n"/>
+      <c r="H50" s="139" t="n"/>
+      <c r="I50" s="139" t="n"/>
+      <c r="J50" s="139" t="n"/>
+      <c r="K50" s="139" t="n"/>
+      <c r="L50" s="140" t="n"/>
+      <c r="M50" s="139" t="n"/>
+      <c r="N50" s="139" t="n"/>
+      <c r="O50" s="140" t="n"/>
+      <c r="P50" s="140" t="n"/>
+      <c r="Q50" s="141" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="138" t="n"/>
+      <c r="B51" s="139" t="n"/>
+      <c r="C51" s="140" t="n"/>
+      <c r="D51" s="139" t="n"/>
+      <c r="E51" s="139" t="n"/>
+      <c r="F51" s="139" t="n"/>
+      <c r="G51" s="140" t="n"/>
+      <c r="H51" s="139" t="n"/>
+      <c r="I51" s="139" t="n"/>
+      <c r="J51" s="139" t="n"/>
+      <c r="K51" s="139" t="n"/>
+      <c r="L51" s="140" t="n"/>
+      <c r="M51" s="139" t="n"/>
+      <c r="N51" s="139" t="n"/>
+      <c r="O51" s="140" t="n"/>
+      <c r="P51" s="140" t="n"/>
+      <c r="Q51" s="141" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q51"/>
@@ -3408,11 +3007,8 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L5:L106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="L49 L50 L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="K5:K11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -5963,11 +5559,6 @@
           <t>مرجع Measurement — فرمول‌ها و کالیبراسیون</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="85" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="124" t="inlineStr">
@@ -5975,11 +5566,6 @@
           <t>این صفحه مرجع انتظار است؛ نتیجه واقعی فقط در «برنامه تست» ثبت شود. مقادیر از کد واقعی استخراج شده؛ مقدار حدسی وجود ندارد.</t>
         </is>
       </c>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-      <c r="D2" s="85" t="n"/>
-      <c r="E2" s="85" t="n"/>
-      <c r="F2" s="85" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="94" t="inlineStr">
@@ -6457,18 +6043,6 @@
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="85" t="n"/>
-      <c r="G1" s="85" t="n"/>
-      <c r="H1" s="85" t="n"/>
-      <c r="I1" s="85" t="n"/>
-      <c r="J1" s="85" t="n"/>
-      <c r="K1" s="85" t="n"/>
-      <c r="L1" s="85" t="n"/>
-      <c r="M1" s="85" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="87" t="inlineStr">
@@ -6476,18 +6050,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
       </c>
-      <c r="B2" s="88" t="n"/>
-      <c r="C2" s="88" t="n"/>
-      <c r="D2" s="88" t="n"/>
-      <c r="E2" s="88" t="n"/>
-      <c r="F2" s="88" t="n"/>
-      <c r="G2" s="88" t="n"/>
-      <c r="H2" s="88" t="n"/>
-      <c r="I2" s="88" t="n"/>
-      <c r="J2" s="88" t="n"/>
-      <c r="K2" s="88" t="n"/>
-      <c r="L2" s="88" t="n"/>
-      <c r="M2" s="89" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="94" t="inlineStr">
@@ -6741,11 +6315,6 @@
           <t>تأیید نهایی اعتبارسنجی روی برد — Measurement — ADC/ کالیبراسیون</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
-      <c r="D1" s="85" t="n"/>
-      <c r="E1" s="85" t="n"/>
-      <c r="F1" s="85" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="130" t="inlineStr">
@@ -6753,11 +6322,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بستن ایرادهای باز امضا شود. بدون تکمیل این صفحه، اعتبارسنجی ناقص است.</t>
         </is>
       </c>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-      <c r="D2" s="85" t="n"/>
-      <c r="E2" s="85" t="n"/>
-      <c r="F2" s="85" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="93" t="inlineStr">
@@ -6765,11 +6329,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="85" t="n"/>
-      <c r="C3" s="85" t="n"/>
-      <c r="D3" s="85" t="n"/>
-      <c r="E3" s="85" t="n"/>
-      <c r="F3" s="85" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="131" t="inlineStr">
@@ -6793,7 +6352,7 @@
         </is>
       </c>
       <c r="E4" s="98" t="n"/>
-      <c r="F4" s="89" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="131" t="inlineStr">
@@ -6817,7 +6376,7 @@
         </is>
       </c>
       <c r="E5" s="98" t="n"/>
-      <c r="F5" s="89" t="n"/>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="131" t="inlineStr">
@@ -6837,7 +6396,7 @@
       </c>
       <c r="D6" s="132" t="inlineStr"/>
       <c r="E6" s="98" t="n"/>
-      <c r="F6" s="89" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="131" t="inlineStr">
@@ -6853,7 +6412,7 @@
       </c>
       <c r="D7" s="132" t="inlineStr"/>
       <c r="E7" s="98" t="n"/>
-      <c r="F7" s="89" t="n"/>
+      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="131" t="inlineStr">
@@ -6873,7 +6432,7 @@
         </is>
       </c>
       <c r="E8" s="98" t="n"/>
-      <c r="F8" s="89" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="131" t="inlineStr">
@@ -6889,7 +6448,7 @@
       <c r="C9" s="131" t="inlineStr"/>
       <c r="D9" s="132" t="inlineStr"/>
       <c r="E9" s="98" t="n"/>
-      <c r="F9" s="89" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="131" t="inlineStr">
@@ -6961,11 +6520,6 @@
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="85" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="94" t="inlineStr">
@@ -6988,8 +6542,8 @@
           <t>فرمول پیشنهادی</t>
         </is>
       </c>
-      <c r="E15" s="88" t="n"/>
-      <c r="F15" s="89" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="96" t="inlineStr">
@@ -7007,8 +6561,8 @@
         </is>
       </c>
       <c r="D16" s="96" t="inlineStr"/>
-      <c r="E16" s="88" t="n"/>
-      <c r="F16" s="89" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="96" t="inlineStr">
@@ -7030,8 +6584,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E17" s="88" t="n"/>
-      <c r="F17" s="89" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="96" t="inlineStr">
@@ -7053,8 +6607,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E18" s="88" t="n"/>
-      <c r="F18" s="89" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="96" t="inlineStr">
@@ -7076,8 +6630,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E19" s="88" t="n"/>
-      <c r="F19" s="89" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="96" t="inlineStr">
@@ -7095,8 +6649,8 @@
         </is>
       </c>
       <c r="D20" s="96" t="inlineStr"/>
-      <c r="E20" s="88" t="n"/>
-      <c r="F20" s="89" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="96" t="inlineStr">
@@ -7114,8 +6668,8 @@
         </is>
       </c>
       <c r="D21" s="96" t="inlineStr"/>
-      <c r="E21" s="88" t="n"/>
-      <c r="F21" s="89" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="93" t="inlineStr">
@@ -7123,11 +6677,6 @@
           <t>امضاها</t>
         </is>
       </c>
-      <c r="B22" s="85" t="n"/>
-      <c r="C22" s="85" t="n"/>
-      <c r="D22" s="85" t="n"/>
-      <c r="E22" s="85" t="n"/>
-      <c r="F22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="94" t="inlineStr">
@@ -7155,7 +6704,7 @@
           <t>توضیحات</t>
         </is>
       </c>
-      <c r="F23" s="89" t="n"/>
+      <c r="F23" s="9" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="96" t="inlineStr">
@@ -7167,7 +6716,7 @@
       <c r="C24" s="96" t="inlineStr"/>
       <c r="D24" s="96" t="inlineStr"/>
       <c r="E24" s="96" t="inlineStr"/>
-      <c r="F24" s="89" t="n"/>
+      <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="96" t="inlineStr">
@@ -7179,7 +6728,7 @@
       <c r="C25" s="96" t="inlineStr"/>
       <c r="D25" s="96" t="inlineStr"/>
       <c r="E25" s="96" t="inlineStr"/>
-      <c r="F25" s="89" t="n"/>
+      <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="96" t="inlineStr">
@@ -7191,7 +6740,7 @@
       <c r="C26" s="96" t="inlineStr"/>
       <c r="D26" s="96" t="inlineStr"/>
       <c r="E26" s="96" t="inlineStr"/>
-      <c r="F26" s="89" t="n"/>
+      <c r="F26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="130" t="inlineStr">
@@ -7199,11 +6748,6 @@
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
       </c>
-      <c r="B27" s="85" t="n"/>
-      <c r="C27" s="85" t="n"/>
-      <c r="D27" s="85" t="n"/>
-      <c r="E27" s="85" t="n"/>
-      <c r="F27" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -7477,8 +7021,6 @@
           <t>ماشین حالت ماژول اندازه‌گیری (Measurement)</t>
         </is>
       </c>
-      <c r="B1" s="85" t="n"/>
-      <c r="C1" s="85" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="85" t="n"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1809,10 +1809,7 @@
         <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
         <v/>
       </c>
-      <c r="Q5" s="110">
-        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
-        <v/>
-      </c>
+      <c r="Q5" s="110" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="103" t="inlineStr">
@@ -1879,10 +1876,7 @@
         <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
         <v/>
       </c>
-      <c r="Q6" s="110">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
+      <c r="Q6" s="110" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="103" t="inlineStr">
@@ -1949,10 +1943,7 @@
         <f>IF(OR(K7="",K7="در انتظار"),"",IF(P7="",TODAY(),P7))</f>
         <v/>
       </c>
-      <c r="Q7" s="115">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
+      <c r="Q7" s="115" t="n"/>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="103" t="inlineStr">
@@ -2021,10 +2012,7 @@
         <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
         <v/>
       </c>
-      <c r="Q8" s="110">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="Q8" s="110" t="n"/>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="103" t="inlineStr">
@@ -2091,10 +2079,7 @@
         <f>IF(OR(K9="",K9="در انتظار"),"",IF(P9="",TODAY(),P9))</f>
         <v/>
       </c>
-      <c r="Q9" s="110">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="Q9" s="110" t="n"/>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="103" t="inlineStr">
@@ -2163,10 +2148,7 @@
         <f>IF(OR(K10="",K10="در انتظار"),"",IF(P10="",TODAY(),P10))</f>
         <v/>
       </c>
-      <c r="Q10" s="115">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="Q10" s="115" t="n"/>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="103" t="inlineStr">
@@ -2235,10 +2217,7 @@
         <f>IF(OR(K11="",K11="در انتظار"),"",IF(P11="",TODAY(),P11))</f>
         <v/>
       </c>
-      <c r="Q11" s="110">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="Q11" s="110" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="136" t="n"/>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1564,6 +1564,7 @@
       <c r="O23" s="85" t="n"/>
       <c r="P23" s="85" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="135" t="inlineStr">
         <is>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="C6" s="105" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D6" s="104" t="inlineStr">
@@ -1891,7 +1892,7 @@
       </c>
       <c r="C7" s="112" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="111" t="inlineStr">
@@ -1958,7 +1959,7 @@
       </c>
       <c r="C8" s="106" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="104" t="inlineStr">

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1317,7 +1317,10 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="86" t="inlineStr">
         <is>
-          <t>ChangeOver | ADC1 5ch + DMA + bsp_measurement | نسخه 1.0 — دوره 10ms، warmup 3 فریم، فرمول‌های BSP واقعی</t>
+          <t>ChangeOver | اندازه‌گیری با ADC1 انجام می‌شود: ۵ کانال با DMA (bsp_measurement).
+نسخه 1.0. هر 10 میلی‌ثانیه یک بار اندازه می‌گیریم.
+برای معتبر شدن، 3 فریم کامل لازم است (warmup).
+فرمول‌ها از خود کد BSP گرفته شده‌اند.</t>
         </is>
       </c>
     </row>
@@ -1346,21 +1349,24 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="90" t="inlineStr">
         <is>
-          <t>این فایل مستقل فقط Measurement را اعتبارسنجی می‌کند؛ هر تست valid، فریم ADC، فرمول mV/mA، ورودی‌ها و snapshot اتمیک را چک می‌کند.</t>
+          <t>این فایل فقط ماژول Measurement را چک می‌کند.
+در هر تست این‌ها بررسی می‌شود: معتبر بودن داده، فریم‌های ADC، تبدیل به میلی‌ولت و میلی‌آمپر، ورودی‌ها و اینکه عکس لحظه‌ای (snapshot) کامل و یکجا خوانده شود.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="90" t="inlineStr">
         <is>
-          <t>هیچ ردیفی بدون «روش اجرا» و «نتیجه مورد انتظار» نیست؛ هر PASS/FAIL با مقدار عددی و tolerance از کالیبراسیون BSP تعریف شده است.</t>
+          <t>در هر ردیف، روش اجرا و نتیجهٔ مورد انتظار نوشته شده است.
+قبول یا رد هر تست با عدد مشخص است. تلرانس از کالیبراسیون BSP گرفته شده است.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="90" t="inlineStr">
         <is>
-          <t>قبل از تست برد، «نتیجه واقعی» خالی و «وضعیت» = در انتظار بماند؛ ادعای PASS برای تست انجام‌نشده ممنوع است.</t>
+          <t>قبل از تست روی برد، ستون «نتیجه واقعی» را خالی بگذار و وضعیت را «در انتظار» نگه دار.
+برای تستی که انجام نشده، «قبول» ننویس.</t>
         </is>
       </c>
     </row>
@@ -1374,35 +1380,51 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="90" t="inlineStr">
         <is>
-          <t>پس از Init، valid=false؛ تا 3 فریم کامل و پایدار، valid همچنان false؛ پس از فریم سوم، valid=true و همه mV/mA/input_present به‌روز می‌شوند.</t>
+          <t>بعد از روشن‌شدن (Init)، داده نامعتبر است (valid=false).
+تا وقتی ۳ فریم کامل و پایدار نیامده، داده نامعتبر می‌ماند.
+بعد از فریم سوم، داده معتبر می‌شود (valid=true) و همهٔ مقدارها تازه می‌شوند: میلی‌ولت، میلی‌آمپر و حاضر بودن ورودی (input_present).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="90" t="inlineStr">
         <is>
-          <t>فریم ناقص/ناپایدار → valid=false و warmup از نو (counter reset). قطع ورودی 24V نباید به تنهایی ADC را invalid کند.</t>
+          <t>اگر فریمی ناقص یا ناپایدار باشد، داده نامعتبر می‌شود و شمارش ۳ فریم از نو شروع می‌شود.
+قطع‌شدن ورودی ۲۴ ولت به‌تنهایی نباید دادهٔ ADC را نامعتبر کند.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="92" t="inlineStr">
         <is>
-          <t>کالیبراسیون از bsp_measurement.c: Vref=3300mV، ADC=4095، Div24 69200+6800/6800 (≈11.176)، Div12 34200+6800/6800 (≈6.029)، شانت 10mΩ و گین 101.</t>
+          <t>کالیبراسیون از فایل bsp_measurement.c:
+ولتاژ مرجع: 3300 میلی‌ولت. بیشترین عدد ADC: 4095.
+تقسیم ولتاژ ۲۴ ولت: مقاومت‌های 69200+6800 و 6800 اهم (ضریب حدود 11.176).
+تقسیم ولتاژ ۱۲ ولت: مقاومت‌های 34200+6800 و 6800 اهم (ضریب حدود 6.029).
+مقاومت شانت: 10 میلی‌اهم. گین: 101.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="90" t="inlineStr">
         <is>
-          <t>فرمول‌ها: CountsToMv = counts*3300/4095؛ V24 = adcPinMv*(76000)/6800؛ V12 = adcPinMv*(41000)/6800؛ Current = counts*3300*1000/(4095*101*10).</t>
+          <t>فرمول‌ها:
+تبدیل عدد ADC به میلی‌ولت روی پایه: عدد × 3300 ÷ 4095.
+ولتاژ ۲۴ ولت: میلی‌ولت پایه × 76000 ÷ 6800.
+ولتاژ ۱۲ ولت: میلی‌ولت پایه × 41000 ÷ 6800.
+جریان (میلی‌آمپر): عدد × 3300 × 1000 ÷ (4095 × 101 × 10).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="90" t="inlineStr">
         <is>
-          <t>زمان واقعی از کد: MEASUREMENT_PERIOD_MS=10ms، MEASUREMENT_WARMUP_FRAME_COUNT=3، DMA دو فریمی 2×5، CNDTR بررسی قبل/بعد، osKernelLock برای snapshot اتمیک.</t>
+          <t>زمان‌ها و عددهای واقعی از کد:
+دورهٔ اندازه‌گیری: 10 میلی‌ثانیه (MEASUREMENT_PERIOD_MS).
+برای معتبر شدن: 3 فریم (MEASUREMENT_WARMUP_FRAME_COUNT).
+DMA دو فریم ۵ کاناله می‌خواند (2×5).
+پایداری فریم با شمارندهٔ DMA (CNDTR) قبل و بعد چک می‌شود.
+عکس لحظه‌ای با قفل سیستم (osKernelLock) یکجا خوانده می‌شود.</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1438,49 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="90" t="inlineStr">
         <is>
-          <t>۱) برد را با منبع آزمایشگاهی تغذیه کن، هر 5 کانال ADC (PA1/2/3/5/7) را با ولتاژ دقیق و منبع جریان کالیبره اعمال کن؛ PB4 را برای input_present کنترل کن.</t>
+          <t>۱) برد را با منبع آزمایشگاهی روشن کن.
+هر ۵ کانال ADC (PA1 و PA2 و PA3 و PA5 و PA7) را با ولتاژ دقیق و منبع جریان کالیبره‌شده بده.
+پایهٔ PB4 را برای «حاضر بودن ورودی» کنترل کن.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="90" t="inlineStr">
         <is>
-          <t>۲) firmware commit c6b084f را پروگرام کن، در «تأیید نهایی» commit/برد/ابزار (DMM، اسکوپ، منبع دقیق) را ثبت کن.</t>
+          <t>۲) برنامه با نسخهٔ c6b084f را فلش کن.
+در «تأیید نهایی» این‌ها را بنویس: نسخهٔ برنامه، شناسهٔ برد و ابزار (مولتی‌متر، اسکوپ و منبع دقیق).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="90" t="inlineStr">
         <is>
-          <t>۳) تست warmup: پس از Init، فریم‌ها را با func__BspAdc_GetRaw یا Live Watch بشمار؛ valid را چک کن.</t>
+          <t>۳) تست گرم‌شدن (warmup): بعد از روشن‌شدن، فریم‌ها را بشمار (با func__BspAdc_GetRaw یا Live Watch) و ببین داده کی معتبر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="90" t="inlineStr">
         <is>
-          <t>۴) تست ولتاژ/جریان: هر کانال را با counts معلوم اعمال کن، مقدار mV/mA را با فرمول BSP محاسبه و با خوانش globals/snapshot مقایسه کن (tolerance ±1 LSB ≈ ±0.8mV pin، برای V24 ≈±9mV، برای V12 ≈±4.8mV، برای جریان ≈±0.8mA).</t>
+          <t>۴) تست ولتاژ و جریان: هر کانال را با عدد (counts) معلوم بده.
+مقدار میلی‌ولت و میلی‌آمپر را با فرمول BSP حساب کن و با عدد خوانده‌شده مقایسه کن.
+تلرانس: روی پایه ±1 پله (LSB) یعنی حدود ±0.8 میلی‌ولت؛ برای ولتاژ ۲۴ ولت حدود ±9 میلی‌ولت؛ برای ولتاژ ۱۲ ولت حدود ±4.8 میلی‌ولت؛ برای جریان حدود ±0.8 میلی‌آمپر.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="90" t="inlineStr">
         <is>
-          <t>۵) تست DMA: دو فریم متوالی را چک کن که CNDTR پایدار باشد و frame 5 نمونه بدون پارگی کپی شود (irq disable و counter قبل/بعد).</t>
+          <t>۵) تست DMA: دو فریم پشت سر هم را چک کن.
+شمارندهٔ DMA (CNDTR) باید پایدار باشد و هر فریم ۵ نمونه کامل و بدون پارگی کپی شود. (وقفه موقع کپی خاموش است و شمارنده قبل و بعد چک می‌شود.)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="90" t="inlineStr">
         <is>
-          <t>۶) تست snapshot اتمیک: حین Run، از دو تسک snapshot را هم‌زمان بخوان و چک کن نیمه‌به‌روزشده نباشد (osKernelLock).</t>
+          <t>۶) تست عکس لحظه‌ای: وقتی برنامه در حال کار است، از دو تسک هم‌زمان عکس لحظه‌ای بخوان.
+نباید نصفه‌نیمه باشد؛ یا همه‌اش قدیمی است یا همه‌اش تازه. (قفل سیستم osKernelLock همین را تضمین می‌کند.)</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1509,7 @@
       </c>
       <c r="D21" s="94" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="E21" s="95" t="n"/>
@@ -1509,7 +1538,7 @@
       </c>
       <c r="C22" s="97" t="inlineStr">
         <is>
-          <t>ایجاد مستقل Measurement_Board_Validation با ۲۱ تست، فرمول‌ها و tolerance از bsp_measurement.c، دوره 10ms و warmup 3</t>
+          <t>این فایل جدا برای Measurement ساخته شد. ۲۱ تست دارد. فرمول‌ها و تلرانس‌ها از فایل bsp_measurement.c گرفته شده‌اند. دورهٔ اندازه‌گیری 10 میلی‌ثانیه است و برای معتبر شدن 3 فریم لازم است.</t>
         </is>
       </c>
       <c r="D22" s="96" t="inlineStr">
@@ -1564,12 +1593,15 @@
       <c r="O23" s="85" t="n"/>
       <c r="P23" s="85" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="135" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1761,7 @@
       </c>
       <c r="N4" s="87" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="87" t="inlineStr">
@@ -3163,7 +3195,7 @@
       </c>
       <c r="N4" s="87" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="87" t="inlineStr">
@@ -3339,10 +3371,12 @@
       </c>
       <c r="E7" s="120" t="inlineStr">
         <is>
-          <t>گام ۱: ادامهٔ MS-003 (دو فریم داده‌ای و warmup=2).
-گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts 2482 (2 ولت روی پایه) و کانال‌های جریان counts 610 (0.49 ولت روی پایه).
+          <t>گام ۱: ادامهٔ MS-003 است: دو فریم داده‌ای آمده و warmup=2 شده است.
+گام ۲: فریم سوم کامل را اعمال کن: کانال‌های ولتاژ counts برابر 2482 (یعنی 2 ولت روی پایه) و کانال‌های جریان counts برابر 610 (یعنی 0.49 ولت روی پایه).
 گام ۳: یک Run بزن.
-گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند: V24 حدود 22352 میلی‌ولت، V12 حدود 12058 میلی‌ولت، جریان حدود 486 میلی‌آمپر و input_present مطابق وضعیت PB4. اگر هنوز false بود تست رد است.</t>
+گام ۴: حالا باید valid=true شود و همهٔ globals به‌روز باشند.
+V24 حدود 22352 میلی‌ولت است. V12 حدود 12058 میلی‌ولت است. جریان حدود 486 میلی‌آمپر است. input_present هم مطابق وضعیت PB4 است.
+گام ۵: اگر هنوز false بود، تست رد است.</t>
         </is>
       </c>
       <c r="F7" s="113" t="inlineStr">
@@ -3617,8 +3651,9 @@
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی پایهٔ ADC مقدار counts=1241 بده (حدود 1 ولت روی پایه).
-گام ۳: اول خودت حساب کن: 1241 ضربدر 3300 تقسیم بر 4095 می‌شود حدود 1000 میلی‌ولت روی پایه؛ بعد ضربدر 76000 تقسیم بر 6800 می‌شود حدود 11176 میلی‌ولت.
-گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن: خطای مجاز ±9 میلی‌ولت است؛ خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
+گام ۳: اول خودت حساب کن: 1241 ضربدر 3300 تقسیم بر 4095 می‌شود حدود 1000 میلی‌ولت روی پایه. بعد ضربدر 76000 تقسیم بر 6800 می‌شود حدود 11176 میلی‌ولت.
+گام ۴: مقدار خوانده‌شدهٔ v_in_mv را با 11176 مقایسه کن. خطای مجاز ±9 میلی‌ولت است.
+گام ۵: خطای بیشتر از 20 میلی‌ولت یعنی رد تست.</t>
         </is>
       </c>
       <c r="F11" s="113" t="inlineStr">
@@ -4100,8 +4135,8 @@
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
-گام ۳: با دست حساب کن: ولتاژ پایه 3300 میلی‌ولت، V24 می‌شود 3300 ضربدر 76000 تقسیم بر 6800 یعنی حدود 36882 میلی‌ولت، V12 حدود 19897 میلی‌ولت و جریان 3300 ضربدر 1000 تقسیم بر (101 ضربدر 10) یعنی حدود 3267 میلی‌آمپر.
-گام ۴: هر سه مقدار خوانده‌شده را با همین حساب مقایسه کن؛ باید در تلرانس مجاز همان‌ها باشند.</t>
+گام ۳: با دست حساب کن: ولتاژ پایه 3300 میلی‌ولت می‌شود. V24 می‌شود 3300 ضربدر 76000 تقسیم بر 6800، یعنی حدود 36882 میلی‌ولت. V12 حدود 19897 میلی‌ولت می‌شود. جریان هم 3300 ضربدر 1000 تقسیم بر (101 ضربدر 10)، یعنی حدود 3267 میلی‌آمپر.
+گام ۴: هر سه مقدار خوانده‌شده را با همین حساب‌ها مقایسه کن. باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
       <c r="F18" s="113" t="inlineStr">
@@ -4768,7 +4803,7 @@
       </c>
       <c r="N4" s="87" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="O4" s="87" t="inlineStr">
@@ -4808,7 +4843,8 @@
         <is>
           <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
 گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
-گام ۳: تابع باید false برگرداند، هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد؛ کرش یا true برگشتن یعنی رد تست.</t>
+گام ۳: تابع باید false برگرداند. هیچ کرشی نباید اتفاق بیفتد و snapshot قبلی هم نباید دست خورده باشد.
+گام ۴: کرش یا true برگشتن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F5" s="106" t="inlineStr">
@@ -4874,10 +4910,11 @@
       </c>
       <c r="E6" s="111" t="inlineStr">
         <is>
-          <t>گام ۱: از valid=true شروع کن و مقادیر را در حال تغییر نگه دار.
-گام ۲: درست حین اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
-گام ۳: 20 میلی‌ثانیه این خواندن هم‌زمان را تکرار کن.
-گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید، نه مخلوطی از هر دو (این اتمیک بودن با osKernelLock تضمین می‌شود)؛ خواندن پاره‌پاره (torn) یعنی رد تست.</t>
+          <t>گام ۱: از valid=true شروع کن و مقدارها را در حال تغییر نگه دار.
+گام ۲: درست هنگام اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
+گام ۳: این خواندن هم‌زمان را 20 میلی‌ثانیه تکرار کن.
+گام ۴: هر snapshot کپی‌شده باید یا کاملاً نسخهٔ قدیم باشد یا کاملاً نسخهٔ جدید؛ نه مخلوطی از هر دو. (این یکجایی با osKernelLock تضمین می‌شود.)
+گام ۵: خواندن پاره‌پاره (torn) یعنی رد تست.</t>
         </is>
       </c>
       <c r="F6" s="113" t="inlineStr">
@@ -6091,7 +6128,7 @@
       </c>
       <c r="J3" s="94" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="94" t="inlineStr">
@@ -6361,12 +6398,12 @@
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="131" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B6" s="96" t="inlineStr">
         <is>
-          <t>TESTER: fill flashed firmware commit</t>
+          <t>نسخهٔ برنامهٔ فلش‌شده (تست‌کننده پر کند)</t>
         </is>
       </c>
       <c r="C6" s="131" t="inlineStr">

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -377,7 +377,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -443,6 +443,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -531,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -918,6 +928,56 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="62" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1308,7 +1368,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Measurement — ADC و کالیبراسیون</t>
         </is>
@@ -1325,7 +1385,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="87" t="inlineStr">
+      <c r="A3" s="143" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -1371,7 +1431,7 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="144" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
@@ -1429,7 +1489,7 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="91" t="inlineStr">
+      <c r="A13" s="144" t="inlineStr">
         <is>
           <t>روش اجرای تست</t>
         </is>
@@ -1485,34 +1545,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="93" t="inlineStr">
+      <c r="A20" s="145" t="inlineStr">
         <is>
           <t>تاریخچه نسخه</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="inlineStr">
+      <c r="A21" s="146" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B21" s="146" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
+      <c r="C21" s="146" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D21" s="94" t="inlineStr">
+      <c r="D21" s="146" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="E21" s="95" t="n"/>
+      <c r="E21" s="147" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
@@ -1593,6 +1653,7 @@
       <c r="O23" s="85" t="n"/>
       <c r="P23" s="85" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="135" t="inlineStr">
         <is>
@@ -1670,7 +1731,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="100" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Measurement</t>
         </is>
@@ -1694,87 +1755,87 @@
       <c r="Q3" s="85" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="143" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="143" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="143" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="87" t="inlineStr">
+      <c r="D4" s="143" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="87" t="inlineStr">
+      <c r="E4" s="143" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="87" t="inlineStr">
+      <c r="F4" s="143" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="87" t="inlineStr">
+      <c r="G4" s="143" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="87" t="inlineStr">
+      <c r="H4" s="143" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="87" t="inlineStr">
+      <c r="I4" s="143" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="J4" s="87" t="inlineStr">
+      <c r="J4" s="143" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="87" t="inlineStr">
+      <c r="K4" s="143" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="87" t="inlineStr">
+      <c r="L4" s="143" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="87" t="inlineStr">
+      <c r="M4" s="143" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="87" t="inlineStr">
+      <c r="N4" s="143" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="87" t="inlineStr">
+      <c r="O4" s="143" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="87" t="inlineStr">
+      <c r="P4" s="143" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="87" t="n"/>
+      <c r="Q4" s="143" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="103" t="inlineStr">
@@ -1782,49 +1843,49 @@
           <t>MS-001</t>
         </is>
       </c>
-      <c r="B5" s="104" t="inlineStr">
+      <c r="B5" s="111" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="104" t="inlineStr">
+      <c r="D5" s="111" t="inlineStr">
         <is>
           <t>دستگاه خاموش؛ باتری و برق شهر وصل؛ مولتی‌متر دستی آماده</t>
         </is>
       </c>
-      <c r="E5" s="104" t="inlineStr">
+      <c r="E5" s="111" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: عدد ولتاژ باتری و ورودی را در پنل بخوان.
 گام ۳: همان لحظه با مولتی‌متر روی ترمینال‌ها اندازه بگیر.</t>
         </is>
       </c>
-      <c r="F5" s="106" t="inlineStr">
+      <c r="F5" s="113" t="inlineStr">
         <is>
           <t>روشن‌کردن ساده</t>
         </is>
       </c>
-      <c r="G5" s="106" t="inlineStr">
+      <c r="G5" s="113" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="104" t="inlineStr">
+      <c r="H5" s="111" t="inlineStr">
         <is>
           <t>عددهای پنل زنده‌اند و با مولتی‌متر دستی می‌خوانند (اختلاف در حد چند صدم ولت)</t>
         </is>
       </c>
-      <c r="I5" s="104" t="inlineStr">
+      <c r="I5" s="111" t="inlineStr">
         <is>
           <t>باید ببینید: عددهای پنل زنده‌اند و با مولتی‌متر دستی می‌خوانند (اختلاف در حد چند صدم ولت). اگر عدد ثابت بود یا اختلاف زیاد داشت، قبول نیست.</t>
         </is>
       </c>
-      <c r="J5" s="107" t="n"/>
+      <c r="J5" s="111" t="n"/>
       <c r="K5" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -1832,13 +1893,13 @@
       </c>
       <c r="L5" s="109" t="n"/>
       <c r="M5" s="104" t="n"/>
-      <c r="N5" s="104" t="inlineStr">
+      <c r="N5" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O5" s="106" t="n"/>
-      <c r="P5" s="106">
+      <c r="P5" s="113">
         <f>IF(OR(K5="",K5="در انتظار"),"",IF(P5="",TODAY(),P5))</f>
         <v/>
       </c>
@@ -1850,48 +1911,48 @@
           <t>MS-013</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="148" t="inlineStr">
         <is>
           <t>بررسی input_present / High</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="149" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="104" t="inlineStr">
+      <c r="D6" s="148" t="inlineStr">
         <is>
           <t>دستگاه روی باتری روشن است و برق شهر قطع است</t>
         </is>
       </c>
-      <c r="E6" s="104" t="inlineStr">
+      <c r="E6" s="148" t="inlineStr">
         <is>
           <t>گام ۱: برق شهر را وصل کن.
 گام ۲: در پنل ببین ورودی «حاضر» می‌شود و عددش را با مولتی‌متر چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="106" t="inlineStr">
+      <c r="F6" s="150" t="inlineStr">
         <is>
           <t>وصل‌کردن برق شهر</t>
         </is>
       </c>
-      <c r="G6" s="106" t="inlineStr">
+      <c r="G6" s="150" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="104" t="inlineStr">
+      <c r="H6" s="148" t="inlineStr">
         <is>
           <t>پنل ورودی را حاضر و با ولتاژ درست نشان می‌دهد</t>
         </is>
       </c>
-      <c r="I6" s="104" t="inlineStr">
+      <c r="I6" s="148" t="inlineStr">
         <is>
           <t>باید ببینید: پنل ورودی را حاضر و با ولتاژ درست نشان می‌دهد. اگر هنوز قطع نشان داد، قبول نیست.</t>
         </is>
       </c>
-      <c r="J6" s="107" t="n"/>
+      <c r="J6" s="111" t="n"/>
       <c r="K6" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -1899,13 +1960,13 @@
       </c>
       <c r="L6" s="109" t="n"/>
       <c r="M6" s="104" t="n"/>
-      <c r="N6" s="104" t="inlineStr">
+      <c r="N6" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O6" s="106" t="n"/>
-      <c r="P6" s="106">
+      <c r="P6" s="150">
         <f>IF(OR(K6="",K6="در انتظار"),"",IF(P6="",TODAY(),P6))</f>
         <v/>
       </c>
@@ -1984,22 +2045,22 @@
           <t>MS-023</t>
         </is>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="148" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C8" s="106" t="inlineStr">
+      <c r="C8" s="150" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="104" t="inlineStr">
+      <c r="D8" s="148" t="inlineStr">
         <is>
           <t>منبع دقیق آزمایشگاهی و مولتی‌متر</t>
         </is>
       </c>
-      <c r="E8" s="104" t="inlineStr">
+      <c r="E8" s="148" t="inlineStr">
         <is>
           <t>گام ۱: منبع را دقیقاً روی 24.0 ولت تنظیم کن و به ورودی وصل کن؛ یک باتری 24 ولت هم وصل باشد.
 گام ۲: ولتاژ منبع را با مولتی‌متر خودت هم اندازه بگیر.
@@ -2007,27 +2068,27 @@
 گام ۴: هر دو باید نزدیک همان عددی باشند که مولتی‌متر می‌گوید؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F8" s="104" t="inlineStr">
+      <c r="F8" s="148" t="inlineStr">
         <is>
           <t>ورودی و باتری 24 ولت</t>
         </is>
       </c>
-      <c r="G8" s="106" t="inlineStr">
+      <c r="G8" s="150" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="104" t="inlineStr">
+      <c r="H8" s="148" t="inlineStr">
         <is>
           <t>عددهای پنل نزدیک مقدار واقعی مولتی‌متر</t>
         </is>
       </c>
-      <c r="I8" s="104" t="inlineStr">
+      <c r="I8" s="148" t="inlineStr">
         <is>
           <t>باید ببینید: عددهای پنل نزدیک مقدار واقعی مولتی‌مترند. اگر دور بودند، قبول نیست.</t>
         </is>
       </c>
-      <c r="J8" s="104" t="inlineStr">
+      <c r="J8" s="148" t="inlineStr">
         <is>
           <t>اختلاف پنل با مولتی‌متر کم و منطقی باشد</t>
         </is>
@@ -2041,7 +2102,7 @@
       <c r="M8" s="104" t="n"/>
       <c r="N8" s="104" t="n"/>
       <c r="O8" s="106" t="n"/>
-      <c r="P8" s="106">
+      <c r="P8" s="150">
         <f>IF(OR(K8="",K8="در انتظار"),"",IF(P8="",TODAY(),P8))</f>
         <v/>
       </c>
@@ -2053,48 +2114,48 @@
           <t>MS-021</t>
         </is>
       </c>
-      <c r="B9" s="104" t="inlineStr">
+      <c r="B9" s="111" t="inlineStr">
         <is>
           <t>کالیبراسیون برد / tolerance</t>
         </is>
       </c>
-      <c r="C9" s="106" t="inlineStr">
+      <c r="C9" s="113" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="104" t="inlineStr">
+      <c r="D9" s="111" t="inlineStr">
         <is>
           <t>مولتی‌متر مرجع مطمئن و پنل در حالت کالیبراسیون</t>
         </is>
       </c>
-      <c r="E9" s="104" t="inlineStr">
+      <c r="E9" s="111" t="inlineStr">
         <is>
           <t>گام ۱: طبق راهنمای پنل، در یک ولتاژ پایین و یک ولتاژ بالا عدد دستگاه را با مولتی‌متر یکی کن.
 گام ۲: در یک ولتاژ میانی هر دو را مقایسه کن.</t>
         </is>
       </c>
-      <c r="F9" s="106" t="inlineStr">
+      <c r="F9" s="113" t="inlineStr">
         <is>
           <t>کالیبراسیون دو نقطه و چک میانی</t>
         </is>
       </c>
-      <c r="G9" s="106" t="inlineStr">
+      <c r="G9" s="113" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H9" s="104" t="inlineStr">
+      <c r="H9" s="111" t="inlineStr">
         <is>
           <t>بعد از کالیبراسیون، عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند</t>
         </is>
       </c>
-      <c r="I9" s="104" t="inlineStr">
+      <c r="I9" s="111" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از کالیبراسیون عدد پنل در نقطهٔ میانی هم با مولتی‌متر می‌خواند. اگر اختلاف محسوس داشت، قبول نیست.</t>
         </is>
       </c>
-      <c r="J9" s="107" t="n"/>
+      <c r="J9" s="111" t="n"/>
       <c r="K9" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -2102,13 +2163,13 @@
       </c>
       <c r="L9" s="109" t="n"/>
       <c r="M9" s="104" t="n"/>
-      <c r="N9" s="104" t="inlineStr">
+      <c r="N9" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O9" s="106" t="n"/>
-      <c r="P9" s="106">
+      <c r="P9" s="113">
         <f>IF(OR(K9="",K9="در انتظار"),"",IF(P9="",TODAY(),P9))</f>
         <v/>
       </c>
@@ -2120,22 +2181,22 @@
           <t>MS-024</t>
         </is>
       </c>
-      <c r="B10" s="111" t="inlineStr">
+      <c r="B10" s="148" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C10" s="113" t="inlineStr">
+      <c r="C10" s="150" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="111" t="inlineStr">
+      <c r="D10" s="148" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل عددها را نشان می‌دهد</t>
         </is>
       </c>
-      <c r="E10" s="111" t="inlineStr">
+      <c r="E10" s="148" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه روشن باشد و در پنل عددهای ولتاژ را ببین.
 گام ۲: ورودی را کامل قطع کن (صفر ولت).
@@ -2143,27 +2204,27 @@
 گام ۴: دستگاه نباید خطای اندازه‌گیری بگیرد یا خاموش شود.</t>
         </is>
       </c>
-      <c r="F10" s="111" t="inlineStr">
+      <c r="F10" s="148" t="inlineStr">
         <is>
           <t>قطع کامل ورودی</t>
         </is>
       </c>
-      <c r="G10" s="113" t="inlineStr">
+      <c r="G10" s="150" t="inlineStr">
         <is>
           <t>چند ثانیه</t>
         </is>
       </c>
-      <c r="H10" s="111" t="inlineStr">
+      <c r="H10" s="148" t="inlineStr">
         <is>
           <t>ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم</t>
         </is>
       </c>
-      <c r="I10" s="111" t="inlineStr">
+      <c r="I10" s="148" t="inlineStr">
         <is>
           <t>باید ببینید: با ورودی صفر، بقیهٔ اندازه‌گیری‌ها سالم و عادی‌اند. اگر بقیه هم خراب شدند، قبول نیست.</t>
         </is>
       </c>
-      <c r="J10" s="111" t="inlineStr">
+      <c r="J10" s="148" t="inlineStr">
         <is>
           <t>فقط ورودی صفر شود و دستگاه عادی بماند</t>
         </is>
@@ -2177,7 +2238,7 @@
       <c r="M10" s="111" t="n"/>
       <c r="N10" s="111" t="n"/>
       <c r="O10" s="113" t="n"/>
-      <c r="P10" s="113">
+      <c r="P10" s="150">
         <f>IF(OR(K10="",K10="در انتظار"),"",IF(P10="",TODAY(),P10))</f>
         <v/>
       </c>
@@ -2189,22 +2250,22 @@
           <t>MS-025</t>
         </is>
       </c>
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="111" t="inlineStr">
         <is>
           <t>عملکرد واقعی اندازه‌گیری</t>
         </is>
       </c>
-      <c r="C11" s="106" t="inlineStr">
+      <c r="C11" s="113" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="104" t="inlineStr">
+      <c r="D11" s="111" t="inlineStr">
         <is>
           <t>بار معلوم و مولتی‌متر سری</t>
         </is>
       </c>
-      <c r="E11" s="104" t="inlineStr">
+      <c r="E11" s="111" t="inlineStr">
         <is>
           <t>گام ۱: یک بار معلوم روی مسیر شارژ بگذار و جریان واقعی را با مولتی‌متر اندازه بگیر (مثلاً باری که حدود 500 میلی‌آمپر می‌کشد).
 گام ۲: شارژ را راه بینداز.
@@ -2212,27 +2273,27 @@
 گام ۴: باید نزدیک هم باشند؛ اختلاف زیاد یعنی رد.</t>
         </is>
       </c>
-      <c r="F11" s="104" t="inlineStr">
+      <c r="F11" s="111" t="inlineStr">
         <is>
           <t>بار حدود 500 میلی‌آمپر</t>
         </is>
       </c>
-      <c r="G11" s="106" t="inlineStr">
+      <c r="G11" s="113" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="104" t="inlineStr">
+      <c r="H11" s="111" t="inlineStr">
         <is>
           <t>جریان پنل نزدیک جریان واقعی</t>
         </is>
       </c>
-      <c r="I11" s="104" t="inlineStr">
+      <c r="I11" s="111" t="inlineStr">
         <is>
           <t>باید ببینید: جریان پنل نزدیک جریان واقعی است. اگر دور بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="J11" s="104" t="inlineStr">
+      <c r="J11" s="111" t="inlineStr">
         <is>
           <t>اختلاف جریان پنل با مولتی‌متر کم باشد</t>
         </is>
@@ -2246,7 +2307,7 @@
       <c r="M11" s="104" t="n"/>
       <c r="N11" s="104" t="n"/>
       <c r="O11" s="106" t="n"/>
-      <c r="P11" s="106">
+      <c r="P11" s="113">
         <f>IF(OR(K11="",K11="در انتظار"),"",IF(P11="",TODAY(),P11))</f>
         <v/>
       </c>
@@ -3063,7 +3124,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="118" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -3128,87 +3189,87 @@
       <c r="Q3" s="85" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="143" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="143" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="143" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="87" t="inlineStr">
+      <c r="D4" s="143" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="87" t="inlineStr">
+      <c r="E4" s="143" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="87" t="inlineStr">
+      <c r="F4" s="143" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="87" t="inlineStr">
+      <c r="G4" s="143" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="87" t="inlineStr">
+      <c r="H4" s="143" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="87" t="inlineStr">
+      <c r="I4" s="143" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="87" t="inlineStr">
+      <c r="J4" s="143" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="87" t="inlineStr">
+      <c r="K4" s="143" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="87" t="inlineStr">
+      <c r="L4" s="143" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="87" t="inlineStr">
+      <c r="M4" s="143" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="87" t="inlineStr">
+      <c r="N4" s="143" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="87" t="inlineStr">
+      <c r="O4" s="143" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="87" t="inlineStr">
+      <c r="P4" s="143" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="87" t="n"/>
+      <c r="Q4" s="143" t="n"/>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="103" t="inlineStr">
@@ -3285,22 +3346,22 @@
           <t>MS-003</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="148" t="inlineStr">
         <is>
           <t>Warmup / فریم دوم</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="121" t="inlineStr">
+      <c r="D6" s="152" t="inlineStr">
         <is>
           <t>پس از MS-002</t>
         </is>
       </c>
-      <c r="E6" s="121" t="inlineStr">
+      <c r="E6" s="152" t="inlineStr">
         <is>
           <t>گام ۱: ادامهٔ MS-002 (یک فریم داده‌ای و warmup=1).
 گام ۲: فریم دوم کامل و پایدار را با همان counts 2482 اعمال کن.
@@ -3308,27 +3369,27 @@
 گام ۴: هنوز باید valid=false باشد و شمارندهٔ warmup برابر 2 شده باشد؛ true شدن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="106" t="inlineStr">
+      <c r="F6" s="150" t="inlineStr">
         <is>
           <t>فریم 2 کامل, counts 2482</t>
         </is>
       </c>
-      <c r="G6" s="106" t="inlineStr">
+      <c r="G6" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H6" s="104" t="inlineStr">
+      <c r="H6" s="148" t="inlineStr">
         <is>
           <t>valid همچنان false، counter=2. PASS: still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="I6" s="104" t="inlineStr">
+      <c r="I6" s="148" t="inlineStr">
         <is>
           <t>PASS: فریم2 still false. FAIL: true.</t>
         </is>
       </c>
-      <c r="J6" s="107" t="n"/>
+      <c r="J6" s="111" t="n"/>
       <c r="K6" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3336,14 +3397,14 @@
       </c>
       <c r="L6" s="109" t="n"/>
       <c r="M6" s="104" t="n"/>
-      <c r="N6" s="104" t="inlineStr">
+      <c r="N6" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O6" s="106" t="n"/>
       <c r="P6" s="106" t="n"/>
-      <c r="Q6" s="110">
+      <c r="Q6" s="153">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -3425,22 +3486,22 @@
           <t>MS-005</t>
         </is>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="148" t="inlineStr">
         <is>
           <t>Warmup / فریم ناقص</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="104" t="inlineStr">
+      <c r="D8" s="148" t="inlineStr">
         <is>
           <t>پس از valid=true</t>
         </is>
       </c>
-      <c r="E8" s="121" t="inlineStr">
+      <c r="E8" s="152" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن (پایان MS-004).
 گام ۲: یک فریم ناپایدار اعمال کن؛ مثلاً کاری کن GetRaw مقدار false بدهد (شمارندهٔ DMA وسط کپی حرکت کند).
@@ -3448,27 +3509,27 @@
 گام ۴: باید همان لحظه valid=false شود، شمارندهٔ warmup به صفر برگردد و snapshot.valid هم false باشد؛ true ماندن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F8" s="106" t="inlineStr">
+      <c r="F8" s="150" t="inlineStr">
         <is>
           <t>فریم ناقص/ناپایدار (GetRaw false)</t>
         </is>
       </c>
-      <c r="G8" s="106" t="inlineStr">
+      <c r="G8" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H8" s="104" t="inlineStr">
+      <c r="H8" s="148" t="inlineStr">
         <is>
           <t>valid=false فوری، warmupCounter reset به 0، snapshot.valid false. PASS: invalid و reset. FAIL: همچنان true.</t>
         </is>
       </c>
-      <c r="I8" s="104" t="inlineStr">
+      <c r="I8" s="148" t="inlineStr">
         <is>
           <t>PASS: unstable → invalid+reset. FAIL: remains true.</t>
         </is>
       </c>
-      <c r="J8" s="107" t="n"/>
+      <c r="J8" s="111" t="n"/>
       <c r="K8" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3476,14 +3537,14 @@
       </c>
       <c r="L8" s="109" t="n"/>
       <c r="M8" s="104" t="n"/>
-      <c r="N8" s="104" t="inlineStr">
+      <c r="N8" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O8" s="106" t="n"/>
       <c r="P8" s="106" t="n"/>
-      <c r="Q8" s="110">
+      <c r="Q8" s="153">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -3563,22 +3624,22 @@
           <t>MS-007</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="148" t="inlineStr">
         <is>
           <t>ورودی 24V قطع</t>
         </is>
       </c>
-      <c r="C10" s="106" t="inlineStr">
+      <c r="C10" s="150" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="104" t="inlineStr">
+      <c r="D10" s="148" t="inlineStr">
         <is>
           <t>valid=true با Vin=0</t>
         </is>
       </c>
-      <c r="E10" s="104" t="inlineStr">
+      <c r="E10" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و ولتاژ ورودی را صفر بده (Vin=0 ولت، counts صفر)، ولی بقیهٔ کانال‌ها معتبر بمانند (مثلاً 2 ولت).
 گام ۲: یک Run بزن.
@@ -3586,27 +3647,27 @@
 گام ۴: v_in_mv باید حدود صفر باشد و بقیهٔ مقادیر به‌روز شده باشند؛ false شدن valid یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F10" s="106" t="inlineStr">
+      <c r="F10" s="150" t="inlineStr">
         <is>
           <t>v_in 0V (counts 0), سایر 2V</t>
         </is>
       </c>
-      <c r="G10" s="106" t="inlineStr">
+      <c r="G10" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H10" s="104" t="inlineStr">
+      <c r="H10" s="148" t="inlineStr">
         <is>
           <t>valid همچنان true (قطع ورودی ADC را invalid نمی‌کند)، v_in_mv≈0، سایر مقادیر به‌روز. PASS: valid true با Vin صفر. FAIL: valid false.</t>
         </is>
       </c>
-      <c r="I10" s="104" t="inlineStr">
+      <c r="I10" s="148" t="inlineStr">
         <is>
           <t>PASS: Vin zero still valid. FAIL: invalid.</t>
         </is>
       </c>
-      <c r="J10" s="107" t="n"/>
+      <c r="J10" s="111" t="n"/>
       <c r="K10" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3614,14 +3675,14 @@
       </c>
       <c r="L10" s="109" t="n"/>
       <c r="M10" s="104" t="n"/>
-      <c r="N10" s="104" t="inlineStr">
+      <c r="N10" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O10" s="106" t="n"/>
       <c r="P10" s="106" t="n"/>
-      <c r="Q10" s="110">
+      <c r="Q10" s="153">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -3702,22 +3763,22 @@
           <t>MS-009</t>
         </is>
       </c>
-      <c r="B12" s="104" t="inlineStr">
+      <c r="B12" s="148" t="inlineStr">
         <is>
           <t>بررسی v_bat24_mv</t>
         </is>
       </c>
-      <c r="C12" s="105" t="inlineStr">
+      <c r="C12" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="104" t="inlineStr">
+      <c r="D12" s="148" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E12" s="104" t="inlineStr">
+      <c r="E12" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال باتری 24 ولت counts=2482 بده (2 ولت روی پایه).
@@ -3725,27 +3786,27 @@
 گام ۴: باید حدود 22352 میلی‌ولت باشد با خطای حداکثر ±9 میلی‌ولت؛ بیشتر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="106" t="inlineStr">
+      <c r="F12" s="150" t="inlineStr">
         <is>
           <t>counts 2482</t>
         </is>
       </c>
-      <c r="G12" s="106" t="inlineStr">
+      <c r="G12" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H12" s="104" t="inlineStr">
+      <c r="H12" s="148" t="inlineStr">
         <is>
           <t>v_bat24_mv≈22352mV ±9mV. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I12" s="104" t="inlineStr">
+      <c r="I12" s="148" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول V24. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J12" s="107" t="n"/>
+      <c r="J12" s="111" t="n"/>
       <c r="K12" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3753,14 +3814,14 @@
       </c>
       <c r="L12" s="109" t="n"/>
       <c r="M12" s="104" t="n"/>
-      <c r="N12" s="104" t="inlineStr">
+      <c r="N12" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O12" s="106" t="n"/>
       <c r="P12" s="106" t="n"/>
-      <c r="Q12" s="110">
+      <c r="Q12" s="153">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -3840,22 +3901,22 @@
           <t>MS-011</t>
         </is>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="148" t="inlineStr">
         <is>
           <t>بررسی current1</t>
         </is>
       </c>
-      <c r="C14" s="105" t="inlineStr">
+      <c r="C14" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="104" t="inlineStr">
+      <c r="D14" s="148" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E14" s="104" t="inlineStr">
+      <c r="E14" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی کانال جریان شارژ ۱ counts=610 بده (حدود 0.49 ولت روی پایه).
@@ -3863,27 +3924,27 @@
 گام ۴: i_ch1 خوانده‌شده باید حدود 485 تا 486 میلی‌آمپر با خطای حداکثر ±1 میلی‌آمپر باشد.</t>
         </is>
       </c>
-      <c r="F14" s="106" t="inlineStr">
+      <c r="F14" s="150" t="inlineStr">
         <is>
           <t>counts 610 (0.49V)</t>
         </is>
       </c>
-      <c r="G14" s="106" t="inlineStr">
+      <c r="G14" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H14" s="104" t="inlineStr">
+      <c r="H14" s="148" t="inlineStr">
         <is>
           <t>i_ch1≈ counts*3300*1000/(4095*101*10) ≈ 486mA ±1mA. PASS. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I14" s="104" t="inlineStr">
+      <c r="I14" s="148" t="inlineStr">
         <is>
           <t>PASS: مطابق فرمول جریان. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="J14" s="107" t="n"/>
+      <c r="J14" s="111" t="n"/>
       <c r="K14" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -3891,14 +3952,14 @@
       </c>
       <c r="L14" s="109" t="n"/>
       <c r="M14" s="104" t="n"/>
-      <c r="N14" s="104" t="inlineStr">
+      <c r="N14" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O14" s="106" t="n"/>
       <c r="P14" s="106" t="n"/>
-      <c r="Q14" s="110">
+      <c r="Q14" s="153">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -3978,22 +4039,22 @@
           <t>MS-017</t>
         </is>
       </c>
-      <c r="B16" s="104" t="inlineStr">
+      <c r="B16" s="148" t="inlineStr">
         <is>
           <t>دوره 10ms تسک Measurement</t>
         </is>
       </c>
-      <c r="C16" s="105" t="inlineStr">
+      <c r="C16" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="104" t="inlineStr">
+      <c r="D16" s="148" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E16" s="104" t="inlineStr">
+      <c r="E16" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: اسیلوسکوپ را روی یک GPIO بگذار که ابتدای هر Run تغییر می‌کند (toggle) یا از Live Watch استفاده کن.
@@ -4001,27 +4062,27 @@
 گام ۴: فاصله باید 10 میلی‌ثانیه ±1 میلی‌ثانیه باشد (MEASUREMENT_PERIOD_MS با osDelayUntil)؛ فاصلهٔ 5 یا 20 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="106" t="inlineStr">
+      <c r="F16" s="150" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="106" t="inlineStr">
+      <c r="G16" s="150" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H16" s="104" t="inlineStr">
+      <c r="H16" s="148" t="inlineStr">
         <is>
           <t>فاصله بین Runها باید 10ms ±1ms (MEASUREMENT_PERIOD_MS) با osDelayUntil. PASS: 10ms period. FAIL: 5ms یا 20ms.</t>
         </is>
       </c>
-      <c r="I16" s="104" t="inlineStr">
+      <c r="I16" s="148" t="inlineStr">
         <is>
           <t>PASS: 10ms period. FAIL: otherwise.</t>
         </is>
       </c>
-      <c r="J16" s="107" t="n"/>
+      <c r="J16" s="111" t="n"/>
       <c r="K16" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4029,14 +4090,14 @@
       </c>
       <c r="L16" s="109" t="n"/>
       <c r="M16" s="104" t="n"/>
-      <c r="N16" s="104" t="inlineStr">
+      <c r="N16" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O16" s="106" t="n"/>
       <c r="P16" s="106" t="n"/>
-      <c r="Q16" s="110">
+      <c r="Q16" s="153">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -4047,22 +4108,22 @@
           <t>MS-019</t>
         </is>
       </c>
-      <c r="B17" s="104" t="inlineStr">
+      <c r="B17" s="111" t="inlineStr">
         <is>
           <t>تطبیق فرمول و کالیبراسیون / صفر</t>
         </is>
       </c>
-      <c r="C17" s="105" t="inlineStr">
+      <c r="C17" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="104" t="inlineStr">
+      <c r="D17" s="111" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E17" s="104" t="inlineStr">
+      <c r="E17" s="111" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=0 بده.
@@ -4070,27 +4131,27 @@
 گام ۴: CountsToMv و V24 و V12 و جریان همه باید دقیقاً 0 میلی‌ولت و 0 میلی‌آمپر باشند؛ هر عدد غیرصفر یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="106" t="inlineStr">
+      <c r="F17" s="113" t="inlineStr">
         <is>
           <t>counts 0</t>
         </is>
       </c>
-      <c r="G17" s="106" t="inlineStr">
+      <c r="G17" s="113" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H17" s="104" t="inlineStr">
+      <c r="H17" s="111" t="inlineStr">
         <is>
           <t>همه 0mV/mA. PASS: 0. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="I17" s="104" t="inlineStr">
+      <c r="I17" s="111" t="inlineStr">
         <is>
           <t>PASS: zero. FAIL: non-zero.</t>
         </is>
       </c>
-      <c r="J17" s="107" t="n"/>
+      <c r="J17" s="111" t="n"/>
       <c r="K17" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4098,14 +4159,14 @@
       </c>
       <c r="L17" s="109" t="n"/>
       <c r="M17" s="104" t="n"/>
-      <c r="N17" s="104" t="inlineStr">
+      <c r="N17" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O17" s="106" t="n"/>
       <c r="P17" s="106" t="n"/>
-      <c r="Q17" s="110">
+      <c r="Q17" s="115">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
@@ -4116,22 +4177,22 @@
           <t>MS-020</t>
         </is>
       </c>
-      <c r="B18" s="111" t="inlineStr">
+      <c r="B18" s="148" t="inlineStr">
         <is>
           <t>تطبیق فرمول / فول</t>
         </is>
       </c>
-      <c r="C18" s="112" t="inlineStr">
+      <c r="C18" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="111" t="inlineStr">
+      <c r="D18" s="148" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E18" s="111" t="inlineStr">
+      <c r="E18" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن.
 گام ۲: روی همهٔ کانال‌ها counts=4095 بده (فول‌اسکیل).
@@ -4139,42 +4200,42 @@
 گام ۴: هر سه مقدار خوانده‌شده را با همین حساب‌ها مقایسه کن. باید در تلرانس مجاز همان‌ها باشند.</t>
         </is>
       </c>
-      <c r="F18" s="113" t="inlineStr">
+      <c r="F18" s="150" t="inlineStr">
         <is>
           <t>counts 4095 (فول)</t>
         </is>
       </c>
-      <c r="G18" s="113" t="inlineStr">
+      <c r="G18" s="150" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H18" s="111" t="inlineStr">
+      <c r="H18" s="148" t="inlineStr">
         <is>
           <t>V24≈36882mV، V12≈19897mV، Current≈3267mA ±tolerance (V12 با 41000/6800). PASS: فول مطابق فرمول. FAIL: خطا.</t>
         </is>
       </c>
-      <c r="I18" s="111" t="inlineStr">
+      <c r="I18" s="148" t="inlineStr">
         <is>
           <t>PASS: فول 36882/19897/3267. FAIL: خطا.</t>
         </is>
       </c>
       <c r="J18" s="111" t="n"/>
-      <c r="K18" s="111" t="inlineStr">
+      <c r="K18" s="148" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L18" s="114" t="n"/>
       <c r="M18" s="111" t="n"/>
-      <c r="N18" s="111" t="inlineStr">
+      <c r="N18" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O18" s="113" t="n"/>
       <c r="P18" s="113" t="n"/>
-      <c r="Q18" s="115">
+      <c r="Q18" s="153">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -4644,7 +4705,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4671,7 +4732,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="118" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -4736,87 +4797,87 @@
       <c r="Q3" s="85" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="143" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="143" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="143" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="87" t="inlineStr">
+      <c r="D4" s="143" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="87" t="inlineStr">
+      <c r="E4" s="143" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="87" t="inlineStr">
+      <c r="F4" s="143" t="inlineStr">
         <is>
           <t>ورودی‌ها</t>
         </is>
       </c>
-      <c r="G4" s="87" t="inlineStr">
+      <c r="G4" s="143" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="87" t="inlineStr">
+      <c r="H4" s="143" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="87" t="inlineStr">
+      <c r="I4" s="143" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="J4" s="87" t="inlineStr">
+      <c r="J4" s="143" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="K4" s="87" t="inlineStr">
+      <c r="K4" s="143" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="L4" s="87" t="inlineStr">
+      <c r="L4" s="143" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="M4" s="87" t="inlineStr">
+      <c r="M4" s="143" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="N4" s="87" t="inlineStr">
+      <c r="N4" s="143" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="O4" s="87" t="inlineStr">
+      <c r="O4" s="143" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="P4" s="87" t="inlineStr">
+      <c r="P4" s="143" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="Q4" s="87" t="n"/>
+      <c r="Q4" s="143" t="n"/>
     </row>
     <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="103" t="inlineStr">
@@ -4824,22 +4885,22 @@
           <t>MS-015</t>
         </is>
       </c>
-      <c r="B5" s="104" t="inlineStr">
+      <c r="B5" s="111" t="inlineStr">
         <is>
           <t>NULL در GetSnapshot</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="104" t="inlineStr">
+      <c r="D5" s="111" t="inlineStr">
         <is>
           <t>هر زمان</t>
         </is>
       </c>
-      <c r="E5" s="104" t="inlineStr">
+      <c r="E5" s="111" t="inlineStr">
         <is>
           <t>گام ۱: در هر وضعیتی که هستی، func__Measurement_GetSnapshot را با اشاره‌گر NULL صدا بزن.
 گام ۲: 100 میلی‌ثانیه صبر کن و واکنش برد را ببین.
@@ -4847,27 +4908,27 @@
 گام ۴: کرش یا true برگشتن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="106" t="inlineStr">
+      <c r="F5" s="113" t="inlineStr">
         <is>
           <t>NULL pointer</t>
         </is>
       </c>
-      <c r="G5" s="106" t="inlineStr">
+      <c r="G5" s="113" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="104" t="inlineStr">
+      <c r="H5" s="111" t="inlineStr">
         <is>
           <t>return false، بدون کرش، snapshot تغییر نکند. PASS: false. FAIL: کرش یا true.</t>
         </is>
       </c>
-      <c r="I5" s="104" t="inlineStr">
+      <c r="I5" s="111" t="inlineStr">
         <is>
           <t>PASS: NULL → false. FAIL: true/crash.</t>
         </is>
       </c>
-      <c r="J5" s="107" t="n"/>
+      <c r="J5" s="111" t="n"/>
       <c r="K5" s="108" t="inlineStr">
         <is>
           <t>در انتظار</t>
@@ -4875,14 +4936,14 @@
       </c>
       <c r="L5" s="109" t="n"/>
       <c r="M5" s="104" t="n"/>
-      <c r="N5" s="104" t="inlineStr">
+      <c r="N5" s="111" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O5" s="106" t="n"/>
       <c r="P5" s="106" t="n"/>
-      <c r="Q5" s="110">
+      <c r="Q5" s="115">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -4893,22 +4954,22 @@
           <t>MS-016</t>
         </is>
       </c>
-      <c r="B6" s="111" t="inlineStr">
+      <c r="B6" s="148" t="inlineStr">
         <is>
           <t>Snapshot چندفیلدی اتمیک</t>
         </is>
       </c>
-      <c r="C6" s="112" t="inlineStr">
+      <c r="C6" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="111" t="inlineStr">
+      <c r="D6" s="148" t="inlineStr">
         <is>
           <t>valid=true</t>
         </is>
       </c>
-      <c r="E6" s="111" t="inlineStr">
+      <c r="E6" s="148" t="inlineStr">
         <is>
           <t>گام ۱: از valid=true شروع کن و مقدارها را در حال تغییر نگه دار.
 گام ۲: درست هنگام اجرای func__Measurement_Run، از دو تسک مختلف هم‌زمان GetSnapshot بخوان.
@@ -4917,42 +4978,42 @@
 گام ۵: خواندن پاره‌پاره (torn) یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="113" t="inlineStr">
+      <c r="F6" s="150" t="inlineStr">
         <is>
           <t>concurrent read</t>
         </is>
       </c>
-      <c r="G6" s="113" t="inlineStr">
+      <c r="G6" s="150" t="inlineStr">
         <is>
           <t>20ms</t>
         </is>
       </c>
-      <c r="H6" s="111" t="inlineStr">
+      <c r="H6" s="148" t="inlineStr">
         <is>
           <t>هر دو snapshot کپی‌شده باید یا کامل قدیمی یا کامل جدید باشد، نه ترکیبی. با osKernelLock تضمین. PASS: atomic. FAIL: torn read.</t>
         </is>
       </c>
-      <c r="I6" s="111" t="inlineStr">
+      <c r="I6" s="148" t="inlineStr">
         <is>
           <t>PASS: no torn data. FAIL: partial.</t>
         </is>
       </c>
       <c r="J6" s="111" t="n"/>
-      <c r="K6" s="111" t="inlineStr">
+      <c r="K6" s="148" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
       <c r="L6" s="114" t="n"/>
       <c r="M6" s="111" t="n"/>
-      <c r="N6" s="111" t="inlineStr">
+      <c r="N6" s="148" t="inlineStr">
         <is>
           <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
         </is>
       </c>
       <c r="O6" s="113" t="n"/>
       <c r="P6" s="113" t="n"/>
-      <c r="Q6" s="115">
+      <c r="Q6" s="153">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -5032,22 +5093,22 @@
           <t>ME-022</t>
         </is>
       </c>
-      <c r="B8" s="111" t="inlineStr">
+      <c r="B8" s="148" t="inlineStr">
         <is>
           <t>snapshot zeroing مصرف‌کننده</t>
         </is>
       </c>
-      <c r="C8" s="112" t="inlineStr">
+      <c r="C8" s="149" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="111" t="inlineStr">
+      <c r="D8" s="148" t="inlineStr">
         <is>
           <t>Measurement خاموش</t>
         </is>
       </c>
-      <c r="E8" s="111" t="inlineStr">
+      <c r="E8" s="148" t="inlineStr">
         <is>
           <t>گام ۱: Measurement را خاموش کن (MODULE_MEASUREMENT=0) و برد را بوت کن.
 گام ۲: task_control و task_comm و task_protection را اجرا کن (3 ثانیه).
@@ -5055,27 +5116,27 @@
 گام ۴: مصرف‌کننده‌ها (Changeover و Charger و Fault و Imbalance) باید بدون خواندن زباله، safe-idle بمانند.</t>
         </is>
       </c>
-      <c r="F8" s="113" t="inlineStr">
+      <c r="F8" s="150" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="113" t="inlineStr">
+      <c r="G8" s="150" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H8" s="111" t="inlineStr">
+      <c r="H8" s="148" t="inlineStr">
         <is>
           <t>مصرف‌کننده‌ها (Changeover/Charger/Fault/Imbalance) بدون خواندن زباله safe-idle بمانند</t>
         </is>
       </c>
-      <c r="I8" s="111" t="inlineStr">
+      <c r="I8" s="148" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="111" t="inlineStr">
+      <c r="J8" s="148" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
@@ -5088,13 +5149,13 @@
       </c>
       <c r="M8" s="111" t="n"/>
       <c r="N8" s="111" t="n"/>
-      <c r="O8" s="113" t="inlineStr">
+      <c r="O8" s="150" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P8" s="113" t="n"/>
-      <c r="Q8" s="115" t="inlineStr">
+      <c r="Q8" s="153" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -5571,7 +5632,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>مرجع Measurement — فرمول‌ها و کالیبراسیون</t>
         </is>
@@ -5585,32 +5646,32 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="146" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="146" t="inlineStr">
         <is>
           <t>شرط / مقدار (از کد)</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="146" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="94" t="inlineStr">
+      <c r="D3" s="146" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="94" t="inlineStr">
+      <c r="E3" s="146" t="inlineStr">
         <is>
           <t>توضیح تکمیلی</t>
         </is>
       </c>
-      <c r="F3" s="94" t="inlineStr">
+      <c r="F3" s="146" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
@@ -6055,14 +6116,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده روی برد</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسه یکتا ثبت کن؛ پس از رفع، تست مربوطه را تکرار و در «برنامه تست» وضعیت را به‌روز کن.</t>
         </is>
@@ -6081,86 +6142,86 @@
       <c r="M2" s="9" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="146" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="146" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="146" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="94" t="inlineStr">
+      <c r="D3" s="146" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="94" t="inlineStr">
+      <c r="E3" s="146" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="94" t="inlineStr">
+      <c r="F3" s="146" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="94" t="inlineStr">
+      <c r="G3" s="146" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="94" t="inlineStr">
+      <c r="H3" s="146" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="94" t="inlineStr">
+      <c r="I3" s="146" t="inlineStr">
         <is>
           <t>مدرک / مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="94" t="inlineStr">
+      <c r="J3" s="146" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="K3" s="94" t="inlineStr">
+      <c r="K3" s="146" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="94" t="inlineStr">
+      <c r="L3" s="146" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="94" t="inlineStr">
+      <c r="M3" s="146" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="127" t="inlineStr"/>
-      <c r="B4" s="127" t="inlineStr"/>
-      <c r="C4" s="127" t="inlineStr"/>
-      <c r="D4" s="127" t="inlineStr"/>
-      <c r="E4" s="127" t="inlineStr"/>
-      <c r="F4" s="127" t="inlineStr"/>
-      <c r="G4" s="127" t="inlineStr"/>
-      <c r="H4" s="127" t="inlineStr"/>
-      <c r="I4" s="127" t="inlineStr"/>
-      <c r="J4" s="127" t="inlineStr"/>
-      <c r="K4" s="127" t="inlineStr"/>
-      <c r="L4" s="127" t="inlineStr"/>
-      <c r="M4" s="127" t="inlineStr"/>
+      <c r="A4" s="154" t="inlineStr"/>
+      <c r="B4" s="154" t="inlineStr"/>
+      <c r="C4" s="154" t="inlineStr"/>
+      <c r="D4" s="154" t="inlineStr"/>
+      <c r="E4" s="154" t="inlineStr"/>
+      <c r="F4" s="154" t="inlineStr"/>
+      <c r="G4" s="154" t="inlineStr"/>
+      <c r="H4" s="154" t="inlineStr"/>
+      <c r="I4" s="154" t="inlineStr"/>
+      <c r="J4" s="154" t="inlineStr"/>
+      <c r="K4" s="154" t="inlineStr"/>
+      <c r="L4" s="154" t="inlineStr"/>
+      <c r="M4" s="154" t="inlineStr"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="128" t="inlineStr"/>
@@ -6178,19 +6239,19 @@
       <c r="M5" s="128" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="127" t="inlineStr"/>
-      <c r="B6" s="127" t="inlineStr"/>
-      <c r="C6" s="127" t="inlineStr"/>
-      <c r="D6" s="127" t="inlineStr"/>
-      <c r="E6" s="127" t="inlineStr"/>
-      <c r="F6" s="127" t="inlineStr"/>
-      <c r="G6" s="127" t="inlineStr"/>
-      <c r="H6" s="127" t="inlineStr"/>
-      <c r="I6" s="127" t="inlineStr"/>
-      <c r="J6" s="127" t="inlineStr"/>
-      <c r="K6" s="127" t="inlineStr"/>
-      <c r="L6" s="127" t="inlineStr"/>
-      <c r="M6" s="127" t="inlineStr"/>
+      <c r="A6" s="154" t="inlineStr"/>
+      <c r="B6" s="154" t="inlineStr"/>
+      <c r="C6" s="154" t="inlineStr"/>
+      <c r="D6" s="154" t="inlineStr"/>
+      <c r="E6" s="154" t="inlineStr"/>
+      <c r="F6" s="154" t="inlineStr"/>
+      <c r="G6" s="154" t="inlineStr"/>
+      <c r="H6" s="154" t="inlineStr"/>
+      <c r="I6" s="154" t="inlineStr"/>
+      <c r="J6" s="154" t="inlineStr"/>
+      <c r="K6" s="154" t="inlineStr"/>
+      <c r="L6" s="154" t="inlineStr"/>
+      <c r="M6" s="154" t="inlineStr"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="128" t="inlineStr"/>
@@ -6208,19 +6269,19 @@
       <c r="M7" s="128" t="inlineStr"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="127" t="inlineStr"/>
-      <c r="B8" s="127" t="inlineStr"/>
-      <c r="C8" s="127" t="inlineStr"/>
-      <c r="D8" s="127" t="inlineStr"/>
-      <c r="E8" s="127" t="inlineStr"/>
-      <c r="F8" s="127" t="inlineStr"/>
-      <c r="G8" s="127" t="inlineStr"/>
-      <c r="H8" s="127" t="inlineStr"/>
-      <c r="I8" s="127" t="inlineStr"/>
-      <c r="J8" s="127" t="inlineStr"/>
-      <c r="K8" s="127" t="inlineStr"/>
-      <c r="L8" s="127" t="inlineStr"/>
-      <c r="M8" s="127" t="inlineStr"/>
+      <c r="A8" s="154" t="inlineStr"/>
+      <c r="B8" s="154" t="inlineStr"/>
+      <c r="C8" s="154" t="inlineStr"/>
+      <c r="D8" s="154" t="inlineStr"/>
+      <c r="E8" s="154" t="inlineStr"/>
+      <c r="F8" s="154" t="inlineStr"/>
+      <c r="G8" s="154" t="inlineStr"/>
+      <c r="H8" s="154" t="inlineStr"/>
+      <c r="I8" s="154" t="inlineStr"/>
+      <c r="J8" s="154" t="inlineStr"/>
+      <c r="K8" s="154" t="inlineStr"/>
+      <c r="L8" s="154" t="inlineStr"/>
+      <c r="M8" s="154" t="inlineStr"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="128" t="inlineStr"/>
@@ -6238,19 +6299,19 @@
       <c r="M9" s="128" t="inlineStr"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="127" t="inlineStr"/>
-      <c r="B10" s="127" t="inlineStr"/>
-      <c r="C10" s="127" t="inlineStr"/>
-      <c r="D10" s="127" t="inlineStr"/>
-      <c r="E10" s="127" t="inlineStr"/>
-      <c r="F10" s="127" t="inlineStr"/>
-      <c r="G10" s="127" t="inlineStr"/>
-      <c r="H10" s="127" t="inlineStr"/>
-      <c r="I10" s="127" t="inlineStr"/>
-      <c r="J10" s="127" t="inlineStr"/>
-      <c r="K10" s="127" t="inlineStr"/>
-      <c r="L10" s="127" t="inlineStr"/>
-      <c r="M10" s="127" t="inlineStr"/>
+      <c r="A10" s="154" t="inlineStr"/>
+      <c r="B10" s="154" t="inlineStr"/>
+      <c r="C10" s="154" t="inlineStr"/>
+      <c r="D10" s="154" t="inlineStr"/>
+      <c r="E10" s="154" t="inlineStr"/>
+      <c r="F10" s="154" t="inlineStr"/>
+      <c r="G10" s="154" t="inlineStr"/>
+      <c r="H10" s="154" t="inlineStr"/>
+      <c r="I10" s="154" t="inlineStr"/>
+      <c r="J10" s="154" t="inlineStr"/>
+      <c r="K10" s="154" t="inlineStr"/>
+      <c r="L10" s="154" t="inlineStr"/>
+      <c r="M10" s="154" t="inlineStr"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="128" t="inlineStr"/>
@@ -6268,19 +6329,19 @@
       <c r="M11" s="128" t="inlineStr"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="127" t="inlineStr"/>
-      <c r="B12" s="127" t="inlineStr"/>
-      <c r="C12" s="127" t="inlineStr"/>
-      <c r="D12" s="127" t="inlineStr"/>
-      <c r="E12" s="127" t="inlineStr"/>
-      <c r="F12" s="127" t="inlineStr"/>
-      <c r="G12" s="127" t="inlineStr"/>
-      <c r="H12" s="127" t="inlineStr"/>
-      <c r="I12" s="127" t="inlineStr"/>
-      <c r="J12" s="127" t="inlineStr"/>
-      <c r="K12" s="127" t="inlineStr"/>
-      <c r="L12" s="127" t="inlineStr"/>
-      <c r="M12" s="127" t="inlineStr"/>
+      <c r="A12" s="154" t="inlineStr"/>
+      <c r="B12" s="154" t="inlineStr"/>
+      <c r="C12" s="154" t="inlineStr"/>
+      <c r="D12" s="154" t="inlineStr"/>
+      <c r="E12" s="154" t="inlineStr"/>
+      <c r="F12" s="154" t="inlineStr"/>
+      <c r="G12" s="154" t="inlineStr"/>
+      <c r="H12" s="154" t="inlineStr"/>
+      <c r="I12" s="154" t="inlineStr"/>
+      <c r="J12" s="154" t="inlineStr"/>
+      <c r="K12" s="154" t="inlineStr"/>
+      <c r="L12" s="154" t="inlineStr"/>
+      <c r="M12" s="154" t="inlineStr"/>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="128" t="inlineStr"/>
@@ -6327,7 +6388,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="129" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — Measurement — ADC/ کالیبراسیون</t>
         </is>
@@ -6341,14 +6402,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="145" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="159" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
@@ -6358,7 +6419,7 @@
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="159" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
@@ -6372,7 +6433,7 @@
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="159" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
@@ -6382,7 +6443,7 @@
           <t>2026-09-16 (1.0)</t>
         </is>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="159" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
@@ -6396,7 +6457,7 @@
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="159" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
@@ -6406,7 +6467,7 @@
           <t>نسخهٔ برنامهٔ فلش‌شده (تست‌کننده پر کند)</t>
         </is>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="159" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
@@ -6416,13 +6477,13 @@
       <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="159" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="132" t="inlineStr"/>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="159" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -6432,18 +6493,18 @@
       <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="159" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="132" t="inlineStr"/>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="159" t="inlineStr">
         <is>
           <t>ابزار اندازه‌گیری</t>
         </is>
       </c>
-      <c r="D8" s="96" t="inlineStr">
+      <c r="D8" s="155" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسیلوسکوپ + تایمر RTOS</t>
         </is>
@@ -6452,109 +6513,109 @@
       <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="159" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="B9" s="156" t="inlineStr">
         <is>
           <t>از osKernelGetTickFreq (قابل‌حمل)</t>
         </is>
       </c>
-      <c r="C9" s="131" t="inlineStr"/>
+      <c r="C9" s="159" t="inlineStr"/>
       <c r="D9" s="132" t="inlineStr"/>
       <c r="E9" s="98" t="n"/>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="159" t="inlineStr">
         <is>
           <t>دامنه</t>
         </is>
       </c>
-      <c r="B10" s="96" t="inlineStr">
+      <c r="B10" s="155" t="inlineStr">
         <is>
           <t>ADC 5ch + DMA + کالیبراسیون</t>
         </is>
       </c>
-      <c r="C10" s="131" t="inlineStr"/>
+      <c r="C10" s="159" t="inlineStr"/>
       <c r="D10" s="132" t="inlineStr"/>
       <c r="E10" s="98" t="n"/>
       <c r="F10" s="98" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="159" t="inlineStr">
         <is>
           <t>آستانه warmup</t>
         </is>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="156" t="inlineStr">
         <is>
           <t>3 فریم</t>
         </is>
       </c>
-      <c r="C11" s="131" t="inlineStr"/>
+      <c r="C11" s="159" t="inlineStr"/>
       <c r="D11" s="132" t="inlineStr"/>
       <c r="E11" s="98" t="n"/>
       <c r="F11" s="98" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="159" t="inlineStr">
         <is>
           <t>دوره</t>
         </is>
       </c>
-      <c r="B12" s="96" t="inlineStr">
+      <c r="B12" s="155" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="C12" s="131" t="inlineStr"/>
+      <c r="C12" s="159" t="inlineStr"/>
       <c r="D12" s="132" t="inlineStr"/>
       <c r="E12" s="98" t="n"/>
       <c r="F12" s="98" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="159" t="inlineStr">
         <is>
           <t>کالیبراسیون</t>
         </is>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="156" t="inlineStr">
         <is>
           <t>Vref3300/4095 Div24/Div12 Shunt10 Gain101</t>
         </is>
       </c>
-      <c r="C13" s="131" t="inlineStr"/>
+      <c r="C13" s="159" t="inlineStr"/>
       <c r="D13" s="132" t="inlineStr"/>
       <c r="E13" s="98" t="n"/>
       <c r="F13" s="98" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="93" t="inlineStr">
+      <c r="A14" s="145" t="inlineStr">
         <is>
           <t>خلاصه خودکار وضعیت تست‌ها (پس از تست برد پر شود)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="inlineStr">
+      <c r="A15" s="146" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B15" s="146" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="146" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="D15" s="94" t="inlineStr">
+      <c r="D15" s="146" t="inlineStr">
         <is>
           <t>فرمول پیشنهادی</t>
         </is>
@@ -6563,7 +6624,7 @@
       <c r="F15" s="9" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="96" t="inlineStr">
+      <c r="A16" s="157" t="inlineStr">
         <is>
           <t>تعداد کل تست‌ها</t>
         </is>
@@ -6572,7 +6633,7 @@
         <f>COUNTA('برنامه تست'!A5:A200)</f>
         <v/>
       </c>
-      <c r="C16" s="96" t="inlineStr">
+      <c r="C16" s="155" t="inlineStr">
         <is>
           <t>کل ردیف‌های برنامه تست</t>
         </is>
@@ -6582,7 +6643,7 @@
       <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="96" t="inlineStr">
+      <c r="A17" s="157" t="inlineStr">
         <is>
           <t>تعداد قبول (PASS)</t>
         </is>
@@ -6591,12 +6652,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"قبول")</f>
         <v/>
       </c>
-      <c r="C17" s="96" t="inlineStr">
+      <c r="C17" s="156" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = قبول</t>
         </is>
       </c>
-      <c r="D17" s="96" t="inlineStr">
+      <c r="D17" s="156" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
@@ -6605,7 +6666,7 @@
       <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="96" t="inlineStr">
+      <c r="A18" s="157" t="inlineStr">
         <is>
           <t>تعداد رد (FAIL)</t>
         </is>
@@ -6614,12 +6675,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"رد")</f>
         <v/>
       </c>
-      <c r="C18" s="96" t="inlineStr">
+      <c r="C18" s="155" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = رد</t>
         </is>
       </c>
-      <c r="D18" s="96" t="inlineStr">
+      <c r="D18" s="155" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
@@ -6628,7 +6689,7 @@
       <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="96" t="inlineStr">
+      <c r="A19" s="157" t="inlineStr">
         <is>
           <t>تعداد در انتظار</t>
         </is>
@@ -6637,12 +6698,12 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C19" s="96" t="inlineStr">
+      <c r="C19" s="156" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = در انتظار</t>
         </is>
       </c>
-      <c r="D19" s="96" t="inlineStr">
+      <c r="D19" s="156" t="inlineStr">
         <is>
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
@@ -6651,7 +6712,7 @@
       <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="96" t="inlineStr">
+      <c r="A20" s="157" t="inlineStr">
         <is>
           <t>تعداد مسدود</t>
         </is>
@@ -6660,7 +6721,7 @@
         <f>COUNTIF('برنامه تست'!K5:K200,"مسدود")</f>
         <v/>
       </c>
-      <c r="C20" s="96" t="inlineStr">
+      <c r="C20" s="155" t="inlineStr">
         <is>
           <t>تعداد ردیف با وضعیت = مسدود</t>
         </is>
@@ -6670,7 +6731,7 @@
       <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="157" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
@@ -6679,7 +6740,7 @@
         <f>IF(B16=0,"",TEXT(B17/B16,"0%"))</f>
         <v/>
       </c>
-      <c r="C21" s="96" t="inlineStr">
+      <c r="C21" s="156" t="inlineStr">
         <is>
           <t>PASS / TOTAL</t>
         </is>
@@ -6689,34 +6750,34 @@
       <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="93" t="inlineStr">
+      <c r="A22" s="145" t="inlineStr">
         <is>
           <t>امضاها</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="94" t="inlineStr">
+      <c r="A23" s="146" t="inlineStr">
         <is>
           <t>نقش</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="146" t="inlineStr">
         <is>
           <t>نام و نام خانوادگی</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
+      <c r="C23" s="146" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="D23" s="94" t="inlineStr">
+      <c r="D23" s="146" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
-      <c r="E23" s="94" t="inlineStr">
+      <c r="E23" s="146" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
@@ -6724,7 +6785,7 @@
       <c r="F23" s="9" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="96" t="inlineStr">
+      <c r="A24" s="157" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
@@ -6736,7 +6797,7 @@
       <c r="F24" s="9" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="96" t="inlineStr">
+      <c r="A25" s="157" t="inlineStr">
         <is>
           <t>بازبین فنی</t>
         </is>
@@ -6748,7 +6809,7 @@
       <c r="F25" s="9" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="96" t="inlineStr">
+      <c r="A26" s="157" t="inlineStr">
         <is>
           <t>تأیید نهایی</t>
         </is>
@@ -6760,7 +6821,7 @@
       <c r="F26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="130" t="inlineStr">
+      <c r="A27" s="158" t="inlineStr">
         <is>
           <t>یادداشت: بدون ثبت commit، شناسه برد، نام تست‌کننده، تاریخ و ابزار اندازه‌گیری، این فرم ناقص است. برای هر ردیف «رد»، یک ردیف در «ثبت ایراد» الزامی است.</t>
         </is>
@@ -6801,7 +6862,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6812,7 +6873,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -6861,7 +6922,7 @@
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="145" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -6899,7 +6960,7 @@
       <c r="A13" s="85" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="93" t="inlineStr">
+      <c r="A14" s="145" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
@@ -6979,7 +7040,7 @@
       <c r="A25" s="85" t="n"/>
     </row>
     <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="93" t="inlineStr">
+      <c r="A26" s="145" t="inlineStr">
         <is>
           <t>نتیجه ایراد</t>
         </is>
@@ -7039,11 +7100,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="85" t="n"/>
-      <c r="B2" s="85" t="n"/>
-      <c r="C2" s="85" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -7055,7 +7112,6 @@
           <t>Measurement_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="85" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="32" t="inlineStr">
@@ -7068,7 +7124,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="85" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="32" t="inlineStr">
@@ -7081,7 +7136,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="85" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="32" t="inlineStr">
@@ -7089,12 +7143,11 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7103,7 +7156,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="63">
+  <fonts count="65">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -376,8 +376,19 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -453,6 +464,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -979,6 +995,24 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1346,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1653,7 +1687,6 @@
       <c r="O23" s="85" t="n"/>
       <c r="P23" s="85" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="135" t="inlineStr">
         <is>
@@ -1663,6 +1696,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="160" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B27" s="161" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1728,15 +1773,23 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="142" t="inlineStr">
         <is>
           <t>برنامه تست عملی — ماژول Measurement</t>
         </is>
       </c>
       <c r="Q1" s="85" t="n"/>
+      <c r="T1" s="162" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="101" t="inlineStr">
@@ -1745,6 +1798,14 @@
         </is>
       </c>
       <c r="Q2" s="85" t="n"/>
+      <c r="T2" s="163" t="inlineStr">
+        <is>
+          <t>عدد ADC کانال ولتاژ (0 تا 4095)</t>
+        </is>
+      </c>
+      <c r="U2" s="164" t="n">
+        <v>2482</v>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="102" t="inlineStr">
@@ -1753,6 +1814,14 @@
         </is>
       </c>
       <c r="Q3" s="85" t="n"/>
+      <c r="T3" s="163" t="inlineStr">
+        <is>
+          <t>عدد ADC کانال جریان (0 تا 4095)</t>
+        </is>
+      </c>
+      <c r="U3" s="164" t="n">
+        <v>610</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="143" t="inlineStr">
@@ -1836,6 +1905,19 @@
         </is>
       </c>
       <c r="Q4" s="143" t="n"/>
+      <c r="R4" s="143" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="163" t="inlineStr">
+        <is>
+          <t>فریم کامل از روشن‌شدن</t>
+        </is>
+      </c>
+      <c r="U4" s="164" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="103" t="inlineStr">
@@ -1904,6 +1986,18 @@
         <v/>
       </c>
       <c r="Q5" s="110" t="n"/>
+      <c r="R5" s="161">
+        <f>IF($U$4&gt;=3,"داده معتبر: ولتاژ ۲۴ ≈ "&amp;TEXT(ROUND($U$2*3300/4095*76000/6800,0),"0")&amp;" mV و جریان ≈ "&amp;TEXT(ROUND($U$3*3300*1000/(4095*101*10),0),"0")&amp;" mA","هنوز معتبر نیست: به ۳ فریم کامل نرسیده")</f>
+        <v/>
+      </c>
+      <c r="T5" s="163" t="inlineStr">
+        <is>
+          <t>ورودی حاضر است؟ PB4 (1/0)</t>
+        </is>
+      </c>
+      <c r="U5" s="164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="103" t="inlineStr">
@@ -1971,6 +2065,15 @@
         <v/>
       </c>
       <c r="Q6" s="110" t="n"/>
+      <c r="R6" s="161">
+        <f>IF($U$5=1,"ورودی حاضر شناخته می‌شود (input_present=1)","ورودی حاضر نیست: مقدار PB4 را چک کن")</f>
+        <v/>
+      </c>
+      <c r="T6" s="165" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="103" t="inlineStr">
@@ -2038,6 +2141,10 @@
         <v/>
       </c>
       <c r="Q7" s="115" t="n"/>
+      <c r="R7" s="161">
+        <f>IF($U$5=1,"الان حاضر شناخته می‌شود؛ برای این تست باید 0 باشد","ورودی حاضر شناخته نمی‌شود (input_present=0)")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="103" t="inlineStr">
@@ -2107,6 +2214,10 @@
         <v/>
       </c>
       <c r="Q8" s="110" t="n"/>
+      <c r="R8" s="161">
+        <f>IF($U$4&gt;=3,"داده معتبر: ولتاژ ۲۴ ≈ "&amp;TEXT(ROUND($U$2*3300/4095*76000/6800,0),"0")&amp;" mV و جریان ≈ "&amp;TEXT(ROUND($U$3*3300*1000/(4095*101*10),0),"0")&amp;" mA","هنوز معتبر نیست: به ۳ فریم کامل نرسیده")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="103" t="inlineStr">
@@ -2174,6 +2285,10 @@
         <v/>
       </c>
       <c r="Q9" s="110" t="n"/>
+      <c r="R9" s="161">
+        <f>"با این عددها: ولتاژ ۲۴ = "&amp;TEXT(ROUND($U$2*3300/4095*76000/6800,0),"0")&amp;" mV، ولتاژ ۱۲ = "&amp;TEXT(ROUND($U$2*3300/4095*41000/6800,0),"0")&amp;" mV، جریان = "&amp;TEXT(ROUND($U$3*3300*1000/(4095*101*10),0),"0")&amp;" mA؛ با مولتی‌متر مرجع مقایسه کن"</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="103" t="inlineStr">
@@ -2243,6 +2358,10 @@
         <v/>
       </c>
       <c r="Q10" s="115" t="n"/>
+      <c r="R10" s="161">
+        <f>IF($U$4&gt;=3,"داده معتبر: ولتاژ ۲۴ ≈ "&amp;TEXT(ROUND($U$2*3300/4095*76000/6800,0),"0")&amp;" mV و جریان ≈ "&amp;TEXT(ROUND($U$3*3300*1000/(4095*101*10),0),"0")&amp;" mA","هنوز معتبر نیست: به ۳ فریم کامل نرسیده")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="103" t="inlineStr">
@@ -2312,6 +2431,10 @@
         <v/>
       </c>
       <c r="Q11" s="110" t="n"/>
+      <c r="R11" s="161">
+        <f>IF($U$4&gt;=3,"داده معتبر: ولتاژ ۲۴ ≈ "&amp;TEXT(ROUND($U$2*3300/4095*76000/6800,0),"0")&amp;" mV و جریان ≈ "&amp;TEXT(ROUND($U$3*3300*1000/(4095*101*10),0),"0")&amp;" mA","هنوز معتبر نیست: به ۳ فریم کامل نرسیده")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="136" t="n"/>
@@ -3075,8 +3198,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q51"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:P1"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -7100,7 +7225,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>

--- a/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
+++ b/Firmware/Modules/Measurement/Measurement_Board_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$51</definedName>
